--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -484,6 +484,38 @@
 Concernant les stratégies - et c'étaient plusieurs points forts de l'année dernière -, notamment la stratégie nationale contre le racisme et l'antisémitisme pour la période 2026-2031, la stratégie Asie G20 2025-2028 et la stratégie du Conseil fédéral en matière de politique d'armement, elles ont été adoptées. Le Conseil fédéral a aussi adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
 J'en arrive aux conclusions. Vous trouverez l'intégralité des messages, rapports, plans d'action et stratégies détaillés, avec la date de leur adoption, dans notre rapport de gestion 2025. 
 Au nom du Conseil fédéral, je vous remercie de votre reconnaissance, de votre coopération et de votre soutien. Le Conseil fédéral va continuer à s'engager pleinement pour la défense des intérêts du pays et pour le bien de sa population.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de Montmollin Simone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités né</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités nécessaires à cet effet. Selon les auteurs de l'initiative, cet objectif implique notamment de pouvoir recourir à toutes les technologies de production disponibles, y compris le nucléaire. Ils soulèvent ainsi à la fois la question de la sécurité d'approvisionnement et remettent en question la répartition des compétences entre Confédération, cantons et acteurs du secteur électrique. L'objectif du contre-projet est de rétablir l'ouverture technologique en supprimant l'interdiction légale du nucléaire tout en refusant la modification constitutionnelle proposée dans l'initiative.
+Dans le cadre de ces travaux préparatoires, la commission a procédé à de nombreuses auditions et notamment entendu des représentants de l'Inspection fédérale de la sécurité nucléaire, de l'Association des entreprises électriques suisses, de Swissgrid, de la Conférence des directeurs cantonaux de l'énergie ainsi que de l'industrie électrique, du monde scientifique et d'organisations concernées.
+En outre, lors de sa séance du 30 mars, elle a chargé l'administration d'établir huit rapports complémentaires, notamment sur la rentabilité des projets hydroélectriques, sur les conséquences militaires et sécuritaires liées aux installations nucléaires, sur les questions de responsabilité civile et de couverture des dommages, sur les chaînes d'approvisionnement en combustible nucléaire, sur les réacteurs de quatrième génération, sur les besoins éventuels en centrales à gaz ainsi que sur le développement des énergies renouvelables.
+Les auditions ont montré un consensus sur la nécessité de poursuivre les développements des énergies renouvelables, de renforcer les réseaux électriques et de garantir la sécurité d'approvisionnement à long terme. Les besoins futurs en électricité seront vraisemblablement plus élevés que ceux évalués en 2017 lors de l'adoption de la stratégie énergétique 2050, notamment en raison de l'électrification croissante des usages, des centres de données et du développement de l'intelligence artificielle. Une réévaluation de ces besoins est en cours. La commission a d'ailleurs déposé les deux postulats 26.3019 et 26.3020 pour lesquels des réponses sont attendues d'ici fin 2027 dans le cadre des nouvelles perspectives énergétiques 2060 en cours d'élaboration, qui devront permettre des analyses actualisées de l'approvisionnement futur en électricité. À cet égard, les auditions ont fait apparaître des appréciations divergentes quant au rôle du nucléaire.
+La Conférence des directeurs cantonaux de l'énergie a indiqué que si les cantons rejetaient très largement l'initiative populaire, les positions sont plus nuancées sur le contre-projet indirect. Dix cantons demandent des analyses complémentaires, sept le soutiennent sous réserve du maintien du soutien aux énergies renouvelables et à l'hydraulique, tandis que huit s'y opposent. Les cantons ont demandé une actualisation des perspectives énergétiques et des précisions concernant les coûts, le financement, l'intégration d'éventuelles nouvelles centrales dans le système électrique suisse ainsi que la gestion à long terme des déchets radioactifs. Ils ont en revanche confirmé leur soutien à la poursuite de l'exploitation des centrales existantes, aussi longtemps que les exigences de sécurité sont remplies.
+Ces appréciations ont émaillé également le débat d'entrée en matière de la commission. Plusieurs membres ont demandé le renvoi du projet au Conseil fédéral, estimant que les bases décisionnelles demeuraient insuffisantes, notamment en ce qui concerne les coûts, le financement, les risques résiduels, les conséquences sur le développement des énergies renouvelables et la gestion des déchets radioactifs. La majorité de la commission a toutefois considéré que ces interrogations, bien que légitimes, ne justifiaient pas un renvoi. D'une part, le contre-projet ne préjuge pas d'une future décision de construire de nouvelles centrales et, d'autre part, il ne remet pas en cause la stratégie énergétique 2050 ni les lois votées par le peuple en la matière ces dernières années. Le contre-projet vise uniquement à supprimer une interdiction générale afin de préserver toutes les options susceptibles de contribuer à la sécurité d'approvisionnement dans un contexte marqué par des incertitudes géopolitiques et une demande d'électricité en hausse. Maintenir une interdiction revient à donner un signal paradoxal qui consiste à vouloir garantir notre approvisionnement sans intégrer toutes les technologies dans la réflexion.
+La commission est entrée en matière, par 13 voix contre 12. Elle a ensuite refusé la proposition de renvoi du contre-projet au Conseil fédéral, par 13 voix contre 11.
+Ces demandes de précision, bien que légitimes, sont prématurées. Elles ne pourront trouver de réponse en cohérence qu'en cas de projet concret, et non de manière théorique. Il y a quatre minorités à cet égard : les minorités I (Wismer Priska), II (Masshardt), III (Bäumle) et IV (Schlatter).
+La commission a ensuite procédé à la discussion par article de la modification de la loi sur l'énergie nucléaire, soit du contre-projet à l'initiative, et s'est ralliée en tous points à la position du Conseil des États en refusant plusieurs propositions.
+À l'article 12a, la minorité Wismer Priska vise à limiter la levée de l'interdiction aux seules centrales de quatrième génération. La majorité relève qu'une telle restriction reviendrait pratiquement à maintenir l'interdiction actuelle, car il existe actuellement plus de 90 concepts différents dans le monde, aucune définition n'existant pour qualifier ce que sera une centrale de quatrième génération. Cette proposition a été rejetée, par 13 voix contre 12.
+À l'article 12b, la minorité Bäumle porte sur la responsabilité civile et les conséquences financières d'un accident nucléaire majeur. L'auteur considère que toute nouvelle centrale devrait être soumise à des exigences de couverture financière plus élevées. Pour la majorité, augmenter substantiellement les règles de couverture reviendrait à imposer des exigences plus élevées aux installations futures qu'aux centrales existantes, alors que celles-ci devraient être plus sûres. De tels coûts empêcheraient de facto tout nouveau projet. Cette proposition a été rejetée, par 13 voix contre 11.
+Les questions de sécurité ont occupé une place importante dans les débats, notamment au regard des conflits récents et des risques d'attaques militaires hybrides ou terroristes. À l'article 13 alinéa 1 lettre ebis, une proposition exigeant une démonstration d'un niveau de protection complet et garanti contre ces menaces a été rejetée, par 13 voix contre 12, le risque zéro n'existant pour aucune infrastructure, fut-elle nucléaire.
+Sur les questions de prolifération nucléaire, des dépendances géopolitiques et des chaînes d'approvisionnement, plusieurs propositions, à l'article 13 alinéa 1 lettres i et j, demandaient que les requérants démontrent le respect du droit international, des principes de non-prolifération ainsi que de standards élevés en matière de droits humains et d'environnement tout au long de la chaîne d'approvisionnement du combustible nucléaire. La majorité de la commission a reconnu l'importance de ces préoccupations, mais estime que les exigences proposées vont au-delà des mécanismes existants à l'échelle internationale et seraient extrêmement difficiles à mettre en oeuvre. Ces propositions aux lettres i et j ont donc été rejetées, par 16 voix contre 9. Il y a deux minorités.
+Aux lettres k et l, selon certains membres de la commission, il n'est pas acceptable d'autoriser de nouvelles centrales sans solution pleinement établie pour l'élimination définitive des déchets. La majorité relève que la lettre d permettrait déjà d'imposer des conditions particulières le cas échéant. Certaines technologies en développement pourraient par ailleurs réduire la quantité ou la durée ainsi que la dangerosité des déchets produits. C'est pourquoi la majorité a rejeté ces propositions, par 16 voix contre 9, à la lettre k, et par 13 voix contre 9 et 3 abstentions, à la lettre l.
+La commission s'est ensuite penchée sur la participation des populations concernées. À l'article 15, la commission a refusé, par 15 voix contre 9, que les communes situées dans la zone de protection d'urgence autour d'une centrale disposent d'un droit de codécision contraignant. Un tel mécanisme serait difficilement compatible avec le système actuel d'autorisation générale qui est accordée par l'instance fédérale, en l'occurrence par le Parlement, et non par les cantons ou les communes. Cela créerait un précédent.
+S'agissant du financement, une proposition visait à introduire un nouvel article 86a pour exclure explicitement toute forme de soutien financier public, direct ou indirect, à de nouvelles centrales nucléaires, y compris par le biais de suppléments réseau, ainsi que toutes mesures d'encouragement. Cela a également été rejeté, par 13 voix contre 10, la commission constatant que le droit en vigueur ne permet de toute manière pas un tel soutien. Il n'est donc pas nécessaire d'inscrire une interdiction supplémentaire dans la loi.
+Enfin, une proposition présentée comme un compromis visait à remplacer la suppression de l'interdiction par un moratoire jusqu'en 2035. Elle a été rejetée, par 13 voix contre 12. C'est l'article 106 alinéas 1bis et 1ter. La majorité considère qu'un nouveau moratoire reporterait tout simplement les mêmes questions à une date ultérieure. L'expérience du moratoire entre 1990 et 2000 a montré par ailleurs qu'aucune réflexion sérieuse n'a pu être menée pendant cette période.
+Au terme de ses travaux, la commission a adopté le contre-projet dit indirect, par 13 voix contre 12.
+À l'attention de la Commission de rédaction, elle relève qu'il n'est pas conforme à la pratique législative de faire figurer entre parenthèses, dans le titre de la loi, une référence au contre-projet indirect à l'initiative. Elle prie donc la Commission de rédaction de bien vouloir adapter ce titre.
+Quant à l'initiative populaire, une proposition visant à recommander son acceptation a été rejetée, par 15 voix contre 9. La commission suit donc la position du Conseil fédéral et du Conseil des États.
 </t>
   </si>
   <si>
@@ -616,8 +648,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I22" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I23" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I23"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1472,75 +1504,104 @@
         <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
         <v>27</v>
       </c>
       <c r="H20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" t="s">
         <v>108</v>
-      </c>
-      <c r="I20" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
         <v>110</v>
       </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" t="s">
         <v>111</v>
       </c>
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" t="s">
         <v>112</v>
       </c>
-      <c r="E21" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>113</v>
-      </c>
-      <c r="I21" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" t="s">
-        <v>111</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22"/>
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -142,7 +142,7 @@
   <si>
     <t xml:space="preserve">Wir haben in den letzten 18 Monaten intensiv über die Finanzpolitik gesprochen sowie das Budget 2026, das sogenannte Entlastungspaket 2027 und zuletzt auch die Armeefinanzierung diskutiert. Deshalb blicke ich kurz auf die Debatte zum Budget 2025 zurück, um in Erinnerung zu rufen, wie Sie damals gedacht und gehandelt haben.
 Damals, im Herbst 2024, hat die bürgerliche Mehrheit ein Sparprogramm durchgesetzt. Zusätzlich zu den Querschnittkürzungen des Bundesrates von 1,4 Prozent in allen Bereichen - mit Ausnahme der Armee - hat das Parlament zugunsten einer massiven Aufstockung der Rüstungsausgaben der Armee um 530 Millionen Franken insbesondere in den Bereichen der internationalen Zusammenarbeit und der Migration Kürzungen beschlossen. Beide Räte verabschiedeten schliesslich einen Voranschlag 2025, der die Schuldenbremse deutlich übererfüllte.
-Was ist daraus geworden? Das interessiert offenbar nicht allzu viele; wenn ich in den Saal schaue, ist er ziemlich leer. Die Rechnung zeigt, dass die viel zitierte angespannte Haushaltslage in dieser Form nicht - glücklicherweise nicht - eingetreten ist. Sie schliesst positiver als veranschlagt ab, insbesondere aufgrund von Mehreinnahmen bei den Gewinnsteuern von 1,8 Milliarden Franken. Das Einnahmenwachstum von 4,3 Prozent lag deutlich über jenem der Ausgaben von 3,9 Prozent. Die Nettoschuldenquote sinkt weiter auf nahezu rekordtiefe 16,1 Prozent. Allerdings konnte die Armee die zusätzlich bewilligten Mittel nicht ausschöpfen; das VBS stellte 360 Millionen Franken zurück, weil die gesprochenen Mittel nicht verwendet werden konnten.
+Was ist daraus geworden? Das interessiert offenbar nicht allzu viele; wenn ich in den Saal schaue, ist er ziemlich leer. Die Rechnung zeigt, dass die viel zitierte angespannte Haushaltslage in dieser Form nicht - glücklicherweise nicht - eingetreten ist. Sie schliesst positiver als veranschlagt ab, insbesondere aufgrund von Mehreinnahmen bei den Gewinnsteuern von 1,8 Milliarden Franken. Das Wachstum der Einnahmen von 4,3 Prozent lag deutlich über jenem der Ausgaben von 3,9 Prozent. Die Nettoschuldenquote sinkt weiter auf nahezu rekordtiefe 16,1 Prozent. Allerdings konnte die Armee die zusätzlich bewilligten Mittel nicht ausschöpfen; das VBS stellte 360 Millionen Franken zurück, weil die gesprochenen Mittel nicht verwendet werden konnten.
 Diese Situation und auch der Ausblick zeigen klar: Der Bund steht nicht kurz vor einem finanziellen Kollaps. Finanzpolitische Glaubwürdigkeit und Nachhaltigkeit bedeuten jedoch, Prioritäten offen zu benennen und nicht dort zu sparen, wo die langfristigen Kosten die kurzfristigen Einsparungen übersteigen. Wer bei der Bildung spart, spart an den Fachkräften von morgen. Wer bei der Forschung spart, gefährdet Innovation und Wertschöpfung. Wer bei der internationalen Zusammenarbeit spart, schwächt Stabilität, Friedensförderung und letztlich auch unsere eigene Sicherheit. Wer bei den sozialen Leistungen spart, belastet genau jene Menschen, die bereits heute unter steigenden Krankenkassenprämien, hohen Mieten und steigenden Lebenskosten leiden. Finanzpolitische Verantwortung bedeutet, die langfristigen Interessen unseres Landes in den Mittelpunkt zu stellen. Daran richtet die SP ihr Handeln aus.
 Mir ist es ein Anliegen, an dieser Stelle allen Mitarbeitenden der Verwaltung herzlich zu danken, insbesondere der Eidgenössischen Finanzverwaltung für ihre grosse Arbeit sowie dem Sekretariat. Ein besonderer Dank gilt zudem dem Bundesrat, vor allem Frau Karin Keller-Sutter, für die gute Zusammenarbeit.
 In diesem Sinne kann ich bekannt geben, dass wir der Rechnung sowie allen Bundesbeschlüssen zustimmen. Wir hoffen jedoch, dass die kommenden Budgetdebatten etwas sachlicher geführt werden.
@@ -165,13 +165,12 @@
   </si>
   <si>
     <t xml:space="preserve">Der Bund schliesst das Jahr 2025 mit einem Finanzierungsüberschuss von 259 Millionen Franken ab. Die Vorgaben der Schuldenbremse wurden eingehalten, und die Nettoschulden sind leicht rückläufig. Wenn man sich diese Eckwerte vor Augen hält, könnte man fast meinen, wir hätten alles im Griff; dem ist aber leider nicht so. Bei genauer Betrachtung offenbart die Staatsrechnung 2025 laute Warnsignale, und zwar bei den stark angestiegenen Ausgaben, bei den Gründen für die höheren Einnahmen, bei der immer noch ausserordentlichen Verbuchung von Ukraine-Ausgaben sowie bei der Entwicklung der Personalausgaben.
-Zuerst zu den stark angestiegenen Ausgaben: Der jahrzehntelange Trend des ständigen Ausgabenwachstums hält unvermindert an. Mit rund 88 Milliarden Franken lagen die Gesamtausgaben im Jahr 2025 um weitere fast dreieinhalb Milliarden Franken beziehungsweise 4 Prozent höher als im Vorjahr. Die ordentlichen Ausgaben wachsen damit mehr als doppelt so stark wie das nominale Bruttoinlandprodukt und damit die Wirtschaft. Genau darin liegt das Kernproblem unseres Bundeshaushalts. Nicht die Einnahmen wachsen zu wenig, sondern die Ausgaben wachsen zu schnell, und das seit Jahrzehnten. Davon entfallen wiederum Milliardenbeträge auf die soziale Wohlfahrt. Mittlerweile geben wir für die soziale Wohlfahrt jährlich über 30 Milliarden Franken an Steuergeldern aus. Diese Entwicklung ist alarmierend.
-Kommen wir zur Einnahmenseite: Ich bedanke mich im Namen der SVP-Fraktion herzlich bei unseren Unternehmungen, insbesondere den KMU, dem Rückgrat unserer Wirtschaft. Sie schaffen nicht nur Arbeitsplätze und Lehrstellen und versorgen unsere Bevölkerung mit hochwertigen Produkten und Dienstleistungen, nein, sie generieren auch noch Steuern zur Finanzierung unseres zu teuren Staatsapparats. Glücklicherweise haben sie auch im vergangenen Jahr erneut gut gearbeitet. Insbesondere unserer Wirtschaft ist es zu verdanken, dass die Einnahmen deutlich gestiegen sind. Die Einnahmen aus der direkten Bundessteuer nahmen um satte 8 Prozent zu. Besonders stark fiel das Wachstum bei den Unternehmensgewinnen aus. Allerdings müssen wir auch hier genauer hinschauen.
-Ein erheblicher Teil dieser Mehreinnahmen sind die Folgen eines Sondereffekts im Kanton Genf, der dem Bund rund 1,5 Milliarden Franken zusätzliche Einnahmen eingebracht hat. Hinzu kommt eine Gewinnausschüttung der Schweizerischen Nationalbank in der Höhe von 1 Milliarde Franken. 
+Zuerst zu den stark angestiegenen Ausgaben: Der jahrzehntelange Trend des ständigen Ausgabenwachstums hält unvermindert an. Mit rund 88 Milliarden Franken lagen die Gesamtausgaben im Jahr 2025 um weitere fast dreieinhalb Milliarden Franken bzw. 4 Prozent höher als im Vorjahr. Die ordentlichen Ausgaben wachsen damit mehr als doppelt so stark wie das nominale Bruttoinlandprodukt und damit die Wirtschaft. Genau darin liegt das Kernproblem unseres Bundeshaushalts. Nicht die Einnahmen wachsen zu wenig, sondern die Ausgaben wachsen zu schnell, und das seit Jahrzehnten. Davon entfallen wiederum Milliardenbeträge auf die soziale Wohlfahrt. Mittlerweile geben wir für die soziale Wohlfahrt jährlich über 30 Milliarden Franken an Steuergeldern aus. Diese Entwicklung ist alarmierend.
+Kommen wir zur Einnahmenseite: Ich bedanke mich im Namen der SVP-Fraktion herzlich bei unseren Unternehmungen, insbesondere den KMU, dem Rückgrat unserer Wirtschaft. Sie schaffen nicht nur Arbeitsplätze und Lehrstellen und versorgen unsere Bevölkerung mit hochwertigen Produkten und Dienstleistungen, nein, sie generieren auch noch Steuern zur Finanzierung unseres zu teuren Staatsapparats. Glücklicherweise haben sie auch im vergangenen Jahr erneut gut gearbeitet. Insbesondere unserer Wirtschaft ist es zu verdanken, dass die Einnahmen deutlich gestiegen sind. Die Einnahmen aus der direkten Bundessteuer nahmen um satte 8 Prozent zu. Besonders stark fiel das Wachstum bei den Unternehmensgewinnen aus. Allerdings müssen wir auch hier genauer hinschauen. Ein erheblicher Teil dieser Mehreinnahmen sind die Folgen eines Sondereffekts im Kanton Genf, der dem Bund rund 1,5 Milliarden Franken zusätzliche Einnahmen eingebracht hat. Hinzu kommt eine Gewinnausschüttung der Schweizerischen Nationalbank in der Höhe von 1 Milliarde Franken. 
 Das positive Rechnungsergebnis beruht somit nicht nur auf einer starken Wirtschaft, sondern auch auf ausserordentlichen Faktoren. Diese dürfen nicht darüber hinwegtäuschen, dass die strukturellen Probleme des Bundeshaushalts weiterhin bestehen. Ein weiterer grosser "Tolggen" im Reinheft der Staatsrechnung 2025 ist die nach wie vor ausserordentliche Verbuchung der Ausgaben für Status-S-Flüchtlinge aus der Ukraine im Umfang von 700 Millionen Franken. Diese Praxis ist mittlerweile unter keinem Titel mehr nachvollziehbar, das muss in aller Klarheit festgehalten werden. Nach rund viereinhalb Jahren oder 52 Monaten, also über 1500 Tage nach Kriegsausbruch, können diese Ausgaben beim besten Willen nicht mehr als unvorhersehbar bezeichnet werden. Wer Jahr für Jahr dieselben Ausgaben ausserordentlich verbucht, unterläuft ohne Wenn und Aber die Schuldenbremse. Dieses Vorgehen steht klar im Widerspruch zu unserer Verfassung. 
-Ich komme zum Personalbestand: Auch im Jahr 2025 ist die Bundesverwaltung weiter gewachsen. Der durchschnittliche Stellenbestand nahm wiederum um Hunderte Vollzeitstellen zu. Die Personalausgaben stiegen erneut an. Mittlerweile gibt der Bund jedes Jahr rund 6,5 Milliarden Franken für Personal aus - 6,5 Milliarden Franken Jahr für Jahr. Das zeigt, dass auch die Bundesverwaltung ihren Beitrag zur Haushaltsdisziplin noch nicht ausreichend leistet. 
+Ich komme zum Personalbestand: Auch im Jahr 2025 ist die Bundesverwaltung weitergewachsen. Der durchschnittliche Stellenbestand nahm wiederum um Hunderte Vollzeitstellen zu. Die Personalausgaben stiegen erneut an. Mittlerweile gibt der Bund jedes Jahr rund 6,5 Milliarden Franken für Personal aus - 6,5 Milliarden Franken Jahr für Jahr. Das zeigt, dass auch die Bundesverwaltung ihren Beitrag zur Haushaltsdisziplin noch nicht ausreichend leistet. 
 Fazit: Die Staatsrechnung 2025 hätte schlechter ausfallen können. Genaueres Hinschauen trübt das Ergebnis jedoch. Das gute Rechnungsergebnis darf keinesfalls über die strukturellen Herausforderungen hinwegtäuschen. Die Finanzpläne des Bundes weisen auch für die Jahre 2027 bis 2029 weiterhin Defizite aus, obwohl die Einnahmen kräftig wachsen. Das eigentliche Problem liegt auf der Ausgabenseite. Die Einnahmen steigen, die Ausgaben steigen aber noch schneller.
-Wer diese Herausforderungen ernst nimmt, muss den Mut haben, Prioritäten zu setzen. Wir schicken nach wie vor zu viel Steuergeld ins Ausland, anstatt es dort einzusetzen, wo es unserer Bevölkerung zugutekommt: bei der AHV, bei der Sicherheit unseres Landes, bei der Stärkung unserer Landwirtschaft oder bei der Bewältigung von Naturkatastrophen oder anderer Krisen im Inland. Wir wollen endlich unsere Verantwortung wahrnehmen, sorgsam mit dem Steuerfranken umgehen, die Prioritäten richtig setzen und den Bundeshaushalt langfristig wieder ins Lot bringen. Mit den erwähnten Mängeln in der Staatsrechnung 2025 wird dies nicht möglich sein. 
+Wer diese Herausforderungen ernst nimmt, muss den Mut haben, Prioritäten zu setzen. Wir schicken nach wie vor zu viel Steuergeld ins Ausland, anstatt es dort einzusetzen, wo es unserer Bevölkerung zugutekommt: bei der AHV, bei der Sicherheit unseres Landes, bei der Stärkung unserer Landwirtschaft oder bei der Bewältigung von Naturkatastrophen oder anderen Krisen im Inland. Wir wollen endlich unsere Verantwortung wahrnehmen, sorgsam mit dem Steuerfranken umgehen, die Prioritäten richtig setzen und den Bundeshaushalt langfristig wieder ins Lot bringen. Mit den erwähnten Mängeln in der Staatsrechnung 2025 wird dies nicht möglich sein. 
 Die SVP-Fraktion wird die Rechnung 2025 ohne Begeisterung genehmigen, sich in kommenden Budgetdebatten jedoch konsequent für eine vernünftige Prioritätensetzung einsetzen. Besten Dank, wenn Sie uns dabei unterstützen.
 </t>
   </si>
@@ -191,13 +190,13 @@
   <si>
     <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
 Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordentlichen Haushalt.
-Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter der Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
+Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
 Im ausserordentlichen Haushalt waren hingegen die Ausgaben grösser als die Einnahmen. Die beiden grössten ausserordentlichen Ausgaben waren diejenigen für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB. Dieser war ursprünglich für das Jahr 2024 budgetiert gewesen und konnte erst 2025 ausgerichtet werden, was damals die Verbesserung der Rechnung 2024 generiert hat. Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich verbucht, 333 Millionen Franken. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
-Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspressen würde. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man würde immer weniger für die wichtigen Bereiche ausgeben.
-Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und Finanzplan 2028 bis 2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
+Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete; dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
+Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
 Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt - und dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
-Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, wo wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungsprogramm 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
 Der Bundesrat beantragt Ihnen, der Staatsrechnung für das Jahr 2025 zuzustimmen.
 </t>
   </si>
@@ -600,6 +599,159 @@
 En matière d'énergie, le Conseil fédéral a adopté le message concernant une révision de la loi sur les installations électriques visant à accélérer les procédures d'autorisation pour l'extension et la transformation des réseaux électriques.
 Parmi les autres points forts de l'année dernière figurait également l'adoption de plusieurs stratégies, notamment la stratégie nationale contre le racisme et l'antisémitisme 2026-2031, la stratégie Asie G20 pour la période 2025 à 2028, et la stratégie du Conseil fédéral en matière de politique d'armement. Le Conseil fédéral a également adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
 En conclusion, vous trouvez la totalité des messages, rapports, plans d'action et stratégies détaillés, avec la date de leur adoption, dans notre rapport de gestion pour l'année 2025. Encore une fois, au nom du Conseil fédéral, je vous remercie de votre reconnaissance, de votre coopération et de votre soutien. Le Conseil fédéral va continuer à s'engager pleinement pour la défense des intérêts du pays et pour le bien de sa population.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knutti Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kommission hat an ihrer Sitzung vom 24. April 2026 die von Ständerätin Esther Friedli am 18. September 2025 eingereichte und vom Ständerat am 10. Dezember 2025 mit 27 zu 12 Stimmen angenommene Motion vorberaten.
+Mit der Motion soll der Bundesrat beauftragt werden, dem Parlament die erforderlichen Gesetzesänderungen zu unterbreiten und weitere notwendige Massnahmen zu ergreifen, um Ehegatten, die mit einer sogenannten Stellvertreterehe in Abwesenheit zumindest eines Ehepartners verheiratet wo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kommission hat an ihrer Sitzung vom 24. April 2026 die von Ständerätin Esther Friedli am 18. September 2025 eingereichte und vom Ständerat am 10. Dezember 2025 mit 27 zu 12 Stimmen angenommene Motion vorberaten.
+Mit der Motion soll der Bundesrat beauftragt werden, dem Parlament die erforderlichen Gesetzesänderungen zu unterbreiten und weitere notwendige Massnahmen zu ergreifen, um Ehegatten, die mit einer sogenannten Stellvertreterehe in Abwesenheit zumindest eines Ehepartners verheiratet worden sind, vom Familiennachzug auszuschliessen. Die Kommission beantragt mit 14 zu 11 Stimmen, die Motion anzunehmen.
+In der Schweiz ist die Ehe ein höchstpersönliches Recht. Grundsätzlich wird eine im Ausland gültig geschlossene Ehe in der Schweiz anerkannt. Der Familiennachzug ist nur bei Zwangsehen und bei von der Schweiz aus geschlossenen Minderjährigenehen ausgeschlossen. In patriarchalischen Kulturen und islamischen Ländern sind sogenannte Handschuhehen weit verbreitet. Dabei ist zumindest eine der verlobten Personen bei der Eheschliessung nicht anwesend. Mit der verlangten Einschränkung des Familiennachzugs beabsichtigt die Kommission, das Recht jedes Menschen auf freie Entscheidung über die eigene Lebensgestaltung zu stärken. Eine Ehe soll aus freiem Willen und in Anwesenheit von beiden Partnern geschlossen werden können. Diese Voraussetzung ist im Fall einer Stellvertreterehe nicht gegeben.
+Die Unterbindung des Familiennachzugs versteht sich nicht zuletzt auch als Massnahme gegen häusliche Gewalt, von der insbesondere Frauen nach einem Familiennachzug aufgrund ihres Abhängigkeitsverhältnisses weitaus häufiger betroffen sind. So zeigt eine Studie des Bundesamtes für Statistik, dass jede siebte Ehe mit ausländischen Ehepartnern unter Umständen geschlossen wird, die auf potenziellen Zwang oder fehlende persönliche Anwesenheit schliessen lassen können. Die Schweiz darf nicht tolerieren, dass Stellvertreterehen instrumentalisiert werden, um die gesetzlichen Anforderungen an den Familiennachzug zu umgehen. Auch wenn das internationale Privatrecht bei der Anerkennung von Stellvertreterehen eine eher grosszügige Regelung kennt, kann die Schweiz im Ausländerrecht ihre eigenen Regeln festlegen und dem Familiennachzug Grenzen setzen.
+Die Minderheit der Kommission beantragt, die Motion abzulehnen, weil eine spezifische Gesetzgebung aufgrund der geringeren Zahl erhärteter Verdachtsfälle von Stellvertreterehen unverhältnismässig sei und zudem den verfassungsmässigen Schutz der Privatsphäre sowie das Recht auf Ehe und Familie infrage stelle. Mit einer solchen Gesetzgebung würde die Schweiz auch gegen die Europäische Menschenrechtskonvention (EMRK) verstossen, in der das Recht auf Achtung des Privat- und Familienlebens als Grundrecht festgeschrieben ist.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jost Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welches ist die erste Frage, die wir uns stellen müssen, um einen Vorstoss einschätzen zu können? Genau, sie lautet: Gibt es Handlungsbedarf? Die Antwort im Falle der Motion Friedli Esther lautet: Nein. In den Beratungen haben wir gehört, dass den Behörden in den letzten fünf Jahren 12 problematische Fälle von sogenannten Telefonehen bekannt geworden sind. Diese Zahl zeigt uns zweierlei auf: Erstens, es handelt sich nicht um ein Massenphänomen und zweitens - und noch wichtiger -, die heutigen In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welches ist die erste Frage, die wir uns stellen müssen, um einen Vorstoss einschätzen zu können? Genau, sie lautet: Gibt es Handlungsbedarf? Die Antwort im Falle der Motion Friedli Esther lautet: Nein. In den Beratungen haben wir gehört, dass den Behörden in den letzten fünf Jahren 12 problematische Fälle von sogenannten Telefonehen bekannt geworden sind. Diese Zahl zeigt uns zweierlei auf: Erstens, es handelt sich nicht um ein Massenphänomen und zweitens - und noch wichtiger -, die heutigen Instrumente funktionieren. Unsere Behörden können Missbrauch erkennen und in solchen Fällen einschreiten - insbesondere dort, wo konkrete Hinweise auf Zwang, Missbrauch oder Umgehungstatbestände bestehen. 
+Ich halte im Namen der Minderheit fest: Zwangsheiraten lehnen wir entschieden ab, ebenso Minderjährigenehen oder missbräuchliche Umgehungen unseres Migrationsrechts. Solche Fälle müssen bekämpft werden, und sie werden heute bereits bekämpft. Das zentrale Problem dieser Motion liegt aber aus Sicht der Minderheit darin, dass sie einen Automatismus verlangt. Künftig soll jeder Familiennachzug ausgeschlossen werden, sobald eine Ehe in Abwesenheit eines Ehepartners geschlossen wurde, unabhängig von der konkreten Situation. Und genau das ist problematisch, denn eine Stellvertreterehe bedeutet nicht automatisch eine Zwangsheirat oder eine Scheinehe. In gewissen Ländern sind solche Eheschliessungen rechtlich zulässig, sofern beide Ehepartner zustimmen. Und bereits heute prüft die Schweiz bei der Anerkennung solcher Ehen, ob sie mit unserem "ordre public" vereinbar sind, also insbesondere, ob eine freie Zustimmung vorliegt, keine Minderjährigenehe besteht und keine Umgehung des Ausländerrechts vorhanden ist.
+Hinzu kommt eine bereits heute strenge Voraussetzung für den Familiennachzug, das bedeutet: gemeinsame Wohnung, finanzielle Unabhängigkeit, Sprachkenntnisse und Integrationskriterien. Die Motion geht deshalb viel weiter, als es in diesem Bereich nötig wäre. Stellen wir uns ein Ehepaar vor, das mehrere Jahre gemeinsam in seinem Herkunftsland gelebt hat, gemeinsame Kinder hat und dort eine Stellvertreterehe zustande kam, weil der Mann im Militärdienst war oder weil eine Krankheit oder eine Abwesenheit aus anderen zwingenden Gründen dazu führte, dass die Ehe in Abwesenheit geschlossen wurde. Dann tritt die Situation ein, dass ein Krieg ausbricht, politische oder religiöse Verfolgung eintritt und eine Flucht für einen Ehepartner notwendig ist. Er flieht in die Schweiz und erhält hier Asylschutz. Die Frau und die Kinder bleiben zurück. Nach Annahme dieser Motion könnte diese Familie trotz echter und gelebter Familiengemeinschaft nicht mehr zusammengeführt werden - einzig aufgrund der Form der Eheschliessung.
+Das Recht auf Familienleben, auch der Mehrheitssprecher hat es erwähnt, ist durch unsere Bundesverfassung geschützt, ebenso durch die Europäische Menschenrechtskonvention. Einschränkungen solcher Grundrechte müssen verhältnismässig sein, und genau das ist bei diesem Automatismus nicht gegeben und problematisch. Denn eine pauschale Regelung würde den Behörden jede Möglichkeit nehmen, die konkrete familiäre Situation zu prüfen, etwa die Dauer der Ehe, das Vorhandensein gemeinsamer Kinder und die tatsächlich gelebte Familiengemeinschaft. Gerade die Einzelfallprüfung würde mit dieser Motion faktisch ausgeschlossen. Ein Rechtsstaat zeichnet sich doch gerade dadurch aus, dass er nicht pauschal verbietet, sondern differenziert prüft. Deshalb bitte ich Sie im Namen der Minderheit, lehnen Sie diese Motion ab.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zryd Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Tuena, vielen Dank für Ihre hoch spannende Frage. Sie haben mich falsch verstanden, ich habe gesagt: Der Druck auf die Migration würde ansteigen, wenn es Spannungen im Westbalkan gibt, wenn die zunehmen. Es ist logisch, dass das irgendeine Bewegung geben würde. 
+Nein, ich habe keine genauen Zahlen. Ich denke, es sollte Ihrer Partei entgegenkommen, dass wir unsere friedensfördernden Massnahmen im Westbalkan ernst nehmen und so dort ein bisschen mehr Frieden haben. Das gibt dann auch weniger </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Tuena, vielen Dank für Ihre hoch spannende Frage. Sie haben mich falsch verstanden, ich habe gesagt: Der Druck auf die Migration würde ansteigen, wenn es Spannungen im Westbalkan gibt, wenn die zunehmen. Es ist logisch, dass das irgendeine Bewegung geben würde. 
+Nein, ich habe keine genauen Zahlen. Ich denke, es sollte Ihrer Partei entgegenkommen, dass wir unsere friedensfördernden Massnahmen im Westbalkan ernst nehmen und so dort ein bisschen mehr Frieden haben. Das gibt dann auch weniger Bewegung für die Schweiz. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfister Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zunächst möchte ich Ihnen für die grossmehrheitlich positive Aufnahme des Engagements unserer Soldatinnen und Soldaten im Kosovo danken. Es ist wichtig, dass Sie die Arbeit anerkennen, die in diesem schwierigen Gebiet seit Jahrzehnten täglich gemacht wird.
+Letzten Sommer habe ich unsere Armeeangehörigen der Swisscoy besucht und mir selbst ein Bild von der Lage vor Ort gemacht. Meine persönlichen Eindrücke, die Gespräche und die Entwicklung der Sicherheitslage haben mir bestätigt, dass die Präsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zunächst möchte ich Ihnen für die grossmehrheitlich positive Aufnahme des Engagements unserer Soldatinnen und Soldaten im Kosovo danken. Es ist wichtig, dass Sie die Arbeit anerkennen, die in diesem schwierigen Gebiet seit Jahrzehnten täglich gemacht wird.
+Letzten Sommer habe ich unsere Armeeangehörigen der Swisscoy besucht und mir selbst ein Bild von der Lage vor Ort gemacht. Meine persönlichen Eindrücke, die Gespräche und die Entwicklung der Sicherheitslage haben mir bestätigt, dass die Präsenz der Kfor und der Beitrag der Schweiz zu dieser Mission nicht nur für die Sicherheit der Region, sondern auch für die Sicherheit Europas weiterhin unverzichtbar sind. Der Bundesrat teilt diese Einschätzung. Er hat am 19. November 2025 beschlossen, das Mandat der Swisscoy um drei Jahre, also bis zum 31. Dezember 2029, zu verlängern.
+Seit dem Ende des Kosovo-Kriegs im Jahr 1999 wurden erhebliche Fortschritte erzielt. Heute verfügt Kosovo über funktionierende demokratische Institutionen. Die Wahlen gelten als frei und fair. Kosovo steht jedoch weiterhin vor erheblichen Herausforderungen. Obwohl die Sicherheitslage im Land insgesamt ruhig ist, bleibt sie weiterhin fragil, insbesondere im Norden. Darauf haben Sie in mehreren Voten hingewiesen. Die Vorfälle, die sich dort im Jahr 2023 ereigneten, waren so schwerwiegend, dass die Nato die Kfor zweimal verstärken musste. Die Kfor erfüllt weiterhin den Auftrag des UNO-Sicherheitsrates. Sie sorgt für Sicherheit und Stabilität, damit ein erneuter bewaffneter Konflikt verhindert wird. Die Kfor ist das einzige Sicherheitsinstrument, das von allen Seiten anerkannt und respektiert wird.
+Die Truppenstärke der Kfor wurde laufend an die Lageentwicklung angepasst. Sie wurde zwischenzeitlich reduziert und seit 2023 wieder aufgestockt. Der Beitrag der Schweiz ist bedeutsam und weiterhin notwendig, was mir auch in meinen persönlichen Gesprächen mit Vertretern aus dem Kosovo, der Kfor und der Nato bestätigt wurde. Auch darauf hat die letztjährige Nationalratspräsidentin hingewiesen.
+Der Einsatz stärkt auch die Verteidigungsfähigkeit der Schweiz, weil in zentralen Fähigkeitsbereichen praktische Erfahrungen im Einsatz gesammelt werden. In dieser Hinsicht sind das Training und die standardisierten Einsatzverfahren in der Zusammenarbeit von grossem Nutzen für die Schweizer Armee. Der Einsatz ermöglicht es, über einen längeren Zeitraum Erfahrungen bezüglich Tauglichkeit, Leistungsfähigkeit und Instandhaltungsbedarf von bestehendem wie auch neuem Material zu sammeln. Solche Erkenntnisse sind für die Verteidigungsfähigkeit der Armee ebenfalls von grossem Nutzen.
+Der Bundesrat beantragt, den Beitrag weiterzuführen. Der Maximalbestand der Swisscoy umfasst aktuell 215 Armeeangehörige. Der Bundesrat hat derzeit die Kompetenz, eine unbefristete Erhöhung um bis zu 30 Armeeangehörige zu beschliessen. Im November 2023 hat er davon Gebrauch gemacht. Nach dem Abzug von zwei österreichischen Kompanien aus der Kfor hat er entschieden, den Bestand der Swisscoy ab April 2024 von 195 auf 215 aufzustocken, um einen Teil der Leistungen zu übernehmen, die Österreich bis dahin erbracht hatte. Diese Stärkung lag in unserem sicherheitspolitischen Interesse, die militärische Machbarkeit war gegeben.
+Dass die Schweiz willens und imstande ist, auch kurzfristig zusätzliche Leistungen zu übernehmen, ist ein starkes Zeichen. Um auch künftig solche kurzfristig auftretenden zusätzlichen Aufgaben übernehmen zu können, beantragt der Bundesrat, dass er diese Kompetenz auch für das Mandat von 2027 bis 2029 erhält, sprich, dass er den Maximalbestand bei Bedarf von 215 auf maximal 245 Armeeangehörige erhöhen kann. Eine allfällige Erhöhung des Swisscoy-Bestands um zusätzliche 30 Armeeangehörige muss Voraussetzungen erfüllen. Eine Erhöhung des Bestands muss den sicherheitspolitischen Interessen der Schweiz dienen, und die militärische Machbarkeit muss gegeben sein. Unabhängig davon - wie bei bisherigen Mandaten - sieht auch der vorliegende Bundesbeschluss zwei Möglichkeiten vor, das Kontingent für spezifische Zwecke befristet aufzustocken.
+Dies soll in zwei Fällen möglich sein; erstens, wenn es für die Sicherheit des Schweizer Kontingents notwendig ist, also im Fall einer drastischen Verschlechterung der Lage, oder zweitens für Logistik und Instandhaltungsarbeiten. Die Kosten des Einsatzes mit einem Maximalbestand von 250 Armeeangehörigen betragen pro Jahr rund 48,9 Millionen Franken. Finanziert wird der Einsatz wie bislang aus dem regulären Armeebudget. Hier kann ich Nationalrat Tuena antworten: Der Bundesrat hat nicht die Absicht, einfach per se und ohne Grund auf 300 aufzustocken, zumal er das ja auch nicht beantragt. In die Prävention zu investieren, ist ein wichtiger Punkt und besonders wichtig im Kosovo.
+Zusammenfassend: Das Ausbrechen eines bewaffneten Konflikts im Westbalkan hätte direkte Auswirkungen auf die Sicherheit Europas und der Schweiz. Wir haben das in den 1990er-Jahren erlebt, wobei die Sicherheitslage in Europa heute noch angespannter ist als damals. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan - Sie haben in Ihren Voten auch darauf hingewiesen. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
+Der Schweizer Beitrag zur Kfor dient konkreten nationalen Sicherheitsinteressen. Die Schweiz leistet mit der Swisscoy aber auch einen solidarischen Beitrag für die Sicherheit Europas. Die Schweiz leistet als neutraler Staat keine militärische Unterstützung. Umso wichtiger ist es, dass wir dort, wo wir können und wo unser Know-how besonders wertvoll ist und geschätzt wird, zur Sicherheit Europas beitragen. Die Swisscoy ist unser wichtigster Beitrag in der militärischen Friedensförderung. Es ist auch der grösste und sichtbarste Beitrag der Schweiz in der Zusammenarbeit mit der Nato. 
+Aus diesen Gründen bitte ich Sie, auf die Vorlage einzutreten und den Minderheitsantrag auf Nichteintreten abzulehnen. 
+Ich möchte hier noch eine kleine Ergänzung anbringen zu den Fragen bezüglich der Menschenrechtslage im Kosovo, die vielleicht nachher auch noch einmal gestellt werden. Die Schweiz verfolgt die Situation im Kosovo selbstverständlich sehr aufmerksam. Die erwähnten Probleme beim Schutz von Minderheiten sind bekannt. Der Bundesrat geht ja auch in der vorliegenden Botschaft unter den Ziffern 2.2.1 bis 2.2.4 darauf ein. Der Schutz von Minderheiten ist ein zentrales Element der Menschenrechte und eine Voraussetzung für Stabilität und sozialen Frieden. Minderheitenrechte sind zudem ein Pfeiler der Verfassung des Kosovo. Daher erwarten wir, dass der Kosovo Menschen- und Minderheitsrechte auch akzeptiert und respektiert. 
+Die Schweiz hat ihre Besorgnis über diese Entwicklung gegenüber der kosovarischen Regierung zum Ausdruck gebracht und das Thema auch in multilateralen Gremien wie der OSZE besprochen. Neben ihrem Engagement in der militärischen Friedensförderung setzt sich die Schweiz auch mit anderen Aktivitäten für Frieden, Stabilität und Sicherheit im Kosovo sowie auf dem weiteren Westbalkan ein - das wäre auch eine Antwort auf das Votum von Nationalrat Andrey. Die Schweiz engagiert sich zudem für eine Normalisierung der Beziehungen zwischen Serbien und dem Kosovo. Das EDA führt hierzu den sogenannten Solothurner Prozess. Es ist ein informelles Format, bei dem sich hochrangige Politikerinnen und Politiker beider Länder regelmässig treffen. Dieser Prozess ergänzt den von der EU geführten Dialog zwischen dem Kosovo und Serbien. 
+Als Vorsteher des VBS möchte ich an dieser Stelle betonen, dass die Aufgabe der Kfor, an der wir uns mit der Swisscoy beteiligen, darin besteht, eine Eskalation zu verhindern und gegebenenfalls einzugreifen. Die von Nationalrat Imark angesprochenen Entwicklungen zeigen, dass im Kosovo die Gefahr einer Eskalation weiterhin besteht, und genau deshalb ist die Präsenz der Kfor im Kosovo nach wie vor notwendig. 
+Zur Frage von Nationalrat Büchel bezüglich konkreter Beiträge: Neben den Beiträgen in den Stäben dieser Einheiten im Kosovo und für die Logistik für die Nato-Truppen, die dort im Einsatz sind, leisten insbesondere auch die Liaison and Monitoring Teams (LMT) an den verschiedenen Orten einen sehr wichtigen Beitrag für die Befriedung der Region und übernehmen eben auch eine präventive Rolle, damit Konflikte gar nicht ausbrechen. Ich habe persönlich die LMT in Mitrovica besucht; die jungen Schweizerinnen und Schweizer, die dort im Einsatz stehen, spielen eine ganz wichtige Rolle zur Prävention von Konflikten.
+Es wurde gefragt, weshalb wir unser Kontingent erhöhen, während andere abbauen. Nicht alle Staaten reduzieren ihre Kontingente. Es besteht jedoch Druck seitens der USA, den Gesamtbestand zu senken. Das heisst nicht, dass auch die Schweiz reduzieren muss. Die Anzahl der beteiligten Staaten hat sich in den letzten drei Jahren sogar erhöht und beträgt heute 33.
+Zur Minderheit I (Tuena) bei Artikel 1: Der Bundesrat beantragt die Verlängerung des Einsatzes zur Unterstützung der Kfor bis am 31. Dezember 2029. Grundlage dieser Beteiligung bzw. der Friedensmission bildet eine kontinuierliche Lagebeurteilung durch die Nato und die Schweiz; wie sich die Lage mittel- und langfristig entwickelt, lässt sich heute nicht voraussagen. Beantragt wird eine Verlängerung bis Ende 2029, wobei das Parlament vor Ablauf dieses neuen Mandates erneut über das weitere Vorgehen entscheiden kann. Ein bereits heute beschlossener Abzug der Truppen bis 2029 würde die Schweiz binden und ihre Handlungsfreiheit aufheben. Zudem wäre diese Ankündigung ein Zeichen der Entsolidarisierung, das von unseren Partnern kaum verstanden würde, und sie liefe der Absicht des Bundesrates zuwider, die internationale Zusammenarbeit zu stärken. Aus diesen Gründen bitte ich Sie, diesen Minderheitsantrag abzulehnen.
+Zum Antrag der Kommissionsmehrheit in Artikel 2: Der Bundesrat beantragt, die Erhöhung des Kontingentes zur Deckung zusätzlicher Bedürfnisse der Kfor um 30 Angehörige zu ermöglichen. Die Kommission beantragt hingegen eine Erhöhung um bis zu 85 Angehörige der Armee; damit würde der Gesamtbestand - wie Nationalrat Tuena ausgeführt hat - auf maximal 300 festgelegt. Dieser Antrag steht im Einklang mit der Absicht des Bundesrates, allfällige kurzfristige Kapazitätslücken der Kfor schliessen zu können. Voraussetzung ist, dass die Armee über das notwendige Material, Personal und die erforderlichen Fähigkeiten verfügt, dass der zusätzliche Beitrag den sicherheitspolitischen Interessen der Schweiz entspricht und dass auch die Kosten berücksichtigt werden. Allfällige Anfragen würden in Bezug auf all diese Punkte geprüft. Aus heutiger Sicht kommen verschiedene Leistungen infrage, z. B. ein Detachement der Spezialkräfte oder zusätzliche Monitoring-Teams. Mit diesem Antrag erhält der Bundesrat gegenüber der in der Botschaft vorgesehenen Erhöhung um 30 Armeeangehörige einen grösseren Handlungsspielraum. Es spricht daher nichts gegen die Annahme dieses Antrages.
+Zur Minderheit I (Tuena) bei Artikel 2: Auch dieser Minderheitsantrag läuft der Absicht des Bundesrates zuwider. Ein bereits heute beschlossener gestaffelter Rückzug würde die Schweiz binden und ihre Handlungsfreiheit aufheben. Zudem wäre eine solche Ankündigung ein Zeichen der Entsolidarisierung, das von unseren Partnern kaum verstanden würde. Ich bitte Sie daher, diesen Minderheitsantrag abzulehnen, ebenso den Minderheitsantrag II (Tuena) zu Artikel 2 Buchstabe c, der das Gegenteil verlangt, d. h. die Streichung der Möglichkeit zur Verstärkung des Kontingentes an Armeeangehörigen.
+Zum Minderheitsantrag Tuena bei Artikel 5: Gemäss dieser Minderheit soll der Bundesbeschluss dem fakultativen Referendum unterstellt werden. Es geht hier nicht um eine Frage des Mutes des Bundesrates; dieser ist mitunter sogar zu tollkühnen Schritten bereit, vielmehr geht es um die Rechtssituation. Das Parlamentsgesetz (ParlG) sieht in Artikel 29 vor, dass die Bundesversammlung Einzelakte, die dem Referendum nicht unterstehen, in der Form des einfachen Bundesbeschlusses erlässt. Einzelakte der Bundesversammlung werden in der Form des Bundesbeschlusses nur dann dem Referendum unterstellt, wenn die notwendige gesetzliche Grundlage weder in der Bundesverfassung noch in einem Bundesgesetz besteht. Diese Voraussetzung ist im vorliegenden Geschäft nicht erfüllt. Artikel 66b Absatz 4 des Militärgesetzes (MG) sieht vor, dass der Swisscoy-Einsatz aufgrund von Bewaffnung, Dauer und Kontingentsgrösse durch die Bundesversammlung genehmigt wird; damit besteht eine gesetzliche Grundlage. Zudem müssen gemäss Artikel 141 Absatz 1 Buchstabe c der Bundesverfassung (BV) Bundesbeschlüsse dem fakultativen Referendum unterstellt werden, soweit Verfassung oder Gesetz dies vorsehen. Für Beschlüsse nach Artikel 66b Absatz 4 MG ist dies gerade nicht vorgesehen. Der Beschluss über den Swisscoy-Einsatz kann daher nicht dem Referendum unterstellt werden. Aus diesen Gründen bitte ich Sie, auch diesen Minderheitsantrag abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es geht um die Schweizer Beteiligung an der KFOR respektive um die Verlängerung des Swisscoy-Einsatzes. 
+Ihre zuständige Kommission hat sich im April 2026 mit dem Einsatz von Militärangehörigen auf dem Balkan beschäftigt. Zum einen ging es um die Beteiligung der Schweiz an der KFOR, zum anderen um die Verlängerung des Swisscoy-Einsatzes für die Jahre 2027 bis 2029. 
+Der Bundesrat hat die Botschaft an seiner Sitzung im November 2025 verabschiedet. Der Einsatz der Schweizer Armee zur Unterstützung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es geht um die Schweizer Beteiligung an der KFOR respektive um die Verlängerung des Swisscoy-Einsatzes. 
+Ihre zuständige Kommission hat sich im April 2026 mit dem Einsatz von Militärangehörigen auf dem Balkan beschäftigt. Zum einen ging es um die Beteiligung der Schweiz an der KFOR, zum anderen um die Verlängerung des Swisscoy-Einsatzes für die Jahre 2027 bis 2029. 
+Der Bundesrat hat die Botschaft an seiner Sitzung im November 2025 verabschiedet. Der Einsatz der Schweizer Armee zur Unterstützung der multinationalen Nato-Truppe in Kosovo soll um drei Jahre bis Ende 2029 verlängert werden. Zudem möchte der Bundesrat die Befugnis erhalten, den maximalen Personalbestand während der Mandatsdauer bei Bedarf um bis zu 30 Angehörige der Armee (AdA) zu erhöhen. 
+Der Ständerat hat den Bundesbeschluss als Erstrat am 10. März dieses Jahres mit 37 zu 2 Stimmen bei 4 Enthaltungen angenommen. 
+Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
+Der Schweizer Beitrag an die KFOR dient konkreten nationalen Sicherheitsinteressen. Mit der Swisscoy leistet die Schweiz einen solidarischen Beitrag zur Sicherheit Europas. Viele an der KFOR beteiligte Staaten engagieren sich stark in der militärischen Unterstützung der Ukraine, was die Schweiz als neutraler Staat nicht tut. Wir profitieren aber von ihren Einsätzen. Die meisten Mitglieder der Kommission und auch der anwesende Korpskommandant Michaud haben betont, dass der Einsatz der Swisscoy unser wichtigster Beitrag zur militärischen Friedensförderung ist. Unser Beitrag zu dieser Mission ist bedeutsam, und der Mehrwert für die Schweizer Armee ist gross. Wir leisten damit einen wichtigen Partnerschaftsbeitrag und übernehmen in der internationalen Gemeinschaft Verantwortung. Die Interoperabilität der Armee als Ganzes wird gestärkt, weil diese Erfahrungen dank unseres Milizsystems in die Truppe einfliessen. 
+Es gab verschiedenste Anträge in der Kommission. Den Antrag des Bundesrates habe ich eben erwähnt: die Verlängerung der Schweizer Beteiligung an der KFOR bis Ende Dezember sowie die Erhöhung des Maximalbestands um 30 AdA. 
+Es gab den Antrag Riniker Nr. 1. Dieser forderte, dass der Bundesrat das Kontingent auf bis zu 85 AdA erhöhen kann. Die Begründung war, dass sich die Sicherheitslage in Europa verschärft hat. Es gibt zahlreiche Nationen, die sich zurückziehen und in der Ukraine aushelfen. Die Schweiz könnte nun in Kosovo in die Bresche springen und genau diese Lücken schliessen. 
+Kollege Tuena stellte mehrere Anträge: den Antrag Tuena Nr. 5 auf Nichteintreten auf das Geschäft und unter anderem den Antrag Tuena Nr. 2, einen Konzeptantrag. Darin wird zu Artikel 1 gefordert, den Einsatz der Schweizer Armee zur Unterstützung der KFOR für eine letzte Zeitspanne, die spätestens am 31. Dezember 2029 enden soll, zu genehmigen. Gestrichen werden soll der Maximalbestand von 215 AdA. Der Antrag fordert zudem die Streichung von Artikel 2 respektive soll der Bundesrat ab 1. Januar 2027 einen gestaffelten Rückzug anordnen. 
+Weiter gab es einen Eventualantrag Tuena Nr. 3. Der Antrag Tuena Nr. 4 forderte in Artikel 5, dass der Bundesbeschluss dem fakultativen Referendum unterstellt werden soll. 
+Die Begründungen bezogen sich meist auf die hohen Kosten und darauf, dass sich auch andere Nationen aus Kosovo zurückziehen. 
+Die Abstimmungen waren folgendermassen: Wir traten mit 17 zu 5 Stimmen bei 1 Enthaltung auf die Vorlage ein. Der Antrag Riniker Nr. 1 obsiegte mit 12 zu 8 Stimmen bei 3 Enthaltungen gegenüber dem Entwurf des Bundesrates. Die beiden Konzeptanträge Tuena Nr. 2 respektive Nr. 3 unterlagen jeweils dem Antrag Riniker Nr. 1 mit 12 zu 7 Stimmen bei 4 Enthaltungen. Der Antrag Tuena Nr. 4 zu Artikel 5 wurde mit 15 zu 8 Stimmen bei 0 Stimmen verworfen. 
+Die Gesamtabstimmung fiel mit 16 zu 7 Stimmen bei 0 Enthaltungen für die Annahme des Entwurfes aus. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nantermod Philippe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous traitons aujourd'hui trouve son origine dans l'échec de l'objet 22.071 concernant l'exécution des sanctions, qui a été rejeté lors du vote final du 14 juin 2024. Cet échec était largement accidentel, dirons-nous. Certains l'ont même qualifié en commission de "Betriebsunfall". En effet, plusieurs éléments du projet faisaient alors l'objet d'un large consensus. À la suite de ce vote, la Commission des affaires juridiques du Conseil national avait déposé l'initiative parlementair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous traitons aujourd'hui trouve son origine dans l'échec de l'objet 22.071 concernant l'exécution des sanctions, qui a été rejeté lors du vote final du 14 juin 2024. Cet échec était largement accidentel, dirons-nous. Certains l'ont même qualifié en commission de "Betriebsunfall". En effet, plusieurs éléments du projet faisaient alors l'objet d'un large consensus. À la suite de ce vote, la Commission des affaires juridiques du Conseil national avait déposé l'initiative parlementaire 24.464, afin de reprendre et compléter certains aspects de cette réforme. La Commission des affaires juridiques du Conseil des États a toutefois estimé qu'il était préférable d'abandonner une approche fragmentée et de charger directement le Conseil fédéral de préparer une réforme plus globale et plus cohérente du droit de l'exécution des sanctions. Elle a donc déposé la motion 25.4415, que nous traitons aujourd'hui, que le Conseil des États a adoptée, sans opposition, le 16 mars dernier. La majorité de notre commission s'est ralliée à cette approche, par 16 voix contre 8.
+Concrètement, quel est le but de cette motion ? Elle charge le Conseil fédéral de reprendre les travaux sur l'exécution des sanctions en s'appuyant notamment sur le projet 1 de l'objet 22.071, celui que nous avions rejeté lors de cet échec accidentel, dirons-nous. Surtout, elle le charge d'examiner de manière approfondie la question des mesures thérapeutiques institutionnelles prévues à l'article 59 du code pénal, ce qu'on appelle parfois le petit internement. Il faut le dire clairement, nous faisons face aujourd'hui à un vrai problème pratique. Le nombre de mesures prononcées augmente fortement et leur durée augmente aussi. Les coûts explosent, les cantons manquent de places adaptées. Dans certains cas, nous nous retrouvons avec des situations extrêmement difficiles à justifier du point de vue de la cohérence du système pénal.
+Soutenir cette motion ne signifie pas remettre en cause le principe des mesures thérapeutiques. Ces mesures restent indispensables dans de nombreux cas. Mais il faut avoir le courage de regarder la réalité en face : un système qui coûte toujours davantage, mobilise des ressources limitées pendant des années et produit parfois des résultats très discutables doit pouvoir être réexaminé. La majorité de la commission estime précisément qu'il faut sortir des bricolages ponctuels et reprendre ce dossier de manière sérieuse, globale et coordonnée avec les cantons qui assument l'essentiel des coûts et des difficultés d'exécution.
+Nous avons d'ailleurs insisté pour que les travaux du Conseil fédéral tiennent compte de l'analyse actuellement menée par les cantons et la Conférence des directrices et directeurs des départements cantonaux de justice et police (CCDJP). Il ne s'agit pas de légiférer à l'aveugle, mais de partir des réalités du terrain. Les débats en commission ont aussi montré un autre problème important : la contradiction entre certaines mesures thérapeutiques de très longue durée et les expulsions pénales obligatoires prévues par le code pénal. Cette question fait l'objet d'une autre motion qui sera débattue plus tard.
+En résumé, pour la commission, le système des mesures thérapeutiques doit impérativement être revu. Leur efficacité n'est pas toujours démontrée, leurs coûts explosent, les places disponibles ne sont pas suffisantes. Ces mesures entraînent une perte de confiance et de compréhension du système. Par ailleurs, pour les prévenus eux-mêmes, la mesure thérapeutique peut impliquer dans les faits une prolongation qui paraît infinie de la sanction, sans perspectives concrètes.
+Pour toutes ces raisons, la majorité de la commission vous invite à adopter la motion 25.4415.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dandrès Christian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui a été fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision de manière générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
+Je pense qu'on doit relever que si on doit analyser la question des coûts dans le domaine de l'exécution, il y a quand même une approche assez si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui a été fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision de manière générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
+Je pense qu'on doit relever que si on doit analyser la question des coûts dans le domaine de l'exécution, il y a quand même une approche assez singulièrement paradoxale de la majorité qui refuse de revoir la question des peines de substitution. En effet, pour 200 francs d'amendes impayées, on va mettre des personnes en prison et cela va coûter 400 francs par jour de détention ; ce sont des milliers de personnes qui sont dans cette situation et des millions de francs qui sont investis. Par contre, on veut restreindre les mesures thérapeutiques qui sont, je le rappelle, ordonnées par des juges pour des personnes qui commettent des actes graves en lien direct avec la pathologie. Ce n'est vraiment pas sérieux comme approche.
+L'autre aspect, c'est que dans les débats au sein de la commission, les délégations des groupes libéral-radical et UDC ont cristallisé le débat sur la question des expulsions pénales des étrangers avec un parti pris très clair. La logique, c'est de dire, en résumé, pourquoi doit-on doit payer si une personne doit être expulsée ?
+Je pense très honnêtement que les enjeux qui sont liés à la sécurité et au droit pénal méritent un peu mieux, et j'aimerais y revenir brièvement. Tout d'abord, parce que le droit pénal, on doit le rappeler, a ses racines dans les Lumières, dans les révolutions bourgeoises des 18e et 19e siècles. On concrétise avec ces mesures une conception de l'État qui est fondée sur la défense des droits, des libertés fondamentales, l'habeas corpus. On sort de la logique de la loi du talion. On doit rappeler aussi que, en lien avec ces révolutions, il y a un caractère universel : ces principes ne s'arrêtent pas aux frontières nationales. La Suisse a aussi des engagements vis-à-vis de l'humanité, qui ne se limitent pas uniquement aux détentrices et détenteurs du passeport rouge à la croix blanche. Or, ce qui est admis depuis deux siècles, c'est que le crime n'est pas toujours et uniquement lié à des choix intentionnels, assumés et individuels. C'est pour cela qu'on a des mesures thérapeutiques dans le code pénal.
+Le crime peut être en lien avec de graves troubles mentaux du détenu, et c'est pour éviter le danger que la pathologie représente qu'il faut soigner la personne. Or, la question qui est posée - et que s'est aussi posée la commission - est de savoir qui doit assumer cette responsabilité. 
+Je pense, très honnêtement, qu'on doit avoir une approche assez pragmatique dans le domaine : ce sont les pays qui le peuvent et là où se trouve le délinquant malade. Et on ne peut pas se dédouaner, comme veulent le faire le PLR et l'UDC, de cette responsabilité avec des arguments de boutiquier qui consistent à dire qu'il ne faut pas gaspiller puisque la personne doit partir. Parce que cette logique a évidemment un corollaire, c'est que les délinquants, en quelque sorte, n'ont qu'à aller commettre des crimes graves ailleurs qu'en Suisse. Et cela ne va pas, évidemment. Parce que la sécurité, c'est aussi un élément commun qui dépasse les frontières et qui repose sur la responsabilité de tous les États de pouvoir assumer des personnes qui ont ces problèmes.
+Et j'aimerais quand même faire une petite incise. Si on doit répondre à cet argument de boutiquier, on peut aussi rappeler que les populations, les pays dont sont issues les personnes qui ont été stigmatisées dans le cadre des travaux de la commission, ces délinquants, ont en quelque sorte déjà payé le prix pour que la Suisse prenne part à leur sécurité en soignant la poignée de personnes qui font l'objet de mesures. Je crois qu'on doit rappeler ici, on l'a abordé dans le cadre de la restitution des mesures compensatoires, que les caisses de la Confédération ne détiennent pas moins d'un milliard de francs de créances compensatoires pour des actes de corruption qui ont été commis par des multinationales en Suisse et que cet argent pourrait aussi servir notamment à cela. Il n'y a pas si longtemps, on a eu une perquisition à l'encontre de Gunvor, laquelle montre que c'est vraiment une question d'une grande actualité.
+J'aimerais conclure en relevant que les mesures thérapeutiques doivent évidemment être maintenues dans leur principe, parce que c'est absolument odieux que des personnes psychiquement et gravement atteintes croupissent sans soins dans des prisons. Mais, aujourd'hui, le système ne fonctionne pas bien - M. Nantermod l'a dit - faute de places adaptées pour accueillir des malades, d'une part, et en raison de difficultés en termes de ressources, d'autre part. Cela a pour effet que des personnes peuvent rester dans des mesures thérapeutiques parfois bien au-delà des peines plafond prévues dans le code pénal, ce qui n'est évidemment pas acceptable. Il faut donc améliorer ces mesures, c'est une question de dignité. Et c'est aussi une question de sécurité. 
+Évidemment, on ne va pas améliorer les mesures avec le rationnement des soins visé par cette motion que le Conseil des États a adoptée. Au contraire, cela risque de transformer peu à peu le régime des mesures thérapeutiques non plus en petit internement, mais en un internement de fait, ce qu'on ne peut évidemment pas accepter.
+C'est la raison pour laquelle la minorité vous demande de rejeter cette motion parce qu'elle franchit ce cap profondément inacceptable.
 </t>
   </si>
 </sst>
@@ -648,8 +800,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I23" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I30" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I30"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1604,6 +1756,207 @@
         <v>121</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>129</v>
+      </c>
+      <c r="I25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27"/>
+      <c r="F27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" t="s">
+        <v>145</v>
+      </c>
+      <c r="I29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -201,58 +201,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">374713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giacometti Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Commissione delle finanze aveva già preso atto del risultato del Consuntivo 2025 della Confederazion nel mese di febbraio. Per la prima volta dopo la crisi di Covid-19, il consuntivo chiude con un risultato positivo, registrando un'eccedenza di finanziamento di 259 milioni di franchi. Questo risultato, che rappresenta un chiaro miglioramento rispetto al deficit preventivato di 815 milioni di franchi, risulta da un'eccedenza di 1,185 miliardi nel bilancio ordinario a fronte di un deficit di 92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Commissione delle finanze aveva già preso atto del risultato del Consuntivo 2025 della Confederazion nel mese di febbraio. Per la prima volta dopo la crisi di Covid-19, il consuntivo chiude con un risultato positivo, registrando un'eccedenza di finanziamento di 259 milioni di franchi. Questo risultato, che rappresenta un chiaro miglioramento rispetto al deficit preventivato di 815 milioni di franchi, risulta da un'eccedenza di 1,185 miliardi nel bilancio ordinario a fronte di un deficit di 925 milioni iscritto nel bilancio straordinario. Il risultato favorevole è riconducibile principalmente alle entrate fiscali supplementari provenienti da alcune imprese nel Cantone di Ginevra.
-Il disavanzo del bilancio straordinario è dovuto soprattutto ai contributi versati ai Cantoni per le persone con statuto di protezione S provenienti dall'Ucraina, 700 milioni, e al contributo unico alle FFS, 850 milioni, compensati in parte da entrate straordinarie della Banca nazionale svizzera.
-L'avanzo dell'amministrazione ordinaria raggiunge 1,2 miliardi di franchi, mentre la regola del freno all'indebitamento avrebbe consentito un deficit di 262 milioni di franchi. Ne risulta quindi un saldo strutturale positivo di 1,4 miliardi, nettamente superiore al valore previsto nel preventivo.
-Le entrate ordinarie superano il budget di 1,9 miliardi e il risultato dell'anno precedente di ben 3,3 miliardi. La crescita è dovuta soprattutto all'imposta federale diretta sulle imprese, che beneficia delle entrate temporanee dal Cantone di Ginevra per circa 1,5 miliardi di franchi.
-Anche l'imposta federale diretta sui redditi aumenta di 0,5 miliardi, mentre l'IVA aumenta di 700 milioni, grazie alla crescita dell'economia nominale e all'effetto ritardato dell'aumento dell'aliquota dal 2024. Le entrate dell'imposta preventiva, invece, risultano inferiori alle attese.
-Le spese totali sono aumentate del 4 percento e ammontano a 87,6 miliardi di franchi. 
-I principali aumenti riguardano la previdenza sociale, le finanze e imposte, i trasporti, l'istruzione e la ricerca e l'esercito.
-Nel 2025 il numero di posti nella Confederazione è cresciuto di 240 unità, più 0,6 per cento, mentre le spese per il personale sono aumentate di 79 milioni di franchi, soprattutto per il rincaro dell'1 per cento.
-Il debito netto scende leggermente a 140 miliardi di franchi. Il conto di ammortamento del debito Covid si riduce per la prima volta di circa 500 milioni, grazie al saldo strutturale positivo e alle entrate straordinarie, e ammonta a 26,3 miliardi di franchi. Il conto di compensazione rimane stabile a circa 20 miliardi di franchi.
-Nella seduta dell'11 e 12 maggio 2026, la commissione ha proceduto all'esame di dettaglio del consuntivo. Le sue quattro sottocommissioni hanno presentato le conclusioni delle rispettive analisi approfondite dei consuntivi dei singoli servizi federali realizzate nel corso del mese di aprile.
-Il Controllo federale delle finanze, quale organo di revisione, ha presentato alla sua commissione i risultati delle tre verifiche relative al Consuntivo 2025 della Confederazione: la revisione del conto annuale, la verifica del Fondo per l'infrastruttura ferroviaria e quella del Fondo per le strade nazionali e il traffico d'agglomerato. Ogni revisione è stata condotta separatamente e richiede un'approvazione da parte del Parlamento.
-Le verifiche mostrano che i conti rispettano gli standard contabili e che non vi sono carenze significative nei controlli interni. Tuttavia, la situazione finanziaria dei fondi presenta rischi. Le riserve del Fondo per l'infrastruttura ferroviaria saranno esaurite entro il 2028, violando la riserva minima legale di 300 milioni di franchi. Le cause principali sono l'aumento dei costi di esercizio e di manutenzione, la riduzione delle entrate e la restituzione di anticipi. Le sfide finanziarie del fondo sono note, ma ancora irrisolte. Anche il fondo per le strade nazionali e il traffico d'agglomerato rischia, senza misure correttive, di scendere sotto le riserve minime previste dalla legge.
-Il Controllo federale delle finanze conferma che il consuntivo rispetta le prescrizioni legali e le regole del freno all'indebitamento previste dall'articolo 126 della Costituzione federale. Per questo motivo raccomanda all'Assemblea federale di approvare il conto annuale.
-Nel rapporto vengono richiamati due aspetti già evidenziati negli anni precedenti. Il primo riguarda il fatto che la contabilità non permette una valutazione completa della situazione patrimoniale, poiché non considera il capitale proprio del fondo dell'infrastruttura ferroviaria, che è negativo. Se fosse incluso, il capitale proprio della Confederazione risulterebbe inferiore di 1,9 milioni di franchi, ma il metodo attuale è conforme alla legge. Il secondo punto concerne la riscossione dell'imposta federale diretta, che è effettuata dai Cantoni. Il Controllo federale delle finanze sottolinea che le competenze di revisione in questo ambito spettano alle autorità cantonali e non a quelle federali.
-La vostra commissione vi propone all'unanimità di approvare il Consuntivo 2025 della Confederazione come pure i conti speciali concernenti il Fondo per le strade nazionali e il traffico d'agglomerato e il Fondo per l'infrastruttura ferroviaria. La commissione si allinea così alla posizione del Controllo federale delle finanze, che in qualità di organo di revisione ha raccomandato l'approvazione del consuntivo, del sorpasso di credito di 1,86 miliardi di franchi e della costituzione di nuove riserve pari a 569 milioni di franchi.
-Concludo ringraziando il Consiglio federale, in particolare la consigliera federale Karin Keller-Sutter, l'Amministrazione federale delle finanze, il Segretariato commissionale e il Controllo federale delle finanze.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">374817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crevoisier Crelier Mathilde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commençons par un constat sans appel[NB]: la violence sexiste et sexuelle est un fléau qui n'épargne pas notre pays, comme l'a encore rappelé hier le Conseil fédéral, en lançant la deuxième phase de sa campagne contre la violence domestique. En 2025, la police a enregistré 22 000 infractions dues à la violence domestique, un chiffre dont on sait qu'il ne constitue que la partie émergée de l'iceberg et cache une sombre réalité dans laquelle un nombre encore plus élevé de cas n'entrera jamais dans les statistiques de la criminalité. En effet, l'accès à la justice des victimes de violence sexiste, sexuelle et de violence domestique est encore semé d'embûches. Parmi celles-ci, la prise en charge des victimes par les autorités de procédure pénale, soit la police, les ministères publics et les tribunaux, est souvent pointée du doigt comme un facteur de renoncement pour les victimes à poursuivre la procédure. En cause, on peut mentionner notamment un manque de sensibilité dans l'accueil, la prise en charge et l'audition des victimes, avec un risque important de victimisation secondaire pour ces dernières.
-Ainsi, la motion de la Commission des affaires juridiques du Conseil national, "Modification du code de procédure pénale concernant la formation initiale et continue des autorités pénales", vise donc à améliorer cette formation de manière à améliorer l'accès à la justice pour les victimes. Elle se base sur le rapport du Conseil fédéral de 2025, donnant suite au postulat Fehlmann Rielle 21.4215.
-Vous l'avez entendu, la majorité de la commission rejette la motion au motif de la répartition des compétences. Effectivement, les cantons sont responsables de la formation initiale et continue des autorités de poursuite pénale, mais le prétexte du fédéralisme ne saurait nous prémunir d'examiner si nous remplissons nos propres obligations. Que les cantons soient tenus d'assurer la formation continue et initiale, y compris en vertu de l'article 15 de la Convention d'Istanbul, ne signifie pas encore, toutefois, que celle-ci soit assurée. Or, aujourd'hui, on constate que la mise en oeuvre est, sinon lacunaire, encore inégale. Le rapport de 2022 d'évaluation du Groupe d'experts sur la lutte contre la violence à l'égard des femmes et la violence domestique (Grevio) déplore que la Suisse n'ait toujours pas de programme de formation standardisé dans le domaine de la violence sexuelle pour la police, et que celle-ci soit facultative pour les services judiciaires. Le Grevio encourage vivement les autorités suisses à prendre des mesures afin de veiller à dispenser une formation initiale et continue systématique et obligatoire aux professionnels en lien avec les victimes et les auteurs de toutes les formes de violence visées par la Convention d'Istanbul. Ainsi, si l'argument de la compétence cantonale doit évidemment être pris en compte, il doit aussi être soigneusement sous-pesé en regard de nos responsabilités à l'échelon fédéral.
-Dans le cadre de la réponse au postulat précité, la Confédération a commandé un avis de droit qui conclut qu'elle dispose d'une marge de manoeuvre en vertu de l'article 123 de la Constitution qui règle la compétence fédérale en matière de droit pénal et de droit de procédure pénale, lorsqu'il s'agit de garantir l'exécution uniforme du droit fédéral, ainsi que la mise en oeuvre du droit international. Or, ces deux conditions sont remplies. D'une part, aujourd'hui, malgré les efforts d'uniformisation consentis par les cantons, force est de constater que la formation des autorités de poursuite pénale est encore trop fragmentée pour assurer l'égalité de traitement des victimes dans l'ensemble du pays, et que si la formation initiale de la police est désormais généralisée, celle des ministères publics reste encore lacunaire. D'ailleurs, bien que le Conseil fédéral propose lui aussi de rejeter la motion, il admet qu'il reste des efforts à accomplir, par exemple concernant l'audition des victimes ou encore au niveau de la coopération interdisciplinaire et de la formation initiale et continue des acteurs. D'autre part, une intervention de la Confédération au titre de l'article 123 de la Constitution se justifie également par l'obligation qui nous est faite, en vertu de l'article 15 de la Convention d'Istanbul, de garantir la formation des professionnels. Dès lors, rejeter la présente motion, comme le propose la majorité de la commission, ne relève pas du simple respect des compétences cantonales, mais bien d'une appréciation politique. Or, il faut admettre que la situation actuelle en matière de prise en charge des victimes ne permet ni de garantir l'exécution uniforme du droit ni de remplir nos obligations internationales. C'est également la conclusion à laquelle est parvenu le Conseil national, par 127 voix contre 63 et 1 abstention, soit l'intégralité des groupes parlementaires, à une exception près.
-Il a été dit en commission que nous nous rendrions risibles en adoptant cette motion. Le ridicule ne tue pas, contrairement à la violence sexiste et sexuelle qui fait encore et toujours une victime toutes les deux semaines dans notre pays.
-Dans l'intérêt des victimes, mais aussi des autorités chargées de les accompagner dans la procédure pénale, je vous invite à suivre la minorité de la commission et à adopter la motion.
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">375131</t>
   </si>
   <si>
@@ -294,67 +242,6 @@
 Je reviens brièvement à ce stade des débats sur les trois minorités dont nous parlons encore d'aujourd'hui, à la suite de ce qu'ont dit mes collègues précédemment. D'abord, concernant la minorité Bregy, nous vous invitons à suivre la majorité de la commission sur ce point. Il s'agit de la question de savoir s'il doit y avoir une forme de privilège pour les loyers et les charges locatives pendant cette fameuse durée de prélèvement de trois ans, à l'image de ce que l'on fait pour les impôts. La réflexion de la majorité de la commission a été de se dire qu'il était important d'éviter des situations critiques dans lesquelles les loyers ne sont pas payés et dans lesquelles cela pourrait provoquer des expulsions, ce qui n'est dans l'intérêt de personne, puisqu'on se retrouverait ensuite avec des situations d'une grande complexité, à la fois au désavantage des personnes concernées, des locataires, mais aussi au désavantage des bailleurs, qui seraient mis dans une position très délicate. Je dois reconnaître qu'il y a un petit enjeu technique autour du fait que ce fameux privilège qui serait donné pendant ces trois ans de prélèvement pour les loyers et les charges locatives se recoupe, d'une certaine manière, avec la prise en compte du loyer et des charges locatives dans le minimum vital. C'est vrai. La majorité vous propose de maintenir cette divergence et de trouver le cas échéant une solution de compromis avec le Conseil des États qui, lui, a adopté ce mécanisme pour les impôts qui, eux, ne sont pas pris en compte dans le minimum vital ; du moins pas encore aujourd'hui, car le travail est en cours. Cela nous permettrait d'avoir cette discussion avec le Conseil des États dans le cadre de l'élimination des divergences.
 La deuxième minorité concerne la question de la recherche des revenus. Nous vous invitons à soutenir la minorité Schmezer sur ce point. Le projet du Conseil fédéral était intelligent. Il disait qu'il fallait que les recherches de revenus soient manifestement insuffisantes pour que l'on puisse interrompre cette procédure d'assainissement. Le terme "manifestement" permettait d'illustrer le fait qu'on veut que cela saute aux yeux, que ce soit quelque chose de manifeste, pour éviter que l'on pousse les autorités à faire des espèces d'enquêtes sans fin. On ne peut pas exiger des autorités qu'elles viennent poser des caméras derrière chaque personne en procédure, qu'elles viennent mandater des détectives pour faire l'analyse des recherches de revenus. À l'image de ce qui se pratique dans d'autres domaines, on doit s'assurer, sur la base des informations transmises, qui peuvent être vérifiées, que les choses sont faites correctement, sans pour autant avoir des attentes démesurées de la part de l'autorité. Ces attentes, du reste, souvent, ne pourront pas être comblées. J'ai bon espoir, même si la minorité Schmezer n'est pas suivie par notre conseil aujourd'hui, que dans la pratique, les autorités resteront raisonnables et ne pratiqueront pas une espèce de contrôle bureaucratique absurde. Toutefois, nous pensons à ce stade qu'il serait préférable d'en rester au projet du Conseil fédéral.
 Enfin, je termine par la troisième proposition de minorité, qui concerne la fameuse question des gains extraordinaires. La question qui se pose est presque philosophique, et l'on comprend que certains dans cet hémicycle veuillent rattraper, après coup, quand la procédure est clôturée, des gains extraordinaires faits par les personnes concernées. C'est vrai que si l'on devient millionnaire du jour au lendemain et qu'on a bénéficié d'une procédure d'assainissement des dettes, il paraît juste de restituer ce patrimoine dans la procédure pour en faire profiter les créanciers. Cependant, toute la question concerne la durée. Jusqu'à quand peut-on mettre en place ce processus ? Indéfiniment, comme le propose la minorité II (Nantermod), paraît totalement déraisonnable. Ce serait impossible pour des raisons de preuve. 20 ans, c'est la proposition de compromis du Conseil des États. Nous aurions préféré 10 ans et nous proposons d'en rester à la variante de la minorité I (Schmezer) de 10 ans.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chollet Clarence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soyons clairs : le refus d'entrer en matière proposé par cette minorité ne traduit aucune opposition de principe au Service de renseignement de la Confédération (SRC). Face aux guerres, aux cyberattaques, à l'espionnage, aux ingérences étrangères et aux menaces terroristes, la Suisse a besoin d'un service de renseignement efficace, capable d'identifier les menaces et de contribuer à la sécurité de notre pays. Mais précisément parce que le renseignement joue un rôle essentiel dans un état de droi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soyons clairs : le refus d'entrer en matière proposé par cette minorité ne traduit aucune opposition de principe au Service de renseignement de la Confédération (SRC). Face aux guerres, aux cyberattaques, à l'espionnage, aux ingérences étrangères et aux menaces terroristes, la Suisse a besoin d'un service de renseignement efficace, capable d'identifier les menaces et de contribuer à la sécurité de notre pays. Mais précisément parce que le renseignement joue un rôle essentiel dans un état de droit, ses compétences doivent être définies de manière stricte, claire et contrôlée. Or, c'est exactement ce que ce projet ne fait pas.
-Cette révision élargit les compétences du SRC dans de nombreux domaines, alors même que ce service a été marqué ces dernières années par une succession de dysfonctionnements et de scandales. Les rapports de la Délégation des Commissions de gestion, les interventions de l'Autorité de surveillance indépendante des activités de renseignement (AS-Rens) et plusieurs affaires médiatisées ont montré à quel point il reste des problèmes de gouvernance, de contrôle interne et de respect du cadre légal. Face à ce constat, on aurait pu s'attendre à une révision visant d'abord à renforcer les garde-fous, la transparence institutionnelle et les mécanismes de surveillance. Le Conseil fédéral a malheureusement choisi une autre voie. Au lieu de renforcer les contrôles, il renforce les pouvoirs. Au lieu de clarifier les limites, il les repousse. Au lieu de restaurer la confiance, il demande un chèque en blanc.
-Cette logique est particulièrement visible dans le domaine de l'exploration du réseau câblé. Le Tribunal administratif fédéral a constaté que le dispositif actuel soulève de sérieuses questions de compatibilité avec les droits fondamentaux. Nous parlons ici d'un instrument extrêmement intrusif, permettant la collecte et l'analyse de communications transfrontalières à grande échelle. Face à une telle décision, nous nous serions attendus à ce que le Conseil fédéral présente une solution permettant de garantir la conformité du dispositif avec les exigences de l'état de droit. Or, il choisit au contraire de reporter cette discussion à une troisième étape de révision. Cette approche est inacceptable. Lorsque des atteintes aussi importantes à la sphère privée sont en cause, la mise en conformité avec les droits fondamentaux ne peut pas être renvoyée à plus tard. Une révision qui ne traite pas cette question ne peut pas être recevable. Le Parlement ne devrait pas être appelé à étendre ou à consolider des compétences alors même que les bases juridiques actuelles sont contestées.
-Nous sommes également très préoccupés par l'extension des compétences du SRC dans le domaine de l'extrémisme violent. Personne ici ne conteste la nécessité de lutter contre ces violences. Cette révision étend toutefois l'accès à certaines des mesures les plus intrusives du renseignement, alors même que la notion d'extrémisme violent demeure insuffisamment définie.
-Et ce débat ne fait que commencer. Plusieurs projets sont déjà en discussion ou en préparation dans ce domaine. Ils prévoient de nouveaux instruments et de nouvelles possibilités d'intervention. Plus ces compétences s'étendent, plus il devient indispensable de disposer d'une définition claire, précise et prévisible dans la loi. Dans un État de droit, la population doit savoir quels comportements peuvent conduire à des mesures de surveillance. Plus l'atteinte aux libertés fondamentales est importante, plus l'exigence de précision doit être élevée. Cette exigence n'est aujourd'hui pas remplie.
-Nous sommes également préoccupés par les conséquences de cette évolution sur l'engagement politique. La démocratie suisse repose sur la liberté d'opinion, la liberté de réunion et la liberté d'association. Les citoyennes et citoyens doivent pouvoir s'engager dans des partis, des syndicats, des mouvements et des associations sans crainte d'être observés, catalogués ou analysés par les services de renseignement. Il est nécessaire de rappeler le scandale des fiches, une honte pour notre pays qui est encore vivement présente dans les esprits. Aujourd'hui, avec ce projet de modification de loi, nous réouvrons une logique dangereuse qui porte à elle seule le risque d'une surveillance qui nuit aux droits fondamentaux et à la confiance de la population envers l'État.
-Enfin, cette révision ouvre aussi la porte au profilage algorithmique sans répondre aux questions essentielles de transparence, de contrôle et de responsabilité inhérentes à ce domaine. Là encore, les compétences arrivent sans les garanties.
-Nous avons besoin d'un service de renseignement efficace, mais aussi d'un service de renseignement rigoureusement encadré, transparent et respectueux des libertés fondamentales. C'est précisément cet objectif que doit poursuivre la loi fédérale sur le renseignement. Or le projet qui nous est soumis aujourd'hui n'y répond pas.
-Pour ces raisons, je vous invite à refuser l'entrée en matière sur ce projet.
-J'enchaîne avec le renvoi en commission. En cas d'entrée en matière, nous demandons par cette proposition de renvoi que le Conseil fédéral revienne devant le Parlement avec une révision plus cohérente, plus complète et plus respectueuse des principes de l'état de droit. Notre proposition repose sur quatre exigences. Premièrement, la question de la surveillance des réseaux câblés doit être réglée avant toute extension des compétences du SRC. Aujourd'hui, nous nous trouvons dans une situation paradoxale. Le Tribunal administratif fédéral a mis en évidence de sérieux problèmes concernant la légalité du dispositif actuel. Pourtant, le Conseil fédéral nous explique que ces questions seront traitées ultérieurement dans une troisième étape de révision. Cette approche inverse l'ordre des priorités. Lorsque des atteintes potentiellement massives à la sphère privée sont en jeu, la conformité aux droits fondamentaux doit être établie avant toute extension des compétences du renseignement. Le Parlement ne devrait pas être invité à légiférer sur l'avenir de cet instrument, alors que la base juridique actuelle demeure contestée. Nous demandons donc que le Conseil fédéral présente une solution juridiquement solide dans la première étape de la révision. Notre deuxième demande concerne la protection de l'activité politique légitime. La Suisse dispose d'une longue tradition démocratique fondée sur l'engagement citoyen. Les partis politiques, les syndicats, les associations, les mouvements sociaux et les organisations de la société civile jouent un rôle essentiel dans notre système politique. Or plusieurs dispositions du projet suscitent des interrogations quant aux limites entre la prévention des menaces et l'observation d'activités politiques parfaitement légitimes. Même lorsque la surveillance n'est pas effectivement mise en oeuvre, l'incertitude sur son champ d'application produit un effet dissuasif. Nous estimons que la loi doit protéger explicitement l'activité politique légitime contre toute surveillance du SRC. Cette protection mérite d'être formulée de manière plus claire et plus contraignante qu'elle ne l'est aujourd'hui. Nous ne voulons pas d'un nouveau scandale des fiches. Troisièmement, le droit d'accès aux données doit être renforcé. Dans un Etat de droit, toute personne doit pouvoir savoir quelles données sont détenues à son sujet, sous réserve naturellement des exceptions strictement nécessaires à la protection d'intérêts prépondérants de sécurité. Le système proposé demeure extrêmement restrictif.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page Pierre-André</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le président (Page Pierre-André, président): Nous votons maintenant sur la proposition de renvoi de la minorité Chollet. 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addor Jean-Luc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J'aimerais d'abord déclarer un lien d'intérêt : je n'ai pas de frigo connecté. Je ne suis pas sûr d'être le seul dans cette situation.
-Je ne vais pas revenir sur toutes les minorités et toutes les questions qui ont été abordées, soit par le chef du département, soit par ma collègue rapporteuse de langue allemande. J'aimerais revenir sur cinq points particuliers. Le premier concerne principalement la minorité Molina, à l'article 5 alinéa 6. Il y a là une question de principe concernant le champ d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J'aimerais d'abord déclarer un lien d'intérêt : je n'ai pas de frigo connecté. Je ne suis pas sûr d'être le seul dans cette situation.
-Je ne vais pas revenir sur toutes les minorités et toutes les questions qui ont été abordées, soit par le chef du département, soit par ma collègue rapporteuse de langue allemande. J'aimerais revenir sur cinq points particuliers. Le premier concerne principalement la minorité Molina, à l'article 5 alinéa 6. Il y a là une question de principe concernant le champ d'activité du SRC et plus précisément ce qu'il faut bien appeler la police politique. L'activité du SRC doit rester une exception. C'est actuellement assez précisément défini, avec deux critères clairs, à savoir l'espionnage et l'extrémisme violent. Ce qui est proposé dans ce projet, c'est un texte qui est rédigé d'une manière quand même assez alambiquée, avec beaucoup de renvois qui, c'est le moins que l'on puisse dire, ne facilitent pas sa compréhension. On peut lire le message pour essayer de savoir de quoi l'on parle. Je rappelle que, dans le droit en vigueur, si on veut parler d'extrémisme, on parle d'"extrémisme violent". Dans le message, on nous parle d'"idéologie radicale d'extrême droite". On pourrait parler d'autre chose, mais si on prend ce terme que j'ai extrait du message, c'est une notion qui mérite d'être définie. On ne sait pas exactement qui pourrait faire l'objet de surveillance et s'il suffit d'avoir des opinions pour être surveillé, parce qu'actuellement, cela ne suffit pas, il faut que cela puisse déboucher sur de la violence. Il y a donc là une vraie question de principe. Toujours est-il que la commission, par 15 voix contre 9 et 1 abstention, vous propose de passer outre ces scrupules.
-Ensuite, pour illustrer l'approche qui a été celle de la commission par rapport aux conditions que nous voulons donner au travail du SRC, j'aimerais parler de l'article 14 alinéa 3, qui concerne la question de l'engagement d'appareils de localisation.
-La minorité Chollet veut empêcher le SRC d'utiliser ce genre d'appareil. Par 17 voix contre 8, la commission vous propose de ne pas déplumer notre service de renseignement.
-Je passe à une troisième problématique qui est un peu du même genre, à l'article 26 alinéa 1 lettre a : c'est la question de la surveillance de la correspondance par poste et par télécommunication. Là aussi, une minorité Chollet propose d'abroger cette disposition et de restreindre les moyens dont dispose notre service de renseignement. Par 17 voix contre 7 et 1 abstention, la commission vous propose de rejeter cette proposition.
-Le quatrième aspect dont je voulais parler est la question de l'autorisation de la prolongation d'une mesure de recherche à l'article 29b alinéa 2. Il y a là encore une minorité Chollet. Que se passe-t-il en cas de retard imprévisible dans la procédure d'autorisation ? Est-ce que toute une opération va tomber et être compromise, ou est-ce qu'on fait preuve d'un peu d'esprit pratique ? C'est l'avis de la commission qui, par 17 voix contre 6 et 2 abstentions, propose qu'en cas de retard imprévisible dans la procédure d'autorisation, et si la demande a été déposée à temps - il y a quand même des conditions - le SRC puisse continuer à mettre en oeuvre la mesure de recherche, mais évidemment seulement jusqu'à ce que la décision d'autorisation soit rendue et à la condition, en plus, que l'aval soit donné.
-La cinquième problématique sur laquelle je voulais revenir, au nom de la majorité de la commission, c'est la question de l'exploration du réseau câblé.
-On a là un moyen qui est indispensable à l'action du service, pour notre sécurité, et on a un tribunal, le Tribunal administratif fédéral, qui, je le rappelle, n'est pas la plus haute cour de ce pays, qui a rendu un arrêt dont on peut discuter et dont on verra ce qu'il faut en faire. Je rappelle quand même que, dans ce pays, c'est encore le Parlement qui fait les lois et pas les tribunaux, qui sont chargés de les appliquer.
-Concernant les autres minorités, je ne reviens pas sur ce qui a déjà été dit. La majorité de la commission vous propose de toutes les rejeter. Leur esprit, contrairement à l'approche de la commission, c'est en général d'essayer de déplumer le SRC de ses moyens, ou de lui compliquer le travail autant que possible, ou en tout cas de s'opposer à toute simplification de son travail. Ce n'est pas comme ça que la majorité de la commission conçoit le travail d'un service de renseignement. Voilà pourquoi, je le répète, nous vous proposons de rejeter toutes les propositions de minorité.
-Dernier point : je ne veux pas allonger le débat sur la proposition Tuena qui a été retirée, mais elle présente quand même un certain intérêt. Puisqu'elle a été retirée, on ne va pas en débattre, mais j'en dis juste ces quelques mots pour suggérer à la commission du Conseil des États de s'inspirer de cette démarche et de tirer les conséquences de ce qui s'est passé à Winterthour.
 </t>
   </si>
   <si>
@@ -690,19 +577,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">376556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es geht um die Schweizer Beteiligung an der KFOR respektive um die Verlängerung des Swisscoy-Einsatzes. 
-Ihre zuständige Kommission hat sich im April 2026 mit dem Einsatz von Militärangehörigen auf dem Balkan beschäftigt. Zum einen ging es um die Beteiligung der Schweiz an der KFOR, zum anderen um die Verlängerung des Swisscoy-Einsatzes für die Jahre 2027 bis 2029. 
-Der Bundesrat hat die Botschaft an seiner Sitzung im November 2025 verabschiedet. Der Einsatz der Schweizer Armee zur Unterstützung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es geht um die Schweizer Beteiligung an der KFOR respektive um die Verlängerung des Swisscoy-Einsatzes. 
-Ihre zuständige Kommission hat sich im April 2026 mit dem Einsatz von Militärangehörigen auf dem Balkan beschäftigt. Zum einen ging es um die Beteiligung der Schweiz an der KFOR, zum anderen um die Verlängerung des Swisscoy-Einsatzes für die Jahre 2027 bis 2029. 
-Der Bundesrat hat die Botschaft an seiner Sitzung im November 2025 verabschiedet. Der Einsatz der Schweizer Armee zur Unterstützung der multinationalen Nato-Truppe in Kosovo soll um drei Jahre bis Ende 2029 verlängert werden. Zudem möchte der Bundesrat die Befugnis erhalten, den maximalen Personalbestand während der Mandatsdauer bei Bedarf um bis zu 30 Angehörige der Armee (AdA) zu erhöhen. 
-Der Ständerat hat den Bundesbeschluss als Erstrat am 10. März dieses Jahres mit 37 zu 2 Stimmen bei 4 Enthaltungen angenommen. 
-Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
+    <t xml:space="preserve">376585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
+Der Schweizer Beitrag an die KFOR dient konkreten nationalen Sicherheitsinteress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
 Der Schweizer Beitrag an die KFOR dient konkreten nationalen Sicherheitsinteressen. Mit der Swisscoy leistet die Schweiz einen solidarischen Beitrag zur Sicherheit Europas. Viele an der KFOR beteiligte Staaten engagieren sich stark in der militärischen Unterstützung der Ukraine, was die Schweiz als neutraler Staat nicht tut. Wir profitieren aber von ihren Einsätzen. Die meisten Mitglieder der Kommission und auch der anwesende Korpskommandant Michaud haben betont, dass der Einsatz der Swisscoy unser wichtigster Beitrag zur militärischen Friedensförderung ist. Unser Beitrag zu dieser Mission ist bedeutsam, und der Mehrwert für die Schweizer Armee ist gross. Wir leisten damit einen wichtigen Partnerschaftsbeitrag und übernehmen in der internationalen Gemeinschaft Verantwortung. Die Interoperabilität der Armee als Ganzes wird gestärkt, weil diese Erfahrungen dank unseres Milizsystems in die Truppe einfliessen. 
 Es gab verschiedenste Anträge in der Kommission. Den Antrag des Bundesrates habe ich eben erwähnt: die Verlängerung der Schweizer Beteiligung an der KFOR bis Ende Dezember sowie die Erhöhung des Maximalbestands um 30 AdA. 
 Es gab den Antrag Riniker Nr. 1. Dieser forderte, dass der Bundesrat das Kontingent auf bis zu 85 AdA erhöhen kann. Die Begründung war, dass sich die Sicherheitslage in Europa verschärft hat. Es gibt zahlreiche Nationen, die sich zurückziehen und in der Ukraine aushelfen. Die Schweiz könnte nun in Kosovo in die Bresche springen und genau diese Lücken schliessen. 
@@ -720,6 +602,9 @@
     <t xml:space="preserve">Nantermod Philippe</t>
   </si>
   <si>
+    <t xml:space="preserve">VS</t>
+  </si>
+  <si>
     <t xml:space="preserve">La motion que nous traitons aujourd'hui trouve son origine dans l'échec de l'objet 22.071 concernant l'exécution des sanctions, qui a été rejeté lors du vote final du 14 juin 2024. Cet échec était largement accidentel, dirons-nous. Certains l'ont même qualifié en commission de "Betriebsunfall". En effet, plusieurs éléments du projet faisaient alors l'objet d'un large consensus. À la suite de ce vote, la Commission des affaires juridiques du Conseil national avait déposé l'initiative parlementair</t>
   </si>
   <si>
@@ -738,20 +623,39 @@
     <t xml:space="preserve">Dandrès Christian</t>
   </si>
   <si>
-    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui a été fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision de manière générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
-Je pense qu'on doit relever que si on doit analyser la question des coûts dans le domaine de l'exécution, il y a quand même une approche assez si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui a été fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision de manière générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
+    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui est fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
+Je pense qu'on doit relever que si on doit analyser la question des coûts dans le domaine de l'exécution, il y a quand même une approche assez singulièrement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma minorité n'est pas d'accord d'ouvrir cette énième révision de la partie générale du code pénal avec le cap qui est fixé dans cette motion. En effet, cette motion ne prévoit pas d'ouvrir une révision générale, elle fixe un cap. Ce cap est clair, il s'agit de "taper" dans les mesures thérapeutiques avec comme prisme la question des coûts.
 Je pense qu'on doit relever que si on doit analyser la question des coûts dans le domaine de l'exécution, il y a quand même une approche assez singulièrement paradoxale de la majorité qui refuse de revoir la question des peines de substitution. En effet, pour 200 francs d'amendes impayées, on va mettre des personnes en prison et cela va coûter 400 francs par jour de détention ; ce sont des milliers de personnes qui sont dans cette situation et des millions de francs qui sont investis. Par contre, on veut restreindre les mesures thérapeutiques qui sont, je le rappelle, ordonnées par des juges pour des personnes qui commettent des actes graves en lien direct avec la pathologie. Ce n'est vraiment pas sérieux comme approche.
 L'autre aspect, c'est que dans les débats au sein de la commission, les délégations des groupes libéral-radical et UDC ont cristallisé le débat sur la question des expulsions pénales des étrangers avec un parti pris très clair. La logique, c'est de dire, en résumé, pourquoi doit-on doit payer si une personne doit être expulsée ?
-Je pense très honnêtement que les enjeux qui sont liés à la sécurité et au droit pénal méritent un peu mieux, et j'aimerais y revenir brièvement. Tout d'abord, parce que le droit pénal, on doit le rappeler, a ses racines dans les Lumières, dans les révolutions bourgeoises des 18e et 19e siècles. On concrétise avec ces mesures une conception de l'État qui est fondée sur la défense des droits, des libertés fondamentales, l'habeas corpus. On sort de la logique de la loi du talion. On doit rappeler aussi que, en lien avec ces révolutions, il y a un caractère universel : ces principes ne s'arrêtent pas aux frontières nationales. La Suisse a aussi des engagements vis-à-vis de l'humanité, qui ne se limitent pas uniquement aux détentrices et détenteurs du passeport rouge à la croix blanche. Or, ce qui est admis depuis deux siècles, c'est que le crime n'est pas toujours et uniquement lié à des choix intentionnels, assumés et individuels. C'est pour cela qu'on a des mesures thérapeutiques dans le code pénal.
-Le crime peut être en lien avec de graves troubles mentaux du détenu, et c'est pour éviter le danger que la pathologie représente qu'il faut soigner la personne. Or, la question qui est posée - et que s'est aussi posée la commission - est de savoir qui doit assumer cette responsabilité. 
-Je pense, très honnêtement, qu'on doit avoir une approche assez pragmatique dans le domaine : ce sont les pays qui le peuvent et là où se trouve le délinquant malade. Et on ne peut pas se dédouaner, comme veulent le faire le PLR et l'UDC, de cette responsabilité avec des arguments de boutiquier qui consistent à dire qu'il ne faut pas gaspiller puisque la personne doit partir. Parce que cette logique a évidemment un corollaire, c'est que les délinquants, en quelque sorte, n'ont qu'à aller commettre des crimes graves ailleurs qu'en Suisse. Et cela ne va pas, évidemment. Parce que la sécurité, c'est aussi un élément commun qui dépasse les frontières et qui repose sur la responsabilité de tous les États de pouvoir assumer des personnes qui ont ces problèmes.
-Et j'aimerais quand même faire une petite incise. Si on doit répondre à cet argument de boutiquier, on peut aussi rappeler que les populations, les pays dont sont issues les personnes qui ont été stigmatisées dans le cadre des travaux de la commission, ces délinquants, ont en quelque sorte déjà payé le prix pour que la Suisse prenne part à leur sécurité en soignant la poignée de personnes qui font l'objet de mesures. Je crois qu'on doit rappeler ici, on l'a abordé dans le cadre de la restitution des mesures compensatoires, que les caisses de la Confédération ne détiennent pas moins d'un milliard de francs de créances compensatoires pour des actes de corruption qui ont été commis par des multinationales en Suisse et que cet argent pourrait aussi servir notamment à cela. Il n'y a pas si longtemps, on a eu une perquisition à l'encontre de Gunvor, laquelle montre que c'est vraiment une question d'une grande actualité.
-J'aimerais conclure en relevant que les mesures thérapeutiques doivent évidemment être maintenues dans leur principe, parce que c'est absolument odieux que des personnes psychiquement et gravement atteintes croupissent sans soins dans des prisons. Mais, aujourd'hui, le système ne fonctionne pas bien - M. Nantermod l'a dit - faute de places adaptées pour accueillir des malades, d'une part, et en raison de difficultés en termes de ressources, d'autre part. Cela a pour effet que des personnes peuvent rester dans des mesures thérapeutiques parfois bien au-delà des peines plafond prévues dans le code pénal, ce qui n'est évidemment pas acceptable. Il faut donc améliorer ces mesures, c'est une question de dignité. Et c'est aussi une question de sécurité. 
+Je pense très honnêtement que les enjeux qui sont liés à la sécurité et au droit pénal méritent un peu mieux, et j'aimerais y revenir brièvement. Tout d'abord, parce que le droit pénal, on doit le rappeler, a ses racines dans les Lumières, dans les révolutions bourgeoises des 18e et 19e siècles. On concrétise avec ces mesures une conception de l'État qui est fondée sur la défense des droits, des libertés fondamentales, l'habeas corpus. On sort de la logique de la loi du talion. On doit rappeler aussi que, en lien avec ces évolutions, il y a un caractère universel : ces principes ne s'arrêtent pas aux frontières nationales. La Suisse a aussi des engagements vis-à-vis de l'humanité, qui ne se limitent pas uniquement aux détentrices et détenteurs du passeport rouge à la croix blanche. Or, ce qui est admis depuis deux siècles, c'est que le crime n'est pas toujours et uniquement lié à des choix intentionnels, assumés et individuels. C'est pour cela qu'on a des mesures thérapeutiques dans le code pénal.
+Le crime peut être en lien avec de graves troubles mentaux du détenu, et c'est pour éviter le danger que la pathologie représente qu'il faut soigner la personne. Or, la question qui est posée - et que s'est aussi posée la commission - est de savoir qui doit assumer cette responsabilité. Je pense, très honnêtement, qu'on doit avoir une approche assez pragmatique dans le domaine : ce sont les pays qui le peuvent et là où se trouve le délinquant malade. Et on ne peut pas se dédouaner, comme veulent le faire les groupes libéral-radical et l'UDC, de cette responsabilité avec des arguments de boutiquier qui consistent à dire qu'il ne faut pas gaspiller puisque la personne doit partir. Parce que cette logique a évidemment un corollaire, c'est que les délinquants, en quelque sorte, n'ont qu'à aller commettre des crimes graves ailleurs qu'en Suisse. Et cela ne va pas, évidemment, parce que la sécurité, c'est aussi un élément commun qui dépasse les frontières et qui repose sur la responsabilité de tous les États de pouvoir assumer des personnes qui ont ces problèmes.
+Et j'aimerais quand même faire une petite incise. Si on doit répondre à cet argument de boutiquier, on peut aussi rappeler que les populations, les pays dont sont issues les personnes qui ont été stigmatisées dans le cadre des travaux de la commission, ces délinquants ont en quelque sorte déjà payé le prix pour que la Suisse prenne part à leur sécurité en soignant la poignée de personnes qui font l'objet de mesures. Je crois qu'on doit rappeler ici, on l'a abordé dans le cadre de la restitution des mesures compensatoires, que les caisses de la Confédération ne détiennent pas moins d'un milliard de francs de créances compensatoires pour des actes de corruption qui ont été commis par des multinationales en Suisse et que cet argent pourrait aussi servir notamment à cela. Il n'y a pas si longtemps, on a eu une perquisition à l'encontre de Gunvor, laquelle montre que c'est vraiment une question d'une grande actualité.
+J'aimerais conclure en relevant que les mesures thérapeutiques doivent évidemment être maintenues dans leur principe, parce que c'est absolument odieux que des personnes psychiquement et gravement atteintes croupissent sans soins dans des prisons. Mais, aujourd'hui, le système ne fonctionne pas bien - M. Nantermod l'a dit - faute de places adaptées pour accueillir des malades, d'une part, et en raison de difficultés au niveau des ressources, d'autre part. Cela a pour effet que des personnes peuvent rester dans des mesures thérapeutiques parfois bien au-delà des peines plafond prévues dans le code pénal, ce qui n'est évidemment pas acceptable. Il faut donc améliorer ces mesures, c'est une question de dignité. Et c'est aussi une question de sécurité.
 Évidemment, on ne va pas améliorer les mesures avec le rationnement des soins visé par cette motion que le Conseil des États a adoptée. Au contraire, cela risque de transformer peu à peu le régime des mesures thérapeutiques non plus en petit internement, mais en un internement de fait, ce qu'on ne peut évidemment pas accepter.
-C'est la raison pour laquelle la minorité vous demande de rejeter cette motion parce qu'elle franchit ce cap profondément inacceptable.
+C'est la raison pour laquelle ma minorité vous demande de rejeter cette motion, parce qu'elle franchit ce cap profondément inacceptable.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barandun Nicole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der KFOR, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
+Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der KFOR, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
+Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweimal zur Verstärkung der KFOR zwangen. Solange die Beziehungen zwischen Kosovo und Serbien nicht nachhaltig normalisiert sind, halten die Nato und die beteiligten Staaten die KFOR für notwendig, als militärische Garantin eines sicheren Umfelds, die Entwicklung und Stabilität im Kosovo und auf dem gesamten Westbalkan gewährleistet.
+Die Schweiz leistet mit Swisscoy seit 25 Jahren einen verlässlichen Beitrag zu dieser Stabilität, und sie leistet diesen Beitrag auch mit ganz konkreten Handlungen. Ich spreche zum Beispiel die Liaison and Monitoring Teams an, die im direkten Austausch mit der Bevölkerung Spannungen früh erkennen und versuchen, diese zu entschärfen, aber auch unsere Genietruppen, die vor Ort wichtige Dienste leisten u. a. in der Logistik. Darüber hinaus kann die Schweizer Armee mit dem Einsatz wichtige Erfahrungen in einer internationalen Operation sammeln, die auch für unsere Verteidigungsfähigkeit hier Zuhause relevant sind. 
+Die Schweiz hat ein direktes Interesse am Frieden, an der Stabilität und an der wirtschaftlichen Entwicklung des Kosovos und der ganzen Region. Der Westbalkan ist für uns sicherheits-, migrations- und wirtschaftspolitisch relevant. Wir haben aufgrund der engen menschlichen und wirtschaftlichen Beziehungen auch Verpflichtungen gegenüber dieser Region. Mit der Verlängerung unseres Engagements übernehmen wir Verantwortung. Diese Verantwortung tragen wir, weil wir eine enge Beziehung zu dieser Region pflegen. 
+Ich möchte noch ein Wort zur kosovarischen Diaspora in der Schweiz verlieren. Infolge des Kosovokriegs fanden Ende der Neunzigerjahre rund 60 000 Menschen aus dem Kosovo vorübergehend Schutz in der Schweiz. Viele von ihnen sind später zurückgekehrt, aber ein Teil von ihnen hat hier dauerhaft Fuss gefasst. Ihre Kinder und Enkelkinder sind heute ein selbstverständlicher Teil unserer Gesellschaft. Insgesamt leben in der Schweiz deutlich über 100 000 Menschen mit Wurzeln im Kosovo; Schätzungen sprechen von rund 170 000 Kosovo-Albanerinnen und -Albanern. Aus migrationspolitischer Sicht wissen wir, wenn es wieder zu einer schweren Eskalation käme, würden sich die neuen Fluchtbewegungen dorthin richten, wo bereits Familien und etablierte Netzwerke bestehen. Für die Schweiz mit ihrer grossen kosovarischen Community sind Prävention und Stabilität im Kosovo daher auch migrationspolitisch sinnvoll. Das Risiko eines erneuten unkontrollierten Fluchtstroms wird dadurch reduziert anstatt erhöht. 
+Ich sage noch ein Wort zur Neutralität. Sie schwebt immer ein bisschen mit im Raum. Das Mandat der KFOR basiert auf einem klaren Mandat des UNO-Sicherheitsrates. Es handelt sich um eine klassische friedensfördernde Operation. Die Neutralität steht solchen, von der UNO mandatierten Friedensoperationen gerade nicht entgegen. Die Schweizer Beteiligung entspricht einer seit Jahren gefestigten Praxis der schweizerischen Aussen- und Sicherheitspolitik. 
+Ich empfehle Ihnen im Namen der Mitte-Fraktion. Die Mitte. EVP, dieser Vorlage zuzustimmen, das heisst, einzutreten und der Mehrheit zu folgen. Bei der Erhöhung des Kontingents geht es um einen Maximalrahmen, nicht um einen Automatismus. Der Bundesrat bleibt dem Parlament gegenüber verantwortlich. Verteidigungsfähigkeit entsteht nicht in einem Vakuum. Wer eine glaubwürdige Landesverteidigung will, braucht gut ausgebildete Kader mit realer Einsatzerfahrung. Die KFOR bleibt vor dem Hintergrund einer nach wie vor volatilen Lage im Kosovo und einer ungelösten Beziehung zu Serbien deshalb auch aus Sicht der Schweiz notwendig. 
 </t>
   </si>
 </sst>
@@ -800,8 +704,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I30" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I26" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I26"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1303,109 +1207,109 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
         <v>50</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>51</v>
-      </c>
-      <c r="I8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>54</v>
       </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>66</v>
@@ -1419,94 +1323,90 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
         <v>69</v>
       </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="I12" t="s">
         <v>70</v>
-      </c>
-      <c r="G12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>74</v>
       </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
         <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" t="s">
-        <v>38</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E14"/>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -1535,22 +1435,22 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
         <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
         <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H16" t="s">
         <v>89</v>
@@ -1564,397 +1464,285 @@
         <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17"/>
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" t="s">
-        <v>96</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E18"/>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" t="s">
         <v>98</v>
-      </c>
-      <c r="I18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
         <v>100</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
         <v>101</v>
       </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19"/>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" t="s">
         <v>103</v>
-      </c>
-      <c r="I19" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="B20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
         <v>106</v>
       </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>107</v>
-      </c>
-      <c r="I20" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
         <v>109</v>
       </c>
-      <c r="B21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
         <v>110</v>
       </c>
-      <c r="E21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="I21" t="s">
         <v>111</v>
-      </c>
-      <c r="G21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22"/>
+      <c r="F22" t="s">
         <v>114</v>
-      </c>
-      <c r="B22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
-      </c>
-      <c r="E22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
         <v>24</v>
       </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23"/>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
         <v>122</v>
       </c>
-      <c r="B24" t="s">
+      <c r="G24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" t="s">
         <v>123</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="I24" t="s">
         <v>124</v>
-      </c>
-      <c r="E24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" t="s">
         <v>127</v>
       </c>
-      <c r="B25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
         <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>129</v>
-      </c>
-      <c r="I25" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" t="s">
         <v>131</v>
       </c>
-      <c r="B26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="I26" t="s">
         <v>132</v>
-      </c>
-      <c r="E26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>133</v>
-      </c>
-      <c r="I26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>141</v>
-      </c>
-      <c r="I28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" t="s">
-        <v>145</v>
-      </c>
-      <c r="I29" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" t="s">
-        <v>149</v>
-      </c>
-      <c r="I30" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -120,7 +120,8 @@
 J'aimerais mentionner encore deux rapports de la Commission nationale de prévention de la torture et un avis juridique du Centre suisse de compétence pour les droits humains, qui ont confirmé ce problème. C'est pourquoi il est nécessaire d'adapter la loi.
 Le projet prévoit deux changements principaux[NB]: premièrement, toutes les personnes détenues doivent être assurées, et, deuxièmement, les cantons peuvent limiter le choix de l'assureur et des prestataires de services. Ainsi, avec ce projet, toutes les personnes détenues dans notre pays devront avoir une assurance-maladie. Cela garantit quels traitements doivent être dispensés et avec quelle qualité, assure une égalité de traitement, et, surtout, les coûts deviennent plus prévisibles pour les cantons[NB]; d'importantes fluctuations d'une année à l'autre peuvent ainsi être évitées. Cela protège également la santé publique, notamment celle du personnel de prison.
 Conformément à la jurisprudence du Tribunal fédéral, les personnes détenues n'ont en principe pas droit au libre choix du médecin. Avec ce projet, les cantons pourront donc limiter le choix de l'assureur, mais aussi celui des prestataires ou encore la forme d'assurance. Aujourd'hui, les cantons n'ont pas ces possibilités pour garantir des soins de santé dans ce domaine de la manière la plus efficace et la plus économique possible. À cette fin, les cantons peuvent assurer les détenus auprès d'un assureur au moyen d'un contrat-cadre spécial. Cette réglementation s'inspire dans son principe de celle qui s'applique déjà aujourd'hui aux demandeurs d'asile. Concrètement, environ 2300 personnes supplémentaires, qui aujourd'hui ne disposent pas d'une assurance-maladie suisse ou européenne, seront assurées, ce qui reste toutefois très faible eu égard au nombre global d'assurés.
-En conclusion, le projet que vous soumet le Conseil fédéral est équilibré et proportionné. Il a été travaillé en concertation avec les cantons et respecte le système actuel, tout en l'améliorant. Il corrige un problème[NB]; la réforme qui vous est proposée apporte plus d'égalité et de stabilité. Dès lors, je vous invite à entrer en matière et à adopter le projet.
+En conclusion, le projet que vous soumet le Conseil fédéral est équilibré et proportionné. Il a été travaillé en concertation avec les cantons et respecte le système actuel, tout en l'améliorant. Il corrige un problème[NB]; la réforme qui vous est proposée apporte plus d'égalité et de stabilité. 
+Dès lors, je vous invite à entrer en matière et à adopter le projet.
 </t>
   </si>
   <si>
@@ -581,18 +582,38 @@
   </si>
   <si>
     <t xml:space="preserve">Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
-Der Schweizer Beitrag an die KFOR dient konkreten nationalen Sicherheitsinteress</t>
+Der Schweizer Beitrag an die Kfor dient konkreten nationalen Sicherheitsinteress</t>
   </si>
   <si>
     <t xml:space="preserve">Bundesrat Pfister führte aus, dass das Ausbrechen eines bewaffneten Konflikts im Westbalkan direkte Auswirkungen auf die Sicherheit Europas und somit auch auf die Schweiz haben könnte. In der Schweiz lebt eine grosse Diaspora aus dem Westbalkan. Zwischen den Bevölkerungsgruppen der Diaspora wären Spannungen vorprogrammiert. Eine Eskalation in der Region würde zudem den Migrationsdruck auf die Schweiz stark erhöhen. 
-Der Schweizer Beitrag an die KFOR dient konkreten nationalen Sicherheitsinteressen. Mit der Swisscoy leistet die Schweiz einen solidarischen Beitrag zur Sicherheit Europas. Viele an der KFOR beteiligte Staaten engagieren sich stark in der militärischen Unterstützung der Ukraine, was die Schweiz als neutraler Staat nicht tut. Wir profitieren aber von ihren Einsätzen. Die meisten Mitglieder der Kommission und auch der anwesende Korpskommandant Michaud haben betont, dass der Einsatz der Swisscoy unser wichtigster Beitrag zur militärischen Friedensförderung ist. Unser Beitrag zu dieser Mission ist bedeutsam, und der Mehrwert für die Schweizer Armee ist gross. Wir leisten damit einen wichtigen Partnerschaftsbeitrag und übernehmen in der internationalen Gemeinschaft Verantwortung. Die Interoperabilität der Armee als Ganzes wird gestärkt, weil diese Erfahrungen dank unseres Milizsystems in die Truppe einfliessen. 
-Es gab verschiedenste Anträge in der Kommission. Den Antrag des Bundesrates habe ich eben erwähnt: die Verlängerung der Schweizer Beteiligung an der KFOR bis Ende Dezember sowie die Erhöhung des Maximalbestands um 30 AdA. 
-Es gab den Antrag Riniker Nr. 1. Dieser forderte, dass der Bundesrat das Kontingent auf bis zu 85 AdA erhöhen kann. Die Begründung war, dass sich die Sicherheitslage in Europa verschärft hat. Es gibt zahlreiche Nationen, die sich zurückziehen und in der Ukraine aushelfen. Die Schweiz könnte nun in Kosovo in die Bresche springen und genau diese Lücken schliessen. 
-Kollege Tuena stellte mehrere Anträge: den Antrag Tuena Nr. 5 auf Nichteintreten auf das Geschäft und unter anderem den Antrag Tuena Nr. 2, einen Konzeptantrag. Darin wird zu Artikel 1 gefordert, den Einsatz der Schweizer Armee zur Unterstützung der KFOR für eine letzte Zeitspanne, die spätestens am 31. Dezember 2029 enden soll, zu genehmigen. Gestrichen werden soll der Maximalbestand von 215 AdA. Der Antrag fordert zudem die Streichung von Artikel 2 respektive soll der Bundesrat ab 1. Januar 2027 einen gestaffelten Rückzug anordnen. 
+Der Schweizer Beitrag an die Kfor dient konkreten nationalen Sicherheitsinteressen. Mit der Swisscoy leistet die Schweiz einen solidarischen Beitrag zur Sicherheit Europas. Viele an der Kfor beteiligte Staaten engagieren sich stark in der militärischen Unterstützung der Ukraine, was die Schweiz als neutraler Staat nicht tut. Wir profitieren aber von ihren Einsätzen. Die meisten Mitglieder der Kommission und auch der anwesende Korpskommandant Michaud haben betont, dass der Einsatz der Swisscoy unser wichtigster Beitrag zur militärischen Friedensförderung ist. Unser Beitrag zu dieser Mission ist bedeutsam, und der Mehrwert für die Schweizer Armee ist gross. Wir leisten damit einen wichtigen Partnerschaftsbeitrag und übernehmen in der internationalen Gemeinschaft Verantwortung. Die Interoperabilität der Armee als Ganzes wird gestärkt, weil diese Erfahrungen dank unseres Milizsystems in die Truppe einfliessen. 
+Es gab verschiedenste Anträge in der Kommission. Den Antrag des Bundesrates habe ich eben erwähnt: die Verlängerung der Schweizer Beteiligung an der Kfor bis Ende Dezember sowie die Erhöhung des Maximalbestands um 30 AdA. 
+Es gab den Antrag Riniker Nr. 1. Dieser forderte, dass der Bundesrat das Kontingent auf bis zu 85 AdA erhöhen kann. Die Begründung war, dass sich die Sicherheitslage in Europa verschärft hat. Es gibt zahlreiche Nationen, die sich zurückziehen und in der Ukraine aushelfen. Die Schweiz könnte nun im Kosovo in die Bresche springen und genau diese Lücken schliessen. 
+Kollege Tuena stellte mehrere Anträge: den Antrag Tuena Nr. 5 auf Nichteintreten auf das Geschäft und unter anderem den Antrag Tuena Nr. 2, einen Konzeptantrag. Darin wird zu Artikel 1 gefordert, den Einsatz der Schweizer Armee zur Unterstützung der Kfor für eine letzte Zeitspanne, die spätestens am 31. Dezember 2029 enden soll, zu genehmigen. Gestrichen werden soll der Maximalbestand von 215 AdA. Der Antrag fordert zudem die Streichung von Artikel 2, respektive der Bundesrat soll ab 1. Januar 2027 einen gestaffelten Rückzug anordnen. 
 Weiter gab es einen Eventualantrag Tuena Nr. 3. Der Antrag Tuena Nr. 4 forderte in Artikel 5, dass der Bundesbeschluss dem fakultativen Referendum unterstellt werden soll. 
-Die Begründungen bezogen sich meist auf die hohen Kosten und darauf, dass sich auch andere Nationen aus Kosovo zurückziehen. 
+Die Begründungen bezogen sich meist auf die hohen Kosten und darauf, dass sich auch andere Nationen aus dem Kosovo zurückziehen. 
 Die Abstimmungen waren folgendermassen: Wir traten mit 17 zu 5 Stimmen bei 1 Enthaltung auf die Vorlage ein. Der Antrag Riniker Nr. 1 obsiegte mit 12 zu 8 Stimmen bei 3 Enthaltungen gegenüber dem Entwurf des Bundesrates. Die beiden Konzeptanträge Tuena Nr. 2 respektive Nr. 3 unterlagen jeweils dem Antrag Riniker Nr. 1 mit 12 zu 7 Stimmen bei 4 Enthaltungen. Der Antrag Tuena Nr. 4 zu Artikel 5 wurde mit 15 zu 8 Stimmen bei 0 Stimmen verworfen. 
 Die Gesamtabstimmung fiel mit 16 zu 7 Stimmen bei 0 Enthaltungen für die Annahme des Entwurfes aus. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candinas Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Zivilschutz steht seit Jahren vor einem erheblichen Alimentierungsproblem. Zahlreiche Organisationen haben Mühe, ihre Bestände aufrechtzuerhalten und ihre Aufgaben langfristig zu erfüllen. Mit meiner Motion unterbreite ich Ihnen einen pragmatischen und umsetzbaren Vorschlag, um diesem Problem entgegenzuwirken. Konkret geht es um Männer ohne Schweizer Bürgerrecht mit einer Niederlassungsbewilligung, also um Personen, die dauerhaft in unserem Land leben, hier arbeiten und ihren Lebensmittelpun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Zivilschutz steht seit Jahren vor einem erheblichen Alimentierungsproblem. Zahlreiche Organisationen haben Mühe, ihre Bestände aufrechtzuerhalten und ihre Aufgaben langfristig zu erfüllen. Mit meiner Motion unterbreite ich Ihnen einen pragmatischen und umsetzbaren Vorschlag, um diesem Problem entgegenzuwirken. Konkret geht es um Männer ohne Schweizer Bürgerrecht mit einer Niederlassungsbewilligung, also um Personen, die dauerhaft in unserem Land leben, hier arbeiten und ihren Lebensmittelpunkt in der Schweiz haben. Diese sollen künftig analog zu Schweizer Männern schutzdienstpflichtig werden. Leisten Sie den Dienst nicht, sollen Sie analog zu den Schweizer Männern eine Abgabe schulden. Die Ausweitung der Schutzdienstpflicht hat das Potenzial, das Alimentierungsproblem im Zivilschutz zu entschärfen. Zudem könnte sie einen Beitrag zu einer noch besseren Integration leisten. Auch würden Männer ohne Schweizer Bürgerrecht mit einer Niederlassungsbewilligung analog zu den Schweizern einen Beitrag für die Sicherheit und die Gesellschaft leisten. In verschiedenen Gemeinden der Schweiz sind diese beispielsweise auch der Feuerwehrpflicht unterstellt. Die Auswirkungen auf die Alimentierung der Zivilschutzorganisationen sind vielversprechend. So leben heute rund 78 000 Ausländer mit einer Niederlassungsbewilligung im dienstpflichtigen Alter in der Schweiz, rund 6000 pro Jahrgang. Das heisst, es könnte mit jährlich rund 6000 zusätzlichen Rekrutierungspflichtigen gerechnet werden. Wenn die gleichen Bedingungen bezüglich Tauglichkeit angewendet werden wie bei den Schweizer Männern, könnten theoretisch rund 4800 zusätzliche Schutzdienstpflichtige gewonnen werden. Mit dieser Gesetzesanpassung würden nicht nur zusätzliche Angehörige des Zivilschutzes gewonnen. Die Massnahme hätte auch eine integrative Wirkung. Wer dauerhaft in unserem Land lebt, profitiert von dessen Sicherheit und Stabilität. Darum ist es auch legitim, dass diese Menschen einen Beitrag zu deren Erhaltung leisten. 
+Der Bundesrat lehnt die Motion mit dem Hinweis ab, die Dienstpflicht sei eine Bürgerpflicht. Ausländerinnen und Ausländer sind in der Schweiz auf Bundesebene von den politischen Mitbestimmungsrechten ausgeschlossen. Entsprechend sei eine Dienstpflicht eine Ungleichbehandlung. Weiter schreibt er auch, dass volljährige in der Schweiz niedergelassene Ausländerinnen und Ausländer bereits heute gemäss geltendem Gesetz freiwillig Zivilschutz leisten können.
+Er übersieht aber, dass keine Ausländerin und kein Ausländer verpflichtet ist, hier eine Niederlassungsbewilligung zu beantragen. Diesen bescheidenen Dienst an die Sicherheit unseres Landes darf von allen erwartet werden. Es scheint, als sei der Bundesrat von seiner Begründung aber auch nicht vollends überzeugt. Er anerkennt in der Antwort nämlich selbst - das sieht man, wenn man die Antwort bis zum Schluss liest -, dass eine stärkere Beteiligung der ausländischen Wohnbevölkerung an der Gewährleistung der Sicherheit der Schweiz im Zusammenhang mit der Weiterentwicklung des Dienstpflichtsystems geprüft werden soll. Genau darum geht es bei meiner Motion.
+Ich bin überzeugt, dass wir die Diskussion nicht auf die lange Bank schieben sollten. Die Herausforderungen im Zivilschutz bestehen bereits heute. Es ist völlig gerechtfertigt, dass auch in der Schweiz niedergelassene Ausländerinnen und Ausländer einen ebenbürtigen Dienst für die Sicherheit der Schweiz im Bereich des Bevölkerungsschutzes leisten. Mit dieser Motion erhalten wir die Möglichkeit, einen konkreten Beitrag zur Stärkung des Bevölkerungsschutzes zu leisten.
+Entsprechend bitte ich Sie, dieser Motion zuzustimmen.
 </t>
   </si>
   <si>
@@ -651,11 +672,35 @@
   <si>
     <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der KFOR, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
 Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweimal zur Verstärkung der KFOR zwangen. Solange die Beziehungen zwischen Kosovo und Serbien nicht nachhaltig normalisiert sind, halten die Nato und die beteiligten Staaten die KFOR für notwendig, als militärische Garantin eines sicheren Umfelds, die Entwicklung und Stabilität im Kosovo und auf dem gesamten Westbalkan gewährleistet.
-Die Schweiz leistet mit Swisscoy seit 25 Jahren einen verlässlichen Beitrag zu dieser Stabilität, und sie leistet diesen Beitrag auch mit ganz konkreten Handlungen. Ich spreche zum Beispiel die Liaison and Monitoring Teams an, die im direkten Austausch mit der Bevölkerung Spannungen früh erkennen und versuchen, diese zu entschärfen, aber auch unsere Genietruppen, die vor Ort wichtige Dienste leisten u. a. in der Logistik. Darüber hinaus kann die Schweizer Armee mit dem Einsatz wichtige Erfahrungen in einer internationalen Operation sammeln, die auch für unsere Verteidigungsfähigkeit hier Zuhause relevant sind. 
+Die Schweiz leistet mit Swisscoy seit 25 Jahren einen verlässlichen Beitrag zu dieser Stabilität, und sie leistet diesen Beitrag auch mit ganz konkreten Handlungen. Ich spreche zum Beispiel die Liaison and Monitoring Teams an, die im direkten Austausch mit der Bevölkerung Spannungen früh erkennen und versuchen, diese zu entschärfen, aber auch unsere Genietruppen, die vor Ort wichtige Dienste leisten u. a. in der Logistik. Darüber hinaus kann die Schweizer Armee mit dem Einsatz wichtige Erfahrungen in einer internationalen Operation sammeln, die auch für unsere Verteidigungsfähigkeit hier zuhause relevant sind. 
 Die Schweiz hat ein direktes Interesse am Frieden, an der Stabilität und an der wirtschaftlichen Entwicklung des Kosovos und der ganzen Region. Der Westbalkan ist für uns sicherheits-, migrations- und wirtschaftspolitisch relevant. Wir haben aufgrund der engen menschlichen und wirtschaftlichen Beziehungen auch Verpflichtungen gegenüber dieser Region. Mit der Verlängerung unseres Engagements übernehmen wir Verantwortung. Diese Verantwortung tragen wir, weil wir eine enge Beziehung zu dieser Region pflegen. 
-Ich möchte noch ein Wort zur kosovarischen Diaspora in der Schweiz verlieren. Infolge des Kosovokriegs fanden Ende der Neunzigerjahre rund 60 000 Menschen aus dem Kosovo vorübergehend Schutz in der Schweiz. Viele von ihnen sind später zurückgekehrt, aber ein Teil von ihnen hat hier dauerhaft Fuss gefasst. Ihre Kinder und Enkelkinder sind heute ein selbstverständlicher Teil unserer Gesellschaft. Insgesamt leben in der Schweiz deutlich über 100 000 Menschen mit Wurzeln im Kosovo; Schätzungen sprechen von rund 170 000 Kosovo-Albanerinnen und -Albanern. Aus migrationspolitischer Sicht wissen wir, wenn es wieder zu einer schweren Eskalation käme, würden sich die neuen Fluchtbewegungen dorthin richten, wo bereits Familien und etablierte Netzwerke bestehen. Für die Schweiz mit ihrer grossen kosovarischen Community sind Prävention und Stabilität im Kosovo daher auch migrationspolitisch sinnvoll. Das Risiko eines erneuten unkontrollierten Fluchtstroms wird dadurch reduziert anstatt erhöht. 
-Ich sage noch ein Wort zur Neutralität. Sie schwebt immer ein bisschen mit im Raum. Das Mandat der KFOR basiert auf einem klaren Mandat des UNO-Sicherheitsrates. Es handelt sich um eine klassische friedensfördernde Operation. Die Neutralität steht solchen, von der UNO mandatierten Friedensoperationen gerade nicht entgegen. Die Schweizer Beteiligung entspricht einer seit Jahren gefestigten Praxis der schweizerischen Aussen- und Sicherheitspolitik. 
+Ich möchte noch ein Wort zur kosovarischen Diaspora in der Schweiz verlieren. Infolge des Kosovokriegs fanden Ende der Neunzigerjahre rund 60 000 Menschen aus dem Kosovo vorübergehend Schutz in der Schweiz. Viele von ihnen sind später zurückgekehrt, aber ein Teil von ihnen hat hier dauerhaft Fuss gefasst. Ihre Kinder und Enkelkinder sind heute ein selbstverständlicher Teil unserer Gesellschaft. Insgesamt leben in der Schweiz deutlich über 100 000 Menschen mit Wurzeln im Kosovo; Schätzungen sprechen von rund 170 000 Kosovo-Albanerinnen und -Albanern. Aus migrationspolitischer Sicht wissen wir, wenn es wieder zu einer schweren Eskalation käme, würden sich die neuen Fluchtbewegungen dorthin richten, wo bereits Familien und etablierte Netzwerke bestehen. Für die Schweiz mit ihrer grossen kosovarischen Community sind Prävention und Stabilität im Kosovo daher auch migrationspolitisch sinnvoll. Das Risiko eines erneuten unkontrollierten Flüchtlingsstroms wird dadurch reduziert anstatt erhöht. 
+Ich sage noch ein Wort zur Neutralität. Sie schwebt immer ein bisschen mit im Raum. Das Mandat der KFOR basiert auf einem klaren Mandat des UNO-Sicherheitsrates. Es handelt sich um eine klassische friedensfördernde Operation. Die Neutralität steht solchen von der UNO mandatierten Friedensoperationen gerade nicht entgegen. Die Schweizer Beteiligung entspricht einer seit Jahren gefestigten Praxis der schweizerischen Aussen- und Sicherheitspolitik. 
 Ich empfehle Ihnen im Namen der Mitte-Fraktion. Die Mitte. EVP, dieser Vorlage zuzustimmen, das heisst, einzutreten und der Mehrheit zu folgen. Bei der Erhöhung des Kontingents geht es um einen Maximalrahmen, nicht um einen Automatismus. Der Bundesrat bleibt dem Parlament gegenüber verantwortlich. Verteidigungsfähigkeit entsteht nicht in einem Vakuum. Wer eine glaubwürdige Landesverteidigung will, braucht gut ausgebildete Kader mit realer Einsatzerfahrung. Die KFOR bleibt vor dem Hintergrund einer nach wie vor volatilen Lage im Kosovo und einer ungelösten Beziehung zu Serbien deshalb auch aus Sicht der Schweiz notwendig. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caroni Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.
+Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.
+Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schubert-Praxis. Das sind inhaltliche Elemente, mit denen sie begründet, dass sie sich zumindest als gleich oder gar stärker zuständig sieht.
+Ich widerspreche auch der Auffassung, die SPK-S habe einen Fehler gemacht; einen solchen Vorwurf hat im Übrigen sonst niemand erhoben. Weder die APK-S noch das Büro des Ständerates haben je festgehalten, wir hätten einen Fehler gemacht. Zudem haben wir die parlamentarische Initiative der Schwesterkommission inzwischen erhalten, und niemand hat infrage gestellt, dass wir darüber abstimmen dürfen. Es scheint mir daher einhellig, dass die SPK-S zuständig ist, auch im Hinblick auf die Migrations- und Referendumsfragen. Zwar bestehen Berührungs- bzw. Überschneidungspunkte, doch den Vorwurf eines Fehlers weise ich zurück.
+Frau Wasserfallen hat von einem möglichen groben Foul gesprochen. Am Tag der WM-Eröffnung würde ich den Ball eher flach halten, zumal es sich hier um Zustimmungsentscheide dazu handelt, ob ein Vorstoss ausgearbeitet werden darf. Am Ende gelangen die Geschäfte ohnehin in die Räte, und jeder Rat kann ein Geschäft ablehnen; entscheidend ist lediglich, wer die Ausarbeitung vornimmt.
+Mit Kollege Sommaruga sehe ich im Übrigen keine Differenz. Sie haben zwar gesagt, wir hätten die APK-S kritisiert, doch das war keineswegs beabsichtigt. Ich habe den Mitbericht der APK-S ausführlich gewürdigt, und selbstverständlich stand er Ihnen zur Verfügung. Er war rein inhaltlicher Natur und hat nie bestritten, dass die SPK-S handeln darf; die APK-S hat schlicht mit 8 zu 5 Stimmen eine andere Meinung vertreten, was ihr gutes Recht ist. Ebenso wenig haben wir die APK-S umgangen: Wir haben am 5. Mai unseren Entscheid getroffen, und am 22. Mai folgte der Mitbericht der APK-S. Somit hat niemand jemanden umgangen; wir haben eine parlamentarische Initiative lanciert, und die APK-S hat dazu einen Mitbericht verfasst. Das ist im Grunde Courant normal.
+Herr Würth hat Martin Graf erwähnt, den ich sehr schätze, was sich schon daran zeigt, dass ich dieses rote Buch hier in der Hand halte. In diesem Fall habe ich mich jedoch nicht nur auf Martin Graf gestützt, sondern auch die Parlamentsdienste konsultiert. Diese vertreten eine andere, konsolidierte Auffassung, was den Spruch "zwei Juristen, drei Meinungen" bestätigt, auch wenn Martin Graf Historiker ist. Klar zurückweisen muss ich jedoch die Aussage, das Büro des Ständerates habe festgehalten, man müsse dem Nationalrat folgen oder dieser sei zuständig. Im Schreiben des Büros des Ständerates an das Büro des Nationalrates heisst es ausdrücklich: "Das Büro des Ständerates erachtet es nicht als seine Aufgabe, sich zur Frage der Zuständigkeit der nationalrätlichen Kommission zu äussern. Es ist Sache der SPK-S, im Bewusstsein unterschiedlicher Haltungen zweier Kommissionen des Nationalrates, über das weitere Vorgehen zu entscheiden." Daraus ergibt sich gerade keine Zuständigkeitszuweisung an den Nationalrat.
+Ein vorletzter Punkt zum Stichwort Fairplay im Parlament, gerichtet an Kollege Broulis: Sie haben das Stimmverhalten des Präsidenten angesprochen. Dies entspricht nicht unserer Praxis; ich sage dies zur Verteidigung eines Kommissionsmitgliedes und des Präsidenten.
+Abschliessend: Wir haben eine parlamentarische Initiative der Schwesterkommission, der SPK-N, vor uns. Die SPK-S könnte jederzeit darüber entscheiden und ihr aufgrund der Mehrheitsverhältnisse wohl auch zustimmen, wir haben dies bisher lediglich nicht getan. Niemand hat je bestritten, dass die SPK-N diese Initiative einreichen darf oder dass wir ihr zustimmen könnten. Gedanklich weitergeführt könnte die SPK-S kurz nach einem negativen Entscheid hier tagen, der Initiative zustimmen und die Arbeiten würden - wie von der SPK-S gewünscht - weitergeführt, allerdings im anderen Rat, bei der SPK-N. Eine Rückholung erscheint kaum möglich. Das Geschäft würde somit ausgearbeitet in die Räte gelangen, jedoch zeitlich verzögert, sodass eine gleichzeitige Behandlung nicht möglich wäre. Dies noch als letzter Hinweis.
 </t>
   </si>
 </sst>
@@ -704,8 +749,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I26" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I28" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I28"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1672,13 +1717,13 @@
         <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
         <v>122</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
         <v>123</v>
@@ -1701,24 +1746,24 @@
         <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="G25" t="s">
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s">
         <v>100</v>
@@ -1727,22 +1772,80 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
         <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I26" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -62,15 +62,14 @@
     <t xml:space="preserve">DE</t>
   </si>
   <si>
-    <t xml:space="preserve">Ihre Aussenpolitische Kommission stimmte am 23. März dem Abkommen zwischen dem Schweizerischen Bundesrat und dem Ministerkabinett der Ukraine über die Zusammenarbeit im Wiederaufbauprozess der Ukraine mit 19 zu 0 Stimmen bei 6 Enthaltungen zu. 
-Beim Wiederaufbau der Ukraine ist insbesondere im Energie- und Infrastrukturbereich ein verstärktes Engagement privater Unternehmen notwendig, sinnvoll und erwünscht. Das vorliegende bilaterale Abkommen schafft die rechtliche Grundlage dafür. Die Ukraine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ihre Aussenpolitische Kommission stimmte am 23. März dem Abkommen zwischen dem Schweizerischen Bundesrat und dem Ministerkabinett der Ukraine über die Zusammenarbeit im Wiederaufbauprozess der Ukraine mit 19 zu 0 Stimmen bei 6 Enthaltungen zu. 
-Beim Wiederaufbau der Ukraine ist insbesondere im Energie- und Infrastrukturbereich ein verstärktes Engagement privater Unternehmen notwendig, sinnvoll und erwünscht. Das vorliegende bilaterale Abkommen schafft die rechtliche Grundlage dafür. Die Ukraine kann Güter und Dienstleistungen definieren, welche die Schweiz anschliessend im Rahmen des bewilligten Budgets bei Schweizer Unternehmen gemäss öffentlichem Beschaffungsrecht, aber unter Ausschluss ausländischer Anbieter, beschafft. Mit dem Abkommen werden Expertise und Innovation aus der Schweiz stärker genutzt und private Investitionen mobilisiert. Auf diese Weise leistet die Schweiz einen Beitrag zum Wiederaufbau der ukrainischen Infrastruktur und Wirtschaft. Die Einbindung der Schweizer Privatwirtschaft in den Wiederaufbau ist einer der Schwerpunkte des Länderprogramms Ukraine 2025-2028 der IZA.
-Im Rahmen der Beratung wurden zwei Anträge auf eine Kommissionsmotion abgehandelt. Die erste Kommissionsmotion zielt auf die Zuweisung von vorgesehenen Mitteln an ein UN-Wiederaufbauinstrument anstelle einer Verknüpfung mit der Schweizer Privatindustrie. Die Kommission lehnte diesen Antrag mit 16 zu 6 Stimmen bei 3 Enthaltungen ab. Ein weiterer Antrag auf eine Kommissionsmotion zur Verknüpfung des Abkommens mit der Auflösung des Schutzstatus S für ukrainische Staatsangehörige aus stabilen Herkunftsregionen wurde mit 16 zu 9 Stimmen ebenfalls abgelehnt. 
-Schliesslich wurde ein Antrag auf einen neuen Artikel 1 Absatz 3, im Bundesbeschluss bezüglich der Rücksichtnahme auf die Empfehlungen des Development Assistance Committee (DAC) der OECD mit 13 zu 12 Stimmen angenommen. Das DAC erlässt unter anderem Umsetzungsrichtlinien für die Entwicklungszusammenarbeit.
-Die Minderheit Rüegger will diesen neuen Absatz 3 zur Verknüpfung mit den OECD-Richtlinien streichen. Sie findet, dass die DAC-Regeln für Entwicklungshilfe zu eng gefasst sind und den Spielraum für Schweizer Unternehmen bei der Unterstützung des Wiederaufbaus unnötigerweise einengen.
+    <t xml:space="preserve">Ihre Aussenpolitische Kommission stimmte am 23.[NB]März dem Abkommen zwischen dem Schweizerischen Bundesrat und dem Ministerkabinett der Ukraine über die Zusammenarbeit im Wiederaufbauprozess der Ukraine mit 19 zu 0 Stimmen bei 6 Enthaltungen zu. 
+Beim Wiederaufbau der Ukraine ist insbesondere im Energie- und Infrastrukturbereich ein verstärktes Engagement privater Unternehmen notwendig, sinnvoll und erwünscht. Das vorliegende bilaterale Abkommen schafft die rechtliche Grundlage dafür. Die Ukrai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ihre Aussenpolitische Kommission stimmte am 23.[NB]März dem Abkommen zwischen dem Schweizerischen Bundesrat und dem Ministerkabinett der Ukraine über die Zusammenarbeit im Wiederaufbauprozess der Ukraine mit 19 zu 0 Stimmen bei 6 Enthaltungen zu. 
+Beim Wiederaufbau der Ukraine ist insbesondere im Energie- und Infrastrukturbereich ein verstärktes Engagement privater Unternehmen notwendig, sinnvoll und erwünscht. Das vorliegende bilaterale Abkommen schafft die rechtliche Grundlage dafür. Die Ukraine kann Güter und Dienstleistungen definieren, welche die Schweiz anschliessend im Rahmen des bewilligten Budgets bei Schweizer Unternehmen gemäss öffentlichem Beschaffungsrecht, aber unter Ausschluss ausländischer Anbieter beschafft. Mit dem Abkommen werden Expertise und Innovation aus der Schweiz stärker genutzt und private Investitionen mobilisiert. Auf diese Weise leistet die Schweiz einen Beitrag zum Wiederaufbau der ukrainischen Infrastruktur und Wirtschaft. Die Einbindung der Schweizer Privatwirtschaft in den Wiederaufbau ist einer der Schwerpunkte des Länderprogramms Ukraine 2025-2028 der IZA.
+Im Rahmen der Beratung wurden zwei Anträge auf eine Kommissionsmotion abgehandelt. Der erste Antrag auf eine Kommissionsmotion zielte auf die Zuweisung von vorgesehenen Mitteln an ein UN-Wiederaufbauinstrument anstelle einer Verknüpfung mit der Schweizer Privatindustrie. Die Kommission lehnte diesen Antrag mit 16 zu 6 Stimmen bei 3 Enthaltungen ab. Ein weiterer Antrag auf eine Kommissionsmotion zur Verknüpfung des Abkommens mit der Auflösung des Schutzstatus S für ukrainische Staatsangehörige aus stabilen Herkunftsregionen wurde mit 16 zu 9 Stimmen ebenfalls abgelehnt. 
+Schliesslich wurde ein Antrag auf einen neuen Artikel 1 Absatz 3 im Bundesbeschluss bezüglich der Rücksichtnahme auf die Empfehlungen des Development Assistance Committee (DAC) der OECD mit 13 zu 12 Stimmen angenommen. Das DAC erlässt unter anderem Umsetzungsrichtlinien für die Entwicklungszusammenarbeit. Die Minderheit Rüegger will diesen neuen Absatz 3 zur Verknüpfung mit den OECD-Richtlinien streichen. Sie findet, dass die DAC-Regeln für Entwicklungshilfe zu eng gefasst sind und den Spielraum für Schweizer Unternehmen bei der Unterstützung des Wiederaufbaus unnötigerweise einengen.
 </t>
   </si>
   <si>
@@ -92,7 +91,7 @@
 Schon meine Vorrednerin der Grünen Fraktion hat gesagt - auch uns ist das wichtig -, dass im Abkommen einige andere Themen geregelt werden, so zum Beispiel das Thema der Korruption. Wir müssen hier nicht einfach so tun, als ob wir es mit einem total unbescholtenen Partnerstaat zu tun hätten, mit dem wir ein solches Abkommen machen. Die Ukraine hat in vielen Dingen, wie etwa bei den Menschenrechten, bei der Korruption und bei anderen Sachen, noch nicht den Standard, den wir uns wünschen. Trotzdem glauben wir, dass wir mit diesem Beitrag zum Wiederaufbau der Ukraine auch helfen können. Zudem ist auch die Streitschlichtung, die in diesem Abkommen ebenfalls behandelt wird, gerecht und auf Augenhöhe geregelt.
 Was ich aber nicht verstehe, ist, dass der Antrag für Artikel 1 Absatz 3 eine Mehrheit bekommen hat. Hier schaue ich zur Mitte-Fraktion: Dieser Antrag hat eine Mehrheit bekommen, weil Ihre Mitglieder in der APK - es ist kein Kommissionsgeheimnis, Sie können es hier selber herausfinden - ihm zugestimmt haben. Auch Sie sangen erst das Hohelied auf die privatwirtschaftliche Wiederaufbauhilfe, und nun torpedieren Sie diese genau mit diesem Absatz. Die Minderheitssprecherin, Kollegin Rüegger, hat die Details eigentlich exzellent erklärt.
 Lassen Sie mich noch etwas Weiteres sagen: Es handelt sich hier um eine Arbeitsgruppe innerhalb der OECD. Jetzt müssen Sie sich vorstellen, dass diese Arbeitsgruppe, in der rund dreissig andere Länder vertreten sind, dieses Abkommen durchgeht, dieses analysiert und uns dann sagt, was sie findet, was wir tun dürfen und was wir nicht tun dürfen. Diese Arbeitsgruppe wird eben genau auch einen ihrer Grundsätze einbringen, wonach man nämlich die eigene Wirtschaft zum Beispiel nicht mit Entwicklungshilfe begünstigen darf. Aber genau das wollten wir, das ist in der IZA-Strategie so festgehalten, das haben wir auch im Budget so festgehalten. Ich möchte die Mitte-Fraktion daher doch bitten, wieder von diesem Absatz wegzukommen und den Antrag der Minderheit Rüegger zu unterstützen. 
-Lassen Sie mich noch ein Schlusswort sagen. Weshalb leisten wir Wiederaufbauhilfe für die Ukraine? Es ist eine Schwerpunktregion für uns, sie ist in unserer Nachbarschaft, und wir haben alles Interesse daran - sei es beim Thema Migration, sei es beim Thema Sicherheit oder aber auch bei wirtschaftlichen Themen -, dass wir mit der Ukraine eine gute Partnerschaft haben und dass die Ukraine wieder auf die Beine kommt. Aber es ist kein Schuldbekenntnis von uns. Als ich vor dem Pfingstwochenende am Treffen des EWR-Parlamentarierkomitees war, sagte ich, was die Schweiz macht. Ich sagte aber auch: Die Schweiz ist weder Kriegspartei, noch ist es unser Krieg. Und mir hat tatsächlich die Aussenministerin von Liechtenstein im Namen der EWR-Minister widersprochen und gesagt: Doch, das ist unser Krieg, und wir sind Kriegspartei, und deshalb müssen wir der Ukraine beistehen. Nein - und das ist meine persönliche Meinung -: Wir stehen der Ukraine bei, weil sie ungerechtfertigt von einem Aggressor angegriffen wurde, weil sie zerstört wird, weil dort menschliches Leid geschieht. Aber wir stehen der Ukraine nicht bei, weil dies unser Krieg ist oder weil wir Kriegspartei sind.
+Lassen Sie mich noch ein Schlusswort sagen. Weshalb leisten wir Wiederaufbauhilfe für die Ukraine? Es ist eine Schwerpunktregion für uns, sie ist in unserer Nachbarschaft, und wir haben alles Interesse daran - sei es beim Thema Migration, sei es beim Thema Sicherheit oder aber auch bei wirtschaftlichen Themen -, dass wir mit der Ukraine eine gute Partnerschaft haben und dass die Ukraine wieder auf die Beine kommt. Aber es ist kein Schuldbekenntnis von uns. Als ich vor dem Pfingstwochenende am Treffen des EWR-Parlamentarierkomitees war, sagte ich, was die Schweiz macht. Ich sagte aber auch: Die Schweiz ist weder Kriegspartei, noch ist es unser Krieg. Und mir hat tatsächlich die Aussenministerin von Liechtenstein im Namen der EWR-Minister widersprochen und gesagt: "Doch, das ist unser Krieg, und wir sind Kriegspartei, und deshalb müssen wir der Ukraine beistehen." Nein, und das ist meine persönliche Meinung, wir stehen der Ukraine bei, weil sie ungerechtfertigt von einem Aggressor angegriffen wurde, weil sie zerstört wird, weil dort menschliches Leid geschieht. Aber wir stehen der Ukraine nicht bei, weil dies unser Krieg ist oder weil wir Kriegspartei sind.
 </t>
   </si>
   <si>
@@ -666,17 +665,17 @@
     <t xml:space="preserve">Barandun Nicole</t>
   </si>
   <si>
-    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der KFOR, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
+    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der Kfor, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
 Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweima</t>
   </si>
   <si>
-    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der KFOR, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
-Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweimal zur Verstärkung der KFOR zwangen. Solange die Beziehungen zwischen Kosovo und Serbien nicht nachhaltig normalisiert sind, halten die Nato und die beteiligten Staaten die KFOR für notwendig, als militärische Garantin eines sicheren Umfelds, die Entwicklung und Stabilität im Kosovo und auf dem gesamten Westbalkan gewährleistet.
+    <t xml:space="preserve">Seit 1999, wir haben es schon gehört, beteiligt sich die Schweizer Armee mit Swisscoy an der Kfor, der Nato-geführten, aber von der UNO mandatierten Friedensmission in Kosovo. 
+Die Sicherheitslage im Kosovo ist aktuell ruhig, sie bleibt aber weiterhin volatil. Sie ist, ausdrücklich gesagt, nicht stabil, so schätzen es auch unsere europäischen Nachbarländer ein. Insbesondere im Norden sind die Spannungen anhaltend hoch. Erst 2023 kam es zu schweren Sicherheitsvorfällen, die die Nato gleich zweimal zur Verstärkung der Kfor zwangen. Solange die Beziehungen zwischen Kosovo und Serbien nicht nachhaltig normalisiert sind, halten die Nato und die beteiligten Staaten die Kfor für notwendig, als militärische Garantin eines sicheren Umfelds, die Entwicklung und Stabilität im Kosovo und auf dem gesamten Westbalkan gewährleistet.
 Die Schweiz leistet mit Swisscoy seit 25 Jahren einen verlässlichen Beitrag zu dieser Stabilität, und sie leistet diesen Beitrag auch mit ganz konkreten Handlungen. Ich spreche zum Beispiel die Liaison and Monitoring Teams an, die im direkten Austausch mit der Bevölkerung Spannungen früh erkennen und versuchen, diese zu entschärfen, aber auch unsere Genietruppen, die vor Ort wichtige Dienste leisten u. a. in der Logistik. Darüber hinaus kann die Schweizer Armee mit dem Einsatz wichtige Erfahrungen in einer internationalen Operation sammeln, die auch für unsere Verteidigungsfähigkeit hier zuhause relevant sind. 
 Die Schweiz hat ein direktes Interesse am Frieden, an der Stabilität und an der wirtschaftlichen Entwicklung des Kosovos und der ganzen Region. Der Westbalkan ist für uns sicherheits-, migrations- und wirtschaftspolitisch relevant. Wir haben aufgrund der engen menschlichen und wirtschaftlichen Beziehungen auch Verpflichtungen gegenüber dieser Region. Mit der Verlängerung unseres Engagements übernehmen wir Verantwortung. Diese Verantwortung tragen wir, weil wir eine enge Beziehung zu dieser Region pflegen. 
 Ich möchte noch ein Wort zur kosovarischen Diaspora in der Schweiz verlieren. Infolge des Kosovokriegs fanden Ende der Neunzigerjahre rund 60 000 Menschen aus dem Kosovo vorübergehend Schutz in der Schweiz. Viele von ihnen sind später zurückgekehrt, aber ein Teil von ihnen hat hier dauerhaft Fuss gefasst. Ihre Kinder und Enkelkinder sind heute ein selbstverständlicher Teil unserer Gesellschaft. Insgesamt leben in der Schweiz deutlich über 100 000 Menschen mit Wurzeln im Kosovo; Schätzungen sprechen von rund 170 000 Kosovo-Albanerinnen und -Albanern. Aus migrationspolitischer Sicht wissen wir, wenn es wieder zu einer schweren Eskalation käme, würden sich die neuen Fluchtbewegungen dorthin richten, wo bereits Familien und etablierte Netzwerke bestehen. Für die Schweiz mit ihrer grossen kosovarischen Community sind Prävention und Stabilität im Kosovo daher auch migrationspolitisch sinnvoll. Das Risiko eines erneuten unkontrollierten Flüchtlingsstroms wird dadurch reduziert anstatt erhöht. 
-Ich sage noch ein Wort zur Neutralität. Sie schwebt immer ein bisschen mit im Raum. Das Mandat der KFOR basiert auf einem klaren Mandat des UNO-Sicherheitsrates. Es handelt sich um eine klassische friedensfördernde Operation. Die Neutralität steht solchen von der UNO mandatierten Friedensoperationen gerade nicht entgegen. Die Schweizer Beteiligung entspricht einer seit Jahren gefestigten Praxis der schweizerischen Aussen- und Sicherheitspolitik. 
-Ich empfehle Ihnen im Namen der Mitte-Fraktion. Die Mitte. EVP, dieser Vorlage zuzustimmen, das heisst, einzutreten und der Mehrheit zu folgen. Bei der Erhöhung des Kontingents geht es um einen Maximalrahmen, nicht um einen Automatismus. Der Bundesrat bleibt dem Parlament gegenüber verantwortlich. Verteidigungsfähigkeit entsteht nicht in einem Vakuum. Wer eine glaubwürdige Landesverteidigung will, braucht gut ausgebildete Kader mit realer Einsatzerfahrung. Die KFOR bleibt vor dem Hintergrund einer nach wie vor volatilen Lage im Kosovo und einer ungelösten Beziehung zu Serbien deshalb auch aus Sicht der Schweiz notwendig. 
+Ich sage noch ein Wort zur Neutralität. Sie schwebt immer ein bisschen mit im Raum. Das Mandat der Kfor basiert auf einem klaren Mandat des UNO-Sicherheitsrates. Es handelt sich um eine klassische friedensfördernde Operation. Die Neutralität steht solchen von der UNO mandatierten Friedensoperationen gerade nicht entgegen. Die Schweizer Beteiligung entspricht einer seit Jahren gefestigten Praxis der schweizerischen Aussen- und Sicherheitspolitik. 
+Ich empfehle Ihnen im Namen der Mitte-Fraktion. Die Mitte. EVP, dieser Vorlage zuzustimmen, das heisst, einzutreten und der Mehrheit zu folgen. Bei der Erhöhung des Kontingents geht es um einen Maximalrahmen, nicht um einen Automatismus. Der Bundesrat bleibt dem Parlament gegenüber verantwortlich. Verteidigungsfähigkeit entsteht nicht in einem Vakuum. Wer eine glaubwürdige Landesverteidigung will, braucht gut ausgebildete Kader mit realer Einsatzerfahrung. Die Kfor bleibt vor dem Hintergrund einer nach wie vor volatilen Lage im Kosovo und einer ungelösten Beziehung zu Serbien deshalb auch aus Sicht der Schweiz notwendig. 
 </t>
   </si>
   <si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -167,8 +167,9 @@
     <t xml:space="preserve">Der Bund schliesst das Jahr 2025 mit einem Finanzierungsüberschuss von 259 Millionen Franken ab. Die Vorgaben der Schuldenbremse wurden eingehalten, und die Nettoschulden sind leicht rückläufig. Wenn man sich diese Eckwerte vor Augen hält, könnte man fast meinen, wir hätten alles im Griff; dem ist aber leider nicht so. Bei genauer Betrachtung offenbart die Staatsrechnung 2025 laute Warnsignale, und zwar bei den stark angestiegenen Ausgaben, bei den Gründen für die höheren Einnahmen, bei der immer noch ausserordentlichen Verbuchung von Ukraine-Ausgaben sowie bei der Entwicklung der Personalausgaben.
 Zuerst zu den stark angestiegenen Ausgaben: Der jahrzehntelange Trend des ständigen Ausgabenwachstums hält unvermindert an. Mit rund 88 Milliarden Franken lagen die Gesamtausgaben im Jahr 2025 um weitere fast dreieinhalb Milliarden Franken bzw. 4 Prozent höher als im Vorjahr. Die ordentlichen Ausgaben wachsen damit mehr als doppelt so stark wie das nominale Bruttoinlandprodukt und damit die Wirtschaft. Genau darin liegt das Kernproblem unseres Bundeshaushalts. Nicht die Einnahmen wachsen zu wenig, sondern die Ausgaben wachsen zu schnell, und das seit Jahrzehnten. Davon entfallen wiederum Milliardenbeträge auf die soziale Wohlfahrt. Mittlerweile geben wir für die soziale Wohlfahrt jährlich über 30 Milliarden Franken an Steuergeldern aus. Diese Entwicklung ist alarmierend.
 Kommen wir zur Einnahmenseite: Ich bedanke mich im Namen der SVP-Fraktion herzlich bei unseren Unternehmungen, insbesondere den KMU, dem Rückgrat unserer Wirtschaft. Sie schaffen nicht nur Arbeitsplätze und Lehrstellen und versorgen unsere Bevölkerung mit hochwertigen Produkten und Dienstleistungen, nein, sie generieren auch noch Steuern zur Finanzierung unseres zu teuren Staatsapparats. Glücklicherweise haben sie auch im vergangenen Jahr erneut gut gearbeitet. Insbesondere unserer Wirtschaft ist es zu verdanken, dass die Einnahmen deutlich gestiegen sind. Die Einnahmen aus der direkten Bundessteuer nahmen um satte 8 Prozent zu. Besonders stark fiel das Wachstum bei den Unternehmensgewinnen aus. Allerdings müssen wir auch hier genauer hinschauen. Ein erheblicher Teil dieser Mehreinnahmen sind die Folgen eines Sondereffekts im Kanton Genf, der dem Bund rund 1,5 Milliarden Franken zusätzliche Einnahmen eingebracht hat. Hinzu kommt eine Gewinnausschüttung der Schweizerischen Nationalbank in der Höhe von 1 Milliarde Franken. 
-Das positive Rechnungsergebnis beruht somit nicht nur auf einer starken Wirtschaft, sondern auch auf ausserordentlichen Faktoren. Diese dürfen nicht darüber hinwegtäuschen, dass die strukturellen Probleme des Bundeshaushalts weiterhin bestehen. Ein weiterer grosser "Tolggen" im Reinheft der Staatsrechnung 2025 ist die nach wie vor ausserordentliche Verbuchung der Ausgaben für Status-S-Flüchtlinge aus der Ukraine im Umfang von 700 Millionen Franken. Diese Praxis ist mittlerweile unter keinem Titel mehr nachvollziehbar, das muss in aller Klarheit festgehalten werden. Nach rund viereinhalb Jahren oder 52 Monaten, also über 1500 Tage nach Kriegsausbruch, können diese Ausgaben beim besten Willen nicht mehr als unvorhersehbar bezeichnet werden. Wer Jahr für Jahr dieselben Ausgaben ausserordentlich verbucht, unterläuft ohne Wenn und Aber die Schuldenbremse. Dieses Vorgehen steht klar im Widerspruch zu unserer Verfassung. 
-Ich komme zum Personalbestand: Auch im Jahr 2025 ist die Bundesverwaltung weitergewachsen. Der durchschnittliche Stellenbestand nahm wiederum um Hunderte Vollzeitstellen zu. Die Personalausgaben stiegen erneut an. Mittlerweile gibt der Bund jedes Jahr rund 6,5 Milliarden Franken für Personal aus - 6,5 Milliarden Franken Jahr für Jahr. Das zeigt, dass auch die Bundesverwaltung ihren Beitrag zur Haushaltsdisziplin noch nicht ausreichend leistet. 
+Das positive Rechnungsergebnis beruht somit nicht nur auf einer starken Wirtschaft, sondern auch auf ausserordentlichen Faktoren. Diese dürfen nicht darüber hinwegtäuschen, dass die strukturellen Probleme des Bundeshaushalts weiterhin bestehen. 
+Ein weiterer grosser "Tolggen" im Reinheft der Staatsrechnung 2025 ist die nach wie vor ausserordentliche Verbuchung der Ausgaben für Status-S-Flüchtlinge aus der Ukraine im Umfang von 700 Millionen Franken. Diese Praxis ist mittlerweile unter keinem Titel mehr nachvollziehbar; das muss in aller Klarheit festgehalten werden. Nach rund viereinhalb Jahren oder 52 Monaten, also über 1500 Tage nach Kriegsausbruch, können diese Ausgaben beim besten Willen nicht mehr als unvorhersehbar bezeichnet werden. Wer Jahr für Jahr dieselben Ausgaben ausserordentlich verbucht, unterläuft ohne Wenn und Aber die Schuldenbremse. Dieses Vorgehen steht klar im Widerspruch zu unserer Verfassung. 
+Ich komme zum Personalbestand: Auch im Jahr 2025 ist die Bundesverwaltung weitergewachsen. Der durchschnittliche Stellenbestand nahm wiederum um Hunderte Vollzeitstellen zu. Die Personalausgaben stiegen erneut an. Mittlerweile gibt der Bund jedes Jahr rund 6,5 Milliarden Franken für Personal aus - 6,5 Milliarden Franken Jahr für Jahr! Das zeigt, dass auch die Bundesverwaltung ihren Beitrag zur Haushaltsdisziplin noch nicht ausreichend leistet. 
 Fazit: Die Staatsrechnung 2025 hätte schlechter ausfallen können. Genaueres Hinschauen trübt das Ergebnis jedoch. Das gute Rechnungsergebnis darf keinesfalls über die strukturellen Herausforderungen hinwegtäuschen. Die Finanzpläne des Bundes weisen auch für die Jahre 2027 bis 2029 weiterhin Defizite aus, obwohl die Einnahmen kräftig wachsen. Das eigentliche Problem liegt auf der Ausgabenseite. Die Einnahmen steigen, die Ausgaben steigen aber noch schneller.
 Wer diese Herausforderungen ernst nimmt, muss den Mut haben, Prioritäten zu setzen. Wir schicken nach wie vor zu viel Steuergeld ins Ausland, anstatt es dort einzusetzen, wo es unserer Bevölkerung zugutekommt: bei der AHV, bei der Sicherheit unseres Landes, bei der Stärkung unserer Landwirtschaft oder bei der Bewältigung von Naturkatastrophen oder anderen Krisen im Inland. Wir wollen endlich unsere Verantwortung wahrnehmen, sorgsam mit dem Steuerfranken umgehen, die Prioritäten richtig setzen und den Bundeshaushalt langfristig wieder ins Lot bringen. Mit den erwähnten Mängeln in der Staatsrechnung 2025 wird dies nicht möglich sein. 
 Die SVP-Fraktion wird die Rechnung 2025 ohne Begeisterung genehmigen, sich in kommenden Budgetdebatten jedoch konsequent für eine vernünftige Prioritätensetzung einsetzen. Besten Dank, wenn Sie uns dabei unterstützen.
@@ -184,19 +185,23 @@
     <t xml:space="preserve">SG</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
-Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausseror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Sprecherinnen und der Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+    <t xml:space="preserve">Die Sprecherinnen und Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
+Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Sprecherinnen und Sprecher der Kommission und der Fraktionen haben die Rechnung und auch teilweise den Nachtrag bereits ausführlich dargelegt. Ich beschränke mich darum auf die wichtigsten Punkte.
 Zunächst zum Ergebnis der Staatsrechnung: Wie Sie gehört haben, schliesst die Rechnung 2025 erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Wie Sie wissen, unterscheidet die Schuldenbremse zwischen dem ordentlichen und dem ausserordentlichen Haushalt.
-Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
+Im ordentlichen Haushalt verzeichnet der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt. Die Ergebnisverbesserung ist auf die dynamische Einnahmenentwicklung zurückzuführen. 
+Die ordentlichen Einnahmen schlossen um 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Einnahmen aus der direkten Bundessteuer für die Unternehmen, also die Gewinnsteuern. Die Gewinnsteuereinnahmen lagen 1,4 Milliarden Franken über dem Budget. Diese Entwicklung ist auf die temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Allein der Kanton Genf hat 1,5 Milliarden Franken beigesteuert. Das konnte im Budget nur summarisch abgebildet werden. Sie können sich erinnern, wir haben Sie letztes Frühjahr über die Mehreinnahmen aus dem Kanton Genf informiert. Es wurde dann aber erst zu Beginn der Budgetberatung in der Finanzkommission des Ständerates im November 2025 klar, dass eben auch provisorische Rechnungen im Kanton Genf nicht ausgestellt wurden und dass die Mehreinnahmen viel höher ausfallen würden. Wir haben aber auch unter Ausnahme des Effekts Genf eine positive Entwicklung bei den Gewinnsteuereinnahmen, wobei sie allerdings ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären. 
+Gleichzeitig lagen die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden Franken relativ tief ausgefallen sind.
 Im ausserordentlichen Haushalt waren hingegen die Ausgaben grösser als die Einnahmen. Die beiden grössten ausserordentlichen Ausgaben waren diejenigen für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB. Dieser war ursprünglich für das Jahr 2024 budgetiert gewesen und konnte erst 2025 ausgerichtet werden, was damals die Verbesserung der Rechnung 2024 generiert hat. Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich verbucht, 333 Millionen Franken. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
-Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete; dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
+Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
 Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
-Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt - und dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
-Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen, wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
+Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. 
+Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen; wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. 
+Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
 Der Bundesrat beantragt Ihnen, der Staatsrechnung für das Jahr 2025 zuzustimmen.
 </t>
   </si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -198,7 +198,7 @@
 Noch etwas zur Ausgabenentwicklung: Verschiedene Sprecherinnen und Sprecher haben darauf hingewiesen, wie sehr man den Bundeshaushalt sozusagen auspresse. Ich gebe Ihnen einfach bekannt, welches Wachstum wir in den wichtigsten Positionen haben. Soziale Wohlfahrt: insgesamt 2 Prozent, allein die AHV plus 5,7 Prozent. Finanzen und Steuern: 6,3 Prozent Wachstum. Das sind natürlich die Kantonsanteile an den Einnahmen, der Finanzausgleich. Verkehr: Zunahme von 9,1 Prozent bei den Ausgaben. Bildung und Forschung: Zunahme von 5,9 Prozent. Sicherheit: Zunahme von 4,3 Prozent. Beziehung zum Ausland: minus 1,2 Prozent. Landwirtschaft und Ernährung: plus 0,1 Prozent. Und dann kommen noch die übrigen Aufgabengebiete. Dies einfach zum Thema, der Staat spare sich kaputt, man gebe immer weniger für die wichtigen Bereiche aus.
 Nun noch ein Ausblick: Der Bundesrat wird Ende Juni wie üblich die Zahlen zum Voranschlag 2027 und zum Finanzplan 2028-2030 festlegen. Die Arbeiten sind noch am Laufen. Ich möchte Sie an dieser Stelle aber über den Zwischenstand dieser Arbeiten informieren, gestützt auf die inzwischen erfolgten Budgeteingaben der Departemente und gestützt auf die aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge des für die Schätzung wichtigen Monats April gemeldet haben.
 Demnach dürfte sich auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich 300 Millionen Franken ergeben, dies im Vergleich zur Standortbestimmung vom April. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. 
-Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, für juristische Personen eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
+Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer, also bei der Unternehmenssteuer, eine deutliche Verbesserung ab. Neben dem Effekt Genf, den wir bereits kannten und entsprechend eingepreist haben, verzeichnen wir auch im laufenden Jahr ein starkes Einnahmenwachstum. Dies zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen, wobei vor allem das Wachstum in den Kantonen Luzern, Zürich und Basel-Stadt ins Gewicht fällt. Das hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige wenige Unternehmen. Es bestehen natürlich weiterhin grosse Unsicherheiten; unter anderem basieren die Schätzungen der Gewinnsteuer zu diesem Zeitpunkt jeweils auf provisorischen Steuerrechnungen, und es ist auch nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge sind. Einzelne Unternehmen können, ich habe es gesagt, hier grosse Effekte haben. 
 Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer, bei der wir frühestens im Herbst mit verlässlichen Zahlen rechnen können. 
 Unter dem Strich erwarten wir, Stand heute, aber klar eine Entspannung im Voranschlag 2027, dies unter Einschluss der Kürzungen aus dem Entlastungspaket 2027, wie Sie es in der Frühjahrssession verabschiedet haben. Ohne das EP 27 wären wir weiterhin im roten Bereich. Vermutlich können wir aber darüber hinausgehende Massnahmen jetzt streichen; wir können also auf weitere Kürzungen verzichten, die wir vorsorglich im April noch beschlossen hatten, um die Schuldenbremse einzuhalten. Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen wird, falls die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaubt. 
 Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Bis dahin werden wir auch mehr zur Entwicklung in den Finanzplanjahren wissen. Ich kann Ihnen jedenfalls versichern, dass es unser Ziel ist, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren - so viel noch zum Ausblick. 
@@ -215,15 +215,15 @@
     <t xml:space="preserve">Steinemann Barbara</t>
   </si>
   <si>
-    <t xml:space="preserve">Die SVP-Fraktion tritt auf diese Revision ein, jedoch unter zahlreichen Vorbehalten und nicht ohne sehr kritische Anmerkungen. Mit dem Leistungskatalog des heutigen Opferhilfegesetzes sind wir grundsätzlich einverstanden. Die Schweiz hat ein gut organisiertes Netz aus Anlaufstellen, die dem Opfer und seinen Angehörigen umfassende Dienstleistungen bieten. Das darf an dieser Stelle gesagt werden. Wir müssen uns nichts vorwerfen lassen. Die SVP-Fraktion steht hinter den Leistungen der Opferhilfe un</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die SVP-Fraktion tritt auf diese Revision ein, jedoch unter zahlreichen Vorbehalten und nicht ohne sehr kritische Anmerkungen. Mit dem Leistungskatalog des heutigen Opferhilfegesetzes sind wir grundsätzlich einverstanden. Die Schweiz hat ein gut organisiertes Netz aus Anlaufstellen, die dem Opfer und seinen Angehörigen umfassende Dienstleistungen bieten. Das darf an dieser Stelle gesagt werden. Wir müssen uns nichts vorwerfen lassen. Die SVP-Fraktion steht hinter den Leistungen der Opferhilfe und ortet keine grossen Lücken im Gesetz.
+    <t xml:space="preserve">Die SVP-Fraktion tritt auf diese Revision ein, jedoch mit zahlreichen Vorbehalten und nicht ohne sehr kritische Anmerkungen. Mit dem Leistungskatalog des heutigen Opferhilfegesetzes sind wir grundsätzlich einverstanden. Die Schweiz hat ein gut organisiertes Netz aus Anlaufstellen, die dem Opfer und seinen Angehörigen umfassende Dienstleistungen bieten. Das darf an dieser Stelle gesagt werden. Wir müssen uns nichts vorwerfen lassen. Die SVP-Fraktion steht hinter den Leistungen der Opferhilfe und </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion tritt auf diese Revision ein, jedoch mit zahlreichen Vorbehalten und nicht ohne sehr kritische Anmerkungen. Mit dem Leistungskatalog des heutigen Opferhilfegesetzes sind wir grundsätzlich einverstanden. Die Schweiz hat ein gut organisiertes Netz aus Anlaufstellen, die dem Opfer und seinen Angehörigen umfassende Dienstleistungen bieten. Das darf an dieser Stelle gesagt werden. Wir müssen uns nichts vorwerfen lassen. Die SVP-Fraktion steht hinter den Leistungen der Opferhilfe und ortet keine grossen Lücken im Gesetz.
 Mit dieser Revision wird der Leistungskatalog um die rechtsmedizinische Hilfe ergänzt. Opfer sollen sich in der ganzen Schweiz an eine Stelle wenden können, die spezialisierte medizinische und rechtsmedizinische Leistungen erbringt und die entsprechenden Spuren sichert. Einige Kantone verfügen bereits über diese Angebote, neu soll der Zugang zu solchen Leistungen allen Opfern offenstehen. Jedes Verbrechen sollte möglichst auch der Justiz zugeführt werden. Dies gilt umso mehr, als es sich bei den hier behandelten Delikten um schwere Straftaten handelt und das Wiederholungsrisiko bei Sexualdelikten und Gewalt im häuslichen Bereich gross ist. Auch ist diesbezüglich zu hoffen, dass sich mehr Opfer für den Gang zu Polizei und Staatsanwaltschaft entscheiden.
-Wie sich diese Rechtsdokumentation in der Praxis bewährt, wird sich weisen. Zu hoffen ist einerseits auf offensichtlichere Beweislagen und vereinfachte Gerichtsverfahren, auf der anderen Seite aber auch auf schnellere Erledigungen bei ungerechtfertigten Beschuldigungen. Bei den meisten Vergewaltigungen handelt es sich um Vieraugendelikte, entsprechend schwierig ist leider die Beweisfindung. Es ist sehr zu wünschen, dass dieses kostenlose medizinische Gutachten zu mehr Verurteilungen führt. Die SVP-Fraktion steht also hinter den Rechtsgutachten, wir versprechen uns einige Erleichterungen für die juristischen Verfahren. Den zweiten Teil der Revision, die zusätzlichen Unterkünfte, lehnen wir jedoch mehrheitlich ab.
-Es ist wichtig und richtig, dass in der Schweiz Frauenhäuser und andere niederschwellige Notunterkünfte zur Verfügung stehen. Nicht alle Kantone sollen eigene Frauenhäuser betreiben müssen, sondern die heutigen Standortkantone sollten flexibel genug sein, anderen diese Infrastruktur gegen ein entsprechendes Entgelt zur Verfügung zu stellen. Die Kantone können sich untereinander organisieren, so wie das heute auch getan wird. Wenn jeder Kanton nur für sich schauen müsste, würden sich zwei Probleme ergeben: Zum einen wären die Unterkünfte kaum ausgelastet und würden dann zu teuren - provokativ gesagt - Hotels werden, ohne Druck auf die Verantwortlichen, so schnell wie möglich eine Anschlusslösung für die Frauen zu suchen. Opfer sollen unseres Erachtens nicht verwaltet werden. Zum anderen würden die gewalttätigen Männer ihre Frauen sofort finden, weil sie im Haus des entsprechenden Kantons sein müssen. Das würde die Kosten für die Sicherheit nochmals in die Höhe treiben.
-Einer Studie der Konferenz der kantonalen Sozialdirektorinnen und Sozialdirektoren (SODK) zufolge ist zwischen 2017 und 2024 die Zahl der Frauenhäuser von 18 auf 22 und jene der Betten von 292 auf 427 gestiegen. Das sind bloss sieben Jahre. Auch in den anderen Schutzunterkünften hat sich die Bettenzahl von 150 auf 182 erhöht. Im Verhältnis zum Bevölkerungswachstum ist dieser Ausbau weit überproportional erfolgt. Im selben Zeitraum stieg auch die Belegung der Frauenhäuser von 72 auf 76 Prozent. In meiner eigenen Gemeinde mit mehr als 20 000 Einwohnern habe ich mir eine anonymisierte Liste der Aufenthaltsdauer in den Notunterkünften geben lassen. Danach gibt es sowohl Aufenthalte von 291 als auch von 120 Tagen, aber durchaus auch einen kürzeren Verbleib von rund 30 bis 60 Tagen.
-Schliesslich mangelt es - nicht in dieser Revision, hier liegt der Fokus auf den Opfern - völlig am politischen Willen der Ursachenbekämpfung, die angesichts der signifikant überproportional vertretenen ausländischen Täterschaft am effektivsten wäre. Wir wollen mehr Härte des Staates gegenüber den Tätern und damit den Verursachern des Leids. Entsprechend vermissen wir härtere Strafen, einen konsequenteren Entzug des Aufenthaltsrechts, forcierte Ausschaffungen und Schadloshaltungen des Staates gegenüber den Verursachern. Täter sollen wissen, dass ihnen eine Freiheitsstrafe und allenfalls die Ausweisung aus der Schweiz drohen, wenn sie jemandem Gewalt antun.
+Wie sich diese Rechtsdokumentation in der Praxis bewährt, wird sich weisen. Zu hoffen ist einerseits auf offensichtlichere Beweislagen und vereinfachte Gerichtsverfahren, auf der anderen Seite aber auch auf schnellere Erledigungen bei ungerechtfertigten Beschuldigungen. Bei den meisten Vergewaltigungen handelt es sich um Vieraugendelikte, entsprechend schwierig ist leider die Beweisfindung. Es ist sehr zu wünschen, dass dieses kostenlose rechtsmedizinische Gutachten zu mehr Verurteilungen führt. Die SVP-Fraktion steht also hinter den rechtsmedizinischen Gutachten, wir versprechen uns einige Erleichterungen für die juristischen Verfahren.
+Den zweiten Teil der Revision, die zusätzlichen Unterkünfte, lehnen wir jedoch mehrheitlich ab. Es ist wichtig und richtig, dass in der Schweiz Frauenhäuser und andere niederschwellige Notunterkünfte zur Verfügung stehen. Nicht alle Kantone sollen eigene Frauenhäuser betreiben müssen, sondern die heutigen Standortkantone sollten flexibel genug sein, anderen diese Infrastruktur gegen ein entsprechendes Entgelt zur Verfügung zu stellen. Die Kantone können sich untereinander organisieren, so wie das heute auch getan wird. Wenn jeder Kanton nur für sich schauen müsste, würden sich zwei Probleme ergeben: Zum einen wären die Unterkünfte kaum ausgelastet und würden dann zu - provokativ gesagt - teuren Hotels, ohne Druck auf die Verantwortlichen, so schnell wie möglich eine Anschlusslösung für die Frauen zu suchen. Opfer sollen unseres Erachtens nicht verwaltet werden. Zum anderen würden die gewalttätigen Männer ihre Frauen sofort finden, weil sie im Haus des entsprechenden Kantons sein müssen. Das würde die Kosten für die Sicherheit nochmals in die Höhe treiben.
+Einer Studie der Konferenz der kantonalen Sozialdirektorinnen und Sozialdirektoren zufolge ist zwischen 2017 und 2024 die Zahl der Frauenhäuser von 18 auf 22 und jene der Betten von 292 auf 427 gestiegen. Das ist in bloss sieben Jahren geschehen. Auch in den anderen Schutzunterkünften hat sich die Bettenzahl von 150 auf 182 erhöht. Im Verhältnis zum Bevölkerungswachstum ist dieser Ausbau weit überproportional erfolgt. Im selben Zeitraum stieg auch die Belegung der Frauenhäuser von 72 auf 76 Prozent. In meiner eigenen Gemeinde mit mehr als 20 000 Einwohnern habe ich mir eine anonymisierte Liste der Aufenthaltsdauer in den Notunterkünften geben lassen. Danach gibt es sowohl Aufenthalte von 291 als auch von 120 Tagen, aber durchaus auch einen kürzeren Verbleib von rund 30 bis 60 Tagen.
+Schliesslich mangelt es - nicht in dieser Revision, hier liegt der Fokus auf den Opfern - völlig am politischen Willen der Ursachenbekämpfung, die angesichts der signifikant überproportional vertretenen ausländischen Täterschaft am effektivsten wäre. Wir wollen mehr Härte des Staates gegenüber den Tätern und damit den Verursachern des Leids. Entsprechend vermissen wir härtere Strafen, einen konsequenteren Entzug des Aufenthaltsrechts, forcierte Ausschaffungen und die Schadloshaltung des Staates gegenüber den Verursachern. Täter sollen wissen, dass ihnen eine Freiheitsstrafe und allenfalls die Ausweisung aus der Schweiz drohen, wenn sie jemandem Gewalt antun.
 Wir werden auf diese Vorlage eintreten.
 </t>
   </si>
@@ -240,13 +240,13 @@
     <t xml:space="preserve">VD</t>
   </si>
   <si>
-    <t xml:space="preserve">Je commence par déclarer mes intérêts dans ce débat : je suis président de Dettes Conseil Suisse, la faîtière qui regroupe les centres qui font du conseil en matière de surendettement. Cela étant dit, j'aimerais exprimer ici ce soulagement, cette satisfaction de nous voir arriver au terme de ce processus. C'était un long débat et un projet important. Un certain nombre de décisions, parfois, ont été prises à une courte majorité, comme au Conseil des États lors de la dernière session, mais le proj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je commence par déclarer mes intérêts dans ce débat : je suis président de Dettes Conseil Suisse, la faîtière qui regroupe les centres qui font du conseil en matière de surendettement. Cela étant dit, j'aimerais exprimer ici ce soulagement, cette satisfaction de nous voir arriver au terme de ce processus. C'était un long débat et un projet important. Un certain nombre de décisions, parfois, ont été prises à une courte majorité, comme au Conseil des États lors de la dernière session, mais le projet qui est maintenant sur notre table est équilibré, intelligent, et permettra - j'en suis sûr - à toute une série de personnes de sortir de cette spirale du surendettement, pour le bien de tous, y compris des créanciers, de la société dans son ensemble et des finances publiques, puisque la situation actuelle, avec des personnes qui restent dans cette spirale du surendettement, n'est dans l'intérêt de personne.
-Je reviens brièvement à ce stade des débats sur les trois minorités dont nous parlons encore d'aujourd'hui, à la suite de ce qu'ont dit mes collègues précédemment. D'abord, concernant la minorité Bregy, nous vous invitons à suivre la majorité de la commission sur ce point. Il s'agit de la question de savoir s'il doit y avoir une forme de privilège pour les loyers et les charges locatives pendant cette fameuse durée de prélèvement de trois ans, à l'image de ce que l'on fait pour les impôts. La réflexion de la majorité de la commission a été de se dire qu'il était important d'éviter des situations critiques dans lesquelles les loyers ne sont pas payés et dans lesquelles cela pourrait provoquer des expulsions, ce qui n'est dans l'intérêt de personne, puisqu'on se retrouverait ensuite avec des situations d'une grande complexité, à la fois au désavantage des personnes concernées, des locataires, mais aussi au désavantage des bailleurs, qui seraient mis dans une position très délicate. Je dois reconnaître qu'il y a un petit enjeu technique autour du fait que ce fameux privilège qui serait donné pendant ces trois ans de prélèvement pour les loyers et les charges locatives se recoupe, d'une certaine manière, avec la prise en compte du loyer et des charges locatives dans le minimum vital. C'est vrai. La majorité vous propose de maintenir cette divergence et de trouver le cas échéant une solution de compromis avec le Conseil des États qui, lui, a adopté ce mécanisme pour les impôts qui, eux, ne sont pas pris en compte dans le minimum vital ; du moins pas encore aujourd'hui, car le travail est en cours. Cela nous permettrait d'avoir cette discussion avec le Conseil des États dans le cadre de l'élimination des divergences.
-La deuxième minorité concerne la question de la recherche des revenus. Nous vous invitons à soutenir la minorité Schmezer sur ce point. Le projet du Conseil fédéral était intelligent. Il disait qu'il fallait que les recherches de revenus soient manifestement insuffisantes pour que l'on puisse interrompre cette procédure d'assainissement. Le terme "manifestement" permettait d'illustrer le fait qu'on veut que cela saute aux yeux, que ce soit quelque chose de manifeste, pour éviter que l'on pousse les autorités à faire des espèces d'enquêtes sans fin. On ne peut pas exiger des autorités qu'elles viennent poser des caméras derrière chaque personne en procédure, qu'elles viennent mandater des détectives pour faire l'analyse des recherches de revenus. À l'image de ce qui se pratique dans d'autres domaines, on doit s'assurer, sur la base des informations transmises, qui peuvent être vérifiées, que les choses sont faites correctement, sans pour autant avoir des attentes démesurées de la part de l'autorité. Ces attentes, du reste, souvent, ne pourront pas être comblées. J'ai bon espoir, même si la minorité Schmezer n'est pas suivie par notre conseil aujourd'hui, que dans la pratique, les autorités resteront raisonnables et ne pratiqueront pas une espèce de contrôle bureaucratique absurde. Toutefois, nous pensons à ce stade qu'il serait préférable d'en rester au projet du Conseil fédéral.
-Enfin, je termine par la troisième proposition de minorité, qui concerne la fameuse question des gains extraordinaires. La question qui se pose est presque philosophique, et l'on comprend que certains dans cet hémicycle veuillent rattraper, après coup, quand la procédure est clôturée, des gains extraordinaires faits par les personnes concernées. C'est vrai que si l'on devient millionnaire du jour au lendemain et qu'on a bénéficié d'une procédure d'assainissement des dettes, il paraît juste de restituer ce patrimoine dans la procédure pour en faire profiter les créanciers. Cependant, toute la question concerne la durée. Jusqu'à quand peut-on mettre en place ce processus ? Indéfiniment, comme le propose la minorité II (Nantermod), paraît totalement déraisonnable. Ce serait impossible pour des raisons de preuve. 20 ans, c'est la proposition de compromis du Conseil des États. Nous aurions préféré 10 ans et nous proposons d'en rester à la variante de la minorité I (Schmezer) de 10 ans.
+    <t xml:space="preserve">Je commence par déclarer mes liens d'intérêt dans ce débat[NB]: je suis président de Dettes Conseil Suisse, la faîtière qui regroupe les centres qui font du conseil en matière de surendettement. Cela étant dit, j'aimerais exprimer ici ce soulagement, cette satisfaction de nous voir arriver au terme de ce processus. C'était un long débat et un projet important. Un certain nombre de décisions, parfois, ont été prises à une courte majorité, comme au Conseil des États lors de la dernière session, ma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je commence par déclarer mes liens d'intérêt dans ce débat[NB]: je suis président de Dettes Conseil Suisse, la faîtière qui regroupe les centres qui font du conseil en matière de surendettement. Cela étant dit, j'aimerais exprimer ici ce soulagement, cette satisfaction de nous voir arriver au terme de ce processus. C'était un long débat et un projet important. Un certain nombre de décisions, parfois, ont été prises à une courte majorité, comme au Conseil des États lors de la dernière session, mais le projet qui est maintenant sur notre table est équilibré, intelligent, et permettra - j'en suis sûr - à toute une série de personnes de sortir de cette spirale du surendettement, pour le bien de tous, y compris des créanciers, de la société dans son ensemble et des finances publiques, puisque la situation actuelle, avec des personnes qui restent dans cette spirale du surendettement, n'est dans l'intérêt de personne.
+Je reviens brièvement à ce stade des débats sur les trois minorités dont nous parlons encore aujourd'hui, à la suite de ce qu'ont précédemment dit mes collègues. D'abord, concernant la minorité Bregy, nous vous invitons à suivre la majorité de la commission sur ce point. Il s'agit de la question de savoir s'il doit y avoir une forme de privilège pour les loyers et les charges locatives pendant cette fameuse durée de prélèvement de trois ans, à l'image de ce que l'on fait pour les impôts. La réflexion de la majorité de la commission a été de se dire qu'il était important d'éviter des situations critiques dans lesquelles les loyers ne sont pas payés et dans lesquelles cela pourrait provoquer des expulsions, ce qui n'est dans l'intérêt de personne, puisqu'on se retrouverait ensuite avec des situations d'une grande complexité, à la fois au désavantage des personnes concernées, des locataires, mais aussi au désavantage des bailleurs, qui seraient mis dans une position très délicate. Je dois reconnaître qu'il y a un petit enjeu technique autour du fait que ce fameux privilège qui serait donné pendant ces trois ans de prélèvement pour les loyers et les charges locatives se recoupe, d'une certaine manière, avec la prise en compte du loyer et des charges locatives dans le minimum vital. C'est vrai. La majorité vous propose de maintenir cette divergence et de trouver le cas échéant une solution de compromis avec le Conseil des États qui, lui, a adopté ce mécanisme pour les impôts qui, eux, ne sont pas pris en compte dans le minimum vital[NB]; du moins pas encore aujourd'hui, car le travail est en cours. Cela nous permettrait d'avoir cette discussion avec le Conseil des États dans le cadre de l'élimination des divergences.
+La deuxième minorité concerne la question de la recherche des revenus. Nous vous invitons à soutenir la minorité Schmezer sur ce point. Le projet du Conseil fédéral était intelligent. Il disait qu'il fallait que les recherches de revenus soient manifestement insuffisantes pour que l'on puisse interrompre cette procédure d'assainissement. Le terme "manifestement" permettait d'illustrer le fait qu'on veut que cela saute aux yeux, que ce soit quelque chose de manifeste, pour éviter que l'on pousse les autorités à faire des espèces d'enquêtes sans fin. On ne peut pas exiger des autorités qu'elles viennent poser des caméras derrière chaque personne en procédure, qu'elles viennent mandater des détectives pour faire l'analyse des recherches de revenus. À l'image de ce qui se pratique dans d'autres domaines, on doit s'assurer, sur la base des informations transmises, qui peuvent être vérifiées, que les choses sont faites correctement, sans pour autant avoir des attentes démesurées de la part de l'autorité. Ces attentes, du reste, souvent, ne pourront pas être comblées. J'ai bon espoir, même si la minorité Schmezer n'est pas suivie par notre conseil aujourd'hui, que dans la pratique, les autorités resteront raisonnables et ne pratiqueront pas une espèce de contrôle bureaucratique absurde. Toutefois, nous pensons, à ce stade, qu'il serait préférable d'en rester au projet du Conseil fédéral.
+Enfin, je termine par la troisième proposition de minorité, qui concerne la fameuse question des gains extraordinaires. La question qui se pose est presque philosophique, et l'on comprend que certains dans cet hémicycle veuillent rattraper, après coup, quand la procédure est clôturée, des gains extraordinaires faits par les personnes concernées. C'est vrai que si l'on devient millionnaire du jour au lendemain et qu'on a bénéficié d'une procédure d'assainissement des dettes, il paraît juste de restituer ce patrimoine dans la procédure pour en faire profiter les créanciers. Cependant, toute la question concerne la durée. Jusqu'à quand peut-on mettre en place ce processus[NB]? Le faire indéfiniment, comme le propose la minorité II (Nantermod), paraît totalement déraisonnable. Ce serait impossible pour des raisons de preuve. vingt ans, c'est la proposition de compromis du Conseil des États. Nous aurions préféré dix ans et nous proposons d'en rester à la variante de dix ans de la minorité I (Schmezer).
 </t>
   </si>
   <si>
@@ -265,8 +265,8 @@
   <si>
     <t xml:space="preserve">La désinformation est le poison du XXIe siècle. Les "fake news", les théories du complot foisonnent sur les réseaux sociaux. Ces méthodes aussi nauséabondes que redoutables n'ont plus aucune limite. Elles cherchent aussi bien à fragiliser des États qu'à saper la confiance des citoyens à l'égard des institutions et de nos démocraties. Elles remettent en question les valeurs que nous avons héritées du siècle des Lumières.
 Bien sûr, la désinformation en tant qu'instrument d'influence a toujours existé. Toutefois, le développement des technologies numériques liées à l'intelligence artificielle a largement amplifié le phénomène. Il permet de conduire efficacement des campagnes de désinformation et de subversion, et ces dernières ont atteint un niveau inégalé dans l'histoire. Résultat : il est de plus en plus difficile de distinguer le vrai du faux. La désinformation peut aussi engendrer la violence. C'est ce qui s'est passé récemment en Angleterre, à la suite de l'attaque au couteau qui a coûté la vie à trois petites filles. Des émeutes ont éclaté sur fond de rumeurs en ligne selon lesquelles l'auteur était un requérant d'asile. Ce n'était pas le cas.
-Nos enfants sont aussi victimes de ces campagnes d'influence, parce que les extrémistes de tous bords cherchent les jeunes là où ils sont : sur les réseaux sociaux ou encore les plateformes de jeux. Bien sûr, ils se focalisent sur les plus influençables, sur les plus vulnérables. C'est un fait : la désinformation contribue à la montée de la radicalisation. C'est un phénomène bien connu par les services de renseignement, qui doit nous inquiéter.
-Partout dans le monde, le combat contre la désinformation est donc en train de s'organiser. Que fait la Suisse ? Elle est un peu à la traîne. Actuellement, il n'y a pas d'évaluation de l'ampleur de la menace ni de vraies stratégies pour sa gestion. Nous n'avons pas, à l'heure actuelle, les outils nécessaires pour lutter contre ces campagnes de déstabilisation. La coordination des divers organes de surveillance est insuffisante et les mesures d'anticipation pour nous en prémunir manquent dans une large mesure.
+Nos enfants sont aussi victimes de ces campagnes d'influence, parce que les extrémistes de tous bords cherchent les jeunes là où ils sont : sur les réseaux sociaux ou encore les plateformes de jeux. Bien sûr, ils se focalisent sur les plus influençables, sur les plus vulnérables. C'est un fait, la désinformation contribue à la montée de la radicalisation. C'est un phénomène bien connu par les services de renseignement, qui doit nous inquiéter.
+Partout dans le monde, le combat contre la désinformation est donc en train de s'organiser. Que fait la Suisse ? Elle est un peu à la traîne. Actuellement, il n'y a pas d'évaluation de l'ampleur de la menace ni de vraie stratégie pour sa gestion. Nous n'avons pas, à l'heure actuelle, les outils nécessaires pour lutter contre ces campagnes de déstabilisation. La coordination des divers organes de surveillance est insuffisante et les mesures d'anticipation pour nous en prémunir manquent dans une large mesure.
 Avec ma motion, je demande donc au Conseil fédéral de mettre en place une stratégie visant à combattre la désinformation. La Suisse se doit d'anticiper, afin de se prémunir contre les dégâts causés par la désinformation. Il est indispensable de se protéger contre ces zones de non-droit et de tous les dangers qui en découlent. L'avis du Conseil fédéral à ma motion ne m'a pas convaincue sur sa volonté d'agir. Même si le gouvernement prend au sérieux la menace et admet qu'il faut accorder davantage d'attention à cette problématique, il souhaite attendre un nouveau rapport et analyser encore la situation. Moi, je suis d'avis que nous n'avons plus le temps d'attendre, de tergiverser, d'attendre un énième rapport. Au vu de l'urgence de la situation, il m'apparaît que nous avons besoin de mesures efficaces que nous pouvons mettre en oeuvre rapidement. Pas demain, mais aujourd'hui.
 Chers collègues, l'utilisation de fausses informations est devenue une arme de la guerre hybride déjà en cours. Elle exige une réaction rapide et efficace. La réponse à ce nouveau risque est la mise en oeuvre d'une véritable stratégie qui non seulement garantit la libre formation de l'opinion publique, indispensable dans une démocratie comme la nôtre, mais protège aussi nos processus démocratiques et nos institutions. Merci de soutenir ma motion.
 </t>
@@ -301,18 +301,17 @@
     <t xml:space="preserve">375403</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich kann Ihnen klar sagen, dass sich der Bundesrat bewusst ist, dass in verschiedenen Grenzregionen die Situation als belastend wahrgenommen wird - obwohl, das sage ich als ehemalige Polizeidirektorin, die Kriminalität nicht gerade ennet der Grenze stattfindet, sondern entlang der Hauptrouten, beispielsweise auf der A1, wo man schnell hin- und wieder wegkommt. Ich kenne dieses Thema. Ich war mehrfach vor Ort und habe als Polizeidirektorin auch Nachtpatrouillen begleitet. Ich bin hier also etwas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ich kann Ihnen klar sagen, dass sich der Bundesrat bewusst ist, dass in verschiedenen Grenzregionen die Situation als belastend wahrgenommen wird - obwohl, das sage ich als ehemalige Polizeidirektorin, die Kriminalität nicht gerade ennet der Grenze stattfindet, sondern entlang der Hauptrouten, beispielsweise auf der A1, wo man schnell hin- und wieder wegkommt. Ich kenne dieses Thema. Ich war mehrfach vor Ort und habe als Polizeidirektorin auch Nachtpatrouillen begleitet. Ich bin hier also etwas erprobt - auch felderprobt, sozusagen.
-Frau Ständerätin Roth hat darauf hingewiesen, dass der Bundesrat bereit war, die Motionen der Staatspolitischen Kommission anzunehmen. In der Folge hat er diesen Massnahmenplan, diesen Aktionsplan unterbreitet, den Sie in der SiK beraten haben. In diesem Zusammenhang ist aber klar festzuhalten, dass für die Sicherheit auf dem Gebiet bis an die Grenze die Kantone zuständig sind. Sie tragen die Hauptverantwortung für die innere Sicherheit unseres Landes. Das BAZG leistet mit seinen Einsätzen und der Lagebeurteilung ergänzend dazu und dort, wo die Kantone diese Aufgaben teilweise an das BAZG delegiert haben - eine Mehrheit der Kantone hat ja Vereinbarungen mit dem BAZG abgeschlossen -, einen wichtigen Beitrag zur Bekämpfung von grenzüberschreitender Kriminalität und illegaler Migration sowie insgesamt zur Wahrung der inneren Sicherheit des Landes. Es ist an der Grenze sowie im Grenzraum präsent und kontrolliert im Rahmen seines Auftrags lage- und risikoabhängig den grenzüberschreitenden Waren- und Personenverkehr. Im Zwischengelände erfolgen die Kontrollen durch mobile Patrouillen des BAZG. Im Rahmen von Zollkontrollen oder bei Vorliegen eines polizeilichen Verdachts führt das BAZG auch Personenkontrollen durch, bei denen unter anderem die Einreise- und Aufenthaltsvoraussetzungen überprüft werden. Das BAZG arbeitet dabei eng mit den kantonalen Behörden zusammen, tauscht sich mit den Partnerbehörden regelmässig aus und führt gemeinsame Aktionen durch.
+    <t xml:space="preserve">Ich kann Ihnen klar sagen, dass sich der Bundesrat bewusst ist, dass in verschiedenen Grenzregionen die Situation als belastend wahrgenommen wird - obwohl, das sage ich als ehemalige Polizeidirektorin, die Kriminalität nicht gerade bei der Grenze stattfindet, sondern entlang der Hauptrouten, beispielsweise auf der A1, wo man schnell hin- und wieder wegkommt. Ich kenne dieses Thema. Ich war mehrfach vor Ort und habe als Polizeidirektorin auch Nachtpatrouillen begleitet. Ich bin hier also etwas er</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann Ihnen klar sagen, dass sich der Bundesrat bewusst ist, dass in verschiedenen Grenzregionen die Situation als belastend wahrgenommen wird - obwohl, das sage ich als ehemalige Polizeidirektorin, die Kriminalität nicht gerade bei der Grenze stattfindet, sondern entlang der Hauptrouten, beispielsweise auf der A1, wo man schnell hin- und wieder wegkommt. Ich kenne dieses Thema. Ich war mehrfach vor Ort und habe als Polizeidirektorin auch Nachtpatrouillen begleitet. Ich bin hier also etwas erprobt - auch felderprobt, sozusagen.
+Frau Ständerätin Roth hat darauf hingewiesen, dass der Bundesrat beantragte, die Motionen der Staatspolitischen Kommission anzunehmen. In der Folge hat er den Aktionsplan unterbreitet, den Sie in der SiK beraten haben. In diesem Zusammenhang ist aber klar festzuhalten, dass für die Sicherheit auf dem Gebiet bis an die Grenze die Kantone zuständig sind. Sie tragen die Hauptverantwortung für die innere Sicherheit unseres Landes. Das BAZG leistet mit seinen Einsätzen und der Lagebeurteilung, ergänzend dazu und dort, wo die Kantone diese Aufgaben teilweise an das BAZG delegiert haben - eine Mehrheit der Kantone hat ja Vereinbarungen mit dem BAZG abgeschlossen -, einen wichtigen Beitrag zur Bekämpfung von grenzüberschreitender Kriminalität und illegaler Migration sowie insgesamt zur Wahrung der inneren Sicherheit des Landes. Es ist an der Grenze sowie im Grenzraum präsent und kontrolliert im Rahmen seines Auftrags lage- und risikoabhängig den grenzüberschreitenden Waren- und Personenverkehr. Im Zwischengelände erfolgen die Kontrollen durch mobile Patrouillen des BAZG. Im Rahmen von Zollkontrollen oder bei Vorliegen eines polizeilichen Verdachts führt das BAZG auch Personenkontrollen durch, bei denen unter anderem die Einreise- und Aufenthaltsvoraussetzungen überprüft werden. Das BAZG arbeitet dabei eng mit den kantonalen Behörden zusammen, tauscht sich mit den Partnerbehörden regelmässig aus und führt gemeinsame Aktionen durch.
 Ich möchte an dieser Stelle das Ausländer- und Integrationsgesetz in Erinnerung rufen. Manchmal wird das quasi als Ausrede taxiert. Ich zitiere Artikel 9 über die Zuständigkeit für die Grenzkontrolle. Absatz 1: "Die Kantone üben auf ihrem Hoheitsgebiet die Personenkontrolle aus." Absatz 2: "Der Bundesrat regelt im Einvernehmen mit den Grenzkantonen die Personenkontrolle durch den Bund im Grenzraum." Das sind diese Vereinbarungen.
-Ich erinnere Sie an die Diskussion, die wir beim Zollgesetz hatten. Das Zollgesetz war damals unter anderem deshalb fast zurückgewiesen worden, weil man dem BAZG unterstellte, es wolle sich polizeiliche Kompetenzen aneignen. Als ich ins Finanzdepartement kam, war die Diskussion dazu im Rahmen des Zollgesetzes etwas "verkachelt". Ich habe dann alt Regierungsrat Hofmann gebeten, eine Arbeitsgruppe zu leiten, die sich mit den Kompetenzen der Kantone einerseits und den Kompetenzen des BAZG im Grenzraum andererseits auseinandersetzte. Das wurde dann im Zollgesetz festgehalten. Die Mitglieder der WAK können sich an diese Auseinandersetzung sicherlich erinnern.
-Ich sage das deshalb, weil man hier jetzt den Eindruck erweckt, das BAZG sei praktisch eine "Bundespolizei". Und das ist einfach nicht die Meinung.
-Das ist nicht die Meinung des Gesetzgebers, das ist auch nicht die Meinung der Kantone. Aber es ist so, dass man dem BAZG gerne immer mehr Aufgaben überträgt.
+Ich erinnere Sie an die Diskussion, die wir beim Zollgesetz hatten. Das Zollgesetz wurde damals unter anderem deshalb fast zurückgewiesen, weil man dem BAZG unterstellte, es wolle sich polizeiliche Kompetenzen aneignen. Als ich ins Finanzdepartement kam, war die Diskussion dazu im Rahmen des Zollgesetzes etwas "verkachelt". Ich habe dann alt Regierungsrat Urs Hofmann gebeten, eine Arbeitsgruppe zu leiten, die sich mit den Kompetenzen der Kantone einerseits und den Kompetenzen des BAZG im Grenzraum andererseits auseinandersetzte. Das Resultat wurde dann im Zollgesetz festgehalten. Die Mitglieder der WAK können sich an diese Auseinandersetzung sicherlich erinnern.
+Ich sage das deshalb, weil man hier jetzt den Eindruck erweckt, das BAZG sei praktisch eine "Bundespolizei". Und das ist einfach nicht die Meinung. Das ist nicht die Meinung des Gesetzgebers, das ist auch nicht die Meinung der Kantone. Aber es ist so, dass man dem BAZG gerne immer mehr Aufgaben überträgt.
 Nun, Sie haben den Aktionsplan gesehen. Daher sind wir der Meinung, dass diese beiden Motionen - Frau Roth hat es gesagt - eigentlich nicht mehr notwendig sind, denn es wurden schon zwei Motionen der SPK beider Räte überwiesen.
-Es wurde auch noch der Personalaufwand und -bestand erwähnt. Herr Ständerat Salzmann hat zu Recht gesagt, dass im Rahmen von Dazit, also im Rahmen der Digitalisierung, Einsparungen gemacht werden und dass man damals auch versprochen hatte, dass dann eine Verlagerung vom eigentlichen Zollgeschäft hin zum Grenzschutz stattfinden würde. Aber in der Zwischenzeit hat sich die Finanzlage etwas verändert, und wir haben in jedem Jahr Querschnittkürzungen durchgeführt. Diese Querschnittkürzungen haben halt auch Konsequenzen.
-Auch beim BAZG wurden wegen der Digitalisierung, aber auch wegen Einsparungen mehrere hundert Stellen abgebaut. Wenn man sich jetzt vorstellt, dass der Bund hier noch mehr tun muss, dann wird das irgendwann Konsequenzen haben. Dann müssen wir auch darüber sprechen, ob man den Grenzschutz vielleicht im Rahmen der Armeefinanzierung oder im Rahmen dieser Volksinitiative, die ja durchgehende Personenkontrollen verlangt, verstärken will oder nicht. Also: Wer A sagt, muss auch B sagen.
+Es wurde auch noch der Personalaufwand und -bestand erwähnt. Herr Ständerat Salzmann hat zu Recht gesagt, dass im Rahmen von Dazit, also im Rahmen der Digitalisierung, Einsparungen gemacht werden und dass man damals auch versprach, dass dann eine Verlagerung vom eigentlichen Zollgeschäft hin zum Grenzschutz stattfinden würde. Aber in der Zwischenzeit hat sich die Finanzlage etwas verändert, und wir haben in jedem Jahr Querschnittkürzungen durchgeführt. Diese Querschnittkürzungen haben halt auch Konsequenzen.
+Auch beim BAZG wurden wegen der Digitalisierung, aber auch wegen Einsparungen, mehrere hundert Stellen abgebaut. Wenn man sich jetzt vorstellt, dass der Bund hier noch mehr tun müsse, dann wird das irgendwann Konsequenzen haben. Dann müssen wir auch darüber sprechen, ob man den Grenzschutz vielleicht im Rahmen der Armeefinanzierung oder im Rahmen dieser Volksinitiative, die ja durchgehende Personenkontrollen verlangt, verstärken will oder nicht. Also: Wer A sagt, muss auch B sagen.
 Ich erinnere Sie aber auch daran, dass Sie in den Kommissionen für Wirtschaft und Abgaben ebenfalls einen Personaldeckel diskutieren, und auch das hat natürlich Konsequenzen. Es gibt dann immer Aufgaben, die eine saisonale Konjunktur haben - diese findet man gut. Andere Aufgaben findet man nicht so gut, und je nachdem entscheidet man.
 Ich bitte Sie, hier der Minderheit Roth Franziska zu folgen.
 [VS]
@@ -331,15 +330,16 @@
     <t xml:space="preserve">AG</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich vertrete einen Grenzkanton, und das Interesse an verstärkten Grenzkontrollen an unserer sehr langen Grenze zu Deutschland ist bei uns gross. Das drückte auch eine Standesinitiative aus meinem Kanton aus; der Berichterstatter hat es mehrmals erwähnt.
-Natürlich besteht ein Zielkonflikt. Verstärkte Grenzkontrollen, um illegale Migration und grenzüberschreitende Kriminalität zu bekämpfen, können dazu führen, dass der Warenverkehr und der Personenverkehr ins Stocken geraten. Wie schafft man es, d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ich vertrete einen Grenzkanton, und das Interesse an verstärkten Grenzkontrollen an unserer sehr langen Grenze zu Deutschland ist bei uns gross. Das drückte auch eine Standesinitiative aus meinem Kanton aus; der Berichterstatter hat es mehrmals erwähnt.
-Natürlich besteht ein Zielkonflikt. Verstärkte Grenzkontrollen, um illegale Migration und grenzüberschreitende Kriminalität zu bekämpfen, können dazu führen, dass der Warenverkehr und der Personenverkehr ins Stocken geraten. Wie schafft man es, dass die beiden Ziele nicht in einen Konflikt geraten? Indem man verstärkt Ressourcen einsetzt - technische Hilfsmittel, mehr Personal -, indem man die Kooperation zwischen den zuständigen kantonalen Behörden und den Bundesbehörden verstärkt, und vor allem, indem man die internationale Zusammenarbeit verstärkt.
-Ich sage es Ihnen in diesem und auch in einem grösseren Zusammenhang klar und offen: Mein Kanton ist auf die internationale Zusammenarbeit angewiesen, notabene vor allem auf die Zusammenarbeit mit Deutschland. Wir leben in eskalativen Zeiten. Die äussere, aber auch die innere Sicherheit sind bedroht. Die neuesten Exzesse zeigen auf, dass wir handeln müssen. Man kann es drehen und wenden, wie man will: So dringend, wie die Armee auf Mittel für die Wiederherstellung der Verteidigungsfähigkeit angewiesen ist, sind auch unsere Kräfte im Bereich der Grenzsicherheit auf eine Verstärkung angewiesen. Auch diese benötigen die entsprechenden Mittel und die entsprechende Sensibilisierung.
-Frau Kollegin Franziska Roth, das ist nicht einfach Symbolpolitik. Ich kann Ihnen das als Vertreterin dieses Grenzkantons sagen. Und ja, Frau Kollegin Roth, auch ich bin der Meinung, dass man nicht ausgerechnet diesen Behörden die Mittel kürzen kann. Aber gerade deshalb ist es ein falsches Zeichen, diese Vorstösse abzulehnen.
-Ich bitte Sie, diesen Vorstössen zuzustimmen. Wer heute dafür stimmt, verpflichtet sich indirekt ebenfalls, die entsprechenden Mittel nicht zu kürzen, und verpflichtet sich im Grundsatz auch auf internationale Zusammenarbeit; auch diese ist ja ein Mittel für bessere Kontrollen. Ansonsten bringt man sich in einen Widerspruch und kann schlecht schlafen, und genau das wollen Sie ja nicht. Ich danke Ihnen also für die Zustimmung mit der entsprechenden Verpflichtung.
+    <t xml:space="preserve">Ich vertrete einen Grenzkanton. Das Interesse an verstärkten Grenzkontrollen an unserer sehr langen Grenze zu Deutschland ist bei uns gross. Das drückte auch eine Standesinitiative aus meinem Kanton aus; der Berichterstatter hat es mehrmals erwähnt.
+Natürlich besteht ein Zielkonflikt. Verstärkte Grenzkontrollen, um illegale Migration und grenzüberschreitende Kriminalität zu bekämpfen, können dazu führen, dass der Warenverkehr und der Personenverkehr ins Stocken geraten. Wie schafft man es, dafür</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich vertrete einen Grenzkanton. Das Interesse an verstärkten Grenzkontrollen an unserer sehr langen Grenze zu Deutschland ist bei uns gross. Das drückte auch eine Standesinitiative aus meinem Kanton aus; der Berichterstatter hat es mehrmals erwähnt.
+Natürlich besteht ein Zielkonflikt. Verstärkte Grenzkontrollen, um illegale Migration und grenzüberschreitende Kriminalität zu bekämpfen, können dazu führen, dass der Warenverkehr und der Personenverkehr ins Stocken geraten. Wie schafft man es, dafür zu sorgen, dass die beiden Ziele nicht in einen Konflikt geraten? Indem man verstärkt Ressourcen einsetzt - technische Hilfsmittel, mehr Personal -, indem man die Kooperation zwischen den zuständigen kantonalen Behörden und den Bundesbehörden verstärkt und vor allem, indem man die internationale Zusammenarbeit verstärkt.
+Ich sage es Ihnen in diesem und auch in einem grösseren Zusammenhang klar und offen: Mein Kanton ist auf die internationale Zusammenarbeit angewiesen, notabene vor allem auf die Zusammenarbeit mit Deutschland. Wir leben in eskalativen Zeiten. Die äussere, aber auch die innere Sicherheit ist bedroht. Die neuesten Exzesse zeigen auf, dass wir handeln müssen. Man kann es drehen und wenden, wie man will: So dringend, wie die Armee auf Mittel für die Wiederherstellung der Verteidigungsfähigkeit angewiesen ist, sind auch unsere Kräfte im Bereich der Grenzsicherheit auf eine Verstärkung angewiesen. Auch diese benötigen die entsprechenden Mittel und die entsprechende Sensibilisierung.
+Frau Kollegin Franziska Roth, das ist nicht einfach Symbolpolitik. Ich kann Ihnen das als Vertreterin dieses Grenzkantons sagen. Und ja, Frau Kollegin Roth, auch ich bin der Meinung, dass man nicht ausgerechnet diesen Behörden die Mittel kürzen soll. Aber gerade deshalb ist es ein falsches Zeichen, diese Vorstösse abzulehnen.
+Ich bitte Sie, diesen Vorstössen zuzustimmen. Wer heute dafür stimmt, verpflichtet sich indirekt ebenfalls, die entsprechenden Mittel nicht zu kürzen, und verpflichtet sich im Grundsatz auch auf internationale Zusammenarbeit; auch diese ist ja ein Mittel für bessere Kontrollen. Ansonsten bringt man sich in einen Widerspruch und kann schlecht schlafen, und genau das wollen Sie ja nicht.
+Ich danke Ihnen also für die Zustimmung mit der entsprechenden Verpflichtung.
 </t>
   </si>
   <si>
@@ -693,18 +693,113 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.
-Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.
-Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schubert-Praxis. Das sind inhaltliche Elemente, mit denen sie begründet, dass sie sich zumindest als gleich oder gar stärker zuständig sieht.
-Ich widerspreche auch der Auffassung, die SPK-S habe einen Fehler gemacht; einen solchen Vorwurf hat im Übrigen sonst niemand erhoben. Weder die APK-S noch das Büro des Ständerates haben je festgehalten, wir hätten einen Fehler gemacht. Zudem haben wir die parlamentarische Initiative der Schwesterkommission inzwischen erhalten, und niemand hat infrage gestellt, dass wir darüber abstimmen dürfen. Es scheint mir daher einhellig, dass die SPK-S zuständig ist, auch im Hinblick auf die Migrations- und Referendumsfragen. Zwar bestehen Berührungs- bzw. Überschneidungspunkte, doch den Vorwurf eines Fehlers weise ich zurück.
-Frau Wasserfallen hat von einem möglichen groben Foul gesprochen. Am Tag der WM-Eröffnung würde ich den Ball eher flach halten, zumal es sich hier um Zustimmungsentscheide dazu handelt, ob ein Vorstoss ausgearbeitet werden darf. Am Ende gelangen die Geschäfte ohnehin in die Räte, und jeder Rat kann ein Geschäft ablehnen; entscheidend ist lediglich, wer die Ausarbeitung vornimmt.
-Mit Kollege Sommaruga sehe ich im Übrigen keine Differenz. Sie haben zwar gesagt, wir hätten die APK-S kritisiert, doch das war keineswegs beabsichtigt. Ich habe den Mitbericht der APK-S ausführlich gewürdigt, und selbstverständlich stand er Ihnen zur Verfügung. Er war rein inhaltlicher Natur und hat nie bestritten, dass die SPK-S handeln darf; die APK-S hat schlicht mit 8 zu 5 Stimmen eine andere Meinung vertreten, was ihr gutes Recht ist. Ebenso wenig haben wir die APK-S umgangen: Wir haben am 5. Mai unseren Entscheid getroffen, und am 22. Mai folgte der Mitbericht der APK-S. Somit hat niemand jemanden umgangen; wir haben eine parlamentarische Initiative lanciert, und die APK-S hat dazu einen Mitbericht verfasst. Das ist im Grunde Courant normal.
-Herr Würth hat Martin Graf erwähnt, den ich sehr schätze, was sich schon daran zeigt, dass ich dieses rote Buch hier in der Hand halte. In diesem Fall habe ich mich jedoch nicht nur auf Martin Graf gestützt, sondern auch die Parlamentsdienste konsultiert. Diese vertreten eine andere, konsolidierte Auffassung, was den Spruch "zwei Juristen, drei Meinungen" bestätigt, auch wenn Martin Graf Historiker ist. Klar zurückweisen muss ich jedoch die Aussage, das Büro des Ständerates habe festgehalten, man müsse dem Nationalrat folgen oder dieser sei zuständig. Im Schreiben des Büros des Ständerates an das Büro des Nationalrates heisst es ausdrücklich: "Das Büro des Ständerates erachtet es nicht als seine Aufgabe, sich zur Frage der Zuständigkeit der nationalrätlichen Kommission zu äussern. Es ist Sache der SPK-S, im Bewusstsein unterschiedlicher Haltungen zweier Kommissionen des Nationalrates, über das weitere Vorgehen zu entscheiden." Daraus ergibt sich gerade keine Zuständigkeitszuweisung an den Nationalrat.
-Ein vorletzter Punkt zum Stichwort Fairplay im Parlament, gerichtet an Kollege Broulis: Sie haben das Stimmverhalten des Präsidenten angesprochen. Dies entspricht nicht unserer Praxis; ich sage dies zur Verteidigung eines Kommissionsmitgliedes und des Präsidenten.
-Abschliessend: Wir haben eine parlamentarische Initiative der Schwesterkommission, der SPK-N, vor uns. Die SPK-S könnte jederzeit darüber entscheiden und ihr aufgrund der Mehrheitsverhältnisse wohl auch zustimmen, wir haben dies bisher lediglich nicht getan. Niemand hat je bestritten, dass die SPK-N diese Initiative einreichen darf oder dass wir ihr zustimmen könnten. Gedanklich weitergeführt könnte die SPK-S kurz nach einem negativen Entscheid hier tagen, der Initiative zustimmen und die Arbeiten würden - wie von der SPK-S gewünscht - weitergeführt, allerdings im anderen Rat, bei der SPK-N. Eine Rückholung erscheint kaum möglich. Das Geschäft würde somit ausgearbeitet in die Räte gelangen, jedoch zeitlich verzögert, sodass eine gleichzeitige Behandlung nicht möglich wäre. Dies noch als letzter Hinweis.
+    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schuber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Berichterstatter möchte ich zum Abschluss kurz auf einige Voten eingehen bzw. darauf replizieren.Kollege Jositsch hat die Frage des Sachbereiches der verschiedenen Kommissionen aufgeworfen. Seinem Panzerbeispiel würde ich zustimmen, doch befinden wir uns hier nicht in einer solchen Konstellation. Die SPK-N hat in ihrem Schreiben dargelegt, weshalb sie sich als zuständig erachtet, etwa mit Verweis auf die Migration gemäss Artikel 121a BV, das Referendum gemäss Artikel 140 BV sowie die Schubert-Praxis. Das sind inhaltliche Elemente, mit denen sie begründet, dass sie sich zumindest als gleich oder gar stärker zuständig sieht.Ich widerspreche auch der Auffassung, die SPK-S habe einen Fehler gemacht; einen solchen Vorwurf hat im Übrigen sonst niemand erhoben. Weder die APK-S noch das Büro des Ständerates haben je festgehalten, wir hätten einen Fehler gemacht. Zudem haben wir die parlamentarische Initiative der Schwesterkommission inzwischen erhalten, und niemand hat infrage gestellt, dass wir darüber abstimmen dürfen. Es scheint mir daher einhellig, dass die SPK-S zuständig ist, auch im Hinblick auf die Migrations- und Referendumsfragen. Zwar bestehen Berührungs- bzw. Überschneidungspunkte, doch den Vorwurf eines Fehlers weise ich zurück.Frau Wasserfallen hat von einem möglichen groben Foul gesprochen. Am Tag der WM-Eröffnung würde ich den Ball eher flach halten, zumal es sich hier um Zustimmungsentscheide dazu handelt, ob ein Vorstoss ausgearbeitet werden darf. Am Ende gelangen die Geschäfte ohnehin in die Räte, und jeder Rat kann ein Geschäft ablehnen; entscheidend ist lediglich, wer die Ausarbeitung vornimmt.Mit Kollege Sommaruga sehe ich im Übrigen keine Differenz. Sie haben zwar gesagt, wir hätten die APK-S kritisiert, doch das war keineswegs beabsichtigt. Ich habe den Mitbericht der APK-S ausführlich gewürdigt, und dies stand Ihnen selbstverständlich zu. Er war rein inhaltlicher Natur und hat nie bestritten, dass die SPK-S handeln darf; die APK-S hat schlicht mit 8 zu 5 Stimmen eine andere Meinung vertreten, was ihr gutes Recht ist. Ebenso wenig haben wir die APK-S umgangen: Wir haben am 5. Mai unseren Entscheid getroffen, und am 22. Mai folgte der Mitbericht der APK-S. Somit hat niemand jemanden umgangen; wir haben eine parlamentarische Initiative lanciert, und die APK-S hat dazu einen Mitbericht verfasst. Das ist im Grunde Courant normal.Herr Würth hat Martin Graf erwähnt, den ich sehr schätze, was Sie schon sehen, wenn sie das rote Buch anschauen. In diesem Fall habe ich mich jedoch nicht nur auf Martin Graf gestützt, sondern auch die Parlamentsdienste konsultiert. Diese vertreten eine andere, konsolidierte Auffassung, was den Spruch "zwei Juristen, drei Meinungen" bestätigt, auch wenn Martin Graf Historiker ist. Klar zurückweisen muss ich jedoch die Aussage, das Büro des Ständerates habe festgehalten, man müsse dem Nationalrat folgen oder dieser sei zuständig. Im Schreiben des Büros des Ständerates an das Büro des Nationalrates heisst es wörtlich: "Das Büro des Ständerates erachtet es nicht als seine Aufgabe, sich zur Frage der Zuständigkeit der nationalrätlichen Kommission zu äussern. Es ist Sache der SPK-S, im Bewusstsein unterschiedlicher Haltungen zweier Kommissionen des Nationalrates, über das weitere Vorgehen zu entscheiden." Daraus ergibt sich gerade keine Zuständigkeitszuweisung an den Nationalrat.Ein vorletzter Punkt zum Stichwort Fairplay im Parlament, gerichtet an Kollege Broulis: Sie haben das Stimmverhalten des Präsidenten angesprochen. Dies entspricht nicht unseren Regeln; ich sage dies zur Verteidigung eines Kommissionsmitgliedes und des Präsidenten.Abschliessend: Wir haben eine parlamentarische Initiative der Schwesterkommission, der SPK-N, vor uns. Die SPK-S könnte jederzeit darüber entscheiden und ihr aufgrund der Mehrheitsverhältnisse wohl auch zustimmen, wir haben dies bisher lediglich nicht getan. Niemand hat je bestritten, dass die SPK-N diese Initiative einreichen darf oder dass wir ihr zustimmen könnten. Gedanklich weitergeführt könnte die SPK-S kurz nach einem negativen Entscheid hier tagen, der Initiative zustimmen und die Arbeiten würden - wie von der SPK-S gewünscht - weitergeführt, allerdings im anderen Rat, bei der SPK-N. Eine Rückholung erscheint kaum möglich. Das Geschäft würde somit ausgearbeitet in die Räte gelangen, jedoch zeitlich verzögert, sodass eine gleichzeitige Behandlung nicht möglich wäre. Dies noch als letzter Hinweis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzog Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Staatsrechnung 2025 des Bundes schliesst mit einem Finanzierungsüberschuss von 259 Millionen Franken. Sie fällt damit deutlich besser aus als erwartet; veranschlagt war ein Defizit von 815 Millionen Franken. Der negative ausserordentliche Finanzierungssaldo von 926 Millionen Franken wurde durch den positiven ordentlichen Finanzierungssaldo von 1,185 Milliarden Franken mehr als ausgeglichen. Dies ist vor allem auf temporär höhere Gewinnsteuereinnahmen aus dem Kanton Genf im Umfang von 1,5 Mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Staatsrechnung 2025 des Bundes schliesst mit einem Finanzierungsüberschuss von 259 Millionen Franken. Sie fällt damit deutlich besser aus als erwartet; veranschlagt war ein Defizit von 815 Millionen Franken. Der negative ausserordentliche Finanzierungssaldo von 926 Millionen Franken wurde durch den positiven ordentlichen Finanzierungssaldo von 1,185 Milliarden Franken mehr als ausgeglichen. Dies ist vor allem auf temporär höhere Gewinnsteuereinnahmen aus dem Kanton Genf im Umfang von 1,5 Milliarden Franken zurückzuführen. 
+Die ordentlichen Einnahmen fielen insgesamt um 1,9 Milliarden Franken bzw. 2,2 Prozent höher aus als budgetiert und um 3,3 Milliarden Franken höher als im Vorjahr. Zugleich lagen die ordentlichen Ausgaben des Bundes 2025 erstmals seit der Einführung der Schuldenbremse im Jahr 2003 über dem Budgetwert. Dies ist unter anderem auf den Nachtragskredit für Horizon Europe zurückzuführen. Der ordentliche Finanzierungssaldo war positiv. Aus der Differenz ergibt sich ein struktureller Überschuss von 1,4 Milliarden Franken. In diesem Umfang war der ordentliche Finanzierungssaldo höher als von der Schuldenbremse vorgegeben. 
+Nennenswert sind im ausserordentlichen Haushalt die Mehreinnahmen aus der Zusatzausschüttung der Schweizerischen Nationalbank von 333 Millionen Franken und die budgetierte Sonderzuweisung der SNB aus den nicht ausgetauschten Banknoten der sechsten Serie von 237 Millionen Franken. Die beiden grössten Posten auf der Ausgabenseite sind die ausserordentlichen Ausgaben für die Schutzsuchenden aus der Ukraine sowie der einmalige Kapitalzuschuss an die SBB von 850 Millionen Franken, die ursprünglich für 2024 budgetiert waren.
+Weitere wichtige Kennzahlen: Erstmals seit der Corona-Pandemie konnte der Fehlbetrag des Amortisationskontos um 500 Millionen Franken reduziert werden. Neu beläuft sich der Fehlbetrag auf 26,3 Milliarden Franken. Das Ausgleichskonto hat unverändert einen positiven Stand von rund 20 Milliarden Franken. Die Nettoverschuldung hat 2025 leicht abgenommen und beträgt neu 140,1 Milliarden Franken. Die Nettoschuldenquote ging ebenfalls zurück, und zwar auf 16,1 Prozent des BIP. 
+Die Finanzkommission erhielt an ihrer Sitzung vom 26. Februar 2026 erste Informationen zum Ergebnis der Staatsrechnung. Anschliessend tagten die Subkommissionen. An der Sitzung vom 18. Mai 2026 hat die Finanzkommission die Rechnung 2025 und den Nachtrag I zum Voranschlag 2026 beraten. Im Gegensatz zur Einnahmenseite gab es auf der Ausgabenseite keine ausserordentlichen Vorkommnisse. Die Departemente sind daran, die beschlossenen Sparmassnahmen umzusetzen. Die Kommission hat zur Kenntnis genommen, dass die Digitalisierung allgemein vorangeht, aber nicht so schnell wie gewünscht, was auch an den Budgetkürzungen seitens des Parlamentes liegt. Weiter wurde berichtet, dass die erstinstanzlich hängigen Asylgesuche rückläufig sind. Ein Abbau der Gesuche war möglich, die Zahlen beim Bundesverwaltungsgericht sind aber weiter angestiegen. Die Verfahrensdauer ist nach wie vor weit weg von der ursprünglichen Zielsetzung im Rahmen der letzten Asylreform.
+Berichtet wurde über die ersten Gespräche mit dem neuen Leiter des Nachrichtendienstes des Bundes und über die höheren Ausgaben beim NDB.
+Thematisiert wurden ebenfalls die Probleme mit dem neuen Auszahlungssystem der Arbeitslosenkasse, Asalfutur. Die Kommission wurde darüber informiert, dass auf Ende März die Rückstände aufgeholt und alles ausbezahlt worden sei.
+Angesprochen wurde auch die Thematik, dass der Kapitalbezug der zweiten Säule nicht in den nationalen Finanzausgleich integriert ist. Die FK-S wird das Thema weiterverfolgen. 
+Informationen hat die Kommission auch erbeten bezüglich der Verhandlungen über die neue Vereinbarung mit der Schweizerischen Nationalbank. Auslöser waren die Aussagen des SNB-Präsidenten von Ende April in den Medien. Er sagte, dass für die SNB eine Eigenkapitalquote von 15 bis 20 Prozent zu tief sei. Aktuell sind es 19 Prozent. Eine Erhöhung würde bedeuten, dass statt einer Verbesserung sogar eine Verschlechterung gegenüber der heutigen Ausschüttungsvereinbarung drohen könnte, was in der Kommission kritisch gesehen wurde. Die Eidgenössische Finanzverwaltung erläuterte der Kommission die Rückstellungspolitik der SNB und bestätigte, dass sich die SNB eine Eigenkapitalquote zwischen 20 und 30 Prozent vorstelle, während andere Zentralbanken viel tiefere Werte hätten; so hätten beispielsweise die Fed oder die Bank of England eine Eigenkapitalquote von 1 Prozent, in Australien und Schweden sei das Eigenkapital negativ, in Singapur liege die Eigenkapitalquote bei 10 Prozent. Wenn die SNB mit ihrer Rückstellungspolitik tatsächlich dieses Ziel verfolge, müssten sich Bund und Kantone keine Hoffnungen auf höhere Ausschüttungen machen. Die Kommission wird das Thema weiterverfolgen, im Wissen, dass die Entscheide beim Bankrat angesiedelt sind. 
+Die Finanzministerin gab der Kommission auch einen Ausblick auf den Voranschlag 2027 und die kommenden Jahre.
+Nach Verabschiedung des EP 27 in beiden Räten ging der Bundesrat am 15. April noch von einem strukturellen Finanzierungsdefizit von 600 Millionen Franken aus und schlug erste mögliche Massnahmen zu dessen Bereinigung vor. An der Sitzung der FK-S vom 18. Mai konnte Bundesrätin Karin Keller-Sutter Entwarnung geben für den Voranschlag 2027, obwohl das Finanzdepartement für 2027 nochmals mit einer Verschlechterung um voraussichtlich rund 400 Millionen Franken rechnet, insbesondere aufgrund von Schätzkorrekturen bei den Sozialversicherungen und der Migration. Grund dafür sind deutliche Verbesserungen bei der Gewinnsteuer für juristische Personen, auch in anderen Kantonen als Genf. Zwar wies die Finanzministerin darauf hin, dass sich dieses ausserordentliche Wachstum auf einige wenige Unternehmen konzentriere. Sie sagte aber auch, dass die positive Entwicklung der Gewinnsteuern über diese Effekte hinaus breit abgestützt sei. Eine Mehrheit der Kantone habe Anfang Mai gemeldet, dass sie höhere Gewinnsteuereinnahmen hätten.
+Die Mehreinnahmen aus Genf waren hier ja schon mehrfach ein Thema, deshalb lediglich noch ein Wort zu ihrer Verbuchung. Die Eidgenössische Finanzkontrolle (EFK) hat verlangt, dass 1,5 Milliarden Franken schon im Jahr 2025 verbucht werden, ich habe diese eingangs erwähnt. 2026 sind es dann 1,3 Milliarden und 2027 noch 400 Millionen Franken. Es wäre auch denkbar gewesen, die Einnahmen über die Jahre zu glätten und kommende Budgets zu entlasten, doch die EFK bot nicht Hand dazu. So warnte die Finanzministerin auch bereits davor, dass die Lage angesichts der weiterhin bestehenden Herausforderungen, insbesondere bei der Armeefinanzierung und der AHV, ab 2028 wieder schwierig werden dürfte.
+Wenn keine zusätzlichen Einnahmen erschlossen werden könnten, würden ab 2028 beträchtliche strukturelle Defizite drohen. Ein Drittel der vom Bundesrat vorgesehenen Erhöhung der Mehrwertsteuer von 0,8 Prozent soll allein das bereits beschlossene Wachstum der Armee finanzieren, also den Aufwuchs auf 1 Prozent des BIP bis 2032. Der Bundesrat wird die Botschaft zur Armeefinanzierung nach der Sommerpause verabschieden. Neben der federführenden SiK wird sich auch die Finanzkommission in einem Mitbericht mit dem Geschäft befassen.
+Die Kommission tagte stets in Anwesenheit von Bundesrätin Karin Keller-Sutter und der Direktorin der Eidgenössischen Finanzverwaltung Sabine D'Amelio-Favez sowie weiteren Mitarbeiterinnen und Mitarbeitern des EFD, und sie tagte teilweise in Anwesenheit des Leiters der Finanzkontrolle Pascal Stirnimann und der zuständigen Mitarbeiterin. Ich danke den Beteiligten für ihre Begleitung unserer Diskussionen und für die guten Auskünfte.
+Nach Kenntnisnahme der Revisionsberichte der Eidgenössischen Finanzkontrolle sowie der Erwägungen und Schlussfolgerungen der Subkommissionen der FK-S beantragt die Kommission einstimmig, die Staatsrechnung 2025, die Sonderrechnungen für den Bahninfrastrukturfonds sowie den Nationalstrassen- und Agglomerationsverkehrsfonds, die Kreditüberschreitungen von 1,86 Milliarden Franken und die Bildung neuer Reserven in Höhe von 569 Millionen Franken zu genehmigen. Zum Schluss geht mein Dank an das Sekretariat der Finanzkommission für die umsichtige Vorbereitung, Organisation und Begleitung der Sitzungen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bedanke mich herzlich bei der Finanzkommission Ihres Rates für die Arbeit, für die Prüfung der Rechnung in den Subkommissionen und auch für die Berichterstattung durch Ihre Präsidentin, Ständerätin Eva Herzog. Ich werde mich auf die wichtigsten Punkte konzentrieren, gerne Herrn Hurni eine Antwort geben und auch einen Ausblick auf die nächsten Jahre machen. 
+Die Staatsrechnung 2025 schliesst erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bedanke mich herzlich bei der Finanzkommission Ihres Rates für die Arbeit, für die Prüfung der Rechnung in den Subkommissionen und auch für die Berichterstattung durch Ihre Präsidentin, Ständerätin Eva Herzog. Ich werde mich auf die wichtigsten Punkte konzentrieren, gerne Herrn Hurni eine Antwort geben und auch einen Ausblick auf die nächsten Jahre machen. 
+Die Staatsrechnung 2025 schliesst erstmals seit 2019 mit einem Finanzierungsüberschuss ab. Der Überschuss beläuft sich auf 259 Millionen Franken. Man muss das in Relation zu einem Budget von 86,7 Milliarden Franken setzen.
+Heureusement, la clôture était meilleure que prévu. Mais lorsque l'on dit que les estimations tombent à côté, il faut dire que l'écart des estimations, en moyenne, ces 10 dernières années, était de 0,3 pour cent - ce n'est pas beaucoup. Il faut aussi considérer la grandeur des chiffres.
+Zu unterscheiden gilt es auch zwischen dem ordentlichen und dem ausserordentlichen Haushalt. Im ordentlichen Haushalt verzeichnete der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt.
+Die ordentlichen Einnahmen schlossen 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Gewinnsteuereinnahmen, die mit 1,4 Milliarden Franken über dem Budget lagen. Diese Entwicklung ist auf die bereits bekannten temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Der Kanton Genf hat hier alleine 1,5 Milliarden Franken beigetragen. Auch ohne den Effekt Genf haben sich die Gewinnsteuereinnahmen positiv entwickelt, wobei sie ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären.
+Nachdem in der Berichterstattung in den Medien bezüglich dieser Mehreinnahmen aus Genf etwas Verwirrung gestiftet wurde, möchte ich das noch einmal erklären und präzisieren. Ich verweise auch auf die Staatsrechnung, Band IA, Seite 40. Sie können sich erinnern: Im letzten Frühjahr erhielten wir die Meldung aus Genf, dass für die Rechnung 2025 Mehrerträge von etwa 500 Millionen Franken aus den Jahren 2022 und 2023 anfallen werden. Diese Mehrerträge gehen massgeblich auf den Rohstoffhandel zurück. Dann gab es eine weitere Meldung - sie traf just am Tag ein, als die Finanzkommission des Ständerates ihre Beratung aufnahm: Es würden noch einmal Mehreinnahmen aus Genf im Umfang von etwa einer Milliarde Franken kommen. Der Grund dafür war, dass der Kanton Genf während der ziemlich langen Periode zwischen 2019 und 2024 keine provisorischen Rechnungen ausgestellt hatte. Die Einnahmenschätzungen des Bundes basieren auf den provisorischen Gewinnsteuerrechnungen der Kantone. Ohne provisorische Rechnungen weiss man auch nicht, welche Erträge kommen.
+Wenn also in den Medien stand, alle zusätzlichen Einnahmen seien auf den Rohstoffhandel zurückzuführen, ist das nicht korrekt. Ein Teil war wirklich auf diesen Informatikfehler der Genfer zurückzuführen; wir konnten das auch nicht antizipieren.
+Wenn man auf die Ausgaben schaut, dann muss man sagen, dass die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget lagen. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden relativ tief ausfielen. Die Kreditreste sind aufgrund der Kürzungen, die wir in den Budgets 2024 und 2025 vorgenommen hatten, sowieso viel tiefer. Im ausserordentlichen Haushalt hingegen waren die Ausgaben höher als die Einnahmen. Hier verzeichneten wir ein Defizit von rund 900 Millionen Franken. Die beiden grössten ausserordentlichen Ausgaben waren diejenige für die Schutzsuchenden aus der Ukraine - das waren 700 Millionen Franken von total 1,5 Milliarden an ausserordentlichen Ausgaben - sowie der einmalige Kapitalzuschuss an die SBB in Höhe von 850 Millionen. Die Tatsache, dass diese 850 Millionen Franken erst im Jahr 2025 ausbezahlt wurden, war der Grund für die Rechnungsverbesserung im Jahr 2024.
+Vous vous souvenez que nous avions prévu de verser 1 milliard de francs aux CFF en 2024. Le Parlement n'était pas tout à fait prêt ; par la suite, le Parlement a réduit la somme. Cette somme réduite - soit 850 millions de francs - a été versée en 2025 seulement.
+Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich zum Abbau der Covid-Schulden verbucht. Das ist so vorgesehen. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
+Ich komme nun zum Ausblick. Wie üblich wird der Bundesrat Ende Juni die Zahlen zum Voranschlag 2027 und dann auch die Zahlen zum Finanzplan 2028 bis 2030 festlegen. Die Arbeiten hierzu laufen noch. Wie bereits den Nationalrat möchte ich auch Sie an dieser Stelle über den Zwischenstand dieser Arbeiten informieren. Dieser Zwischenstand stützt sich primär auf die erfolgten Budgeteingaben der Departemente und auf die seit April aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge für die Schätzung im wichtigen Monat April gemeldet haben. Der Zwischenstand stützt sich also auf die provisorischen Steuerrechnungen; diese liegen jeweils Ende April vor.
+Demnach dürfte sich im Vergleich zur Standortbestimmung im April auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich rund 300 Millionen Franken ergeben. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer für juristische Personen eine deutliche Verbesserung ab, und dies unabhängig vom Effekt Genf, den wir bereits kannten und den wir entsprechend eingepreist haben. Sie können sich erinnern: Wir haben einen Teil für 2026 budgetiert.
+Das starke Einnahmenwachstum zeigt sich in unterschiedlichem Ausmass in zahlreichen Kantonen. Aber es sind vor allem drei Kantone, die dieses Wachstum befördern, nämlich die Kantone Luzern, Zürich und Basel-Stadt. Dieses hohe Wachstum konzentriert sich in diesen Kantonen wiederum auf einige Unternehmen, nicht zuletzt aus der Pharmabranche.
+Weil ein paar wenige Unternehmen ein so starkes Gewicht haben, bestehen weiterhin grosse Unsicherheiten. Es ist grundsätzlich sehr viel Volatilität im System, und es ist nicht in jedem Fall klar, wie nachhaltig die höheren Steuererträge im Einzelfall sind. Zudem basiert die Schätzung der Gewinnsteuer zu diesem Zeitpunkt, ich habe es erwähnt, jeweils auf den provisorischen Steuerrechnungen der Kantone. 
+Ein weiterer Unsicherheitsfaktor ist auch die OECD-Ergänzungssteuer. Wir können frühestens im Herbst, im September, mit ersten verlässlichen Zahlen rechnen. Aufgrund der vielen Unbekannten weisen die Schätzungen - je nach Kanton - eine relativ grosse Bandbreite auf. Man kann demnach kein zuverlässiges Schätzergebnis verkünden. 
+Unter dem Strich erwarten wir - Stand heute - aber eine klare Entspannung im Voranschlag 2027. Anders sähe es aus, wenn wir das Entlastungspaket nicht hätten. Dann wären wir weiterhin im roten Bereich.
+C'est la réponse que je peux aussi donner au conseiller aux États Hurni. Si nous n'avions pas procédé aux épargnes ou aux coupes que nous avons faites dans le cadre du paquet d'allègement budgétaire pour 2027 et les années suivantes, il y aurait un déficit structurel malgré les très fortes recettes des trois cantons que je viens de nommer. C'était nécessaire. Bien sûr - je le répéterai en allemand - dans les années à venir il faudra beaucoup investir pour l'armée - c'est aussi le souhait du Parlement - , ce qui nous coûtera cher - on parle de 3 milliards de francs par année, ce qui est beaucoup, et ceci, à côté des dépenses supplémentaires de 1 milliard de francs au minimum pour la 13e rente AVS.
+Ich komme zurück zur deutschen Version. Ohne das Entlastungspaket 2027 hätten wir im Voranschlag 2027 trotz der Mehreinnahmen ein strukturelles Defizit. Wir sollten aber auf darüber hinausgehende Massnahmen, wie sie der Bundesrat noch Mitte April 2026 vorsorglich beschlossen hatte, um die Schuldenbremse einzuhalten, verzichten können.
+Vous vous souvenez qu'au mois d'avril, on avait dit qu'il y avait encore un écart de 600 millions de francs. C'est vrai que cela s'est détérioré de 300 millions, mais maintenant, avec les recettes que nous pouvons budgétiser, je pense que nous pouvons renoncer aux mesures que nous avions prévues. Rappelez-vous : je vous avais "menacés" de revenir avec les mêmes mesures que celles que vous avez rejetées. Ce ne sera pas nécessaire. C'est déjà une bonne nouvelle.
+Sie erinnern sich: Der Bundesrat hatte bereits damals in Aussicht gestellt, dass er die Notwendigkeit dieser zusätzlichen Bereinigungsmassnahmen nochmals überprüfen werde, wenn die aktualisierte Ausgaben- und Einnahmenschätzung dies erlaube. Naturgemäss sind die Prognosen für die Finanzplanjahre mit einer noch höheren Unsicherheit behaftet. Da das Wachstum der Gewinnsteuereinnahmen aber auch im langfristigen Durchschnitt hoch war, ist es vertretbar, dass wir uns auch in den kommenden Finanzplanjahren 2028 bis 2030 daran orientieren.
+Erschwerend kommt in den Finanzplanjahren hinzu, dass der Entscheid zur Armeefinanzierung noch ausstehend ist. Wie Sie wissen, rechnen wir im Finanzplan aufgrund der Vernehmlassungsvorlage des VBS derzeit mit einer Mehrwertsteuererhöhung um 0,8 Prozent ab 2028. Die entsprechenden Mittel sind nach Finanzhaushaltsrecht so eingestellt. Wenn es hier zu Anpassungen kommt, kann sich das je nach Ausgestaltung der Vorlage auf den strukturellen Saldo des Bundeshaushaltes und auf die für die Armee zur Verfügung stehenden Mittel auswirken.
+Der Bundesrat wird, wie gesagt, Ende Juni die Zahlen zum Budget definitiv festlegen. Dabei wird es das Ziel des Finanzdepartementes sein, den finanzpolitischen Handlungsspielraum von Bundesrat und Parlament bestmöglich zu wahren.
+Nun, damit beende ich den Ausblick. Ich beantrage Ihnen im Namen des Bundesrates, der Staatsrechnung für das Jahr 2025 zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat hat bereits dargetan, warum er Artikel 7dbis streichen möchte. Ich möchte Sie namens Ihrer einstimmigen Kommission bitten, daran festzuhalten. 
+Der Bundesrat argumentiert, dass es bei Verordnungen, die sich auf gewisse spezialgesetzliche Bestimmungen stützen, eigentlich um normale Verordnungen gehe. Daher soll es für diese Verordnungen auch keine spezielle Begründungspflicht geben. 
+Ich bestreite aber, dass es hier um ganz gewöhnliche Verordnungen geht, und ich tue das nicht aus re</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat hat bereits dargetan, warum er Artikel 7dbis streichen möchte. Ich möchte Sie namens Ihrer einstimmigen Kommission bitten, daran festzuhalten. 
+Der Bundesrat argumentiert, dass es bei Verordnungen, die sich auf gewisse spezialgesetzliche Bestimmungen stützen, eigentlich um normale Verordnungen gehe. Daher soll es für diese Verordnungen auch keine spezielle Begründungspflicht geben. 
+Ich bestreite aber, dass es hier um ganz gewöhnliche Verordnungen geht, und ich tue das nicht aus reiner Fantasie, sondern, weil das Parlamentsgesetz selber sagt, das seien keine normalen Verordnungen. Das Parlamentsgesetz führt im Anhang 2 Bestimmungen aus sechs Gesetzen auf, und es nennt sie selber "gesetzliche Ermächtigungen zur Bewältigung einer Krise". Das Parlamentsgesetz nennt diese Bestimmungen so, "gesetzlichen Ermächtigungen zur Bewältigung einer Krise". Das sind eben gerade nicht Standarddelegationsnormen. Die sechs Gesetze sind das Asylgesetz, das Schuldbetreibungs- und Konkursgesetz, das Landesversorgungsgesetz, das Zolltarifgesetz, das Fernmeldegesetz, und - es wird Ihnen bekannt vorkommen aus den erwähnten Corona-Debatten -, Artikel 6 und 7 des Epidemiengesetzes. Auf Artikel 6 und 7 des Epidemiengesetzes fusste ja fast die ganze Zeit über die Corona-Verordnungsgebung. Da kann man jetzt schlecht sagen, das seien einfach hundskommune Verordnungen. Auch das Parlamentsgesetz zählt sie, wie gesagt, gesondert auf. Und es zählt sie nicht nur gesondert auf, es behandelt sie auch besonders. In Artikel 121 des Parlamentsgesetzes heisst es, wenn eine Kommission mit einer Kommissionsmotion zu einer solchen Verordnungen intervenieren will, dann muss diese Motion ganz schnell behandelt werden, damit auch das Parlament bei solchen Krisenverordnungen eingreifen kann. 
+Aus Sicht des Parlamentsgesetzes befinden wir uns ganz klar in der Notrechts- und Krisengesetzgebung, wenn auch auf Gesetzesstufe. Es geht um grosse Ermessensspielräume für den Bundesrat, wie es sie sonst nicht gibt. Man denke an Artikel 6 und 7 des Epidemiengesetzes, die so formuliert sind, dass sie dem Bundesrat nahezu einen Blankocheck geben. Deshalb glaube ich, dass man solche Verordnungen nicht als normale Verordnungsgebung betrachten kann. 
+In diesem Sinne bitte ich Sie, diese sechs Gesetze auch als begründungspflichtige Notrechtsgrundlagen zu betrachten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">376998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fivaz Fabien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative parlementaire de notre ancienne collègue Stefania Prezioso Batou a été déposée en 2021. Elle visait la réhabilitation des personnes ayant combattu dans la Résistance française contre le fascisme pendant la Seconde Guerre mondiale. La Commission des affaires juridiques du Conseil national y a donné suite en octobre 2021. Elle a été suivie par votre commission en janvier 2022. Le Conseil national a ensuite accepté le texte en mars de cette année.
+Le projet de réhabilitation n'est pas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative parlementaire de notre ancienne collègue Stefania Prezioso Batou a été déposée en 2021. Elle visait la réhabilitation des personnes ayant combattu dans la Résistance française contre le fascisme pendant la Seconde Guerre mondiale. La Commission des affaires juridiques du Conseil national y a donné suite en octobre 2021. Elle a été suivie par votre commission en janvier 2022. Le Conseil national a ensuite accepté le texte en mars de cette année.
+Le projet de réhabilitation n'est pas le premier. En 2003, notre Parlement a annulé les jugements pénaux prononcés contre les personnes ayant aidé les victimes du national-socialisme et du fascisme. Elle n'a, à cette époque, pas jugé opportun de réhabiliter les personnes ayant combattu au côté des républicains espagnols durant la guerre civile ni les personnes ayant combattu dans la Résistance française ou la Résistance italienne. C'est l'article 94 du code pénal militaire qui est évoqué pour justifier ce choix. Pour rappel, il punit les personnes qui s'engagent dans une armée étrangère sans autorisation du Conseil fédéral. Cet article existait déjà à l'époque de la Deuxième Guerre mondiale. Il a en effet été introduit en 1929 dans le code pénal militaire ; le porte-parole de la minorité l'invoquera sans doute pour justifier son refus d'entrer en matière.
+La réhabilitation ne doit pas être comprise comme une critique de l'attitude des autorités de l'époque, en particulier judiciaires. Elles ont agi dans le contexte qui était celui de la Deuxième Guerre mondiale. C'est uniquement avec le recul historique, dans une perspective contemporaine, que la réhabilitation est prévue. Dans ce sens, le Parlement a d'ailleurs refusé, ces derniers mois, des propositions visant à lever l'article 94 du code pénal militaire pour les Suisses combattant aujourd'hui en Ukraine ou contre l'État islamique. En 2009, le Parlement a voté une nouvelle fois sur ce thème, cette fois en proposant la réhabilitation des personnes ayant lutté contre le franquisme dans le cadre de la guerre civile espagnole. À nouveau, à cette époque, la question des volontaires engagés dans la Résistance française a été examinée. À nouveau, le Parlement a décidé de ne pas entrer en matière, estimant cette fois que les bases historiques n'étaient pas suffisantes.
+Depuis lors, de nombreuses recherches ont été menées sur ce thème. Une étude de l'historien Peter Huber a été réalisée dans le cadre d'un projet du Fonds national suisse. Publiée en 2020, elle documente l'implication de citoyens suisses dans la Résistance française dans deux corps militaires, les Forces françaises de l'intérieur (FFI), qui combattaient en France métropolitaine, et les Forces françaises libres (FFL), actives dans les anciennes colonies de la France, en particulier en Afrique du Nord. Cette étude montre, à partir de documents provenant des Archives fédérales suisses et d'archives militaires françaises, le destin de 466 Suisses qui ont participé à cette résistance. Un des constats de M. Huber est l'hétérogénéité du groupe. Un peu moins de la moitié d'entre eux s'étaient engagés par le biais de la Légion étrangère. M. Huber relève que dans presque toutes les biographies de ces personnes, on retrouve un sentiment de consternation face à l'humiliation de la France et à la folie d'Hitler. L'étude documente aussi les conséquences subies au retour. Le droit interdisant le service étranger, je l'ai déjà dit, en vigueur depuis 1929, fut appliqué très strictement. Les Archives fédérales suisses contiennent des documents sur les personnes jugées, et la justice militaire a parfois prononcé des peines très lourdes, allant jusqu'à 5 ans de réclusion dans un cas. Environ 200 personnes furent condamnées à des peines de détention, avec ou sans sursis ; certaines furent expulsées de l'armée ou déchues de leurs droits politiques, d'autres restèrent en France pour échapper à ces sanctions ; certaines personnes, déjà condamnées par contumace, moururent au combat.
+Le Conseil national a décidé d'inclure les personnes ayant combattu dans la Résistance italienne, en particulier les Suissesses et les Suisses, parmi lesquels de nombreuses femmes, qui ont été sanctionnés lors de la chute de la République partisane de l'Ossola pour avoir aidé les réfugiées et réfugiés chassés par les fascistes à passer la frontière pour trouver refuge en Suisse - c'étaient près de 10 000 personnes -, ou qui ont soutenu la Résistance italienne depuis le Tessin.
+Comme en 2003 et en 2009, la réhabilitation de ces personnes est un geste fort. Avec le recul, on se rend compte qu'elles ont combattu pour la liberté et la démocratie, même si sur le moment, les motifs des uns et des autres - on peut le lire dans les biographies - pouvaient diverger. Elles ont permis, chacune et chacun à leur niveau, la chute de l'Allemagne nazie et la réduction des souffrances des personnes persécutées ou ayant dû fuir leur pays. Elles méritent rétrospectivement d'être reconnues et réhabilitées pour cela.
+La Commission de rédaction a proposé de modifier le texte de la loi sur le plan formel en proposant que la réhabilitation soit plus explicite que dans le texte original, qui est un texte repris de la dernière loi que notre Parlement a adoptée à ce sujet, c'est-à-dire en 2009. Après avoir examiné cette proposition, les Commissions des affaires juridiques des deux conseils ont décidé, à leurs séances respectives des 4 et 10 juin de cette année, qu'il était opportun de modifier le texte. Pour simplifier la procédure, elles ont décidé de confier la tâche à la Commission de rédaction, évitant ainsi un tour supplémentaire d'élimination des divergences.
+Sans entrer sur le fond, l'objectif est que l'article 2 soit consacré à la réhabilitation et mentionne que toutes les personnes qui ont été sanctionnées sont réhabilitées. La suite est inchangée. Ensuite, l'article 3 est intitulé "Conséquences juridiques", avec le deuxième alinéa qui devient l'alinéa 1 et énonce que la réhabilitation a pour effet d'annuler les jugements. La suite est inchangée. L'article 4, qui dit que cette réhabilitation n'ouvre aucun droit à des dommages-intérêts ni à une indemnité pour tort moral en raison des sanctions qui ont été prononcées ou des conséquences indirectes des jugements pénaux ou des décisions administratives prononcées à l'époque, devient l'alinéa 2 de l'article 3.
+La minorité défendra sa position.
 </t>
   </si>
 </sst>
@@ -753,8 +848,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I28" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I32"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1852,6 +1947,120 @@
         <v>142</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -264,9 +264,9 @@
   </si>
   <si>
     <t xml:space="preserve">La désinformation est le poison du XXIe siècle. Les "fake news", les théories du complot foisonnent sur les réseaux sociaux. Ces méthodes aussi nauséabondes que redoutables n'ont plus aucune limite. Elles cherchent aussi bien à fragiliser des États qu'à saper la confiance des citoyens à l'égard des institutions et de nos démocraties. Elles remettent en question les valeurs que nous avons héritées du siècle des Lumières.
-Bien sûr, la désinformation en tant qu'instrument d'influence a toujours existé. Toutefois, le développement des technologies numériques liées à l'intelligence artificielle a largement amplifié le phénomène. Il permet de conduire efficacement des campagnes de désinformation et de subversion, et ces dernières ont atteint un niveau inégalé dans l'histoire. Résultat : il est de plus en plus difficile de distinguer le vrai du faux. La désinformation peut aussi engendrer la violence. C'est ce qui s'est passé récemment en Angleterre, à la suite de l'attaque au couteau qui a coûté la vie à trois petites filles. Des émeutes ont éclaté sur fond de rumeurs en ligne selon lesquelles l'auteur était un requérant d'asile. Ce n'était pas le cas.
-Nos enfants sont aussi victimes de ces campagnes d'influence, parce que les extrémistes de tous bords cherchent les jeunes là où ils sont : sur les réseaux sociaux ou encore les plateformes de jeux. Bien sûr, ils se focalisent sur les plus influençables, sur les plus vulnérables. C'est un fait, la désinformation contribue à la montée de la radicalisation. C'est un phénomène bien connu par les services de renseignement, qui doit nous inquiéter.
-Partout dans le monde, le combat contre la désinformation est donc en train de s'organiser. Que fait la Suisse ? Elle est un peu à la traîne. Actuellement, il n'y a pas d'évaluation de l'ampleur de la menace ni de vraie stratégie pour sa gestion. Nous n'avons pas, à l'heure actuelle, les outils nécessaires pour lutter contre ces campagnes de déstabilisation. La coordination des divers organes de surveillance est insuffisante et les mesures d'anticipation pour nous en prémunir manquent dans une large mesure.
+Bien sûr, la désinformation en tant qu'instrument d'influence a toujours existé. Toutefois, le développement des technologies numériques liées à l'intelligence artificielle a largement amplifié le phénomène. Il permet de conduire efficacement des campagnes de désinformation et de subversion, et ces dernières ont atteint un niveau inégalé dans l'histoire. Résultat[NB]: il est de plus en plus difficile de distinguer le vrai du faux. La désinformation peut aussi engendrer la violence. C'est ce qui s'est passé récemment en Angleterre, à la suite de l'attaque au couteau qui a coûté la vie à trois petites filles. Des émeutes ont éclaté sur fond de rumeurs en ligne selon lesquelles l'auteur était un requérant d'asile. Ce n'était pas le cas.
+Nos enfants sont aussi victimes de ces campagnes d'influence, parce que les extrémistes de tous bords cherchent les jeunes là où ils sont[NB]: sur les réseaux sociaux ou encore les plateformes de jeux. Bien sûr, ils se focalisent sur les plus influençables, sur les plus vulnérables. C'est un fait, la désinformation contribue à la montée de la radicalisation. C'est un phénomène bien connu par les services de renseignement, qui doit nous inquiéter.
+Partout dans le monde, le combat contre la désinformation est donc en train de s'organiser. Que fait la Suisse[NB]? Elle est un peu à la traîne. Actuellement, il n'y a pas d'évaluation de l'ampleur de la menace ni de vraie stratégie pour sa gestion. Nous n'avons pas, à l'heure actuelle, les outils nécessaires pour lutter contre ces campagnes de déstabilisation. La coordination des divers organes de surveillance est insuffisante et les mesures d'anticipation pour nous en prémunir manquent dans une large mesure.
 Avec ma motion, je demande donc au Conseil fédéral de mettre en place une stratégie visant à combattre la désinformation. La Suisse se doit d'anticiper, afin de se prémunir contre les dégâts causés par la désinformation. Il est indispensable de se protéger contre ces zones de non-droit et de tous les dangers qui en découlent. L'avis du Conseil fédéral à ma motion ne m'a pas convaincue sur sa volonté d'agir. Même si le gouvernement prend au sérieux la menace et admet qu'il faut accorder davantage d'attention à cette problématique, il souhaite attendre un nouveau rapport et analyser encore la situation. Moi, je suis d'avis que nous n'avons plus le temps d'attendre, de tergiverser, d'attendre un énième rapport. Au vu de l'urgence de la situation, il m'apparaît que nous avons besoin de mesures efficaces que nous pouvons mettre en oeuvre rapidement. Pas demain, mais aujourd'hui.
 Chers collègues, l'utilisation de fausses informations est devenue une arme de la guerre hybride déjà en cours. Elle exige une réaction rapide et efficace. La réponse à ce nouveau risque est la mise en oeuvre d'une véritable stratégie qui non seulement garantit la libre formation de l'opinion publique, indispensable dans une démocratie comme la nôtre, mais protège aussi nos processus démocratiques et nos institutions. Merci de soutenir ma motion.
 </t>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -284,17 +284,16 @@
     <t xml:space="preserve">Le 13 juin 2024, le conseiller national Yvan Pahud a déposé la motion 24.3701, "Garantir une protection permanente des frontières". Cette motion vise à ce que la législation soit adaptée pour bénéficier d'une disponibilité ininterrompue de patrouilles mobiles de l'Office fédéral de la douane et de la sécurité des frontières (OFDF). Le 14 août 2024, le Conseil fédéral a proposé le rejet de la motion, rappelant que la Suisse n'était pas membre de l'Union douanière européenne et pouvait donc contin</t>
   </si>
   <si>
-    <t xml:space="preserve">Le 13 juin 2024, le conseiller national Yvan Pahud a déposé la motion 24.3701, "Garantir une protection permanente des frontières". Cette motion vise à ce que la législation soit adaptée pour bénéficier d'une disponibilité ininterrompue de patrouilles mobiles de l'Office fédéral de la douane et de la sécurité des frontières (OFDF). Le 14 août 2024, le Conseil fédéral a proposé le rejet de la motion, rappelant que la Suisse n'était pas membre de l'Union douanière européenne et pouvait donc continuer à contrôler de manière permanente ses frontières, y compris à procéder à des contrôles de personnes. Les effectifs de l'OFDF, à savoir 3500 personnes, s'occupent de contrôles quotidiens, y compris avec des moyens électroniques. On dénombre 400 caméras qui sont installées précisément pour contrôler les passages de frontières. Le Conseil fédéral a rappelé également les prérogatives des polices cantonales ainsi que de l'armée en cas de fermeture des frontières, étant précisé que cette dernière ne peut pas contrôler les personnes. Pour le Conseil fédéral, la lutte contre la criminalité concerne l'ensemble du territoire national et pas seulement les frontières.
+    <t xml:space="preserve">Le 13 juin 2024, le conseiller national Yvan Pahud a déposé la motion 24.3701, "Garantir une protection permanente des frontières". Cette motion vise à ce que la législation soit adaptée pour bénéficier d'une disponibilité ininterrompue de patrouilles mobiles de l'Office fédéral de la douane et de la sécurité des frontières (OFDF). Le 14 août 2024, le Conseil fédéral a proposé le rejet de la motion, rappelant que la Suisse n'était pas membre de l'Union douanière européenne et pouvait donc continuer à contrôler de manière permanente ses frontières, y compris à procéder à des contrôles de personnes. Les effectifs de l'OFDF, à savoir 3500 personnes, s'occupent de contrôles quotidiens, y compris avec des moyens électroniques. On dénombre 400 caméras installées précisément pour contrôler les passages de frontières. Le Conseil fédéral a rappelé également les prérogatives des polices cantonales ainsi que de l'armée en cas de fermeture des frontières, étant précisé que cette dernière ne peut pas contrôler les personnes. Pour le Conseil fédéral, la lutte contre la criminalité concerne l'ensemble du territoire national et pas seulement les frontières.
 Le 23 septembre 2024, le groupe libéral-radical a également déposé une motion qui vise à prolonger les contrôles aux frontières qui avaient été mis en place durant le Championnat d'Europe de l'UEFA et les Jeux olympiques de Paris et à renforcer les contrôles en fonction des mesures prises par les pays voisins. Elle fixait également un délai pour qu'un rapport soit remis au Parlement par le Conseil fédéral à fin 2025. Le 13 novembre 2024, comme pour la première motion que nous abordons aujourd'hui, le Conseil fédéral a proposé le rejet de cette seconde motion.
-Le 4 juin 2025, le Conseil national a accepté la motion Pahud, par 100 voix contre 92 et 1 abstention, et a accepté la motion du groupe libéral-radical, par 121 voix contre 71 et 1 abstention.
+Le 4 juin 2025, le Conseil national a adopté la motion Pahud, par 100 voix contre 92 et 1 abstention, et a adopté la motion du groupe libéral-radical, par 121 voix contre 71 et 1 abstention.
 Pour être complet, il faut ajouter que le 12 juin 2025, le canton d'Argovie a déposé l'initiative 25.311, que nous n'examinons pas aujourd'hui, qui vise à rétablir temporairement les contrôles aux frontières en les adaptant aux mesures de renforcement qui avaient été prises par l'Allemagne, visant également à ce que ces mesures ne rendent pas moins fluides les passages des frontières.
-Le 30 octobre 2025, la Commission de la politique de sécurité (CPS) du Conseil des États a décidé de suspendre les deux objets que nous traitons aujourd'hui, mais également l'initiative du canton d'Argovie et de charger le Conseil fédéral de lui présenter, d'ici mi-mars 2026, un plan d'action détaillé pour la mise en oeuvre de la motion 25.3021, "Intensification des contrôles aux frontières de la Suisse", déposée par la Commission des institutions politiques du Conseil des États et de la motion 25.3026 de la commission soeur, totalement identique. Le 13 mars 2026, le Conseil fédéral, donnant suite à la demande de la CPS de notre conseil, a rendu son rapport. C'est un rapport dans lequel il indique sa volonté de mettre en oeuvre un contrôle efficace des frontières. Il rappelle que, lors de sa séance du 19 décembre 2025, le Conseil fédéral s'était prononcé sur les modalités de mise en oeuvre des deux motions dont je viens de parler.
-La mise en oeuvre des mesures demandées ne devait toutefois pas revenir à réintroduire des contrôles Schengen aux frontières intérieures.
-Le Conseil fédéral a abordé six mesures qu'il entendait mettre en oeuvre pour répondre à la préoccupation d'une majorité qui s'est déjà exprimée au Conseil national. La mesure numéro 1 indiquait qu'avec les ressources dont il dispose, et nous savons qu'elles sont ce qu'elles sont et les limitations qu'elles impliquent, l'OFDF devait accroître sa présence et sa visibilité le long des frontières et dans l'espace frontalier en fonction de la situation à court et à moyen terme. La mesure numéro 2 voulait que, en fonction des besoins et si la situation l'exige, l'OFDF assigne également le contrôle des personnes à des spécialistes de douane formés aux tâches de sécurité. La mesure numéro 3 prévoyait que l'OFDF cherche à intensifier encore davantage la coopération, qualifiée de déjà fructueuse et étroite, avec les corps de police compétents. La mesure numéro 4 indiquait que les patrouilles mixtes qui sont organisées avec les pays voisins et qui oeuvrent aux frontières doivent être non seulement maintenues, mais intensifiées. La mesure numéro 5 voulait que l'OFDF étudie la possibilité d'utiliser des caméras, des drones et des technologies d'imagerie thermique le long des frontières et dans l'espace frontalier pour soutenir les activités de contrôle. Enfin, la mesure numéro 6 prévoyait que l'OFDF élabore un plan relatif à l'augmentation des effectifs, avec les moyens nécessaires sur le plan financier pour l'acquisition d'outils d'assistance technique.
-Ce rapport se terminait avec une phrase qui exprimait un enthousiasme, je dirais, tempéré puisqu'il indiquait qu'en raison des chiffres actuellement peu élevés dans le domaine de la migration irrégulière et du renforcement ponctuel et ciblé de la présence de l'OFDF aux points névralgiques en matière de migration, on pouvait s'attendre à ce que les résultats et la résonance extérieure soient modérés dans un premier temps. C'est là que les questions de la commission sont venues, le 13 avril 2026, lorsqu'elle a examiné ce rapport. Il a alors été relevé que si le nombre des interpellations pour entrées irrégulières en Suisse avait effectivement diminué, cela n'était pas forcément le résultat d'une baisse des infractions, mais que cela pouvait être - et c'était plutôt la conviction d'une majorité de la commission - le résultat d'une diminution des contrôles eux-mêmes, puisque moins on contrôle, moins on trouve, comme chacun sait - c'est une lapalissade de le dire.
-Dès lors, le 13 avril 2026, la Commission de la politique de sécurité du Conseil des États a accepté la motion Pahud, par 8 voix contre 3 et 1 abstention, et la motion du groupe libéral-radical, par 10 voix contre 2. Simultanément, l'initiative du canton d'Argovie a été suspendue. Voilà le résultat que vous demande de suivre la majorité de la commission, c'est-à-dire d'adopter les deux motions qui vous sont présentées.
-J'ajoute un mot quand même à titre plus personnel, en tant que représentant du canton de Genève. Genève, qui a 100 kilomètres de frontière avec la France et 4 kilomètres qui le rattachent au reste de la Suisse par le canton de Vaud, est un canton particulièrement soumis à la délinquance transfrontalière et je peux vous assurer que la présence d'uniformes aux frontières est extrêmement rare. Si vous en voyez, n'oubliez pas de nous présenter des photographies. Alors que dans le sens inverse, nous voyons des uniformes français qui contrôlent l'entrée en France des personnes qui sortent de la Suisse. Il serait bon effectivement que les bonnes intentions du Conseil fédéral, que nous saluons, exprimées dans ce rapport se trouvent concrétisées.
-La Commission de la politique de sécurité attend des résultats prochains et, en adoptant les deux motions, nous souhaitons inciter le Conseil fédéral à poursuivre dans ce sens.
+Le 30 octobre 2025, la Commission de la politique de sécurité (CPS) du Conseil des États a décidé de suspendre les deux objets que nous traitons aujourd'hui et l'initiative du canton d'Argovie et de charger le Conseil fédéral de lui présenter, d'ici mi-mars 2026, un plan d'action détaillé pour la mise en oeuvre de la motion 25.3021, "Intensification des contrôles aux frontières de la Suisse", déposée par la Commission des institutions politiques du Conseil des États et de la motion 25.3026 de la commission soeur, de teneur totalement identique. Le 13 mars 2026, le Conseil fédéral, donnant suite à la demande de la CPS de notre conseil, a rendu son rapport. C'est un rapport dans lequel il indique sa volonté de mettre en oeuvre un contrôle efficace des frontières. Il rappelle que, lors de sa séance du 19 décembre 2025, le Conseil fédéral s'était prononcé sur les modalités de mise en oeuvre des deux motions dont je viens de parler. La mise en oeuvre des mesures demandées ne devait toutefois pas revenir à réintroduire des contrôles Schengen aux frontières intérieures.
+Le Conseil fédéral a abordé six mesures qu'il entendait mettre en oeuvre pour répondre à la préoccupation de la majorité qui s'est déjà exprimée au Conseil national. La mesure numéro 1 indiquait qu'avec les ressources dont il dispose, et nous savons qu'elles sont ce qu'elles sont et les limitations qu'elles impliquent, l'OFDF devait accroître sa présence et sa visibilité le long des frontières et dans l'espace frontalier en fonction de la situation à court et à moyen terme. La mesure numéro 2 voulait que, en fonction des besoins et si la situation l'exige, l'OFDF assigne également le contrôle des personnes à des spécialistes en douane formés aux tâches de sécurité. La mesure numéro 3 prévoyait que l'OFDF cherche à intensifier davantage la coopération, qualifiée de déjà fructueuse et étroite, avec les corps de police compétents. La mesure numéro 4 indiquait que les patrouilles mixtes qui sont organisées avec les pays voisins et qui oeuvrent aux frontières doivent être non seulement maintenues, mais intensifiées. La mesure numéro 5 voulait que l'OFDF étudie la possibilité d'utiliser des caméras, des drones et des technologies d'imagerie thermique le long des frontières et dans l'espace frontalier pour soutenir les activités de contrôle. Enfin, la mesure numéro 6 prévoyait que l'OFDF élabore un plan relatif à l'augmentation des effectifs, avec les moyens nécessaires sur le plan financier pour l'acquisition d'outils d'assistance technique.
+Ce rapport se terminait avec une phrase qui exprimait un enthousiasme, je dirais, tempéré puisqu'il indiquait qu'en raison des chiffres actuellement peu élevés dans le domaine de la migration irrégulière et du renforcement ponctuel et ciblé de la présence de l'OFDF aux points névralgiques en matière de migration, on pouvait s'attendre à ce que les résultats et la résonance extérieure soient modérés dans un premier temps. C'est là que les questions de la commission sont venues, le 13 avril 2026, lorsqu'elle a examiné ce rapport. Il a alors été relevé que si le nombre des interpellations pour entrées irrégulières en Suisse avait effectivement diminué, cela n'était pas forcément le résultat d'une baisse des infractions, mais que cela pouvait être - et c'était plutôt la conviction de la majorité de la commission - le résultat d'une diminution des contrôles eux-mêmes, puisque moins on contrôle, moins on trouve, comme chacun sait - c'est une lapalissade de le dire.
+Dès lors, le 13 avril 2026, la CPS du Conseil des États a accepté la motion Pahud, par 8 voix contre 3 et 1 abstention, et la motion du groupe libéral-radical, par 10 voix contre 2. Simultanément, l'examen de l'initiative du canton d'Argovie a été suspendue. Voilà le résultat que vous demande de suivre la majorité de la commission, c'est-à-dire d'adopter les deux motions qui vous sont présentées.
+J'ajoute un mot quand même à titre plus personnel, en tant que représentant du canton de Genève. Genève, qui a 100 kilomètres de frontière avec la France et 4 kilomètres qui le rattachent au reste de la Suisse par le canton de Vaud, est un canton particulièrement soumis à la délinquance transfrontalière et je peux vous assurer que la présence d'uniformes aux frontières est extrêmement rare. Si vous en voyez, n'oubliez pas de nous présenter des photographies. Alors que dans le sens inverse, nous voyons des uniformes français qui contrôlent l'entrée en France des personnes qui sortent de la Suisse. Il serait bon, effectivement, que les bonnes intentions du Conseil fédéral, que nous saluons, exprimées dans ce rapport se trouvent concrétisées.
+La CPS attend des résultats prochains et, en adoptant les deux motions, nous souhaitons inciter le Conseil fédéral à poursuivre dans ce sens.
 </t>
   </si>
   <si>
@@ -358,21 +357,20 @@
     <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il fournit de plus des explications concernant les écarts par rapport aux objectifs et présente les principaux objets non planifiés. En 2025, les droits de douane introduits en août sur les exportations suisses vers les États-Unis ont fortement mobilisé le Conseil fédéral. Par ailleurs, les questions de compétitivité de l'économie suisse, les oeuvres sociales et les sujets de sécurité ont figuré au premier plan. Comme chaque année, le rapport de gestion offre une très bonne opportunité de dialogue entre le Parlement et le Conseil fédéral. J'aimerais remercier les Commissions de gestion et les rapporteurs qui se sont exprimés sur ce rapport.
 Je vais maintenant rappeler brièvement le cadre de la politique du Conseil fédéral, à savoir les quatre lignes directrices de la législature 2023 à 2027. Je vous exposerai ensuite les points essentiels du travail accompli par le gouvernement l'année passée, soit la deuxième année de la législature. Les lignes directrices sont les suivantes : 1. "la Suisse assure durablement sa prospérité et saisit les chances qu'offre le numérique" ; 2. "elle encourage la cohésion nationale et intergénérationnelle" ; 3. "elle assure la sécurité, oeuvre en faveur de la paix et agit de manière cohérente et fiable sur le plan international" ; 4. "elle protège le climat et prend soin des ressources naturelles."
 Ces lignes directrices sont divisées en 25 objectifs et regroupent un total de 148 mesures pour l'année 2025. Le Conseil fédéral a entièrement mis en oeuvre 88 de ces objets, et 9 ont été partiellement réalisés.
-J'aborde maintenant les points forts de l'année dernière, et pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices. La première ligne directrice concerne la prospérité et le numérique. En matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur 2 axes principaux : l'amélioration des conditions-cadres de l'ensemble des entreprises et la réduction de la charge réglementaire.
+J'aborde maintenant les points forts de l'année dernière et, pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices. La première ligne directrice concerne la prospérité et le numérique. En matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur 2 axes principaux : l'amélioration des conditions-cadres de l'ensemble des entreprises et la réduction de la charge réglementaire.
 En ce qui concerne les finances, l'année 2025 a été notamment marquée par l'adoption du message concernant le programme d'allègement budgétaire 2027. Ce programme est essentiel pour rétablir l'équilibre entre les recettes et les dépenses de la Confédération dans les années à venir.
 S'agissant de la place financière suisse, le Conseil fédéral a défini les grandes lignes des révisions de lois et autres ordonnances dans le secteur bancaire.
 En matière d'infrastructures et de transports, le Conseil fédéral a pris connaissance du rapport d'expertise "DETEC : Transports 2045" de l'École polytechnique fédérale de Zurich sur l'aménagement des infrastructures de transport. Cette analyse indépendante présente les projets à réaliser en priorité du point de vue technique d'ici 2045.
 Dans le domaine du numérique, en 2025, le Conseil fédéral a approuvé le message concernant la nouvelle loi fédérale sur le dossier électronique de santé. Ce dossier est automatiquement mis à la disposition de toute la population. Il renforce le système de santé en réunissant en un seul endroit toutes les informations de santé pertinentes de son titulaire.
 Consacrons-nous maintenant à la deuxième ligne directrice : la cohésion nationale et intergénérationnelle. Pour ce qui est des affaires sociales, le Conseil fédéral a décidé des lignes directrices de la prochaine réforme de l'AVS. La réforme AVS 2030 vise à stabiliser et moderniser l'AVS. Elle prévoit des mesures visant à rendre le système plus équitable et à prolonger la vie active.
 En matière de santé, en 2025, le Conseil fédéral a approuvé le message concernant la révision partielle de la loi sur les épidémies. Le but est d'améliorer la gestion des crises de santé publique et de mieux protéger la population contre de futures pandémies.
-Concernant le système de santé, le Conseil fédéral a approuvé Tardoc, le nouveau système tarifaire global pour les prestations médicales ambulatoires.
-Celui-ci tient mieux compte des besoins de la médecine de famille, simplifie la facturation et limite les incitations à accroître les quantités de prestations facturées.
+Concernant le système de santé, le Conseil fédéral a approuvé Tardoc, le nouveau système tarifaire global pour les prestations médicales ambulatoires. Celui-ci tient mieux compte des besoins de la médecine de famille, simplifie la facturation et limite les incitations à accroître les quantités de prestations facturées.
 Je passe maintenant à la troisième ligne directrice, relative à la sécurité et à l'action sur le plan international. Sur les plans de la politique extérieure et de la coopération internationale, le Conseil fédéral a défini les priorités thématiques pour la présidence suisse de l'OSCE en 2026. Ces priorités incluent, entre autres, le renforcement du dialogue inclusif entre les 57 États participants.
 Concernant le chapitre de la reconstruction de l'Ukraine, le Conseil fédéral a fixé les priorités du programme pour l'Ukraine 2025-2028. Ce programme marque le début d'un processus de soutien fédéral de 12 ans pour la reconstruction, les réformes et le développement durable en Ukraine.
 En matière de sécurité, le Conseil fédéral, en février 2025, a adopté le message sur l'armée 2025. Le programme d'armement 2025 vise à combler les lacunes capacitaires dans l'effet obtenu contre des cibles au sol, dans les domaines de la conduite, de la mise en réseau et du renseignement, ainsi que dans le cyberespace et l'espace électromagnétique.
 Finalement, j'en arrive à la quatrième et dernière ligne directrice, relative au climat et aux ressources naturelles. Dans le domaine de la politique agricole, le Conseil fédéral a adopté le message sur la révision partielle du droit foncier rural. Il entend, par cette révision, renforcer la position des conjoints dans les exploitations agricoles ainsi que le principe de l'exploitation à titre personnel, tout en accordant aux agriculteurs une plus grande liberté entrepreneuriale.
-En matière d'énergie, le Conseil fédéral a adopté le message concernant une révision de la loi sur les installations électriques qui vise à accélérer les procédures d'autorisation pour l'extension et la transformation des réseaux électriques.
-Concernant les stratégies - et c'étaient plusieurs points forts de l'année dernière -, notamment la stratégie nationale contre le racisme et l'antisémitisme pour la période 2026-2031, la stratégie Asie G20 2025-2028 et la stratégie du Conseil fédéral en matière de politique d'armement, elles ont été adoptées. Le Conseil fédéral a aussi adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
+En matière d'énergie, le Conseil fédéral a adopté le message concernant la révision de la loi sur les installations électriques qui vise à accélérer les procédures d'autorisation pour l'extension et la transformation des réseaux électriques.
+Plusieurs stratégies - qui ont été des points forts de l'année dernière ont été adoptées -, notamment la stratégie nationale contre le racisme et l'antisémitisme pour la période 2026-2031, la stratégie Asie G20 2025-2028 et la stratégie du Conseil fédéral en matière de politique d'armement. Le Conseil fédéral a aussi adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
 J'en arrive aux conclusions. Vous trouverez l'intégralité des messages, rapports, plans d'action et stratégies détaillés, avec la date de leur adoption, dans notre rapport de gestion 2025. 
 Au nom du Conseil fédéral, je vous remercie de votre reconnaissance, de votre coopération et de votre soutien. Le Conseil fédéral va continuer à s'engager pleinement pour la défense des intérêts du pays et pour le bien de sa population.
 </t>
@@ -387,24 +385,24 @@
     <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités né</t>
   </si>
   <si>
-    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités nécessaires à cet effet. Selon les auteurs de l'initiative, cet objectif implique notamment de pouvoir recourir à toutes les technologies de production disponibles, y compris le nucléaire. Ils soulèvent ainsi à la fois la question de la sécurité d'approvisionnement et remettent en question la répartition des compétences entre Confédération, cantons et acteurs du secteur électrique. L'objectif du contre-projet est de rétablir l'ouverture technologique en supprimant l'interdiction légale du nucléaire tout en refusant la modification constitutionnelle proposée dans l'initiative.
-Dans le cadre de ces travaux préparatoires, la commission a procédé à de nombreuses auditions et notamment entendu des représentants de l'Inspection fédérale de la sécurité nucléaire, de l'Association des entreprises électriques suisses, de Swissgrid, de la Conférence des directeurs cantonaux de l'énergie ainsi que de l'industrie électrique, du monde scientifique et d'organisations concernées.
-En outre, lors de sa séance du 30 mars, elle a chargé l'administration d'établir huit rapports complémentaires, notamment sur la rentabilité des projets hydroélectriques, sur les conséquences militaires et sécuritaires liées aux installations nucléaires, sur les questions de responsabilité civile et de couverture des dommages, sur les chaînes d'approvisionnement en combustible nucléaire, sur les réacteurs de quatrième génération, sur les besoins éventuels en centrales à gaz ainsi que sur le développement des énergies renouvelables.
-Les auditions ont montré un consensus sur la nécessité de poursuivre les développements des énergies renouvelables, de renforcer les réseaux électriques et de garantir la sécurité d'approvisionnement à long terme. Les besoins futurs en électricité seront vraisemblablement plus élevés que ceux évalués en 2017 lors de l'adoption de la stratégie énergétique 2050, notamment en raison de l'électrification croissante des usages, des centres de données et du développement de l'intelligence artificielle. Une réévaluation de ces besoins est en cours. La commission a d'ailleurs déposé les deux postulats 26.3019 et 26.3020 pour lesquels des réponses sont attendues d'ici fin 2027 dans le cadre des nouvelles perspectives énergétiques 2060 en cours d'élaboration, qui devront permettre des analyses actualisées de l'approvisionnement futur en électricité. À cet égard, les auditions ont fait apparaître des appréciations divergentes quant au rôle du nucléaire.
+    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités nécessaires à cet effet. Selon les initiants, cet objectif implique notamment de pouvoir recourir à toutes les technologies de production disponibles, y compris le nucléaire. Ils soulèvent ainsi à la fois la question de la sécurité d'approvisionnement et remettent en question la répartition des compétences entre Confédération, cantons et acteurs du secteur électrique. L'objectif du contre-projet est de rétablir l'ouverture technologique en supprimant l'interdiction légale du nucléaire tout en refusant la modification constitutionnelle proposée dans l'initiative.
+Dans le cadre de ses travaux préparatoires, la commission a procédé à de nombreuses auditions et notamment entendu des représentants de l'Inspection fédérale de la sécurité nucléaire, de l'Association des entreprises électriques suisses, de Swissgrid, de la Conférence des directeurs cantonaux de l'énergie ainsi que de l'industrie électrique, du monde scientifique et d'organisations concernées.
+En outre, lors de sa séance du 30 mars dernier, elle a chargé l'administration d'établir huit rapports complémentaires, notamment sur la rentabilité des projets hydroélectriques, sur les conséquences militaires et sécuritaires liées aux installations nucléaires, sur les questions de responsabilité civile et de couverture des dommages, sur les chaînes d'approvisionnement en combustible nucléaire, sur les réacteurs de quatrième génération, sur les besoins éventuels en centrales à gaz ainsi que sur le développement des énergies renouvelables.
+Les auditions ont montré un consensus sur la nécessité de poursuivre le développement des énergies renouvelables, de renforcer les réseaux électriques et de garantir la sécurité d'approvisionnement à long terme. Les besoins futurs en électricité seront vraisemblablement plus élevés que ceux évalués en 2017 lors de l'adoption de la stratégie énergétique 2050, notamment en raison de l'électrification croissante des usages, des centres de données et du développement de l'intelligence artificielle. Une réévaluation de ces besoins est en cours. La commission a d'ailleurs déposé les deux postulats 26.3019 et 26.3020 pour lesquels des réponses sont attendues d'ici fin 2027 dans le cadre des nouvelles perspectives énergétiques 2060 en cours d'élaboration, qui devront permettre des analyses actualisées de l'approvisionnement futur en électricité. À cet égard, les auditions ont fait apparaître des appréciations divergentes quant au rôle du nucléaire.
 La Conférence des directeurs cantonaux de l'énergie a indiqué que si les cantons rejetaient très largement l'initiative populaire, les positions sont plus nuancées sur le contre-projet indirect. Dix cantons demandent des analyses complémentaires, sept le soutiennent sous réserve du maintien du soutien aux énergies renouvelables et à l'hydraulique, tandis que huit s'y opposent. Les cantons ont demandé une actualisation des perspectives énergétiques et des précisions concernant les coûts, le financement, l'intégration d'éventuelles nouvelles centrales dans le système électrique suisse ainsi que la gestion à long terme des déchets radioactifs. Ils ont en revanche confirmé leur soutien à la poursuite de l'exploitation des centrales existantes, aussi longtemps que les exigences de sécurité sont remplies.
 Ces appréciations ont émaillé également le débat d'entrée en matière de la commission. Plusieurs membres ont demandé le renvoi du projet au Conseil fédéral, estimant que les bases décisionnelles demeuraient insuffisantes, notamment en ce qui concerne les coûts, le financement, les risques résiduels, les conséquences sur le développement des énergies renouvelables et la gestion des déchets radioactifs. La majorité de la commission a toutefois considéré que ces interrogations, bien que légitimes, ne justifiaient pas un renvoi. D'une part, le contre-projet ne préjuge pas d'une future décision de construire de nouvelles centrales et, d'autre part, il ne remet pas en cause la stratégie énergétique 2050 ni les lois votées par le peuple en la matière ces dernières années. Le contre-projet vise uniquement à supprimer une interdiction générale afin de préserver toutes les options susceptibles de contribuer à la sécurité d'approvisionnement dans un contexte marqué par des incertitudes géopolitiques et une demande d'électricité en hausse. Maintenir une interdiction revient à donner un signal paradoxal qui consiste à vouloir garantir notre approvisionnement sans intégrer toutes les technologies dans la réflexion.
 La commission est entrée en matière, par 13 voix contre 12. Elle a ensuite refusé la proposition de renvoi du contre-projet au Conseil fédéral, par 13 voix contre 11.
-Ces demandes de précision, bien que légitimes, sont prématurées. Elles ne pourront trouver de réponse en cohérence qu'en cas de projet concret, et non de manière théorique. Il y a quatre minorités à cet égard : les minorités I (Wismer Priska), II (Masshardt), III (Bäumle) et IV (Schlatter).
+Ces demandes de précision, bien que légitimes, sont prématurées. Elles ne pourront trouver de réponse cohérente qu'en cas de projet concret, et non de manière théorique. Il y a quatre minorités à cet égard : les minorités I (Wismer Priska), II (Masshardt), III (Bäumle) et IV (Schlatter).
 La commission a ensuite procédé à la discussion par article de la modification de la loi sur l'énergie nucléaire, soit du contre-projet à l'initiative, et s'est ralliée en tous points à la position du Conseil des États en refusant plusieurs propositions.
 À l'article 12a, la minorité Wismer Priska vise à limiter la levée de l'interdiction aux seules centrales de quatrième génération. La majorité relève qu'une telle restriction reviendrait pratiquement à maintenir l'interdiction actuelle, car il existe actuellement plus de 90 concepts différents dans le monde, aucune définition n'existant pour qualifier ce que sera une centrale de quatrième génération. Cette proposition a été rejetée, par 13 voix contre 12.
 À l'article 12b, la minorité Bäumle porte sur la responsabilité civile et les conséquences financières d'un accident nucléaire majeur. L'auteur considère que toute nouvelle centrale devrait être soumise à des exigences de couverture financière plus élevées. Pour la majorité, augmenter substantiellement les règles de couverture reviendrait à imposer des exigences plus élevées aux installations futures qu'aux centrales existantes, alors que celles-ci devraient être plus sûres. De tels coûts empêcheraient de facto tout nouveau projet. Cette proposition a été rejetée, par 13 voix contre 11.
 Les questions de sécurité ont occupé une place importante dans les débats, notamment au regard des conflits récents et des risques d'attaques militaires hybrides ou terroristes. À l'article 13 alinéa 1 lettre ebis, une proposition exigeant une démonstration d'un niveau de protection complet et garanti contre ces menaces a été rejetée, par 13 voix contre 12, le risque zéro n'existant pour aucune infrastructure, fut-elle nucléaire.
-Sur les questions de prolifération nucléaire, des dépendances géopolitiques et des chaînes d'approvisionnement, plusieurs propositions, à l'article 13 alinéa 1 lettres i et j, demandaient que les requérants démontrent le respect du droit international, des principes de non-prolifération ainsi que de standards élevés en matière de droits humains et d'environnement tout au long de la chaîne d'approvisionnement du combustible nucléaire. La majorité de la commission a reconnu l'importance de ces préoccupations, mais estime que les exigences proposées vont au-delà des mécanismes existants à l'échelle internationale et seraient extrêmement difficiles à mettre en oeuvre. Ces propositions aux lettres i et j ont donc été rejetées, par 16 voix contre 9. Il y a deux minorités.
+Sur les questions de prolifération nucléaire, des dépendances géopolitiques et des chaînes d'approvisionnement, plusieurs propositions, à l'article 13 alinéa 1 lettres i et j, demandaient que les requérants démontrent le respect du droit international, des principes de non-prolifération ainsi que de standards élevés en matière de droits humains et d'environnement tout au long de la chaîne d'approvisionnement du combustible nucléaire. La majorité de la commission a reconnu l'importance de ces préoccupations, mais a estimé que les exigences proposées vont au-delà des mécanismes existants à l'échelle internationale et seraient extrêmement difficiles à mettre en oeuvre. Ces propositions aux lettres i et j ont donc été rejetées, par 16 voix contre 9. Il y a deux minorités.
 Aux lettres k et l, selon certains membres de la commission, il n'est pas acceptable d'autoriser de nouvelles centrales sans solution pleinement établie pour l'élimination définitive des déchets. La majorité relève que la lettre d permettrait déjà d'imposer des conditions particulières le cas échéant. Certaines technologies en développement pourraient par ailleurs réduire la quantité ou la durée ainsi que la dangerosité des déchets produits. C'est pourquoi la majorité a rejeté ces propositions, par 16 voix contre 9, à la lettre k, et par 13 voix contre 9 et 3 abstentions, à la lettre l.
 La commission s'est ensuite penchée sur la participation des populations concernées. À l'article 15, la commission a refusé, par 15 voix contre 9, que les communes situées dans la zone de protection d'urgence autour d'une centrale disposent d'un droit de codécision contraignant. Un tel mécanisme serait difficilement compatible avec le système actuel d'autorisation générale qui est accordée par l'instance fédérale, en l'occurrence par le Parlement, et non par les cantons ou les communes. Cela créerait un précédent.
 S'agissant du financement, une proposition visait à introduire un nouvel article 86a pour exclure explicitement toute forme de soutien financier public, direct ou indirect, à de nouvelles centrales nucléaires, y compris par le biais de suppléments réseau, ainsi que toutes mesures d'encouragement. Cela a également été rejeté, par 13 voix contre 10, la commission constatant que le droit en vigueur ne permet de toute manière pas un tel soutien. Il n'est donc pas nécessaire d'inscrire une interdiction supplémentaire dans la loi.
-Enfin, une proposition présentée comme un compromis visait à remplacer la suppression de l'interdiction par un moratoire jusqu'en 2035. Elle a été rejetée, par 13 voix contre 12. C'est l'article 106 alinéas 1bis et 1ter. La majorité considère qu'un nouveau moratoire reporterait tout simplement les mêmes questions à une date ultérieure. L'expérience du moratoire entre 1990 et 2000 a montré par ailleurs qu'aucune réflexion sérieuse n'a pu être menée pendant cette période.
-Au terme de ses travaux, la commission a adopté le contre-projet dit indirect, par 13 voix contre 12.
+Enfin, une proposition présentée comme un compromis visant à remplacer la suppression de l'interdiction par un moratoire jusqu'en 2035 a été rejetée, par 13 voix contre 12. C'est l'article 106 alinéas 1bis et 1ter. La majorité considère qu'un nouveau moratoire reporterait tout simplement les mêmes questions à une date ultérieure. L'expérience du moratoire entre 1990 et 2000 a montré par ailleurs qu'aucune réflexion sérieuse n'a pu être menée pendant cette période.
+Au terme de ses travaux, la commission a adopté le contre-projet indirect, par 13 voix contre 12.
 À l'attention de la Commission de rédaction, elle relève qu'il n'est pas conforme à la pratique législative de faire figurer entre parenthèses, dans le titre de la loi, une référence au contre-projet indirect à l'initiative. Elle prie donc la Commission de rédaction de bien vouloir adapter ce titre.
 Quant à l'initiative populaire, une proposition visant à recommander son acceptation a été rejetée, par 15 voix contre 9. La commission suit donc la position du Conseil fédéral et du Conseil des États.
 </t>
@@ -445,51 +443,51 @@
   </si>
   <si>
     <t xml:space="preserve">Il m'appartient de vous présenter un bref rapport de l'audition que la Commission de gestion a menée avec Mme la conseillère fédérale Karin Keller-Sutter, cheffe du Département fédéral des finances, lors de l'examen du rapport de gestion 2025 du Conseil fédéral. Je concentrerai mon propos sur les deux thèmes choisis par Mme la conseillère fédérale, à savoir la situation des finances fédérales et la réglementation bancaire.
-Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon par exemple. 
-Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses, causée par des corrections d'estimations pour les assurances sociales et la migration. 
-Concernant la détente finale et la stabilisation, on relève que malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
+Premièrement, s'agissant des évolutions et perspectives du budget fédéral pour les années 2027 à 2029, il faut constater une détérioration initiale en 2027. Le budget de l'année 2027 tablait d'abord sur un équilibre, avant d'afficher un déficit structurel estimé entre 400 et 600 millions de francs. Ce recul découle des coupes parlementaires dans le programme de réexamen des tâches - ou Programme d'allègement budgétaire 2027 - ou de l'extension du programme européen Horizon, par exemple. 
+Concernant les nouvelles charges, le budget de 2027 subit une aggravation supplémentaire de 400 millions de francs au niveau des dépenses causée par des corrections d'estimations pour les assurances sociales et la migration. 
+Concernant la détente finale et la stabilisation, on relève que, malgré ces hausses de dépenses, une nette embellie du côté des recettes permet d'anticiper une détente pour le budget de 2027. De plus, un équilibre structurel redevient possible pour 2028 et 2029, et l'année 2029 affiche un besoin de correction réduit à 300 millions de francs. 
 Concernant la fin du recours au compte extraordinaire, pour la première fois depuis la pandémie de COVID-19, le budget de 2027 ne sollicitera plus de dépenses extraordinaires. Les coûts liés à l'accueil des personnes en provenance d'Ukraine seront pleinement intégrés au budget ordinaire.
 Concernant la dynamique et les incertitudes du côté des recettes fiscales et la hausse marquée de l'impôt sur le bénéfice, les recettes provenant des entreprises connaissent une forte croissance à large échelle dans de nombreux cantons. L'impact du canton de Genève pèse positivement, de même qu'une forte concentration de rentrées fiscales à Lucerne, Zurich et Bâle-Ville, générées par un petit nombre de sociétés. 
 Concernant le flou autour de l'impôt complémentaire de l'OCDE - c'est un point sur lequel la Commission de gestion s'est déjà penchée plusieurs fois -, cet impôt représente une grande inconnue. La taxe nationale est perçue pour la première fois cette année, et la taxe internationale suivra en 2027.
 Toutefois, à titre de rappel, seuls 25 pour cent de ces recettes reviennent à la Confédération, le reste allant aux cantons. Les cantons prévoient des rendements inférieurs aux attentes, et aucun chiffre fiable ne sera disponible avant septembre.
-Concernant les effets différés de la valeur locative : l'abolition de la valeur locative n'entrera en vigueur qu'en 2029 et la baisse des recettes qui en découlera, d'environ 320 millions francs, ne se fera donc ressentir qu'à partir du budget 2030.
+Concernant les effets différés de la valeur locative, l'abolition de la valeur locative n'entrera en vigueur qu'en 2029 et la baisse des recettes qui en découlera, d'environ 320 millions francs, ne se fera donc ressentir qu'à partir du budget 2030.
 Quant aux questions ou aux remarques qui sont parfois formulées sur la différence qu'il y a entre le budget et les comptes, Mme la conseillère fédérale nous a rappelé qu'à plusieurs reprises, notamment les trois dernières années, cette différence n'est que de l'ordre de 0,3 pour cent de l'ensemble des charges du budget de la Confédération.
 Concernant les grands défis et financements, notamment de l'armée, de l'AVS et de la recherche, j'aborde en premier lieu le financement de l'armée et de la sécurité. Pour faire progresser les dépenses militaires à 1 pour cent du PIB d'ici 2032, l'armée nécessite près de 3 milliards de francs supplémentaires par an. Le Conseil fédéral propose une hausse de la TVA, dont un tiers servira directement à combler ce besoin de financement dès 2028. Le Parlement étudie aussi d'autres pistes, comme la baisse temporaire de la part de l'impôt fédéral direct versé aux cantons. La mise en oeuvre de la 13e rente AVS, qui a été demandée par le peuple, représente une facture ouverte de 1 milliard de francs. Pour 2027, ce montant est compensé par des économies internes, mais son financement à long terme divise le Parlement, comme nous l'avons encore vu hier, entre un financement uniquement via la TVA ou combiné avec des pourcentages salariaux.
 Au sujet des pressions futures sur la recherche, des dépenses supplémentaires potentielles menacent le budget dès 2028, car la Commission européenne souhaite augmenter les budgets des programmes Horizon Europe et Erasmus.
-Concernant la marge de manoeuvre politique et les réformes structurelles, nous avons les mains liées face aux dépenses. La forte extension des dépenses restreint fortement la marge de manoeuvre de la Confédération. Pour retrouver une capacité d'action politique, le Conseil fédéral prône une stricte retenue sur les dépenses plutôt que de nouvelles hausses d'impôts. Concernant le dilemme des dépenses liées, le programme d'allègement budgétaire 2027 ciblait pour deux tiers des dépenses liées, à savoir des subventions. Pour dégager des moyens financiers massifs à l'avenir, la Suisse devra accepter des réformes structurelles profondes - relèvement de l'âge de la retraite, réduction de la part cantonale à l'impôt fédéral direct ou baisse de sa participation à la péréquation financière, soit des sujets qui risquent de fâcher, et pas seulement au Parlement.
+Concernant la marge de manoeuvre politique et les réformes structurelles, nous avons les mains liées face aux dépenses. La forte expansion des dépenses restreint fortement la marge de manoeuvre de la Confédération. Pour retrouver une capacité d'action politique, le Conseil fédéral prône une stricte retenue sur les dépenses plutôt que de nouvelles hausses d'impôts. Concernant le dilemme des dépenses liées, le programme d'allègement budgétaire 2027 ciblait pour deux tiers des dépenses liées, à savoir des subventions. Pour dégager des moyens financiers massifs à l'avenir, la Suisse devra accepter des réformes structurelles profondes[NB]: relèvement de l'âge de la retraite, réduction de la part cantonale à l'impôt fédéral direct ou baisse de sa participation à la péréquation financière, soit des sujets qui risquent de fâcher, et pas seulement au Parlement.
 Concernant l'historique des mesures fiscales déjà prises, le Conseil fédéral rappelle avoir déjà sollicité la population avec la hausse de la TVA pour AVS 21, l'imposition de l'OCDE, l'augmentation de la taxe sur le tabac et la fin de l'allègement fiscal pour les voitures électriques.
 En résumé, la situation financière est en voie d'amélioration, mais un grand nombre d'inconnues ne facilitent pas la planification ni les prévisions. Toutes ces informations sont utiles à la Commission de gestion, même si celle-ci ne s'occupe pas en priorité des finances, mais bel et bien de gestion.
-Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire , afin de combler les failles des banques d'importance systémique.
-Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
-Concernant la tentative de déstabilisation des institutions - autre sujet extrêmement critique pour la Commission de gestion -, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
+Concernant la réglementation bancaire liée à la crise de Credit Suisse, les pressions des lobbies et le chantier législatif "too big to fail", le Département fédéral des finances a fait de cette réglementation sa priorité. Des travaux majeurs sont en cours, basés sur les propositions du Conseil fédéral, les motions parlementaires et les conclusions de la Commission d'enquête parlementaire, afin de combler les failles des banques d'importance systémique.
+Concernant le lobbying agressif et les pressions sur le Parlement, les parlementaires ont confié s'être sentis soumis à une pression intense et inconfortable de la part des lobbyistes, craignant des sanctions financières, notamment la suppression de subventions pour leur parti s'ils soutenaient la réglementation bancaire. Ceci interpelle beaucoup la Commission de gestion.
+Concernant la tentative de déstabilisation des institutions, autre sujet extrêmement critique pour la Commission de gestion, au-delà du cas de la presse où UBS a retiré ses publicités au journal "Finanz und Wirtschaft" en raison de sa ligne éditoriale, des manoeuvres ont été entreprises pour diviser le Conseil fédéral, à tel point que le gouvernement a exceptionnellement rendu public le fait que les choix qu'il a faits quant au projet de réglementation bancaire se sont faits à l'unanimité. Le Conseil fédéral est conscient qu'il évolue en terrain miné, mais il veut tenir le cap qu'il s'est fixé. Il transmettra bientôt ses propositions au Parlement, ce dont nous lui savons gré.
 </t>
   </si>
   <si>
     <t xml:space="preserve">376073</t>
   </si>
   <si>
-    <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il vous fournit aussi des explications concernant les écarts par rapport aux objectifs, et présente les principaux objets non planifiés.
-En 2025, les droits de douane introduits en août sur les exportations suisses vers les États-Unis ont fortement mobilisé le Conseil fédéral. Par ailleurs, les questions de compétitivité de l'économie suisse, les oeuvres </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il vous fournit aussi des explications concernant les écarts par rapport aux objectifs, et présente les principaux objets non planifiés.
+    <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il vous fournit aussi des explications concernant les écarts par rapport aux objectifs et présente les principaux objets non planifiés.
+En 2025, les droits de douane introduits en août sur les exportations suisses vers les États-Unis ont fortement mobilisé le Conseil fédéral. Par ailleurs, les questions de compétitivité de l'économie suisse, les oeuvres s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il vous fournit aussi des explications concernant les écarts par rapport aux objectifs et présente les principaux objets non planifiés.
 En 2025, les droits de douane introduits en août sur les exportations suisses vers les États-Unis ont fortement mobilisé le Conseil fédéral. Par ailleurs, les questions de compétitivité de l'économie suisse, les oeuvres sociales et les sujets de sécurité ont figuré au tout premier plan. Comme chaque année, le rapport de gestion offre une très bonne opportunité d'échange, de dialogue, entre le Parlement et le Conseil fédéral. J'aimerais à mon tour remercier les Commissions de gestion et les rapporteurs qui se sont exprimés sur ce rapport.
 Tout d'abord, je vais rappeler brièvement le cadre politique du Conseil fédéral, à savoir les quatre lignes directrices de la législature de 2023 à 2027. Ensuite, j'en viendrai aux points essentiels du travail accompli par le gouvernement l'année passée, soit la deuxième année de la législature.
-La première ligne directrice s'intitule "la Suisse assure durablement sa prospérité, saisit les chances qu'offre le numérique", la deuxième ligne directrice, "la Suisse encourage la cohésion nationale et intergénérationnelle", la troisième ligne directrice, "la Suisse assure la sécurité, oeuvre en faveur de la paix et agit de manière cohérente et fiable sur le plan international" et la quatrième ligne directrice, "la Suisse protège le climat et prend soin des ressources naturelles". Ces lignes directrices sont subdivisées en 25 objectifs, qui regroupent un total de 148 mesures pour l'année 2025. Le Conseil fédéral a entièrement mis en oeuvre 88 de ces objets, et 9 n'ont été que partiellement réalisés.
-J'aborde maintenant les points forts de l'année passée. Pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices. Tout d'abord la première ligne directrice relative à la prospérité et au numérique : en matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur deux axes principaux : l'amélioration des conditions-cadres pour l'ensemble des entreprises et la réduction de la charge réglementaire.
+La première ligne directrice s'intitule "la Suisse assure durablement sa prospérité, saisit les chances qu'offre le numérique"[NB]; la deuxième ligne directrice, "la Suisse encourage la cohésion nationale et intergénérationnelle"[NB]; la troisième ligne directrice, "la Suisse assure la sécurité, oeuvre en faveur de la paix et agit de manière cohérente et fiable sur le plan international"[NB]; et la quatrième ligne directrice, "la Suisse protège le climat et prend soin des ressources naturelles". Ces lignes directrices sont subdivisées en 25 objectifs, qui regroupent un total de 148 mesures pour l'année 2025. Le Conseil fédéral a entièrement mis en oeuvre 88 de ces objets et 9 n'ont été que partiellement réalisés.
+J'aborde maintenant les points forts de l'année passée. Pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices, tout d'abord la première ligne directrice relative à la prospérité et au numérique. En matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur deux axes principaux[NB]: l'amélioration des conditions-cadres pour l'ensemble des entreprises et la réduction de la charge réglementaire.
 En ce qui concerne les finances, l'année 2025 a notamment été marquée par l'adoption du message concernant le programme d'allègement budgétaire 2027. Ce programme est essentiel pour rétablir l'équilibre entre les recettes et les dépenses de la Confédération dans les années à venir.
-S'agissant de la place financière suisse, le Conseil fédéral a défini les grandes lignes des révisions de loi et autres ordonnances dans le secteur bancaire.
+S'agissant de la place financière suisse, le Conseil fédéral a défini les grandes lignes des révisions de lois et autres ordonnances dans le secteur bancaire.
 En matière d'infrastructures et de transports, le Conseil fédéral a pris connaissance du rapport d'expertise intitulé "Transports 45" de l'École polytechnique fédérale de Zurich (EPFZ) sur l'aménagement des infrastructures de transport. Cette analyse indépendante présente les projets à réaliser en priorité du point de vue technique d'ici l'année 2045.
 Dans le domaine du numérique, l'année passée, le Conseil fédéral a approuvé le message concernant la nouvelle loi fédérale sur le dossier électronique de santé. Ce dossier est automatiquement mis à disposition de toute la population. Il vise à renforcer le système de santé en réunissant en un seul endroit toutes les informations de santé pertinentes de son titulaire.
-Venons-en maintenant à la deuxième ligne directrice relative à la cohésion nationale et intergénérationnelle : en ce qui concerne les affaires sociales, le Conseil fédéral a décidé des lignes directrices de la prochaine réforme de l'AVS. L'AVS 2030 vise à stabiliser et à moderniser cette assurance sociale. Elle prévoit des mesures visant à rendre le système plus équitable et à prolonger la vie active.
-En matière de santé, en 2025, le Conseil fédéral a approuvé le message sur la révision partielle de la loi sur les épidémies. Son but est d'améliorer la gestion des crises de santé publique, et surtout, de mieux protéger la population contre de futures pandémies.
+Venons-en maintenant à la deuxième ligne directrice relative à la cohésion nationale et intergénérationnelle. En ce qui concerne les affaires sociales, le Conseil fédéral a décidé des lignes directrices de la prochaine réforme de l'AVS. L'AVS 2030 vise à stabiliser et à moderniser cette assurance sociale. Elle prévoit des mesures visant à rendre le système plus équitable et à prolonger la vie active.
+En matière de santé, en 2025, le Conseil fédéral a approuvé le message sur la révision partielle de la loi sur les épidémies. Son but est d'améliorer la gestion des crises de santé publique et, surtout, de mieux protéger la population contre de futures pandémies.
 Concernant le système de santé lui-même, le Conseil fédéral a approuvé Tardoc, le nouveau système tarifaire global pour les prestations médicales ambulatoires. Celui-ci tient mieux compte des besoins de la médecine de famille, il simplifie la facturation et limite les incitations à accroître les quantités de prestations facturées.
 J'en viens maintenant à la troisième ligne directrice, qui concerne la sécurité et l'action sur le plan international. Sur le plan de la politique extérieure et de la coopération internationale, le Conseil fédéral a défini les priorités thématiques pour la présidence suisse de l'OCDE cette année, en 2026. Ces priorités incluent, entre autres, un renforcement du dialogue inclusif entre les 57 États participants.
 Concernant le chapitre de la reconstruction de l'Ukraine, le Conseil fédéral a fixé les priorités du programme pour l'Ukraine 2025-2028. Vous le savez, ce programme marque le début d'un processus de soutien fédéral de 12 ans pour la reconstruction, les réformes et le développement durable en Ukraine.
 En matière de sécurité, le Conseil fédéral, en 2025, a adopté le message sur l'armée 2025. Le programme d'armement 2025 vise à combler des lacunes capacitaires dans l'effet obtenu contre des cibles au sol, dans les domaines de la conduite, de la mise en réseau et du renseignement, ainsi que dans le cyberespace et l'espace électromagnétique.
 Finalement, j'en arrive à la quatrième et dernière ligne directrice, qui concerne le climat et les ressources naturelles. Dans le domaine de la politique agricole, le Conseil fédéral a adopté le message sur la révision partielle du droit foncier rural. Il entend, par cette révision, renforcer la position des conjoints dans les exploitations agricoles ainsi que le principe de l'exploitation à titre personnel, tout en accordant aux agriculteurs une plus grande liberté entrepreneuriale.
 En matière d'énergie, le Conseil fédéral a adopté le message concernant une révision de la loi sur les installations électriques visant à accélérer les procédures d'autorisation pour l'extension et la transformation des réseaux électriques.
-Parmi les autres points forts de l'année dernière figurait également l'adoption de plusieurs stratégies, notamment la stratégie nationale contre le racisme et l'antisémitisme 2026-2031, la stratégie Asie G20 pour la période 2025 à 2028, et la stratégie du Conseil fédéral en matière de politique d'armement. Le Conseil fédéral a également adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
+Parmi les autres points forts de l'année dernière figurait également l'adoption de plusieurs stratégies, notamment la stratégie nationale contre le racisme et l'antisémitisme 2026-2031, la stratégie Asie G20 pour la période 2025 à 2028 et la stratégie du Conseil fédéral en matière de politique d'armement. Le Conseil fédéral a également adopté d'importants messages sur des sujets comme les marchés financiers, le logement, la migration et la sécurité.
 En conclusion, vous trouvez la totalité des messages, rapports, plans d'action et stratégies détaillés, avec la date de leur adoption, dans notre rapport de gestion pour l'année 2025. Encore une fois, au nom du Conseil fédéral, je vous remercie de votre reconnaissance, de votre coopération et de votre soutien. Le Conseil fédéral va continuer à s'engager pleinement pour la défense des intérêts du pays et pour le bien de sa population.
 </t>
   </si>
@@ -744,7 +742,7 @@
 Nachdem in der Berichterstattung in den Medien bezüglich dieser Mehreinnahmen aus Genf etwas Verwirrung gestiftet wurde, möchte ich das noch einmal erklären und präzisieren. Ich verweise auch auf die Staatsrechnung, Band IA, Seite 40. Sie können sich erinnern: Im letzten Frühjahr erhielten wir die Meldung aus Genf, dass für die Rechnung 2025 Mehrerträge von etwa 500 Millionen Franken aus den Jahren 2022 und 2023 anfallen werden. Diese Mehrerträge gehen massgeblich auf den Rohstoffhandel zurück. Dann gab es eine weitere Meldung - sie traf just am Tag ein, als die Finanzkommission des Ständerates ihre Beratung aufnahm: Es würden noch einmal Mehreinnahmen aus Genf im Umfang von etwa einer Milliarde Franken kommen. Der Grund dafür war, dass der Kanton Genf während der ziemlich langen Periode zwischen 2019 und 2024 keine provisorischen Rechnungen ausgestellt hatte. Die Einnahmenschätzungen des Bundes basieren auf den provisorischen Gewinnsteuerrechnungen der Kantone. Ohne provisorische Rechnungen weiss man auch nicht, welche Erträge kommen.
 Wenn also in den Medien stand, alle zusätzlichen Einnahmen seien auf den Rohstoffhandel zurückzuführen, ist das nicht korrekt. Ein Teil war wirklich auf diesen Informatikfehler der Genfer zurückzuführen; wir konnten das auch nicht antizipieren.
 Wenn man auf die Ausgaben schaut, dann muss man sagen, dass die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget lagen. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden relativ tief ausfielen. Die Kreditreste sind aufgrund der Kürzungen, die wir in den Budgets 2024 und 2025 vorgenommen hatten, sowieso viel tiefer. Im ausserordentlichen Haushalt hingegen waren die Ausgaben höher als die Einnahmen. Hier verzeichneten wir ein Defizit von rund 900 Millionen Franken. Die beiden grössten ausserordentlichen Ausgaben waren diejenige für die Schutzsuchenden aus der Ukraine - das waren 700 Millionen Franken von total 1,5 Milliarden an ausserordentlichen Ausgaben - sowie der einmalige Kapitalzuschuss an die SBB in Höhe von 850 Millionen. Die Tatsache, dass diese 850 Millionen Franken erst im Jahr 2025 ausbezahlt wurden, war der Grund für die Rechnungsverbesserung im Jahr 2024.
-Vous vous souvenez que nous avions prévu de verser 1 milliard de francs aux CFF en 2024. Le Parlement n'était pas tout à fait prêt ; par la suite, le Parlement a réduit la somme. Cette somme réduite - soit 850 millions de francs - a été versée en 2025 seulement.
+Vous vous souvenez que nous avions prévu de verser 1,15 milliard de francs aux CFF en 2024. Le Parlement n'était pas tout à fait prêt ; par la suite, le Parlement a réduit la somme. Cette somme réduite - soit 850 millions de francs - a été versée en 2025 seulement.
 Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich zum Abbau der Covid-Schulden verbucht. Das ist so vorgesehen. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
 Ich komme nun zum Ausblick. Wie üblich wird der Bundesrat Ende Juni die Zahlen zum Voranschlag 2027 und dann auch die Zahlen zum Finanzplan 2028 bis 2030 festlegen. Die Arbeiten hierzu laufen noch. Wie bereits den Nationalrat möchte ich auch Sie an dieser Stelle über den Zwischenstand dieser Arbeiten informieren. Dieser Zwischenstand stützt sich primär auf die erfolgten Budgeteingaben der Departemente und auf die seit April aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge für die Schätzung im wichtigen Monat April gemeldet haben. Der Zwischenstand stützt sich also auf die provisorischen Steuerrechnungen; diese liegen jeweils Ende April vor.
 Demnach dürfte sich im Vergleich zur Standortbestimmung im April auf der Ausgabenseite für den Voranschlag 2027 nochmals eine Verschlechterung von voraussichtlich rund 300 Millionen Franken ergeben. Grund für diese Verschlechterung sind primär Schätzkorrekturen bei den Sozialversicherungen und bei der Migration. Auf der Einnahmenseite zeichnet sich hingegen bei der Gewinnsteuer für juristische Personen eine deutliche Verbesserung ab, und dies unabhängig vom Effekt Genf, den wir bereits kannten und den wir entsprechend eingepreist haben. Sie können sich erinnern: Wir haben einen Teil für 2026 budgetiert.
@@ -800,6 +798,314 @@
 La Commission de rédaction a proposé de modifier le texte de la loi sur le plan formel en proposant que la réhabilitation soit plus explicite que dans le texte original, qui est un texte repris de la dernière loi que notre Parlement a adoptée à ce sujet, c'est-à-dire en 2009. Après avoir examiné cette proposition, les Commissions des affaires juridiques des deux conseils ont décidé, à leurs séances respectives des 4 et 10 juin de cette année, qu'il était opportun de modifier le texte. Pour simplifier la procédure, elles ont décidé de confier la tâche à la Commission de rédaction, évitant ainsi un tour supplémentaire d'élimination des divergences.
 Sans entrer sur le fond, l'objectif est que l'article 2 soit consacré à la réhabilitation et mentionne que toutes les personnes qui ont été sanctionnées sont réhabilitées. La suite est inchangée. Ensuite, l'article 3 est intitulé "Conséquences juridiques", avec le deuxième alinéa qui devient l'alinéa 1 et énonce que la réhabilitation a pour effet d'annuler les jugements. La suite est inchangée. L'article 4, qui dit que cette réhabilitation n'ouvre aucun droit à des dommages-intérêts ni à une indemnité pour tort moral en raison des sanctions qui ont été prononcées ou des conséquences indirectes des jugements pénaux ou des décisions administratives prononcées à l'époque, devient l'alinéa 2 de l'article 3.
 La minorité défendra sa position.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weichelt Manuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das vergangene Geschäftsjahr stand im Zeichen eines wichtigen rechtsstaatlichen Jubiläums: 150 Jahre Bundesgericht. Tragen wir Sorge zu unseren Errungenschaften. Respektieren wir die Gewaltenteilung und achten wir unsere Bundesverfassung sowie die Gesetze.
+Die Subkommissionen Gerichte/Bundesanwaltschaft der beiden GPK haben ihre Aufsichtssitzung im April zum Geschäftsbericht traditionsgemäss in Lausanne am Bundesgericht durchgeführt. An der Mai-Sitzung des Plenums der GPK-N haben zudem sowohl de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das vergangene Geschäftsjahr stand im Zeichen eines wichtigen rechtsstaatlichen Jubiläums: 150 Jahre Bundesgericht. Tragen wir Sorge zu unseren Errungenschaften. Respektieren wir die Gewaltenteilung und achten wir unsere Bundesverfassung sowie die Gesetze.
+Die Subkommissionen Gerichte/Bundesanwaltschaft der beiden GPK haben ihre Aufsichtssitzung im April zum Geschäftsbericht traditionsgemäss in Lausanne am Bundesgericht durchgeführt. An der Mai-Sitzung des Plenums der GPK-N haben zudem sowohl der Gerichtspräsident als auch die Subkommission entsprechend informiert.
+Bis auf das Patentgericht haben alle Gerichte einen Geschäftsanstieg zu verzeichnen. Das Bundesgericht hat einen Anstieg von rund 7 Prozent gegenüber dem Vorjahr zu verzeichnen. Dieser im Vergleich zu früheren Jahren geringere Anstieg zeigt, dass die Neuorganisation vor einigen Jahren allmählich Früchte trägt. Die durchschnittliche Verfahrensdauer verkürzte sich um einige Tage. Leicht weniger Beschwerden wurden gutgeheissen. Das Bundesgericht veröffentlichte 213 Urteile, auch, um die Transparenz der Rechtsprechung zu gewährleisten.
+Im Vergleich zum Bundesgericht verfügt das Bundesstrafgericht über eine kurze institutionelle Geschichte. Die Strafkammer konnte die Zahl der hängigen Verfahren reduzieren, hatte aber gleichzeitig mehrere grosse bedeutende Verfahren zu bearbeiten, beispielsweise bezüglich Bestechung fremder Amtsträger im internationalen Handel mit Erdölprodukten.
+Die Beschwerdekammer hatte Ende des Jahres mehr hängige Verfahren. Dies unter anderem aufgrund der Zunahme der Verfahren im Verwaltungsstrafrecht und im Bereich der internationalen Rechtshilfe.
+Die Berufungskammer hatte eine weitere Zunahme der Verfahren zu verzeichnen; diese betrafen das Unternehmensstrafrecht, Geldwäscherei, Insider Tradings, Terrorismus sowie die Bankomatensprengungen.
+Es wurde auch darauf hingewiesen, dass die nebenamtlichen Richterpersonen aufgrund ihrer hauptberuflichen Auslastung zeitlich nicht so flexibel sind, wie es ursprünglich angedacht war.
+Interessant für das Parlament sind auch immer die Hinweise an den Gesetzgeber. So hat das Bundesstrafgericht beispielsweise den EFK-Bericht bezüglich den Einziehungen und Ersatzforderungen nach Artikel 70 ff. StGB ernst genommen. Damit sich der Grundsatz "Strafbares Handeln soll sich nicht lohnen" auch richtig umsetzen lässt, wird angeregt, ein vereinfachtes Vollstreckungsverfahren zu schaffen, damit die Ersatzforderungen schnell eingetrieben werden können. Das ist ein wichtiger Punkt bei der Bekämpfung der Wirtschaftskriminalität.
+Das Bundesverwaltungsgericht verzeichnet erneut einen markanten Anstieg der Geschäftslast. Eine bessere Koordination zwischen dem SEM und dem Bundesverwaltungsgericht wäre mehr als wünschenswert. Es gab 70 neue Stellen beim SEM, aber nur eine Mikroerhöhung des Stellenetats beim Bundesverwaltungsgericht in St. Gallen. Eine bessere Koordination hätte da zu einer besseren Lösung führen können.
+Die durchschnittliche Verfahrensdauer konnte man jedoch reduzieren. Gleichzeitig hat man in St. Gallen aber auch viel in die Digitalisierung investiert. Das Ziel, Papier definitiv beiseite zu lassen, rückt immer näher. Die Spruchkörperbildung soll ab 2027 mit dem System "Diva" durchgeführt werden und den Abteilungspräsidien eine grosse Entlastung bringen.
+Das Bundespatentgericht verzeichnete einen Rückgang an Eingängen. Kein Fall ist länger als zwei Jahre hängig. Der Grund liegt vermutlich in der Bildung des Einheitlichen Patentgerichts (EPG). Dieses erlässt Verbote, die für bis zu 18 Länder gelten, und kann Patente für alle angeschlossenen Länder für ungültig erklären. Die Teilnahme am System steht nur für EU-Staaten offen, hat aber auch Auswirkungen auf die Schweiz.
+Das Bundespatentgericht in der Schweiz hat sich das Ziel gesetzt, das schnellste Gericht in Europa zu werden. Hierfür hat es unter anderem ein beschleunigtes Nichtigkeitsverfahren eingeführt.
+Ich sage noch einige wenige Worte zum Militärkassationsgericht. Dieses gehört nicht zum Bundesgericht, wie Sie wissen, aber auch hier hat die Bundesversammlung die Oberaufsicht. Deshalb erlaube ich mir dazu noch zwei, drei Sätze.
+Die zuständigen Subkommissionen des Ständerates und Nationalrates konnten vom Geschäftsbericht des Militärkassationsgerichtes keine Kenntnis nehmen. Grund: Wir haben keinen erhalten. Das ist unbefriedigend und nicht tolerierbar.
+Einige Worte zur Arbeit in der GPK im Zusammenhang mit den Gerichten: Wir haben einige Motionen und Berichte gemacht. Ich möchte Ihnen ganz kurz den Stand mitteilen:
+1. Die parlamentarische Initiative der GPK, "Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken", ist zurzeit in der RK-S.
+2. Die Erhöhung der Obergrenze der Gerichtsgebühren des Bundesgerichtes und der anderen erstinstanzlichen Gerichte wurde von der RK-N im Rahmen einer grösseren Revision behandelt.
+3. Die Motion zur Reorganisation des Bundesstrafgerichtes wurde in der RK-N einstimmig gutgeheissen. Die Unabhängigkeit der ersten und zweiten Instanz soll damit besser gewährleistet werden. Dabei stützt sich die RK auf den Bericht der GPK von 2022.
+4. Den Bericht zum System der nebenamtlichen Richterinnen und Richter konnte die Subkommission Gerichte in der RK-N vorstellen. Wir gehen davon aus, dass sie diesbezüglich ebenfalls aktiv werden.
+Ich möchte nicht schliessen, ohne dem Präsidenten des Bundesgerichtes und allen, die zum reibungslosen Funktionieren der Bundesjustiz beitragen, sowie dem Sekretariat der Geschäftsprüfungskommission für ihre Arbeit ganz herzlich zu danken. Es versteht sich von selbst, dass beaufsichtigte Stellen nicht alle Fragen der Aufsicht lieben. Das müssen sie auch nicht. Wir haben alle das gleiche Ziel: eine gut funktionierende und von der Politik unabhängige Justiz. Eine solche ist unabdingbar für eine Demokratie, in der heutigen Zeit mehr denn je.
+Ich bitte Sie, den Geschäftsbericht 2025 des Bundesgerichtes zu genehmigen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jans Beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerne nehme ich wie folgt zu den einzelnen Vorstössen Stellung. 
+Ich starte mit der Motion 26.3067 der SVP-Fraktion. Keiner der fünf genannten Staaten erfüllt die Bedingungen für die Bezeichnung als "Safe Country". Eine Mitgliedschaft im Europarat oder eine Bezeichnung als "sicher" durch die EU reicht dafür nicht aus. Relevant ist, ob ein Staat tatsächlich die gesamte Bevölkerung vor unrechtmässiger Verfolgung schützt. Dies ist in den Staaten, die Sie erwähnen, nicht der Fall. 
+Wichtig ist aller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerne nehme ich wie folgt zu den einzelnen Vorstössen Stellung. 
+Ich starte mit der Motion 26.3067 der SVP-Fraktion. Keiner der fünf genannten Staaten erfüllt die Bedingungen für die Bezeichnung als "Safe Country". Eine Mitgliedschaft im Europarat oder eine Bezeichnung als "sicher" durch die EU reicht dafür nicht aus. Relevant ist, ob ein Staat tatsächlich die gesamte Bevölkerung vor unrechtmässiger Verfolgung schützt. Dies ist in den Staaten, die Sie erwähnen, nicht der Fall. 
+Wichtig ist allerdings zu wissen: Ein Safe Country in der EU bedeutet nicht dasselbe wie ein Safe Country in der Schweiz. In der EU können Asylgesuche nur dann im beschleunigten Verfahren behandelt werden, wenn sie aus einem Safe Country stammen. Im Gegensatz dazu können wir in der Schweiz Asylgesuche aller Herkunftsstaaten im beschleunigten Verfahren behandeln. Sie sehen: Die Auswirkungen einer Bezeichnung als Safe Country in der Schweiz sind aktuell gering. 
+Wenn wir die Liste der sicheren Herkunftsländer nun einfach nach Belieben erweitern, verletzen wir damit nicht nur das geltende Asylgesetz, das von der Bevölkerung mit deutlicher Mehrheit angenommen wurde, sondern wir täuschen auch eine Wirkung vor, die eine solche Bezeichnung in der Realität gar nicht hat. 
+Vielmehr müssen wir unser Safe-Country-Konzept so anpassen, dass es zu einem griffigen Instrument wird. Die entsprechenden Arbeiten hat mein Departement bereits eingeleitet. Im Rahmen der Asylstrategie werden aktuell Anpassungen und Alternativen geprüft. 
+Vor diesem Hintergrund beantragt der Bundesrat Ihnen, die Motion abzulehnen. 
+Ich komme zur zweiten Motion der SVP-Fraktion (26.3130). Personen, die eine Gefahr für die öffentliche Sicherheit und Ordnung darstellen, sollen in der Schweiz keine Aufenthaltsbewilligung erhalten. Darüber sind wir uns einig. Die zuständigen Behörden können die Erteilung von Bewilligungen bereits heute konsequent verweigern, wenn Vorstrafen bekannt sind. Es handelt sich um bewährte Bestimmungen, sowohl im Ausländer- und Integrationsgesetz als auch im Freizügigkeitsabkommen. 
+Zu Ihrer Forderung nach dem systematischen Verlangen eines Strafregisterauszugs: Bei Drittstaatsangehörigen können die Behörden bereits heute einen Strafregisterauszug aus dem Herkunftsland verlangen, und zwar auch systematisch. Im Anwendungsbereich des Freizügigkeitsabkommens ist dies rechtlich anders geregelt. Die systematische Einholung von Strafregisterauszügen würde das Freizügigkeitsabkommen und die völkerrechtlichen Pflichten der Schweiz verletzen. Bei Verdachtsmomenten dürfen die Kantone aber jederzeit einen Strafregisterauszug einfordern. Die Kantone sollen weiterhin entscheiden, wann das Einholen eines Strafregisterauszugs aus dem Herkunftsland sinnvoll erscheint. Tatsächlich verlangen viele Kantone bereits heute vor der Erteilung einer Bewilligung einen Strafregisterauszug. Eine Anpassung der gesetzlichen Grundlagen ist deshalb nicht nötig. 
+Der Bundesrat beantragt Ihnen deshalb, die Motion abzulehnen.
+Ich komme nun zur Motion 24.4507 der FDP-Fraktion, "Verschärfung der Landesverweisung für straffällige Drittstaatsangehörige". Um eine Person aus dem Land zu verweisen, muss sie zuerst eine unbedingte und freiheitsentziehende Strafe verbüsst haben. Straffällige Asylsuchende müssen wir aber auch durch das Refoulement-Verbot schützen. Das steht so in unserer Verfassung. Das SEM behandelt ihre Gesuche aber prioritär, sodass die Kantone den Landesverweis, wenn möglich und zulässig, schnell vollziehen können. Bei der obligatorischen Landesverweisung haben die Kantone keinen Ermessensspielraum. Die geltenden Regelungen ermöglichen auch einen konsequenten Vollzug bei einer nicht obligatorischen Landesverweisung. Hier müssen wir aber das Prinzip der Verhältnismässigkeit beachten. Das gibt unsere Verfassung ebenfalls vor.
+Sie wollten noch den Aspekt der EU anschauen. Im Schengen-Raum gibt es kein besonderes Modell, das den Vollzug von Wegweisungen nach einer strafrechtlichen Verurteilung einfacher oder effizienter machen würde. Die Schweiz arbeitet bei Rückführungen eng mit Frontex und den anderen Schengen-Staaten zusammen. Dazu gehören insbesondere gemeinsame Rückführungsflüge, mit denen auch Personen mit einer rechtskräftigen Landesverweisung in ihr Herkunftsland zurückgebracht werden. Schliesslich möchte ich noch darauf hinweisen, dass wir bereits daran sind, Optimierungsmassnahmen zu erarbeiten. Das tun wir im Rahmen der Umsetzung der Motion Salzmann 23.3082, "Rückführungsoffensive und konsequente Ausweisung von Straftätern und Gefährdern", sowie der Arbeiten der Taskforce Intensivtäter im Bereich Ausländer- und Asylbereich. Diese hat nicht nur Leute der Strafverfolgung zugeführt, sondern sie macht uns Vorschläge, wie wir den Handlungsspielraum beim Vollzug von Landesverweisungen erweitern können. Der Bundesrat beantragt deshalb, auch diese Motion abzulehnen.
+Ich komme zur Motion de Quattro 25.3062, "Den Begriff der Zwangskontrolle in unserer Gesetzgebung verankern". Was ist Zwangskontrolle? Unter Zwangskontrolle werden kontrollierende, manipulative Verhaltensweisen in Beziehungen verstanden, also der Umstand, dass ein Mann die Finanzen seiner Frau und ihre sozialen Kontakte kontrolliert oder generell ein respektloses oder eifersüchtiges Verhalten an den Tag legt, das die Bewegungsfreiheit und überhaupt die Freiheit der Partnerin einschränkt. Das ist ein Problem. Zwangskontrolle ist für Betroffene und Kinder schwerwiegend. Sie kann langfristige Folgen haben. Der Begriff ist jedoch weit gefasst und oft schwierig von problematischen, aber nicht zwingend rechtswidrigen Beziehungsmustern abzugrenzen. Der Bundesrat setzt deshalb den Schwerpunkt auf Prävention, Schutz und Unterstützung der Betroffenen. Bereits heute laufen mit dem Nationalen Aktionsplan zur Umsetzung der Istanbul-Konvention sowie der Roadmap "Häusliche Gewalt" zahlreiche Massnahmen, die Bund und Kantone zusammen durchführen. Zudem sollen weitere Verbesserungen beim Schutz vor häuslicher Gewalt im Zivil- und Zivilverfahrensrecht geprüft werden. Eine spezifische gesetzliche Regelung zur Zwangskontrolle lehnt der Bundesrat hingegen ab, und zwar aus rechtlichen Gründen. Im Strafrecht verlangt das Bestimmtheitsgebot klar definierte Straftatbestände. Viele Formen der Zwangskontrolle wären nur schwer abgrenzbar. Erreicht das Verhalten jedoch eine gewisse Schwere, kommen bereits heute Straftatbestände wie Nötigung, Drohung, Körperverletzung oder Stalking zur Anwendung. Auch das Zivil- und das Familienrecht bieten Schutzinstrumente, insbesondere zum Schutz von Kindern. Der Bundesrat beantragt daher, diese Motion abzulehnen.
+Nun zum Postulat Weber 25.4678: Der Bundesrat hat im Dezember 2025 die Strategie zur Bekämpfung der organisierten Kriminalität verabschiedet und erarbeitet nun einen nationalen Aktionsplan mit konkreten Massnahmen sowie ein Paket mit Gesetzesanpassungen. Der Bundesrat begrüsst die geforderte Prüfung. Die Strategie gegen die organisierte Kriminalität wäre nicht vollständig, wenn solche Ansätze nicht auch untersucht würden.
+Bereits jetzt werden rechtliche Anpassungen geprüft, um die Verfolgung von Geldwäscherei zu erleichtern und verdächtige Vermögenswerte schneller einfrieren und einziehen zu können. Alle Spezialistinnen und Spezialisten im Bereich der organisierten Kriminalität sagen, dass der Ansatz der Bekämpfung der Geldwäscherei der effizienteste Ansatz ist, um kriminelle Organisationen letztlich überführen zu können.
+Besondere Aufmerksamkeit gilt dabei der Vereinbarkeit mit den Grundrechten und den verfassungsrechtlichen Garantien. Die geltenden Regelungen müssen mit der Bundesverfassung, der Rechtsprechung des Bundesgerichtes, der Europäischen Menschenrechtskonvention sowie den grundlegenden Prinzipien des Strafrechts vereinbar bleiben. Der Bundesrat ist bereit, die im Postulat aufgeworfenen Fragen im Rahmen der laufenden Arbeiten vertieft zu analysieren und dabei auch internationale Erfahrungen zu berücksichtigen. Aus diesen Gründen beantragt der Bundesrat, dieses Postulat anzunehmen.
+Zum Schluss noch zur Motion Mahaim: Der Bundesrat ist sich der Gefahren im Zusammenhang mit sexualisierten Deepfakes bewusst. Er verfolgt in diesem Zusammenhang aufmerksam die aktuellen Ereignisse und gesetzgeberischen Entwicklungen auf internationaler Ebene, insbesondere in der Europäischen Union. Der schweizerische Rechtsrahmen ermöglicht es bereits heute, gegen Urheber solcher Deepfakes vorzugehen, z. B. zivilrechtlich im Bereich des Persönlichkeitsschutzes oder strafrechtlich wegen Pornografie oder Identitätsmissbrauch. Jedoch greifen diese Bestimmungen erst, wenn der Verstoss bereits stattgefunden hat. Sie schreiben keine besonderen Massnahmen vor, um die Erstellung solcher Inhalte zu verhindern.
+Am 12. Februar 2025 hat der Bundesrat angekündigt, das Rahmenübereinkommen des Europarates über künstliche Intelligenz, die KI-Konvention, ratifizieren zu wollen. Er erteilte meinem Departement diesbezüglich den Auftrag, eine Vernehmlassungsvorlage auszuarbeiten. Die geplanten Massnahmen im Rahmen der KI-Konvention greifen die Anliegen der Motion auf. Deshalb ist der Bundesrat bereit, diese Motion entgegenzunehmen und sie in diesem Rahmen zu beantworten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonio Giorgio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questa mozione nasce da una situazione che in Ticino, e in particolare nel Basso Mendrisiotto, conosciamo molto bene. Il progetto pilota previsto presso il Centro federale d'asilo di Pasture, situato tra Balerna e Novazzano, ha acceso un dibattito importante e ha sollevato interrogativi legittimi da parte delle autorità cantonali e comunali, così come della popolazione che vive quotidianamente quelle realtà. La proposta della SEM prevedeva di accogliere richiedenti l'asilo problematici in un'are</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questa mozione nasce da una situazione che in Ticino, e in particolare nel Basso Mendrisiotto, conosciamo molto bene. Il progetto pilota previsto presso il Centro federale d'asilo di Pasture, situato tra Balerna e Novazzano, ha acceso un dibattito importante e ha sollevato interrogativi legittimi da parte delle autorità cantonali e comunali, così come della popolazione che vive quotidianamente quelle realtà. La proposta della SEM prevedeva di accogliere richiedenti l'asilo problematici in un'area separata, senza tuttavia disporre di una base giuridica sufficientemente chiara che garantisse una gestione efficace delle situazioni più complesse e delle relative conseguenze sul territorio.
+Fin dall'inizio, i Comuni di Balerna, Chiasso e Novazzano, con alla testa i loro sindaci, hanno chiesto una cosa molto semplice, essere ascoltati ed essere coinvolti. Le autorità cantonali e comunali rappresentano infatti un patrimonio di esperienza prezioso. Chi vive quotidianamente una determinata realtà conosce le dinamiche del territorio, ne comprende le sensibilità e può contribuire a costruire soluzioni più efficaci e meglio condivise. I fatti hanno dimostrato la validità delle preoccupazioni espresse dal Cantone e dai Comuni, e la successiva rinuncia al progetto pilota ha confermato la necessità di un approccio maggiormente condiviso e di strumenti più adeguati per affrontare situazioni particolarmente delicate e al contempo complesse. 
+Per questo, la mozione che discutiamo oggi assume un significato che va ben oltre il singolo caso di Pasture. Essa riafferma un principio fondamentale del nostro federalismo. Le comunità che accolgono devono poter partecipare alle decisioni che potenzialmente incidono direttamente sulla loro realtà quotidiana. Cantoni e Comuni devono essere coinvolti fin dall'inizio nei processi decisionali, in qualità di partner istituzionali chiamati a contribuire alla costruzione di soluzioni efficaci e sostenibili.
+Questo principio assume un valore particolare per un Cantone di confine come il Ticino, che da anni affronta le sfide legate alla gestione dei flussi migratori e che si trova spesso in prima linea nell'applicazione concreta delle decisioni che il governo e il Parlamento prendono. Il Basso Mendrisiotto, come l'intero Ticino, ha sempre dimostrato la sua disponibilità e senso di responsabilità nell'accoglienza. Proprio grazie a questa esperienza è importante la loro partecipazione alle decisioni che interessano direttamente il territorio. 
+La mozione chiede inoltre di dotare il sistema di basi giuridiche chiare e strumenti adeguati per affrontare i casi riguardanti i richiedenti l'asilo problematici e con comportamenti recidivi. Anche qui si tratta di una richiesta fondata sul buonsenso e sull'esperienza maturata sul campo. Una politica dell'asilo credibile richiede ovviamente attenzione verso le persone che cercano protezione, ma allo stesso tempo deve garantire il rispetto delle regole condivise nelle realtà comunali e cantonali. Accoglienza e sicurezza devono procedere di pari passo, poiché una gestione ordinata e responsabile rafforza la fiducia della popolazione verso le istituzioni e la politica e crea le condizioni di fondo, affinché la tradizione umanitaria del nostro Paese possa continuare nel tempo. 
+Vi è infine, non certamente per importanza, un elemento politico che merita di essere sottolineato. Anche il Consiglio federale, nella sua presa di posizione del 27 maggio 2026, raccomanda l'accoglimento di questa mozione. Questo è indubbiamente uno dei segnali più significativi, in quanto indica che il governo riconosce il valore del contributo dei territori e la necessità di rendere il sistema più efficace nella gestione delle situazioni complesse. Questo a beneficio degli uni, i richiedenti l'asilo stessi, e degli altri, i Comuni, i Cantoni e i rispettivi cittadini. Quando le esperienze maturate sul territorio trovano ascolto a livello federale, il nostro sistema istituzionale dimostra la propria capacità di correggersi e migliorarsi.
+Per queste ragioni vi invito, a nome della maggioranza della commissione, a sostenere la mozione. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat beantragt die Annahme aller drei Punkte dieser Motion. Ich erlaube mir allerdings zu sagen, dass ich die Einschätzung der Minderheit Gysin Greta teile, dass diese Motion gar nichts ändert. Man kann die Motion deshalb ablehnen oder annehmen - es läuft auf dasselbe hinaus. 
+Zum ersten Punkt, den diese Motion fordert: Das Pilotprojekt "Bedarfsorientierte Unterbringung" ist eine interne Massnahme im Rahmen des Belegungsmanagements der Bundesasylzentren. Der Bundesrat ist jedoch damit e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat beantragt die Annahme aller drei Punkte dieser Motion. Ich erlaube mir allerdings zu sagen, dass ich die Einschätzung der Minderheit Gysin Greta teile, dass diese Motion gar nichts ändert. Man kann die Motion deshalb ablehnen oder annehmen - es läuft auf dasselbe hinaus. 
+Zum ersten Punkt, den diese Motion fordert: Das Pilotprojekt "Bedarfsorientierte Unterbringung" ist eine interne Massnahme im Rahmen des Belegungsmanagements der Bundesasylzentren. Der Bundesrat ist jedoch damit einverstanden, dass allfällige Standorte für das Pilotprojekt nur mit Zustimmung der betroffenen Standortkantone und Standortgemeinden ausgewählt werden. Das erhöht die Akzeptanz für das Projekt. Das SEM hat dem Kanton Tessin die Einstellung des Projekts bereits zugestanden. Ich möchte hier allerdings darauf hinweisen, dass es ein Projekt zum Schutz der Tessiner Bevölkerung ist. Dieses Pilotprojekt soll eben genau die Möglichkeiten dafür verbessern, dass im Umfeld von Asylzentren weniger Sicherheitsrisiken bestehen. Genau das ist das Ziel des Projektes. Wenn der Standortkanton es trotzdem nicht will, dann trägt er auch die Verantwortung dafür, dass die Sicherheit dann halt nicht im Vordergrund steht. 
+Zum zweiten Punkt der Motion: Die Arbeiten zu Gesetzesanpassungen im Bereich der erwähnten Disziplinar- und Verwaltungsinstrumente sind teilweise bereits abgeschlossen. Verschiedene Änderungen im Asylgesetz betreffend die Sicherheit und den Betrieb der Bundesasylzentren sind am 1. Juni 2026 in Kraft getreten. Das SEM hat seither auch die Möglichkeit, Disziplinarmassnahmen auszusprechen, wenn die öffentliche Sicherheit und Ordnung in der Umgebung der Zentren gefährdet werden. Weitere Massnahmen zur Verbesserung des Wegweisungsvollzugs werden derzeit unter anderem im Rahmen der Motion Salzmann 23.3082, "Rückführungsoffensive und konsequente Ausweisung von Straftätern und Gefährdern", geprüft; ich habe das heute schon mal gesagt. Das EJPD wird dem Bundesrat das entsprechende Konzept bis Ende des Jahres unterbreiten. In diesem Rahmen werden ebenfalls Gesetzesanpassungen geprüft. Das Anliegen der Motion wird also bereits längstens aufgenommen; auch hier ist diese Motion eigentlich erfüllt. 
+Zum dritten Punkt: Dem Bundesrat ist es ein grosses Anliegen, dass Kantone und Gemeinden im Rahmen der Asylstrategie 2027 vollständig eingebunden werden. Das ist ja die Idee dieser Asylstrategie. Der Bundesrat hat sie auch deshalb aufgegleist, damit die Kantone von Anfang an vollwertig bei diesen für sie wichtigen Entscheiden dabei sind; das ist heute schon der Fall. Sie können es jetzt auch noch mit dieser Motion fordern, aber auch hier sind wir eigentlich längstens auf Kurs. Zudem sieht das politische Mandat vor, dass die beschlossenen Massnahmen zu keinen Lastenverschiebungen führen dürfen. Die Motion unterstützt die Bestrebungen des Bundesrates bzw. meines Departementes, und in diesem Sinne kann man sie auch annehmen. Aus all diesen Gründen beantragt der Bundesrat, diese Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schmid Pascal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit dieser Motion verlangen wir, dass die drei Maghreb-Staaten Marokko, Tunesien und Algerien sowie Ägypten und die Türkei als sicher eingestuft werden. Diese Einstufung ist ein wichtiges Mittel, um die Attraktivität der Schweiz als Asylland zu senken. Aus diesem Grund hat die EU vor wenigen Monaten eine Ausweitung der Liste der sicheren Länder beschlossen. Deshalb muss die Schweiz jetzt dringend nachziehen. Wenn wir jetzt nicht handeln, dann führt das zu einer riesigen Sogwirkung in die Schweiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit dieser Motion verlangen wir, dass die drei Maghreb-Staaten Marokko, Tunesien und Algerien sowie Ägypten und die Türkei als sicher eingestuft werden. Diese Einstufung ist ein wichtiges Mittel, um die Attraktivität der Schweiz als Asylland zu senken. Aus diesem Grund hat die EU vor wenigen Monaten eine Ausweitung der Liste der sicheren Länder beschlossen. Deshalb muss die Schweiz jetzt dringend nachziehen. Wenn wir jetzt nicht handeln, dann führt das zu einer riesigen Sogwirkung in die Schweiz. Dabei haben wir schon jetzt Rekordbestände im Asylbereich, wir haben Milliardenkosten und riesige, ungelöste Probleme. Auch die Staatspolitische Kommission des Nationalrats hat entschieden, Marokko und Tunesien als sicher einzustufen, und eine an den Bundesrat überwiesene Motion der Finanzkommission des Ständerates fordert dasselbe. 
+Überall in Europa werden die Schrauben im Asylbereich angezogen. Länder wie Dänemark, Schweden und Österreich haben begriffen, dass es so wie bisher nicht weitergehen kann. Nur der Bundesrat will nichts tun. Personen aus sicheren Ländern werden nicht vom Asylrecht ausgeschlossen; es gilt einfach eine erhöhte Mitwirkungspflicht, und diese dürfen wir hier auch verlangen. Seit 2010 haben sich die Asylgesuche aus Nordafrika und der Türkei verfünffacht - verfünffacht! -, und das, ohne dass sich an der Situation in den Herkunftsländern wirklich etwas negativ verändert hätte, im Gegenteil: Diese sind alle sicherer geworden. Es sind alles Tourismusdestinationen, die jährlich zu Tausenden von Schweizern und Schweizerinnen bereist werden. Der massive Anstieg liegt also offensichtlich nur an der viel zu hohen Attraktivität unseres Landes. 
+Bei Nordafrikanern ist die Anerkennungsquote extrem tief. Die allermeisten Asylsuchenden aus Nordafrika sind keine Flüchtlinge, dafür sind sie extrem häufig kriminell. So begehen zum Beispiel Algerier 45-mal mehr Gewaltdelikte als Schweizer und 17-mal mehr Sexualdelikte als Schweizer. Wer will diese Zuwanderung in unser Land? Diese Personen geben vor, zu Hause verfolgt zu sein, und sie werden zum Dank hier zu Tausenden kriminell. Diese Zuwanderung bringt uns keine Fachkräfte, sondern Probleme, Gewalt und Kriminalität. Wenn unsere Bevölkerung im eigenen Land vor Schutzsuchenden Schutz suchen muss, dann stimmt etwas nicht mehr. Und ich staune immer wieder, mit welcher Gelassenheit das hier in Bern einfach hingenommen wird. Denken Sie an den Abstimmungssonntag: Über 45 Prozent der Schweizerinnen und Schweizer und zwölf Kantone haben klargemacht, dass es so wie bisher mit der Zuwanderung in unser Land nicht weitergehen kann. Die Gegner der Initiative haben im Abstimmungskampf viel versprochen, sehr viel. Sogar der Bundesrat hat angekündigt, die Asylgesuche deutlich zu senken. So steht im Abstimmungsbüchlein auf Seite 19, er wolle "die Zahl der Asylgesuche deutlich reduzieren". Heute können Sie alle beweisen, dass Sie ihr Wort halten, auch Sie, Herr Bundesrat Jans. 
+Es braucht jetzt eine Kehrtwende im Asylbereich. Es braucht endlich eine Asylpolitik für unsere Bevölkerung. Denn die heutige Asylpolitik der Schweiz ist das Gegenteil davon: Sie ist eine Zumutung für unsere Bevölkerung. Um nichts tun zu müssen, werden uns vom Bundesrat bei den Beantwortungen unserer Vorstösse in den Kommissionen und hier drin immer die gleichen Ausreden, Ausflüchte und Gründe aufgezählt, wieso man nichts tun könne. Was dabei vergessen geht: Nicht nur Asylsuchende haben Menschenrechte, auch unsere Bevölkerung hat Menschenrechte. Und die Sicherheit unserer Bevölkerung hat Vorrang. Wenn wir jetzt nicht handeln, wenn wir jetzt nichts tun, dann haben wir auch in der Schweiz irgendwann - und das geht nicht mehr so lange - Zustände wie in Deutschland, wie in Frankreich, wie in Grossbritannien, wie in Schweden, und das wollen wir nicht. Der Messerterror von Winterthur ist ein ultimatives Warnsignal. 
+Die Zuwanderung aus Nordafrika macht die Schweiz immer unsicherer. Das ist offensichtlich; schauen Sie in die Kriminalstatistik. Deshalb ist es doch ein Gebot des gesunden Menschenverstands, die Asylmigration aus diesen Ländern endlich einzudämmen. Sie haben es heute in der Hand. Ich danke Ihnen für die Annahme dieser Motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Jahr 2025 - das ist also noch nicht so lange her - haben Sie sich in diesem Rat im Rahmen der Debatte rund um das Projekt Prävention und Sicherheit in den Bundesasylzentren (Presec) genau mit diesem Thema vertieft auseinandergesetzt. Das Parlament beschloss entsprechende Gesetzesänderungen. Seit dem 1. Juni 2026 sind diese Änderungen im Asylgesetz nun in Kraft. Das Staatssekretariat für Migration SEM hat dank dieser Änderungen die Möglichkeit, Disziplinarmassnahmen zu ergreifen, wenn die öffe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Jahr 2025 - das ist also noch nicht so lange her - haben Sie sich in diesem Rat im Rahmen der Debatte rund um das Projekt Prävention und Sicherheit in den Bundesasylzentren (Presec) genau mit diesem Thema vertieft auseinandergesetzt. Das Parlament beschloss entsprechende Gesetzesänderungen. Seit dem 1. Juni 2026 sind diese Änderungen im Asylgesetz nun in Kraft. Das Staatssekretariat für Migration SEM hat dank dieser Änderungen die Möglichkeit, Disziplinarmassnahmen zu ergreifen, wenn die öffentliche Sicherheit und Ordnung im Umfeld der Zentren gefährdet ist. Ansätze wie jenen der Motion lehnten Sie in diesem Rat vor einem Jahr ab.
+Die verlangte Ausgangssperre von bis zu zehn Tagen aus disziplinarischen Gründen stellt einen unverhältnismässigen Freiheitsentzug dar. Sie ist mit den geltenden Rechtsgrundlagen sowie der Rechtsprechung nicht vereinbar. Für die Strafverfolgung und den Strafvollzug sind die Kantone zuständig. Eine Inhaftierung durch das SEM im Rahmen eines Strafverfahrens wäre nicht zulässig - sie wäre verfassungswidrig. Wenn Sie die Motion annehmen würden, würden Sie die Umsetzung von weiteren Massnahmen in Auftrag geben, und zwar bereits wenige Tage nach Inkrafttreten der vom Parlament beschlossenen Verschärfungen, noch bevor überhaupt beurteilt werden kann, ob und wie die neuen Regelungen die gewünschte Wirkung entfalten.
+Der Bundesrat hat bereits bessere und wirksamere Massnahmen an die Hand genommen, um gegen Intensivtäter im Asylbereich vorzugehen. Diese Massnahmen hebeln die verfassungsmässig garantierten Kompetenzen zwischen Bund und Kantonen nicht aus, sind aber bereits wirksam. Das Pilotprojekt Taskforce Intensivtäter läuft seit bald einem Jahr und zeigt Wirkung. Von den im ersten Halbjahr gemeldeten 87 Fällen konnten 51 Personen dank dieser Taskforce in Haft genommen werden. Wir werden Ihnen die Auswertung des Projekts und die Schlussfolgerungen in Bezug auf Gesetzesanpassungen bald präsentieren. Diese Motion verfolgt einen falschen Ansatz.
+Aus all diesen Gründen beantragt der Bundesrat Ablehnung der Motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hier bittet Sie der Bundesrat, diese Motion anzunehmen, und zwar, weil sie die Bestrebungen des Bundesrates in diesem Zusammenhang unterstützt. Im Rahmen einer humanitären Aktion haben der Bund und einige Kantone Ende letzten Jahres die Evakuierung und Aufnahme von 20 verletzten Kindern mit ihren Familienangehörigen aus dem Gazastreifen durchgeführt. Insgesamt waren es 98 Personen. Die Kinder wurden in der Schweiz medizinisch betreut. Sie und ihre Familienangehörigen durchlaufen ein ordentliches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hier bittet Sie der Bundesrat, diese Motion anzunehmen, und zwar, weil sie die Bestrebungen des Bundesrates in diesem Zusammenhang unterstützt. Im Rahmen einer humanitären Aktion haben der Bund und einige Kantone Ende letzten Jahres die Evakuierung und Aufnahme von 20 verletzten Kindern mit ihren Familienangehörigen aus dem Gazastreifen durchgeführt. Insgesamt waren es 98 Personen. Die Kinder wurden in der Schweiz medizinisch betreut. Sie und ihre Familienangehörigen durchlaufen ein ordentliches Asylverfahren. Medizinische Evakuierungen von verletzten Kindern aus dem Gazastreifen wurden erfolgreich abgeschlossen. Zwischen dem Ausbruch des Konfliktes am 7. Oktober 2023 und Ende April 2026 wurden zusätzlich zur Evakuierungsaktion 56 humanitäre Visa an Personen aus dem besetzten palästinensischen Gebiet ausgestellt. Die Visumsgesuche werden einzelfallweise und gemäss den ordentlichen Voraussetzungen geprüft. Für Personen aus dem Gazastreifen ist der Zugang zur Gesuchstellung für ein humanitäres Visum gewährleistet. Der Bundesrat ist hier, wie gesagt, gleicher Meinung wie die Motionärin bzw. der Motionär und beantragt Ihnen deshalb, die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gianini Simone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grazie, collega Greta Gysin, della sua domanda. Essa è imprecisa, io non ho detto questo. Ho detto due cose: la prima cosa che ho detto è che separando le persone problematiche, dette anche recalcitranti, soltanto internamente, senza porre delle limitazioni alla loro uscita dai centri, i problemi che queste persone provocano all'uscita dei centri rimangono a carico, tra l'altro, delle comunità e delle polizie locali. La seconda cosa che ho detto è che, visto che il centro di Pasture e quello del</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grazie, collega Greta Gysin, della sua domanda. Essa è imprecisa, io non ho detto questo. Ho detto due cose: la prima cosa che ho detto è che separando le persone problematiche, dette anche recalcitranti, soltanto internamente, senza porre delle limitazioni alla loro uscita dai centri, i problemi che queste persone provocano all'uscita dei centri rimangono a carico, tra l'altro, delle comunità e delle polizie locali. La seconda cosa che ho detto è che, visto che il centro di Pasture e quello del Canton Soletta, a detta della SEM, sembra che siano gli unici due già strutturati in modo da poter fare questa separazione, ebbene, le comunità locali, in particolare i Comuni ticinesi toccati, temono che il centro di Pasture, essendo, appunto, l'unico o uno dei pochissimi centri adatti a attuare questa separazione, potrebbe poi comportare il rischio concreto di far arrivare richiedenti l'asilo problematici dagli altri centri.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserfallen Christian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion der FDP-Liberalen Fraktion beinhaltet im Wesentlichen drei Punkte. Es geht um die Verschärfung der Landesverweisung für straffällige Drittstaatenangehörige. Drittstaatenangehörige im Sinne des Schengen-Systems sind per Definition all jene Personen, die einem Staat ausserhalb von Europa, eben ausserhalb des Schengen-Raums angehören, also zum Beispiel aus Asien oder den USA stammen, oder südamerikanische Staatsangehörige sind. 
+Der Bundesrat wird beauftragt, die rechtlichen Grundlagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion der FDP-Liberalen Fraktion beinhaltet im Wesentlichen drei Punkte. Es geht um die Verschärfung der Landesverweisung für straffällige Drittstaatenangehörige. Drittstaatenangehörige im Sinne des Schengen-Systems sind per Definition all jene Personen, die einem Staat ausserhalb von Europa, eben ausserhalb des Schengen-Raums angehören, also zum Beispiel aus Asien oder den USA stammen, oder südamerikanische Staatsangehörige sind. 
+Der Bundesrat wird beauftragt, die rechtlichen Grundlagen der Landesverweisung gemäss Artikel 66a und 66abis des Strafgesetzbuches zu überarbeiten und zu ergänzen, um sicherzustellen, dass die straffälligen Drittstaatenangehörigen, die eine schwere Straftat - und ich betone das bewusst: eine schwere Straftat - begangen haben, automatisch ausgeschafft werden können. Als Freisinnige sind wir der Überzeugung, dass dieser Automatismus notwendig ist, insbesondere, weil dadurch auch Asylverfahrenskosten gespart werden können. Für uns gilt auch bei diesem Automatismus das sogenannte Non-Refoulement-Prinzip, das heisst: Man darf eine Person nicht in einen Staat ausschaffen, wenn man riskiert, dass sie dort an Leib und Leben bedroht ist. Die Umsetzung der Ausschaffungs-Initiative ist in diesen Punkten immer noch offen.
+Wir wollen auch, dass darauf hingewirkt wird, dass die kantonalen Vollzugsbehörden endlich eine einheitliche Praxis in Bezug auf die Ausschaffungen einführen; es besteht ja oftmals das Problem, dass sie hier eine unterschiedliche Praxis anwenden. 
+Die Anwendung der Landesverweisung soll zudem stärker an das EU-Modell angelehnt werden, das unter bestimmten Voraussetzungen eine effizientere Rückführung ermöglicht. Es ist mir wichtig zu betonen, dass all diese Möglichkeiten nur darum bestehen, weil die Schweiz als assoziierter Staat bei Schengen-Dublin dabei ist. Die Rückführungsrichtlinie und die Schengen-Grenzsicherung sind enorm wichtige Voraussetzungen, damit wir überhaupt mit den EU-Staaten verhandeln und eine effizientere Rückführung veranlassen können. Es ist auch so, dass beispielsweise die Zusammenarbeit mit der Europäischen Agentur für die Grenz- und Küstenwache (Frontex), also der Grenzsicherungsbehörde der Europäischen Union für den Schengen-Raum, sehr vonnöten ist, denn ohne Frontex wären wir aufgeschmissen. Daher wählen wir auch hier das Verfahren so, dass die Rückführungen respektive die Ausschaffungen in Zusammenarbeit mit der EU-Agentur Frontex verbessert und vor allem beschleunigt werden können. 
+Wenn wir die Sicherheit ernst nehmen wollen, dann muss das Anliegen der Motion eigentlich eine Selbstverständlichkeit sein. Ich betone noch einmal: Diese drei Punkte, die ich Ihnen soeben erklärt habe, gilt es für straffällige Drittstaatenangehörige, die eine schwere Straftat begangen haben, konsequent umzusetzen. Es wird immer gesagt, das gehe nicht und man müsse diese Leute schützen, aber man darf nicht vergessen: Das sind alles Leute, die schwer straffällig geworden sind, hier in der Schweiz leben und zum Teil, wenn sie in Bezug auf den Asylstatus eine positive Verfügung erhalten haben, sogar noch Sozialhilfe beziehen. Das können sie der Bevölkerung einfach nicht mehr erklären, dass solche Leute dann nicht das Land verlassen müssen. 
+Aus dieser Optik bittet Sie die FDP-Fraktion, der Motion zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu Beginn des laufenden Jahres kündigte das Staatssekretariat für Migration (SEM) an, Pilotprojekte umsetzen zu wollen, welche die getrennte Unterbringung jener Asylsuchenden vorsehen, die im Sinne von Artikel 24a des Asylgesetzes als problematisch gelten. Diese Trennung von den übrigen Asylsuchenden soll innerhalb derselben Bundesasylzentrums (BAZ) erfolgen. Ziel ist es insbesondere, die grosse Mehrheit der Asylsuchenden zu schützen, die sich korrekt verhält. Eines der beiden dafür ausgewählten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zu Beginn des laufenden Jahres kündigte das Staatssekretariat für Migration (SEM) an, Pilotprojekte umsetzen zu wollen, welche die getrennte Unterbringung jener Asylsuchenden vorsehen, die im Sinne von Artikel 24a des Asylgesetzes als problematisch gelten. Diese Trennung von den übrigen Asylsuchenden soll innerhalb derselben Bundesasylzentrums (BAZ) erfolgen. Ziel ist es insbesondere, die grosse Mehrheit der Asylsuchenden zu schützen, die sich korrekt verhält. Eines der beiden dafür ausgewählten BAZ befindet sich in Pasture im Kanton Tessin zwischen Balerna und Novazzano, das andere ist jenes von Flumenthal im Kanton Solothurn. Die Wahl fiel auf diese beiden Zentren, weil sie die einzigen seien, welche bereits baulich über getrennte Zonen verfügen.
+Dieses Vorhaben stiess insbesondere bei den betroffenen Tessiner Gemeinden - Balerna und Novazzano, aber auch Chiasso - und auch beim Tessiner Regierungsrat auf Widerstand. Neben der Kritik, im Vorfeld nicht ausreichend in die Planung einbezogen worden zu sein, befürchten sie, dass mit dem Pilotprojekt die bereits bestehenden Probleme ausserhalb des BAZ zusätzlich verschärft werden können. Das Hauptproblem besteht nämlich darin, dass abgesehen von der logistischen Trennung von den anderen Bewohnern die problematischen Asylsuchenden keiner weiteren Einschränkung unterliegen würden, insbesondere nicht hinsichtlich des Verlassens des Zentrums. Hinzu kommt, dass die lokalen Behörden trotz der Zusicherungen des SEM befürchten, dass künftig problematische Asylsuchende aus anderen Zentren, die nicht entsprechend ausgestattet sind oder nicht entsprechend ausgerüstet werden können, nach Pasture verlegt werden könnten.
+In Anbetracht dieser Bedenken hat Ihre Staatspolitische Kommission mit 15 zu 8 Stimmen bei 2 Enthaltungen einen von Kollege Piero Marchesi eingebrachten und anschliessend verfeinerten Text als Kommissionsmotion übernommen. Damit wird der Bundesrat aufgefordert, erstens dafür zu sorgen, dass interne Sicherheitsbereiche in den ordentlichen Bundeszentren im Rahmen von vorgesehenen Pilotprojekten nicht ohne die Zustimmung der Standortkantone und der betroffenen Gemeinden eingerichtet werden, zweitens dem Parlament einen Vorschlag für eine Rechtsanpassung zu unterbreiten, mit der klare Disziplinar- und Verwaltungsinstrumente sowie eine Stärkung des Vollzugs des Wegweisungsentscheids bei Straftätern und Wiederholungstätern eingeführt werden, und drittens dafür zu sorgen, dass die betroffenen Kantone und Gemeinden im Rahmen der Asylstrategie 2027 vollständig eingebunden werden und nötigenfalls geeignete Ausgleichsmechanismen für die Grenzkantone vorgesehen werden.
+Den Bedenken Rechnung tragend, empfiehlt der Bundesrat die Annahme dieser Motion. Dies lässt darauf hoffen, dass die betroffenen lokalen Behörden künftig bei sie unmittelbar betreffenden Fragen frühzeitig einbezogen werden und dass der Wille des Bundesrates besteht, Lösungen zu finden, nötigenfalls auch rigorose, um problematische Asylsuchende wirksam unter Kontrolle zu halten. Eine glaubwürdige Asylpolitik erfordert einerseits die Aufmerksamkeit für Menschen, die auf der Suche nach Schutz sind, andererseits muss sie aber auch die Einhaltung der Regeln gewährleisten. Aufnahme und Sicherheit müssen zusammengehen, denn eine geordnete und verantwortungsvolle Steuerung des Asylbereichs ist die grundlegende Voraussetzung dafür, dass er auch von der Bevölkerung mitgetragen wird.
+Una politica d'asilo credibile richiede, da un lato, attenzione e protezione per le persone che cercano soccorso. Dall'altro, deve essere però anche garantito il rispetto delle regole. L'accoglienza e la sicurezza devono andare di pari passo, poiché una gestione ordinata e responsabile del settore dell'asilo è la condizione di base affinché sia poi anche sostenuto e accettato dalla popolazione.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niemand in diesem Rat bestreitet, dass Straftaten im Umfeld von Bundesasylzentren ernst genommen werden müssen. Straffälliges Verhalten ist nicht akzeptabel, unabhängig davon, von wem es ausgeht. Die Bevölkerung hat Anspruch auf Sicherheit, und auch die grosse Mehrheit der Asylsuchenden leidet unter dem Verhalten einzelner Intensivtäter. 
+Die Motion verlangt, dass das Staatssekretariat für Migration (SEM) Ausgangssperren oder gar Haft von bis zu zehn Tagen gegen Asylsuchende anordnen kann. Was d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niemand in diesem Rat bestreitet, dass Straftaten im Umfeld von Bundesasylzentren ernst genommen werden müssen. Straffälliges Verhalten ist nicht akzeptabel, unabhängig davon, von wem es ausgeht. Die Bevölkerung hat Anspruch auf Sicherheit, und auch die grosse Mehrheit der Asylsuchenden leidet unter dem Verhalten einzelner Intensivtäter. 
+Die Motion verlangt, dass das Staatssekretariat für Migration (SEM) Ausgangssperren oder gar Haft von bis zu zehn Tagen gegen Asylsuchende anordnen kann. Was das konkret bedeutet, lässt sich an einem einfachen Beispiel zeigen. Stellen wir uns einen Asylsuchenden vor, gegen den nach einer Auseinandersetzung zum Beispiel vor einem Einkaufszentrum ein Strafverfahren eröffnet wird, vielleicht wegen Rangelei oder des Verdachts auf Diebstahl. Noch bevor ein Gericht diese Vorwürfe prüft, könnte das SEM gemäss dieser Motion eine Ausgangssperre oder sogar Haft anordnen - nicht ein unabhängiges Gericht, kein ordentliches Strafverfahren, sondern eine Verwaltungsbehörde. 
+Genau das entspricht nicht unserem schweizerischen Staatsverständnis. In der Schweiz trennen wir zwischen Verwaltung, Polizei und Justiz, und gerade darin liegt die Stärke eines Rechtsstaats. Macht wird aufgeteilt, kontrolliert und begrenzt. Wir geben einer Behörde nicht gleichzeitig die Rolle von Aufsicht, Anklage und Sanktion. Der Bundesrat weist deshalb zu Recht darauf hin, dass das SEM verfassungsrechtlich weder für Strafverfolgung noch für Strafvollzug zuständig ist. Denn Ausgangssperren oder Haft von bis zu zehn Tagen stellen erhebliche Eingriffe in die Bewegungsfreiheit und damit in ein zentrales Grundrecht dar. Es handelt sich faktisch um Massnahmen, die in einem Rechtsstaat wie der Schweiz ausschliesslich durch die zuständigen Strafbehörden unter gerichtlicher Kontrolle angeordnet werden dürfen. 
+Hinzu kommt: Der Staat handelt bereits. Die Kantone sind zuständig für die Gewährleistung der öffentlichen Sicherheit und Ordnung um die Bundesasylzentren. Sie verfügen entsprechend auch über strafrechtliche Mittel gegen Personen, die Straftaten begehen oder die öffentliche Sicherheit gefährden, wie beispielsweise die Untersuchungshaft. Gleichzeitig laufen auf Bundesebene zahlreiche Reformen, zum Beispiel mit der Asylstrategie 2027, und seit Juni 2025 arbeitet auch eine nationale Taskforce gegen kriminelle Intensivtäter daran, Vollzugslücken zu schliessen und Massnahmen konsequenter anzuwenden. 
+Und jetzt kommt ein ganz wichtiger Punkt: Erst gerade hat das Parlament Verschärfungen in genau diesem Bereich beschlossen. Diese Verschärfungen wurden zu Beginn dieser Session, am 1. Juni 2026, in Kraft gesetzt. Neu kann das SEM nämlich zusätzliche Disziplinarmassnahmen anordnen und in akuten Gefahrensituationen auch eine vorübergehende Festhaltung bis zu 72 Stunden verfügen. Es wurde also bereits gehandelt. Wir müssen uns daher fragen: Braucht es wirklich weitere Sondermassnahmen, die rechtsstaatlich höchst fraglich sind und neue juristische Unsicherheiten provozieren? Oder laufen wir Gefahr, mit symbolischer Härte vor allem Politik für die Schlagzeilen zu machen, statt rechtsstaatlich saubere und wirksame Lösungen umzusetzen? 
+Der Nationalrat hat am 11. März bereits eine gleichlautende Motion der SVP-Fraktion angenommen. Heute haben Sie die Gelegenheit, diese jüngsten Entwicklungen, wie ich sie beschrieben habe, zu berücksichtigen und diesen Entscheid zu korrigieren, der zwar verständlicherweise aus einem Sicherheitsbedürfnis entstanden ist, aber jetzt auf ein falsches Mittel setzt. 
+Ich bitte Sie deshalb, der Minderheit zu folgen und die Motion abzulehnen. Wie der Mehrheitssprecher bereits gesagt hat: Die Motion wurde mit 13 zu 10 Stimmen bei 2 Enthaltungen angenommen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questa mozione è un esempio piuttosto classico di strumentalizzazione politica di un tema più che di un dibattito serio e fondato sul merito. Il fenomeno non è nuovo quando si parla di immigrazione e di asilo. Purtroppo, c'è chi investe più energie nel convincere la popolazione che questo sia il principale problema del Paese che nel discutere soluzioni concrete. Eppure, i dati ci raccontano una realtà diversa da quella che ci viene sempre proposta. Gli arrivi nel settore dell'asilo sono oggi net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questa mozione è un esempio piuttosto classico di strumentalizzazione politica di un tema più che di un dibattito serio e fondato sul merito. Il fenomeno non è nuovo quando si parla di immigrazione e di asilo. Purtroppo, c'è chi investe più energie nel convincere la popolazione che questo sia il principale problema del Paese che nel discutere soluzioni concrete. Eppure, i dati ci raccontano una realtà diversa da quella che ci viene sempre proposta. Gli arrivi nel settore dell'asilo sono oggi nettamente inferiori rispetto a periodi di maggiore pressione del passato e i problemi di sicurezza nei centri federali d'asilo e anche nei dintorni sono in netta diminuzione, parliamo di un meno 60 per cento. Continuare ad alimentare un clima di allarme permanente non ci avvicina a nessuna soluzione, al contrario, rischia di allontanarci da un confronto serio sulle misure che possono davvero migliorare il funzionamento del sistema e la sicurezza di tutte le persone coinvolte. 
+Anche questa mozione commissionale segue la stessa logica, semplicemente riproposta, lo avete visto, in salsa ticinese: dare l'impressione di voler agire senza aggiungere assolutamente nulla ad una soluzione concreta. A ben guardare questa mozione non cambia veramente nulla.
+Prendiamo la cifra 1 e la cifra 3 della mozione: negli ultimi mesi la SEM ha sviluppato un progetto pilota con un obiettivo molto semplice, migliorare la convivenza nei centri federali d'asilo. Non si tratta di creare un centro speciale, e la cosa non diventa più vera se la si ripete sistematicamente, neanche se si è relatore commissionale. Non si tratta di trasferire i richiedenti l'asilo problematici da tutta la Svizzera nei progetti pilota, si tratta semplicemente di separare fisicamente, all'interno del centro federale esistente, la stragrande maggioranza di persone che rispettano le regole da quella piccola minoranza che invece crea dei problemi. Parliamo di un 96 per cento di persone che non crea assolutamente mai nessun problema e di un 4 per cento che invece qualche problema lo crea. In concreto si tratta di spazi comuni separati, refettori separati, aree di vita separati. L'obiettivo è proteggere meglio i bambini, le famiglie, gli altri richiedenti l'asilo e il personale nei centri. Erano previsti due progetti pilota, uno nel Canton Soletta e uno in Ticino a Pasture. Le autorità locali, a differenza di ciò che è stato detto ancora oggi, sono state coinvolte, e il progetto ticinese è stato congelato proprio perché il Cantone e i Comuni si erano opposti. Le loro obiezioni sono state ascoltate, il progetto è stato sospeso - esattamente ciò che la mozione si propone di raggiungere con la cifra 1 e la cifra 3.
+Anche la cifra 2 non aggiunge assolutamente nulla a una soluzione concreta. La questione dell'armonizzazione delle misure amministrative e coercitive è già oggetto di lavori in corso nell'ambito della strategia asilo 2027 e della task force dedicata ai recidivi del settore dell'asilo. Da questi lavori emergeranno proposte concrete di adeguamento legislativo. Quindi, anche qui le richieste avanzate nella mozione sono già in via di attuazione. 
+La verità è che questa mozione non introduce nuovi strumenti, non crea nuove competenze e non migliora la sicurezza né nei centri né fuori dai centri. È una mozione che chiede cose che sono già state fatte e che sono già in preparazione. La domanda, a questo punto, è molto semplice: che cosa cambierebbe concretamente domani, se questa mozione venisse accolta? La risposta è altrettanto semplice: non cambierebbe assolutamente nulla, non per i Cantoni, non per i Comuni, non per il personale nei centri e non per le persone che nei centri ci vivono!
+Una buona politica dell'asilo non si misura in base al numero di mozioni, si misura in base alla capacità di affrontare i problemi reali con strumenti efficaci, proporzionati, rispettosi dello Stato di diritto, senza mettere in discussione i diritti fondamentali e il diritto internazionale vincolante.
+Per tutti questi motivi, e per evitare di accogliere una mozione che nulla toglie e nulla aggiunge alla situazione già esistente, per non alimentare questo clima veramente difficile di discussione nella politica dell'asilo, una minoranza commissionale vi invita a respingere la mozione.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchesi Piero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mozione in oggetto chiede al Consiglio federale di proporre i necessari adeguamenti legislativi e di adottare le misure del caso finché sia possibile ordinare, nei confronti dei richiedenti l'asilo ospitati nei centri federali che violano le regole d'uscita, mettono in pericolo la sicurezza e l'ordine pubblico all'esterno dei centri, oppure sono oggetti di un procedimento penale, un coprifuoco fino a 10 giorni o una detenzione fino a 10 giorni. 
+Il punto centrale è chiaro, la sicurezza all'in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mozione in oggetto chiede al Consiglio federale di proporre i necessari adeguamenti legislativi e di adottare le misure del caso finché sia possibile ordinare, nei confronti dei richiedenti l'asilo ospitati nei centri federali che violano le regole d'uscita, mettono in pericolo la sicurezza e l'ordine pubblico all'esterno dei centri, oppure sono oggetti di un procedimento penale, un coprifuoco fino a 10 giorni o una detenzione fino a 10 giorni. 
+Il punto centrale è chiaro, la sicurezza all'interno dei centri federali è importante ma non basta. Occorre proteggere anche la popolazione che vive e lavora nei pressi di questi centri. La revisione della legge sull'asilo ha già permesso di migliorare alcuni aspetti legati alla sicurezza dei centri. Tuttavia, restano problemi concreti all'esterno, vale dire violazioni dell'ordine pubblico, mancato rispetto delle regole, comportamenti aggressivi, danni materiali, furti e altri reati. 
+La commissione ha preso atto delle osservazioni del Consiglio federale che propone di respingere la mozione richiamando la ripartizione delle competenze tra Confederazione, Cantoni e autorità penali. Il Consiglio federale sostiene in particolare che la SEM è competente per la sicurezza all'interno dei centri, mentre la sicurezza esterna compete di principio alle autorità cantonali. La maggioranza della commissione ritiene però che proprio questa situazione dimostri la necessità di intervenire. I reati e le violazioni dell'ordine pubblico commessi nelle immediate vicinanze dei centri federali d'asilo gravano in modo significativo sulla polizia e sulle autorità penali cantonali. Inoltre, questi episodi compromettono l'accettazione dei centri federali da parte della popolazione residente nelle loro vicinanze.
+La commissione considera le misure proposte nella mozione adeguate, efficaci e proporzionate. Sono limitate nel tempo, con una durata massima appunto di dieci giorni, e mirano a ristabilire ordine e sicurezza in situazioni problematiche. Pur limitando la libertà di movimento delle persone interessate, possono essere considerate misure disciplinari. La commissione ricorda inoltre che in altri ambiti, come ad esempio quello militare, sanzioni analoghe possono già essere applicate nei confronti di reclute o soldati che violano determinate regole. 
+La commissione sottolinea che occorre migliorare anche la sicurezza all'interno dei centri federali d'asilo. Per questo ha accolto anche la mozione della Commissione delle istituzioni politiche del Nazionale 26.3522 sulla gestione efficiente dei richiedenti l'asilo problematici e sull'applicazione coerente della legge sull'asilo. La mozione non intende dunque attuare misure arbitrarie o illimitate, ma strumenti mirati, circoscritti e proporzionati per rispondere a situazioni concrete che oggi ricadono troppo spesso sui Cantoni, sui Comuni e sulla popolazione locale.
+Ricordo infine che il Consiglio degli Stati ha già accolto la mozione il 10 marzo 2026 con 32 voti contro 11. La Commissione delle istituzioni politiche del nostro consiglio propone a sua volta, con 13 voti contro 10 e 2 astensioni, di accogliere la mozione. 
+Per queste ragioni vi invito a seguire la maggioranza della commissione e ad accogliere la mozione.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schaffner Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit der Motion Flach sprechen wir nicht über eine Grundsatzfrage der Migrationspolitik, sondern über ein Einzelschicksal: Soll ein verletztes Kind, das womöglich auch keine Eltern mehr hat, eine medizinische Behandlung erhalten oder nicht? Die Schweiz hat diese Frage eigentlich schon mit Ja beantwortet. Im Oktober und November 2025 hat der Bundesrat zwanzig verletzte Kinder und ihre Begleitpersonen aus dem Gazastreifen evakuiert und hier medizinisch versorgt. Es war kein Problem, die Neutralität</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit der Motion Flach sprechen wir nicht über eine Grundsatzfrage der Migrationspolitik, sondern über ein Einzelschicksal: Soll ein verletztes Kind, das womöglich auch keine Eltern mehr hat, eine medizinische Behandlung erhalten oder nicht? Die Schweiz hat diese Frage eigentlich schon mit Ja beantwortet. Im Oktober und November 2025 hat der Bundesrat zwanzig verletzte Kinder und ihre Begleitpersonen aus dem Gazastreifen evakuiert und hier medizinisch versorgt. Es war kein Problem, die Neutralität wurde nicht verletzt, und die Sicherheit war gewährleistet. Selbst die Kantone haben mitgemacht. Es war zugegebenermassen ein Tropfen auf den heissen Stein, aber für die betroffenen Personen war es umso dringender. Laut dem Schweizerischen Roten Kreuz wurden in den letzten zwei Jahren über 80 Prozent der Gesundheitseinrichtungen in Gaza zerstört oder sehr schwer beschädigt. Kein einziges Spital ist noch voll funktionsfähig. Für schwerverletzte Kinder, die neurochirurgische Eingriffe oder komplexe Rekonstruktionen benötigen, gibt es vor Ort also schlicht keine Infrastruktur.
+Wer heute gegen diese Motion stimmt, stimmt gegen die rechtliche Verankerung von etwas, das die Schweiz vor wenigen Monaten selbst für richtig und machbar befunden hat. Die Motion ist deshalb auch bewusst eng gefasst. Sie verlangt keine offenen Grenzen, kein neues Aufenthaltsrecht, keine Systemänderung. Sie verlangt, dass der Bundesrat die praktischen Hindernisse beseitigt, die heute dazu führen, dass besonders schutzbedürftige Menschen - insbesondere verletzte Kinder und Waisenkinder - humanitäre Visa faktisch nicht beantragen können. Der Grund, wieso sie dies nicht können, ist sehr banal: Für ein Visum braucht es eine persönliche Vorsprache bei einer Auslandvertretung - und die gibt es im Gazastreifen nicht. Das normale Verfahren setzt eine Normalität voraus, die seit Jahren nicht existiert.
+Auch abgesehen vom Gaza-Konflikt dürfen wir uns nichts vormachen: Bewaffnete Konflikte nehmen weltweit zu und eskalieren. Die Frage ist also nicht, ob, sondern wann die Schweiz wieder vor einer vergleichbaren Situation stehen wird. Wer heute Nein stimmt, sorgt dafür, dass der Bundesrat beim nächsten Mal wieder improvisieren muss - ohne Rechtsgrundlage, ohne klare Zuständigkeiten, ohne Planungssicherheit für die Kantone.
+Die Schweiz ist Depositarstaat der Genfer Konventionen. Das Internationale Komitee vom Roten Kreuz wurde hier gegründet. Das ist eine Verpflichtung für unsere humanitäre Tradition. Mit der Annahme der Motion kommen wir dieser Verpflichtung nach - nicht einmalig und improvisiert, sondern mit einem verlässlichen, gut funktionierenden Instrument für die Zukunft.
+Im Namen der GLP-Fraktion und des Motionärs, unseres ehemaligen Kollegen Beat Flach, bitte ich Sie, dem Antrag des Bundesrates zu folgen und die Motion anzunehmen - nicht als migrationspolitisches Signal, sondern als elementaren humanitären Akt.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collega Fonio, questa mozione permetterebbe di evitare imposizioni di fumosi progetti pilota ai Cantoni e Comuni che non sono stati interpellati preventivamente. Chiedo a lei, che ha buoni contatti con i Comuni del Mendrisiotto: Come hanno valutato questa mozione che mira ad evitare imposizioni e portare avanti i progetti pilota solo con l'avallo di Cantoni e Comuni interessati?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous traitons maintenant est directement liée au débat que nous avons eu la semaine dernière concernant l'exécution des sanctions et des mesures thérapeutiques institutionnelles. Elle a été déposée par la Commission des affaires juridiques du Conseil national le 17 avril 2026 à la suite des travaux menés en commission dans le cadre de la motion 25.4415, "Mesures en matière d'exécution des sanctions". Elle a été adoptée par notre commission, par 16 voix contre 9.
+Le problème que cet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous traitons maintenant est directement liée au débat que nous avons eu la semaine dernière concernant l'exécution des sanctions et des mesures thérapeutiques institutionnelles. Elle a été déposée par la Commission des affaires juridiques du Conseil national le 17 avril 2026 à la suite des travaux menés en commission dans le cadre de la motion 25.4415, "Mesures en matière d'exécution des sanctions". Elle a été adoptée par notre commission, par 16 voix contre 9.
+Le problème que cette motion met en évidence est simple à comprendre, mais extrêmement difficile à justifier, pour ne pas dire impossible. Aujourd'hui, notre droit prévoit d'un côté des expulsions pénales obligatoires pour certains criminels étrangers, au sens de l'article 66a du code pénal. De l'autre côté, il prévoit aussi des mesures thérapeutiques institutionnelles, selon l'article 59 du code pénal, qui ont pour objectif la réinsertion du condamné dans la société. C'est là que se trouve la contradiction : comment préparer sérieusement une réinsertion sociale en Suisse pour une personne dont le droit suisse prévoit précisément qu'elle devra obligatoirement quitter le territoire national à l'issue du passage par la case prison ?
+Dans la pratique, cela conduit à des situations absurdes. D'une part, ces mesures sont souvent irréalistes dans leur mise en oeuvre concrète. En effet, la mesure thérapeutique institutionnelle repose généralement sur une progression graduelle. On passe d'un régime fermé à un régime de plus en plus ouvert afin de préparer la réinsertion du condamné dans la société. Or, lorsqu'il s'agit d'une personne qui devra être expulsée, cette logique atteint rapidement ses limites. Il est difficilement concevable d'accorder des ouvertures progressives à une personne dont l'étape suivant la prison sera en définitive l'aéroport pour un retour au pays que l'on souhaite définitif. La mise en oeuvre même de la mesure devient alors largement théorique.
+Toutefois, ce n'est pas tout : des personnes condamnées à une expulsion obligatoire exécutent pendant des années des mesures thérapeutiques extrêmement coûteuses, mobilisent des places limitées dans les institutions spécialisées et restent durablement privées de liberté parce qu'aucune perspective crédible de réinsertion en Suisse ne peut être démontrée. Ces mesures institutionnelles coûtent extrêmement cher. On parle parfois de centaines de milliers de francs, voire davantage, pour des personnes qui, à la fin de la procédure, devront quitter la Suisse. La question n'est pas de nier les problèmes psychiatriques de certaines personnes condamnées. La question est de savoir jusqu'où la Suisse doit financer pendant des années des mesures de réinsertion destinées à des personnes que notre ordre juridique a précisément décidé d'éloigner du territoire national.
+La majorité de la commission considère qu'il faut remettre un peu de cohérence dans ce système. La motion ne vise pas à supprimer toute prise en charge thérapeutique ; elle vise simplement à inverser la logique actuelle. Après l'exécution de la peine privative de liberté, l'expulsion doit en principe primer sur la mesure thérapeutique institutionnelle. Si un suivi thérapeutique demeure nécessaire, il faut examiner comment celui-ci peut être poursuivi dans l'État de destination, dans le respect du droit international et de la Convention européenne des droits de l'homme.
+La minorité Arslan nous dit qu'il existerait des risques pour les droits fondamentaux ou pour la sécurité publique. Toutefois, précisément, la motion charge le Conseil fédéral d'examiner ces questions et de proposer une solution compatible avec les exigences constitutionnelles et conventionnelles. Refuser même d'ouvrir cette réflexion reviendrait simplement à accepter les incohérences actuelles.
+Enfin, j'aimerais dire un mot sur le fond politique du débat. Le peuple suisse a accepté le principe de l'expulsion des criminels étrangers. Ce choix doit être pris au sérieux. On ne peut pas d'un côté affirmer qu'une personne doit quitter la Suisse pour protéger notre sécurité et, de l'autre, construire pendant des années un projet de réinsertion précisément dans le pays qu'elle devra quitter. La Suisse a-t-elle une obligation morale de financer la réinsertion d'un criminel étranger dans son pays d'origine ? Du point de vue de la majorité de la commission, la réponse est non. Notre pays a déjà payé son tribut en subissant les conséquences des actes commis par un criminel étranger sur son territoire. Une fois la peine exécutée et l'expulsion prononcée, il n'appartient pas encore à notre pays d'assumer pendant des années le coût de mesures destinées à préparer une réinsertion ailleurs.
+Pour toutes ces raisons, la majorité de la commission vous invite à adopter la motion 26.3516.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grazie, collega Greta Gysin, per la domanda. Come lei ben sa, vivo quotidianamente la realtà della regione. Non è una questione di trasferimento, la questione è che attualmente non ci sono altri centri per richiedenti l'asilo problematici, e quello che si vuole evitare è che i richiedenti l'asilo problematici non vengano tenuti all'interno dei centri che oggi funzionano. Sul numero, mi dispiace, non sono oggi nella condizione di darglielo. Quello che le posso dire è che il territorio deve essere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grazie, collega Greta Gysin, per la domanda. Come lei ben sa, vivo quotidianamente la realtà della regione. Non è una questione di trasferimento, la questione è che attualmente non ci sono altri centri per richiedenti l'asilo problematici, e quello che si vuole evitare è che i richiedenti l'asilo problematici non vengano tenuti all'interno dei centri che oggi funzionano. Sul numero, mi dispiace, non sono oggi nella condizione di darglielo. Quello che le posso dire è che il territorio deve essere vissuto, il territorio accoglie, ma il territorio non è più disposto ad accettare situazioni con le quali non è d'accordo.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collega Fonio, nel suo intervento ha detto che questo progetto pilota avrebbe portato delle sfide nell'ambito della sicurezza intorno al centro federale d'asilo a Pasture. Secondo la descrizione che ci è stata data in commissione - non quanto si è letto sui giornali o quanto è stato percepito nella regione - quante persone problematiche sarebbero state trasferite da altri centri federali d'asilo al centro di Pasture?
 </t>
   </si>
 </sst>
@@ -848,8 +1154,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I32" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I50" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I50"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2061,6 +2367,520 @@
         <v>158</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>161</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>170</v>
+      </c>
+      <c r="I35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36"/>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" t="s">
+        <v>177</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>187</v>
+      </c>
+      <c r="E40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>188</v>
+      </c>
+      <c r="I40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>192</v>
+      </c>
+      <c r="I41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>194</v>
+      </c>
+      <c r="B42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>88</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>195</v>
+      </c>
+      <c r="I42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>198</v>
+      </c>
+      <c r="I43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>201</v>
+      </c>
+      <c r="I44" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>204</v>
+      </c>
+      <c r="E45" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>205</v>
+      </c>
+      <c r="I45" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>210</v>
+      </c>
+      <c r="I46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>204</v>
+      </c>
+      <c r="E47" t="s">
+        <v>38</v>
+      </c>
+      <c r="F47" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" t="s">
+        <v>213</v>
+      </c>
+      <c r="I47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" t="s">
+        <v>215</v>
+      </c>
+      <c r="I48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" t="s">
+        <v>218</v>
+      </c>
+      <c r="I49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>220</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>87</v>
+      </c>
+      <c r="E50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s">
+        <v>221</v>
+      </c>
+      <c r="H50" t="s">
+        <v>222</v>
+      </c>
+      <c r="I50" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -739,9 +739,9 @@
 Heureusement, la clôture était meilleure que prévu. Mais lorsque l'on dit que les estimations tombent à côté, il faut dire que l'écart des estimations, en moyenne, ces 10 dernières années, était de 0,3 pour cent - ce n'est pas beaucoup. Il faut aussi considérer la grandeur des chiffres.
 Zu unterscheiden gilt es auch zwischen dem ordentlichen und dem ausserordentlichen Haushalt. Im ordentlichen Haushalt verzeichnete der Bund einen Überschuss von 1,2 Milliarden Franken. Die Schuldenbremse hätte konjunkturbedingt ein Defizit von 262 Millionen Franken zugelassen. Der strukturelle Saldo gemäss Schuldenbremse belief sich damit auf 1,4 Milliarden Franken. Budgetiert war ein strukturell ausgeglichener Haushalt.
 Die ordentlichen Einnahmen schlossen 1,9 Milliarden Franken über dem Budget ab. Der Hauptgrund dafür waren die Gewinnsteuereinnahmen, die mit 1,4 Milliarden Franken über dem Budget lagen. Diese Entwicklung ist auf die bereits bekannten temporären Mehreinnahmen aus dem Kanton Genf zurückzuführen. Der Kanton Genf hat hier alleine 1,5 Milliarden Franken beigetragen. Auch ohne den Effekt Genf haben sich die Gewinnsteuereinnahmen positiv entwickelt, wobei sie ohne den Sondereffekt Genf leicht unter dem Budget ausgefallen wären.
-Nachdem in der Berichterstattung in den Medien bezüglich dieser Mehreinnahmen aus Genf etwas Verwirrung gestiftet wurde, möchte ich das noch einmal erklären und präzisieren. Ich verweise auch auf die Staatsrechnung, Band IA, Seite 40. Sie können sich erinnern: Im letzten Frühjahr erhielten wir die Meldung aus Genf, dass für die Rechnung 2025 Mehrerträge von etwa 500 Millionen Franken aus den Jahren 2022 und 2023 anfallen werden. Diese Mehrerträge gehen massgeblich auf den Rohstoffhandel zurück. Dann gab es eine weitere Meldung - sie traf just am Tag ein, als die Finanzkommission des Ständerates ihre Beratung aufnahm: Es würden noch einmal Mehreinnahmen aus Genf im Umfang von etwa einer Milliarde Franken kommen. Der Grund dafür war, dass der Kanton Genf während der ziemlich langen Periode zwischen 2019 und 2024 keine provisorischen Rechnungen ausgestellt hatte. Die Einnahmenschätzungen des Bundes basieren auf den provisorischen Gewinnsteuerrechnungen der Kantone. Ohne provisorische Rechnungen weiss man auch nicht, welche Erträge kommen.
+Nachdem in der Berichterstattung in den Medien bezüglich dieser Mehreinnahmen aus Genf etwas Verwirrung gestiftet wurde, möchte ich das noch einmal erklären und präzisieren. Ich verweise auch auf die Staatsrechnung, Band IA, Seite 40. Sie können sich erinnern: Im letzten Frühjahr erhielten wir die Meldung aus Genf, dass für die Rechnung 2025 Mehrerträge von etwa 500 Millionen Franken aus den Jahren 2022 und 2023 anfallen werden. Diese Mehrerträge gehen massgeblich auf den Rohstoffhandel zurück. Dann gab es eine weitere Meldung - sie traf just am Tag ein, als die Finanzkommission des Ständerates ihre Beratung für das Budget 2026 aufnahm: Es würden noch einmal Mehreinnahmen aus Genf im Umfang von etwa einer Milliarde Franken kommen. Der Grund dafür war, dass der Kanton Genf während der ziemlich langen Periode zwischen 2019 und 2024 keine provisorischen Rechnungen ausgestellt hatte. Die Einnahmenschätzungen des Bundes basieren auf den provisorischen Gewinnsteuerrechnungen der Kantone. Ohne provisorische Rechnungen weiss man auch nicht, welche Erträge kommen.
 Wenn also in den Medien stand, alle zusätzlichen Einnahmen seien auf den Rohstoffhandel zurückzuführen, ist das nicht korrekt. Ein Teil war wirklich auf diesen Informatikfehler der Genfer zurückzuführen; wir konnten das auch nicht antizipieren.
-Wenn man auf die Ausgaben schaut, dann muss man sagen, dass die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget lagen. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden relativ tief ausfielen. Die Kreditreste sind aufgrund der Kürzungen, die wir in den Budgets 2024 und 2025 vorgenommen hatten, sowieso viel tiefer. Im ausserordentlichen Haushalt hingegen waren die Ausgaben höher als die Einnahmen. Hier verzeichneten wir ein Defizit von rund 900 Millionen Franken. Die beiden grössten ausserordentlichen Ausgaben waren diejenige für die Schutzsuchenden aus der Ukraine - das waren 700 Millionen Franken von total 1,5 Milliarden an ausserordentlichen Ausgaben - sowie der einmalige Kapitalzuschuss an die SBB in Höhe von 850 Millionen. Die Tatsache, dass diese 850 Millionen Franken erst im Jahr 2025 ausbezahlt wurden, war der Grund für die Rechnungsverbesserung im Jahr 2024.
+Wenn man auf die Ausgaben schaut, dann muss man sagen, dass die ordentlichen Ausgaben erstmals seit Einführung der Schuldenbremse über dem Budget lagen. Der Grund dafür waren die hohen Kreditaufstockungen von insgesamt 2,4 Milliarden Franken, während gleichzeitig die Kreditreste mit 2,1 Milliarden relativ tief ausfielen. Die Kreditreste sind aufgrund der Kürzungen, die wir in den Budgets 2024 und 2025 vorgenommen hatten, sowieso viel tiefer. Im ausserordentlichen Haushalt hingegen waren die Ausgaben höher als die Einnahmen. Hier verzeichneten wir ein Defizit von rund 900 Millionen Franken. Die beiden grössten ausserordentlichen Ausgaben waren diejenige für die Schutzsuchenden aus der Ukraine - das waren 700 Millionen Franken von total 1,4 Milliarden an ausserordentlichen Ausgaben - sowie der einmalige Kapitalzuschuss an die SBB in Höhe von 850 Millionen. Die Tatsache, dass diese 850 Millionen Franken erst im Jahr 2025 ausbezahlt wurden, war der Grund für die Rechnungsverbesserung im Jahr 2024.
 Vous vous souvenez que nous avions prévu de verser 1,15 milliard de francs aux CFF en 2024. Le Parlement n'était pas tout à fait prêt ; par la suite, le Parlement a réduit la somme. Cette somme réduite - soit 850 millions de francs - a été versée en 2025 seulement.
 Auf der Einnahmenseite wurde ein Teil der SNB-Gewinnausschüttung ausserordentlich zum Abbau der Covid-Schulden verbucht. Das ist so vorgesehen. Dazu kam die budgetierte Sonderzuweisung der SNB aus den nicht umgetauschten Banknoten der sechsten Serie.
 Ich komme nun zum Ausblick. Wie üblich wird der Bundesrat Ende Juni die Zahlen zum Voranschlag 2027 und dann auch die Zahlen zum Finanzplan 2028 bis 2030 festlegen. Die Arbeiten hierzu laufen noch. Wie bereits den Nationalrat möchte ich auch Sie an dieser Stelle über den Zwischenstand dieser Arbeiten informieren. Dieser Zwischenstand stützt sich primär auf die erfolgten Budgeteingaben der Departemente und auf die seit April aktualisierte Einnahmenschätzung, nachdem uns die Kantone die Eingänge für die Schätzung im wichtigen Monat April gemeldet haben. Der Zwischenstand stützt sich also auf die provisorischen Steuerrechnungen; diese liegen jeweils Ende April vor.
@@ -896,7 +896,7 @@
   </si>
   <si>
     <t xml:space="preserve">Der Bundesrat beantragt die Annahme aller drei Punkte dieser Motion. Ich erlaube mir allerdings zu sagen, dass ich die Einschätzung der Minderheit Gysin Greta teile, dass diese Motion gar nichts ändert. Man kann die Motion deshalb ablehnen oder annehmen - es läuft auf dasselbe hinaus. 
-Zum ersten Punkt, den diese Motion fordert: Das Pilotprojekt "Bedarfsorientierte Unterbringung" ist eine interne Massnahme im Rahmen des Belegungsmanagements der Bundesasylzentren. Der Bundesrat ist jedoch damit einverstanden, dass allfällige Standorte für das Pilotprojekt nur mit Zustimmung der betroffenen Standortkantone und Standortgemeinden ausgewählt werden. Das erhöht die Akzeptanz für das Projekt. Das SEM hat dem Kanton Tessin die Einstellung des Projekts bereits zugestanden. Ich möchte hier allerdings darauf hinweisen, dass es ein Projekt zum Schutz der Tessiner Bevölkerung ist. Dieses Pilotprojekt soll eben genau die Möglichkeiten dafür verbessern, dass im Umfeld von Asylzentren weniger Sicherheitsrisiken bestehen. Genau das ist das Ziel des Projektes. Wenn der Standortkanton es trotzdem nicht will, dann trägt er auch die Verantwortung dafür, dass die Sicherheit dann halt nicht im Vordergrund steht. 
+Zum ersten Punkt, den diese Motion fordert: Das Pilotprojekt "Bedarfsorientierte Unterbringung" ist eine interne Massnahme im Rahmen des Belegungsmanagements der Bundesasylzentren. Der Bundesrat ist jedoch damit einverstanden, dass allfällige Standorte für das Pilotprojekt nur mit Zustimmung der betroffenen Standortkantone und Standortgemeinden ausgewählt werden. Das erhöht die Akzeptanz für das Projekt. Das SEM hat dem Kanton Tessin die Einstellung des Projekts bereits zugestanden. Ich möchte hier allerdings darauf hinweisen, dass es ein Projekt zum Schutz der Bevölkerung ist. Dieses Pilotprojekt soll eben genau die Möglichkeiten dafür verbessern, dass im Umfeld von Asylzentren weniger Sicherheitsrisiken bestehen. Genau das ist das Ziel des Projektes. Wenn der Standortkanton es trotzdem nicht will, dann trägt er auch die Verantwortung dafür, dass die Sicherheit dann halt nicht im Vordergrund steht. 
 Zum zweiten Punkt der Motion: Die Arbeiten zu Gesetzesanpassungen im Bereich der erwähnten Disziplinar- und Verwaltungsinstrumente sind teilweise bereits abgeschlossen. Verschiedene Änderungen im Asylgesetz betreffend die Sicherheit und den Betrieb der Bundesasylzentren sind am 1. Juni 2026 in Kraft getreten. Das SEM hat seither auch die Möglichkeit, Disziplinarmassnahmen auszusprechen, wenn die öffentliche Sicherheit und Ordnung in der Umgebung der Zentren gefährdet werden. Weitere Massnahmen zur Verbesserung des Wegweisungsvollzugs werden derzeit unter anderem im Rahmen der Motion Salzmann 23.3082, "Rückführungsoffensive und konsequente Ausweisung von Straftätern und Gefährdern", geprüft; ich habe das heute schon mal gesagt. Das EJPD wird dem Bundesrat das entsprechende Konzept bis Ende des Jahres unterbreiten. In diesem Rahmen werden ebenfalls Gesetzesanpassungen geprüft. Das Anliegen der Motion wird also bereits längstens aufgenommen; auch hier ist diese Motion eigentlich erfüllt. 
 Zum dritten Punkt: Dem Bundesrat ist es ein grosses Anliegen, dass Kantone und Gemeinden im Rahmen der Asylstrategie 2027 vollständig eingebunden werden. Das ist ja die Idee dieser Asylstrategie. Der Bundesrat hat sie auch deshalb aufgegleist, damit die Kantone von Anfang an vollwertig bei diesen für sie wichtigen Entscheiden dabei sind; das ist heute schon der Fall. Sie können es jetzt auch noch mit dieser Motion fordern, aber auch hier sind wir eigentlich längstens auf Kurs. Zudem sieht das politische Mandat vor, dass die beschlossenen Massnahmen zu keinen Lastenverschiebungen führen dürfen. Die Motion unterstützt die Bestrebungen des Bundesrates bzw. meines Departementes, und in diesem Sinne kann man sie auch annehmen. Aus all diesen Gründen beantragt der Bundesrat, diese Motion anzunehmen.
 </t>
@@ -1106,6 +1106,486 @@
   </si>
   <si>
     <t xml:space="preserve">Collega Fonio, nel suo intervento ha detto che questo progetto pilota avrebbe portato delle sfide nell'ambito della sicurezza intorno al centro federale d'asilo a Pasture. Secondo la descrizione che ci è stata data in commissione - non quanto si è letto sui giornali o quanto è stato percepito nella regione - quante persone problematiche sarebbero state trasferite da altri centri federali d'asilo al centro di Pasture?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Subkommissionen Gerichte/Bundesanwaltschaft der beiden Geschäftsprüfungskommissionen, also des Nationalrates und des Ständerates, tagen in der Regel gemeinsam. Traditionellerweise findet die Sitzung, in welcher sie den Geschäftsbericht des Bundesgerichtes diskutieren und zur Kenntnis nehmen, am Bundesgericht in Lausanne statt; dies - nebenbei bemerkt - in einem Raum mit ikonischen Bildern. Eines zeigt die archaische Szene des salomonischen Urteils und bringt mich jedes Mal ins Grübeln, wenn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Subkommissionen Gerichte/Bundesanwaltschaft der beiden Geschäftsprüfungskommissionen, also des Nationalrates und des Ständerates, tagen in der Regel gemeinsam. Traditionellerweise findet die Sitzung, in welcher sie den Geschäftsbericht des Bundesgerichtes diskutieren und zur Kenntnis nehmen, am Bundesgericht in Lausanne statt; dies - nebenbei bemerkt - in einem Raum mit ikonischen Bildern. Eines zeigt die archaische Szene des salomonischen Urteils und bringt mich jedes Mal ins Grübeln, wenn ich ein Urteil wieder einmal als salomonisch loben will. Da kommen zwei Frauen zu Salomon mit einem Kind, beide behaupten, es sei ihres. König Salomon befiehlt, das Kind mit einem Schwert auseinanderzuhauen, damit jede Frau ihre Hälfte bekäme. Die eine Frau sagte dann, man solle es der anderen geben, damit das Kind überlebe. Voilà, da hat Salomon gemerkt, dass das die richtige Mutter ist. Wenn Sie also das Wort "salomonisch" bei einem Urteil verwenden, geht das auf diese Geschichte zurück. 
+Anwesend am 22. April 2026 in Lausanne war der Bundesgerichtspräsident, verschiedene weitere Mitglieder des Bundesgerichtes, die Präsidentinnen und Präsidenten der erstinstanzlichen Gerichte und weitere Mitglieder. In ihrer Plenarsitzung im Mai 2026 hat auch die Geschäftsprüfungskommission den Bericht zur Kenntnis genommen, der ihr dann auch vom Bundesgericht vorgestellt wurde.
+Zur Einordnung der Aufgaben der Geschäftsprüfungskommissionen gegenüber dem Bundesgericht: Die Bundesversammlung übt die Oberaufsicht über das Bundesgericht, die oberste gerichtliche Instanz der Eidgenossenschaft, aus. Das heisst, sie übt die Oberaufsicht über die Geschäftsführung des Bundesgerichtes aus, selbstverständlich geht es nicht um die Wertung von Urteilen. Das Bundesgericht übt seinerseits die Aufsicht über das Bundesstrafgericht, das Bundesverwaltungsgericht und das Bundespatentgericht aus, wobei das Bundesgericht nach wie vor nicht über die Befugnisse und Mittel verfügt, um in persönlichen Angelegenheiten umfassend einzugreifen. Wie die jüngsten Ereignisse jedoch zeigen, bereiten bestimmte Fälle nach wie vor Probleme. Wir werden bei der Prüfung des Geschäftsberichtes des Jahres 2026 darauf zurückkommen müssen.
+Im Jahr 2025 haben die verschiedenen Kammern des Bundesgerichtes über 7883 Fälle entschieden, was rund 7 Prozent mehr als dem Wert des Vorjahres entspricht; im Jahr 2024 wurden 7351 Fälle entschieden. Dieser geringere Anstieg als zuvor zeigt, dass die 2020 eingeleitete Reorganisation der Kammern allmählich Früchte trägt. Die durchschnittliche Verfahrensdauer verkürzte sich um einige Tage. Leicht weniger Beschwerden wurden gutgeheissen. Das Bundesgericht veröffentlichte 213 Urteile, auch um die Transparenz der Rechtsprechung zu gewährleisten. All dies ersehen Sie im Detail im Bericht des Bundesgerichtes. 
+Zu den erstinstanzlichen Gerichten: Das Bundesstrafgericht verzeichnete im Jahr 2025 insgesamt einen Anstieg der Eingänge auf 686 neue Fälle gegenüber 619 im Jahr 2024. Die Erledigungsquote blieb stabil bei 93 Prozent statt 94 Prozent im Jahr 2024. Die Strafkammer hatte mehrere bedeutende Verfahren zu bearbeiten, beispielsweise bezüglich Bestechung fremder Amtsträger im internationalen Handel mit Erdölprodukten. Die Beschwerdekammer hatte Ende des Jahres mehr hängige Verfahren, dies unter anderem aufgrund der Zunahme der Verfahren im Verwaltungsstrafrecht und im Bereich der internationalen Rechtshilfe. Die Berufungskammer hatte eine weitere Zunahme der Verfahren zu verzeichnen. Diese betrafen das Unternehmensstrafrecht, Geldwäscherei, Insiderhandel, Terrorismus sowie die Bankomatsprengungen. 
+Es wurde auch darauf hingewiesen, dass die nebenamtlichen Richterpersonen aufgrund ihrer hauptberuflichen Auslastung zeitlich nicht so flexibel sind, wie es ursprünglich angedacht war. 
+Interessant für das Parlament sind auch immer die Hinweise an den Gesetzgeber, die wir unterdessen auch noch direkt den Sachbereichskommissionen mitteilen. So hat das Bundesstrafgericht beispielsweise den EFK-Bericht bezüglich der Einziehungen und Ersatzforderungen nach Artikel 70 StGB ernst genommen. Damit sich der Grundsatz "Strafbares Handeln soll sich nicht lohnen" auch richtig umsetzen lässt, wird angeregt, ein vereinfachtes Vollstreckungsverfahren zu schaffen, damit die Ersatzforderungen schnell eingetrieben werden können. Das ist ein wichtiger Punkt bei der Bekämpfung der Wirtschaftskriminalität.
+Das Bundesverwaltungsgericht verzeichnet erneut einen markanten Anstieg der Geschäftslast. Eine bessere Koordination zwischen dem SEM und dem Bundesverwaltungsgericht wäre wünschenswert. Es gab 70 neue Stellen beim SEM, aber nur eine Mikroerhöhung des Stellenetats beim Bundesverwaltungsgericht in St. Gallen. Eine bessere Koordination hätte da, wie betont, zu einer besseren Lösung führen können. Die durchschnittliche Verfahrensdauer konnte man jedoch reduzieren. Gleichzeitig hat man in St. Gallen auch viel in die Digitalisierung investiert. Das Ziel, Papier definitiv beiseitezulassen, rückt näher.
+Das Bundespatentgericht verzeichnete einen Rückgang an Eingängen. Kein Fall ist länger als zwei Jahre hängig. Der Grund liegt vermutlich in der Bildung des Einheitlichen Patentgerichtes. Dieses erlässt Verbote, die für bis zu 18 Länder gelten, und kann Patente für alle angeschlossenen Länder für ungültig erklären. Die Teilnahme am System steht nur EU-Staaten offen, das System hat aber auch Auswirkungen auf die Schweiz. Das Bundespatentgericht hat sich zum Ziel gesetzt, das schnellste Gericht in Europa zu werden. Hierfür hat es unter anderem ein beschleunigtes Nichtigkeitsverfahren eingeführt.
+Einige Worte noch zur Arbeit in der Geschäftsprüfungskommission im Zusammenhang mit den Gerichten: Wir haben einige Vorstösse und Berichte ausgearbeitet. Ganz kurz zum Stand: 
+Erstens hat die GPK-S die parlamentarische Initiative 25.401, "Eidgenössische Gerichte. Disziplinarsystem einführen, um das Vertrauen in diese Institutionen zu stärken", eingereicht. Dieser Vorstoss, dieses Anliegen liegt zurzeit in der Kommission für Rechtsfragen des Ständerates. Die Motion 22.4250, "Erhöhung der Obergrenze der Gerichtsgebühren des Bundesgerichtes, des Bundesverwaltungsgerichtes und des Bundesstrafgerichtes", wurde von der Kommission für Rechtsfragen des Nationalrates im Rahmen einer grösseren Revision behandelt. Die Motion 25.4395 der RK-S, "Reorganisation des Bundesstrafgerichtes", wurde ebenfalls in der Kommission für Rechtsfragen des Nationalrates einstimmig gutgeheissen. Die Unabhängigkeit der ersten und zweiten Instanz soll damit besser gewährleistet werden. Dabei stützt sich die Kommission für Rechtsfragen auf den Bericht der GPK aus dem Jahre 2022. Weiter konnte die GPK-Subkommission Gerichte/BA den Bericht zum System der nebenamtlichen Richterinnen und Richter in der Kommission für Rechtsfragen des Nationalrates vorstellen. Wir gehen davon aus, dass sie diesbezüglich ebenfalls aktiv wird.
+Letztlich sei daran erinnert, dass das Bundesgericht im Jahr 2025 sein 150-jähriges Bestehen feierte. Zu diesem Anlass wurden unter anderem ein wissenschaftliches Kolloquium, eine Festschrift, eine offizielle Feier sowie Tage der offenen Tür mit etwa zweitausend Besuchern organisiert. 
+Ich möchte, Herr Bundesgerichtspräsident, diesen Bericht nicht abschliessen, ohne Ihre Arbeit zu verdanken, die gute Zusammenarbeit mit den Bundesbehörden und auch die Arbeit Ihres Sekretariats, unter anderem im Zusammenhang mit der Tätigkeit unserer Kommission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chassot Isabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous soumet le Conseil national entend charger notre gouvernement de présenter une modification des bases légales de sorte qu'il soit possible de rendre une ordonnance pénale pour expulser un étranger sans droit de séjour. Votre commission vous propose à l'unanimité de rejeter cette motion. Cette unanimité peut surprendre, mais elle s'explique par les travaux en cours et les décisions déjà prises par notre conseil. Permettez-moi d'en relever les principales étapes.
+À sa séance du 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion que nous soumet le Conseil national entend charger notre gouvernement de présenter une modification des bases légales de sorte qu'il soit possible de rendre une ordonnance pénale pour expulser un étranger sans droit de séjour. Votre commission vous propose à l'unanimité de rejeter cette motion. Cette unanimité peut surprendre, mais elle s'explique par les travaux en cours et les décisions déjà prises par notre conseil. Permettez-moi d'en relever les principales étapes.
+À sa séance du 19 février 2026, notre commission avait examiné l'initiative du canton de Saint-Gall 25.306, visant notamment à permettre l'expulsion d'étrangers sans droit de séjour dans le cadre d'une procédure d'ordonnance pénale. Elle avait à cette occasion élargi ses travaux et examiné l'historique et les interventions similaires portant sur la question de l'expulsion. Elle avait commencé l'examen de la motion faisant l'objet du rapport de ce matin et d'une initiative de même teneur, 25.436, aussi déposée par la Commission des affaires juridiques du Conseil national (CAJ-N). Notre commission avait estimé à cette occasion, comme son homologue du Conseil national, qu'il était nécessaire d'agir en ce qui concerne la procédure d'expulsion. Estimant toutefois que l'initiative et la motion de la CAJ-N étaient trop restrictives, notre commission avait déposé sa propre initiative, l'initiative 26.405, "Simplifier la procédure d'expulsion", qui demande qu'à l'avenir, l'expulsion des étrangers sans droit de séjour puisse être ordonnée soit par ordonnance pénale, soit par l'autorité de migration. En attendant la détermination de la commission soeur du Conseil national et dans l'objectif de pouvoir avancer de manière ordonnée et coordonnée, notre commission avait suspendu l'examen des deux objets parlementaires venant du Conseil national.
+Avec ce même objectif, elle vous avait proposé de ne pas donner suite à l'initiative du canton de Saint-Gall. Peut-être vous en souvenez-vous, vous avez accepté cette proposition le 16 mars dernier. Comme rapporteuse pour cet objet, je vous avais indiqué lors des débats les prochaines étapes, à savoir l'examen par la CAJ-N de notre initiative parlementaire, puis la reprise dans notre commission des travaux sur la motion qui nous occupent ce matin. La CAJ-N a procédé le 16 avril dernier à l'examen de notre initiative parlementaire et y a donné suite, chargeant ainsi notre commission d'élaborer un projet en vue de simplifier la procédure d'expulsion. Notre commission a donc repris l'examen de la présente motion lors de sa séance du 23 avril et, prenant acte de la décision de la CAJ-N, la commission vous propose sans opposition de rejeter la motion 25.3428, ce qui nous permettra de nous concentrer sur l'initiative parlementaire.
+Comme déjà indiqué, votre commission est d'avis qu'il est nécessaire d'agir dans le domaine des expulsions pour pouvoir accélérer les procédures, ne serait-ce déjà que pour décharger les autorités pénales - nous l'avons déjà aussi entendu ce matin - également surchargées par ces questions. Elle entend dès lors engager dans les meilleurs délais les travaux. Ils permettront de tenir compte de deux motions, 18.3408 et 21.3009, qui n'ont pas encore été mises en oeuvre par le Conseil fédéral. Le lancement de ces travaux par la commission permettra par ailleurs d'intégrer le rapport attendu du Conseil fédéral sur le postulat Schmid Pascal 25.3394, "Décharger la justice pénale en transférant les expulsions aux autorités de migration". Il sera en effet utile de disposer des résultats de cette analyse, en particulier de l'examen de la pondération des avantages et des inconvénients d'une réglementation, en droit pénal ou en droit des étrangers, afin d'optimiser et d'accélérer la procédure d'expulsion.
+C'est avec ces considérations, et en raison des nombreuses motions et interventions parlementaires que je vous ai signalées, que la commission vous propose le rejet de la présente motion. Cette étape nous permettra en effet de poursuivre les travaux de manière ordonnée, en évitant des procédures parlementaires parallèles qui pourraient en fin de compte retarder les travaux.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die vorliegende Motion verlangt, dass eine Landesverweisung gegenüber ausländischen Personen ohne Aufenthaltsrecht auch im Strafbefehlsverfahren angeordnet werden kann. Die Motion zielt damit auf eine punktuelle Anpassung innerhalb des geltenden strafrechtlichen Systems ab. Sowohl Ihre Kommission für Rechtsfragen als auch der Bundesrat erachten diesen Ansatz als zu eng. Er berücksichtigt ausschliesslich die strafrechtliche Schiene und blendet andere Möglichkeiten aus.
+In diesem Zusammenhang ist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die vorliegende Motion verlangt, dass eine Landesverweisung gegenüber ausländischen Personen ohne Aufenthaltsrecht auch im Strafbefehlsverfahren angeordnet werden kann. Die Motion zielt damit auf eine punktuelle Anpassung innerhalb des geltenden strafrechtlichen Systems ab. Sowohl Ihre Kommission für Rechtsfragen als auch der Bundesrat erachten diesen Ansatz als zu eng. Er berücksichtigt ausschliesslich die strafrechtliche Schiene und blendet andere Möglichkeiten aus.
+In diesem Zusammenhang ist auf das überwiesene Postulat 25.3394 Schmid Pascal, "Strafjustiz entlasten. Landesverweisungen den Migrationsbehörden übertragen?", hinzuweisen. Dieses verlangt eine grundlegende Prüfung der Zuständigkeitsfrage zwischen Strafrecht und Ausländerrecht. Die Arbeiten an diesem Postulatsbericht laufen bereits. Zudem lancierte die RK-S am 19. Februar 2026 eine eigene Kommissionsinitiative 26.405, "Verfahren der Landesverweisungen vereinfachen". Diese verfolgt einen breiteren Ansatz und berücksichtigt sowohl strafrechtliche als auch verwaltungsrechtliche Aspekte. Die RK-N hat dieser Initiative inzwischen Folge gegeben, weshalb die RK-S nun die entsprechenden Umsetzungsarbeiten aufnimmt und die Ablehnung der vorliegenden Motion 25.3428 beantragt.
+Der Bundesrat teilt die Einschätzung der RK-S. Ich bitte Sie, dem einstimmigen Entscheid Ihrer Kommission zu folgen und die Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Berichterstatter aus der Kommission hat es sehr gut dargestellt: Diese Motion wäre kontraproduktiv. Der Bundesrat kommt auch zu diesem Schluss und bittet Sie deshalb, die Motion abzulehnen - auch wenn er natürlich das Anliegen teilt, die Asylentscheide zu beschleunigen.
+Mit dieser Motion würden Sie eher das Gegenteil machen. Nach dem erstinstanzlichen Entscheid, im beschleunigten oder im Dublin-Verfahren, führt die Rechtsvertretung mit der asylsuchenden Person heute eine Chancenberatung durc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Berichterstatter aus der Kommission hat es sehr gut dargestellt: Diese Motion wäre kontraproduktiv. Der Bundesrat kommt auch zu diesem Schluss und bittet Sie deshalb, die Motion abzulehnen - auch wenn er natürlich das Anliegen teilt, die Asylentscheide zu beschleunigen.
+Mit dieser Motion würden Sie eher das Gegenteil machen. Nach dem erstinstanzlichen Entscheid, im beschleunigten oder im Dublin-Verfahren, führt die Rechtsvertretung mit der asylsuchenden Person heute eine Chancenberatung durch. Sie erhebt nur dann Beschwerde, wenn diese nicht zum Vornherein aussichtslos erscheint, ansonsten legt sie das Mandat nieder; diese Pflicht ergibt sich aus Artikel 102h des Asylgesetzes. Die Statistiken zeigen, dass das funktioniert. Die Statistiken zur Beständigkeit der Asylentscheide zeigen, dass der Anteil der Beschwerden seit der Einführung dieses neuen Systems im Jahr 2019 abgenommen hat. Gleichzeitig sind die Kassations- und Gutheissungsquoten der Beschwerden deutlich gesunken: Rund 99 Prozent aller Asylentscheide bleiben auch nach einer allfälligen Beschwerde rechtskräftig. Die statistischen Auswertungen des Bundesverwaltungsgerichtes zeigen aber auch, dass die vom SEM mandatierten Rechtsschutzorganisationen Beschwerden nur in Fällen mit realistischen Erfolgsaussichten einreichen. Die Erfolgsquote ihrer Beschwerden ist deutlich höher als jene von Rechtsvertretern, die Asylsuchende eben selbst mandatieren. Das wollen wir nicht wieder umkehren. Das aktuelle System des unentgeltlichen Rechtsschutzes funktioniert sicher besser. Es mag, insbesondere auf Gerichtsebene, immer noch Verbesserungsbedarf geben, aber es funktioniert sicher besser, als wenn es im Sinne der Motion geändert würde.
+Eine Änderung der Gesetzesbestimmungen ist nicht zweckmässig, ja, kontraproduktiv. Der Bundesrat lehnt daher diese Motion genau wie Ihre Kommission ab und bittet Sie, das auch so zu tun.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwander Pirmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bitte Sie, dieser Motion zuzustimmen. Ich halte mich kurz, ich gehe davon aus, dass der Motionär auch noch sprechen wird.
+Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese, in der Bundesverfassung verankerte Rechtsweggarantie, im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich bitte Sie, dieser Motion zuzustimmen. Ich halte mich kurz, ich gehe davon aus, dass der Motionär auch noch sprechen wird.
+Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese, in der Bundesverfassung verankerte Rechtsweggarantie, im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshalb diese Rechtsweggarantie nicht überall gleich umgesetzt werden soll. Das ist die Kernfrage. Ich glaube, wir müssen hier besonders diese Fragen stellen.
+Es geht ja - entgegen dem Titel - nicht um die unentgeltliche Rechtspflege als Ganzes, sondern es geht um einen Teilbereich, nämlich um die unentgeltliche Rechtsvertretung. Hierzu steht in Artikel 29 Absatz 3 der Bundesverfassung, jede Person habe ausserdem Anspruch auf unentgeltlichen Rechtsbeistand, soweit dies zur Wahrung ihrer Rechte notwendig sei. Sie haben das angeschnitten mit der Frage der Komplexität. "Soweit es zur Wahrung ihrer Rechte notwendig ist" - und meine Erfahrung in der Praxis, in der Umsetzung ist, dass die Hürden sehr hoch sind. Die Gerichte sagen: Ja, du kannst dich ja selber vertreten, es ist nicht so komplex. Und dann bekommen Sie eben keine unentgeltliche Rechtsvertretung.
+Die Problematik bei den Bürgerinnen und Bürgern ist, dass sie diese Frage erst im Hauptverfahren beantwortet bekommen, Herr Kollege Zopfi, erst im Hauptverfahren. Sie wissen also das ganze Verfahren hindurch nicht, ob Sie tatsächlich diese unentgeltliche Rechtsvertretung bekommen. Gegebenenfalls müssen Sie den Anwalt am Schluss doch selbst bezahlen. Ein konkretes Beispiel: Eine Familie mit zwei Kindern wollte eben eine unentgeltliche Rechtsvertretung, hatte aber 8000 Franken auf einem Sparkonto. Das Gericht sagte, dass von den 8000 Franken die 5000 Franken für den Anwalt selbst bezahlt werden können. Das ist die Problematik, die Bürger sehen diese Vergleiche. Das ist nicht ein Einzelfall, das sehe ich ständig, fast wöchentlich, bezüglich unentgeltlicher Rechtsvertretung und nicht bezüglich genereller Rechtspflege.
+Deshalb glaube ich, dass wir hier gut daran tun, wenn wir die in der Bundesverfassung verankerte Rechtsweggarantie in allen Gesetzen gleich anwenden. Ich bitte Sie daher, die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte Sie in aller Kürze bitten, der Mehrheit zu folgen. 
+Herr Zopfi hat dargelegt, warum das heutige System funktioniert. Die Rechtsvertreter haben die richtigen Anreize und sorgen in 80 Prozent der Fälle dafür, dass keine Beschwerde erhoben wird. Zudem ist die Alternative, dass entweder das Ganze später verzögert geprüft wird oder aber die Leute selber einen Rechtsbeistand nehmen, Stichwort "türkische Verhältnisse". Also: Das heutige System funktioniert und würde sonst verschlechtert. 
+Di</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte Sie in aller Kürze bitten, der Mehrheit zu folgen. 
+Herr Zopfi hat dargelegt, warum das heutige System funktioniert. Die Rechtsvertreter haben die richtigen Anreize und sorgen in 80 Prozent der Fälle dafür, dass keine Beschwerde erhoben wird. Zudem ist die Alternative, dass entweder das Ganze später verzögert geprüft wird oder aber die Leute selber einen Rechtsbeistand nehmen, Stichwort "türkische Verhältnisse". Also: Das heutige System funktioniert und würde sonst verschlechtert. 
+Die Kernfrage von Herrn Schwander ist ja: Warum wird im allgemeinen Recht die Frage des Rechtsbeistands anders behandelt? Wir sind hier in einer ganz besonderen Konstellation, im Asylverfahren, in dem wir in möglichst kurzer Frist über ganz existenzielle Fragen entscheiden; also im Extremfall darüber, ob jemand in einen angeblichen Folterstaat zurückgehen muss oder nicht. Das wollen wir eben möglichst schnell entscheiden. Weil es immer um diese spezielle Konstellation geht, hat der Gesetzgeber gesagt, in diesem Sonderfall werde eine allgemeine Entscheidung getroffen. Hier ist der Rechtsbeistand fast in jedem Fall angemessen. Schweizerinnen und Schweizer kommen zum Glück gar nicht in diese Situation, aber auch sie würden ihn in dieser Situation natürlich erhalten. Also: Man hat für eine Standortkonstellation unter besonderen Verhältnissen diese besondere Lösung gefunden. Das ist eigentlich kein Ausbruch aus dem System.
+Ich bitte Sie, mit der klaren Mehrheit zu stimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sommaruga Carlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne pensais pas prendre la parole, mais j'avoue que les propos de notre collègue Rieder me font bondir de mon fauteuil. Dire qu'il y a une licence pour ne rien faire, c'est choquant. Je suis choqué parce que ce n'est pas la réalité. La réalité est très simple : on a vu aujourd'hui que la durée moyenne du traitement des dossiers de requérants d'asile s'est réduite avec le temps. Je donne quelques chiffres, cher collègue Rieder. Je tiens à préciser que les procédures accélérées durent environ 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne pensais pas prendre la parole, mais j'avoue que les propos de notre collègue Rieder me font bondir de mon fauteuil. Dire qu'il y a une licence pour ne rien faire, c'est choquant. Je suis choqué parce que ce n'est pas la réalité. La réalité est très simple : on a vu aujourd'hui que la durée moyenne du traitement des dossiers de requérants d'asile s'est réduite avec le temps. Je donne quelques chiffres, cher collègue Rieder. Je tiens à préciser que les procédures accélérées durent environ 50 jours, alors que la loi prévoit qu'elles doivent durer entre 100 et 140 jours au maximum, que les procédures Dublin ont une durée moyenne de 35 jours, c'est-à-dire extrêmement courte, et que les procédures dites de 24 heures, spécifiquement mises en place pour les demandes à faible taux de protection, ont un traitement effectif d'une durée moyenne de 17 jours. La durée des procédures a donc été raccourcie. La durée des procédures complexes, hors des centres fédéraux, a aussi été réduite. En moyenne, la procédure étendue dure 100 jours, alors que la loi fixe l'objectif idéal d'un an. On voit donc bien que ce qui a été dit ne correspond pas à ce qui se passe dans la réalité.
+Je pense qu'il faut aussi prendre note que tout cela a été permis grâce au renforcement qui a été mis en place au sein du SEM, sous la responsabilité de Mme Simonetta Sommaruga et de M. Beat Jans au Conseil fédéral. Je pense qu'il n'est pas nécessaire de venir nous dire une phrase qui n'a aucun sens, à savoir qu'il y a une licence pour ne rien faire. Le stock des demandes a été réduit aujourd'hui à tel point que des personnes ont été licenciées au SEM avec fin de leur contrat de travail, dans la mesure où il n'y avait plus de nécessité de les employer.
+Vous venez ensuite avec le Tribunal administratif fédéral, cher collègue. Vous avez raison, il y a un problème là-bas. Mais est-ce de la compétence du Conseil fédéral de le régler ? Non, nous connaissons la séparation des pouvoirs, que vous êtes le premier à défendre. Vous êtes membre de la Commission des affaires juridiques, vous pouvez décider d'augmenter le nombre de juges, vous êtes membre de la Commission judiciaire, vous pouvez élire les juges les plus efficients possibles pour traiter au Tribunal administratif fédéral ces affaires. On a maintenant un nombre de juges supplémentaires au Tribunal administratif fédéral, ce qui permet aussi de traiter le nombre de cas supplémentaires qui sont arrivés au Tribunal administratif fédéral en raison du traitement rapide des dossiers et de la liquidation du stock des procédures qui étaient au SEM.
+Il faut donc garder les pieds sur terre, regarder les chiffres et regarder la réalité en face et ne pas venir nous raconter qu'il y a en Suisse une licence pour ne rien faire en matière d'asile.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z'graggen Heidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Dabtte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspaketeds sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Dabtte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspaketeds sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbeit zwischen Bund, Kantonen, Städten und Gemeinden vereinbar ist. 
+Die Kommission hat zur Asylstrategie und der nun laufenden Umsetzung eine allgemeine, nicht nur gestützt auf diese Motion umfassende Anhörung durchgeführt. Sie hat den Bundesrat, das Staatssekretariat für Migration, die Konferenz der Kantonsregierungen, die KKJPD, die SODK angehört. Ebenfalls einbezogen wurden weitere Kantone, so zum Beispiel der Kanton St. Gallen und der Kanton Waadt sowie Vertreterinnen und Vertreter der Städte und Gemeinden. Im Rahmen dieser Anhörungen wurde der aktuelle Stand der Arbeiten im Asylbereich sowie die Umsetzung der Asylstrategie 2027 diskutiert. Dabei wurde deutlich, dass Bund, Kantone, Städte und Gemeinden in enger Abstimmung zusammenarbeiten und dass die Beschleunigung der Verfahren ein zentrales Anliegen aller beteiligten Akteure ist.
+Ihre Kommission hält fest, dass das Asylwesen nur gemeinsam, im Verbund von Bund, Kantonen, Städten und Gemeinden, bei der Planung, der Steuerung und vor allem dann in der Umsetzung gemeinsam erfolgen kann. Nach den Anhörungen wurde festgestellt, dass die Motion in ihrer aktuellen Form die Gefahr einer Übersteuerung der laufenden Arbeiten zwischen Bund und Kantonen und Gemeinden beinhalten könnte und dass bei einer wörtlichen Umsetzung der Forderung der Motion insbesondere im Hinblick auf die Zurückstellung der Asylstrategie laufende Arbeiten faktisch neu priorisiert oder unterbrochen werden müssten, was nicht im Sinne der geforderten Beschleunigung wäre.
+Wir haben in der Kommission weiter festgestellt, dass zum Zeitpunkt der Einreichung der Motion unseres Kollegen die Ausgestaltung der Asylstrategie 2027 noch nicht in der heutigen Form bekannt war, sodass die Motion mit einer anderen Ausgangslage allenfalls politisch anders zu beurteilen gewesen wäre. 
+Der Bundesrat hat in der Kommission in seinen Ausführungen im Kern betont, dass der Beschleunigungsauftrag bereits aufgenommen wurde und das im Rahmen der Motion 24.4171 und die Umsetzung bereits läuft. Bundesrat und Staatssekretär haben in der Kommission zudem darauf hingewiesen, Bundesrat oder Staatssekretär für Migration darauf hingewiesen, dass sich die Arbeiten inzwischen in einer Umsetzungsphase und nicht mehr in einer Strategiephase befinden. Das heisst: Die Strategiephase ist abgeschlossen, jetzt laufen die Umsetzungsarbeiten in Zusammenarbeit Bund, Kantone, Städte, Gemeinden.
+Weiter wurde in der Kommission festgehalten, dass die Motion ja in zwei Elemente aufgeteilt ist. Zum einen enthält sie die Forderung nach prioritärer Umsetzung des Beschleunigungsauftrages, zum anderen verlangt sie die Zurückstellung der Asylstrategie 2027. Die Kommission hat im Besonderen den zweiten Punkt in der aktuellen Umsetzungspraxis als nichtzielführend beurteilt, weil ja die Umsetzungsmassnahmen laufen und die Asylstrategie in dem Sinn als Grundlagenarbeit abgeschlossen ist.
+Die Kommission vertritt deshalb die Auffassung, dass die Beschleunigung im Rahmen der bestehenden Strategie - die eigentliche Stossrichtung des Vorstosses, die auch gut ist und in der Kommission geteilt wird - stärker zu gewichten ist und die bereits überwiesenen parlamentarischen Aufträge konsequent umzusetzen sind, parallel laufende Arbeiten jetzt jedoch nicht zu unterbrechen seien. Wir haben in der Kommission überlegt, ob eine Anpassung des Vorstosses im Sinne einer stärkeren Integration in die laufenden Arbeiten naheliegend gewesen wäre. Es ist uns aber - das wissen Sie - gemäss Parlamentsrecht nicht möglich, eine Anpassung der Motion vorzunehmen. In der Kommission haben wir den angehörten Stellen gegenüber - Kantonen und Gemeinden, aber natürlich auch dem Bund - auf jeden Fall deutlich gemacht, dass im Parlament eine gewisse Ungeduld in Bezug auf die Umsetzungen der überwiesenen Motionen und Postulate im Asylbereich besteht und die laufenden Arbeiten an bereits überwiesenen Vorstössen des Parlamentes und weiteren politischen Aufträgen zwingend in die Umsetzung der Massnahmen der Asylstrategie einzuschliessen sind.
+Zusammenfassend lässt sich sagen: Die Anliegen der Motion sind im Grundsatz bereits in die laufenden Arbeiten zur Umsetzung der Asylstrategie 2027 integriert. Die entsprechenden Prozesse sind aufeinander abgestimmt und werden gemeinsam weitergeführt. Eine zusätzliche Priorisierung oder eine Zurückstellung der laufenden Strategiearbeiten würde, je nach Ausgestaltung, Auswirkungen auf die bestehende Koordination zwischen den Staatsebenen haben. Damit befürchtet die Kommission das Gegenteil einer Beschleunigung. Aus diesen Gründen beantragt Ihre Kommission mit 7 zu 3 Stimmen bei 3 Enthaltungen, die Motion nicht anzunehmen. Das zentrale Anliegen der Motion, die Beschleunigung der Verfahren und die Weiterentwicklung der Systemsteuerung, wird von allen Seiten und auch von Ihrer Kommission geteilt, ist aber bereits Gegenstand der laufenden Arbeiten.
+Eine Minderheit der Kommission beantragt die Annahme der Motion. Sie ist der Auffassung, dass eine zusätzliche politische Priorisierung in einzelnen Bereichen angezeigt ist, um die laufenden Arbeiten gezielt zu verstärken. Sie verweist dabei insbesondere auf klar identifizierte Problemfelder wie Mehrfachgesuche oder vergleichbare Konstellationen. Aus Sicht der Minderheit ergänzt die Motion die Asylstrategie, indem sie den Fokus auf einzelne prioritäre Bereiche lege und verstärke, ohne die laufenden Arbeiten grundsätzlich infrage zu stellen. Sie beantragt daher die Annahme der Motion. Ich gehe davon aus, dass die Minderheitssprecherin, Frau Ständerätin Friedli, das selbst noch im Detail ausführen wird.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zopfi Mathias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt. Nicht irgendein Gefühl im Einzelfall, sondern ob wir diese Pendenzen senken können, wird einschenken. Es mag eine Wiederholung se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt. Nicht irgendein Gefühl im Einzelfall, sondern ob wir diese Pendenzen senken können, wird einschenken. Es mag eine Wiederholung sein, aber lassen Sie mich noch konkret auf das, was Sie gesagt haben, Kollege Stark, reagieren. 
+Wenn die Kommission sich mit diesen Rädchen und mit diesem System auseinandergesetzt hat und mit 10 zu 2 Stimmen zum Schluss kommt, dass es eben nicht funktioniert - und Ihre Überlegungen kann ich zu 100 Prozent nachvollziehen -, dann frage ich Sie, ob es klug ist, dass der Rat das hier übersteuert aus dem Gefühl heraus, dass man hier vielleicht optimieren könnte. 
+Tatsache ist, Kollege Stark: Sie haben gesagt, dass man diesen Entscheid, ob eine unentgeltliche Rechtsvertretung gewährt wird oder nicht, schnell treffen muss. Und Kollege Schwander hat gesagt, dass diese Frage im normalen Verfahren einer Schweizerin oder eines Schweizers vor einem Gericht erst im Laufe des Verfahrens geklärt wird. Ich sage Ihnen nochmals, und das ist das Entscheidende: Sie können es doch nicht schneller klären als die zuständige Person, die es innerhalb der Beschwerdefrist klärt - und die ist kurz. Und sie ist deshalb kurz, weil wir diese Rechtsvertretung gewähren. Deshalb können Sie die Frist so kurz machen. Innerhalb dieser Frist wird das heute geklärt. 
+Und 80 Prozent der Fälle fallen einfach weg. Das ist eine sagenhafte Quote, denn ich sage Ihnen, Anwälte führen gerne Beschwerde. Das ist ihr Beruf. 80 Prozent fallen weg. Und irgendjemand muss es ja klären. Sie können ja nicht sagen, die betroffene Person klärt das. Sie wird zu 100 Prozent Beschwerde erheben. Mein Fall ist immer der wichtigste für mich. Irgendjemand muss es klären. Sie können es in keinem Fall schneller klären als durch das heutige System. Wenn es neu ein Gericht klären muss, dauert es Wochen, wenn nicht Monate. Und ich sage Ihnen, das kostet. 
+Sie operieren hier am offenen Herzen eines Systems, in dem dieser Teil funktioniert. Der Teil Pendenzen funktioniert nicht. Ich möchte eigentlich, Kollege Stark, dass Sie Ihre Energie und Ihren Willen, das zu verbessern, auf das Bundesverwaltungsgericht richten und schauen, wie man dort beschleunigen kann. Dort muss man beschleunigen. Indem dort Verfahrensrechte geprüft und nochmals geprüft werden, indem es noch einmal und noch einmal einen Schriftenwechsel gibt, wird verzögert, und die Fälle stapeln sich. 
+Schnelles Recht ist gutes Recht. Ein schneller Entscheid ist ein guter Entscheid. Der Entscheid über die unentgeltliche Rechtsvertretung wird innerhalb von wenigen Tagen durch die zuständigen Personen gefällt und führt zu deutlich tieferen Kosten. Ich bitte Sie, sich die Überlegungen, die die SPK mit 10 zu 2 Stimmen zu diesem Entscheid geführt haben, wirklich zu überlegen und hier nicht aus dem Gefühl heraus, dass es eine Ungleichbehandlung sei - die es nicht ist -, diese Motion gutzuheissen. Sie würden nicht dem SEM einen Denkzettel verpassen, sondern Ihrer Kommission, die sich damit wirklich vertieft auseinandergesetzt hat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedli Esther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Asylpolitik beschäftigt unseren Rat, aber auch die Bürgerinnen und Bürger in diesem Land sehr. Das haben wir auch bei der Abstimmung vom letzten Sonntag bemerkt. Es kommen zu viele Menschen über die Asylschiene in unser Land, die gar nicht an Leib und Leben bedroht sind und daher eigentlich auch kein Asylgesuch stellen sollten. Sie kommen zu uns mit der Aussicht auf eine bessere Zukunft, erfüllen jedoch den Asyltatbestand nicht. Diese Personen belasten unser System, denn sind sie einmal im L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Asylpolitik beschäftigt unseren Rat, aber auch die Bürgerinnen und Bürger in diesem Land sehr. Das haben wir auch bei der Abstimmung vom letzten Sonntag bemerkt. Es kommen zu viele Menschen über die Asylschiene in unser Land, die gar nicht an Leib und Leben bedroht sind und daher eigentlich auch kein Asylgesuch stellen sollten. Sie kommen zu uns mit der Aussicht auf eine bessere Zukunft, erfüllen jedoch den Asyltatbestand nicht. Diese Personen belasten unser System, denn sind sie einmal im Land und im Asylsystem, ist eine Rückkehr schwierig. Die Verfahren dauern lange, können verzögert und mit vielen Rechtsmitteln verlängert werden. Das bringt viel Sand ins Getriebe und belastet vor allem auch die Kantone und die Gemeinden. Zudem gibt es einen Teil der Personen im Asylsystem, welche mit den Behörden nicht kooperieren oder gar kriminell werden. Diese Personen missbrauchen unser Asylsystem, und das führt dazu, dass die Glaubwürdigkeit und Akzeptanz sinken.
+Bis jetzt ist es dem Bundesrat und dem Staatssekretariat für Migration nicht gelungen, diese, ich nenne es Grossbaustelle, anzugehen und vor allem nicht, griffige Massnahmen gegen Missbräuche zu ergreifen. Wir hören immer wieder: Wir sind daran, wir haben eine Strategie, wir sind am Arbeiten. Das reicht jedoch nicht mehr, und das führt eben dazu, dass praktisch in jeder Session mehrere Vorstösse zum Asylbereich eingereicht werden. Ich habe gezählt; wir haben über zwanzig überwiesene Vorstösse im Asylbereich, die der Bundesrat in Gesetzesvorlagen umsetzen sollte. Die Themen kreisen eigentlich immer um die Beschleunigung der Verfahren, Massnahmen für mehr Ausschaffungen und eine härtere Gangart gegenüber Kriminellen. Und wie ich gesagt habe, haben wir bis jetzt weder vom EJPD noch vom Bundesrat gehört, wann diese Vorstösse konkret umgesetzt werden und wann wir eine Botschaft ans Parlament erwarten können.
+Um all diese Massnahmen zu bündeln, hat die Finanzkommission des Ständerates im Rahmen der Erarbeitung des Voranschlages 2025 eine Motion für ein sogenanntes Beschleunigungspaket für das Asylwesen eingereicht. Es ist eigentlich dazu gekommen, weil die Kosten im Asylbereich laufend steigen. Der Bundeshaushalt wird damit immer mehr belastet. Man hat damals festgestellt, dass sich die Anzahl der Gesuche zwar immer wieder verändert oder auch zurückgeht, aber aufgrund der langen Verfahren sich der Pendenzenberg nicht wirklich abbaut. Das SEM sagt immer wieder, der Pendenzenberg sinke. Aber per 30. April dieses Jahres waren immer noch 7881 Asylgesuche sowie 3642 Gesuche um den Schutzstatus S erstinstanzlich pendent. Insgesamt warten nach wie vor über 20 000 Personen auf einen Entscheid. Im Jahr 2025 betrug die durchschnittliche erstinstanzliche Verfahrensdauer 571 Tage. Der Zielwert liegt bei 90 Tagen. Das zeigt: Es besteht dringender Handlungsbedarf. Das hat man mit der Motion 24.4271 gesehen und daher ein Paket mit gezielten regulatorischen und technischen Massnahmen angestossen, welche zur Beschleunigung und damit zum Pendenzenabbau beitragen.
+Ich erlaube mir einfach nochmals, auch zu erwähnen, welche ganz konkreten Massnahmen in dieser Motion erwähnt wurden. Beispiele sind: Vorverfahren: Länder mit einer Bleibequote unter 5 Prozent werden als Safe Countries eingestuft. Oder Angehörige von EU-/EFTA Staaten und Angehörige von Staaten, denen die EU den offiziellen Status "Beitrittskandidat" vergeben hat, können kein Begehren auf vorläufige Aufnahme infolge Unzumutbarkeit geltend machen. Der Status S bleibt vorbehalten. Oder Mehrfachgesuchen um Asyl soll die aufschiebende Wirkung entzogen werden. Oder bei Personen, die ihre Mitwirkungspflicht grob verletzen, soll das Asylgesuch in einem raschen Verfahren abgeschrieben werden. Oder stärkere Verbindlichkeit und Durchsetzung der geltenden Behandlungsfristen des Asylgesetzes mit entsprechenden Instrumenten. Oder generell Verkürzung der Fristen. Oder Einschränkung des Umfangs der Begründungspflicht im Beschwerdeverfahren.
+Kollege Zopfi hat beim vorangehenden Geschäft gesagt, schnelles Recht ist gutes Recht. Das sollten wir uns hier als Vorbild nehmen. Und Sie sehen, die Motion schlägt einen ganzen Strauss von Massnahmen vor. Auch der Bundesrat hat ja damals die Annahme dieser Motion beantragt. Unser Rat hat sie einstimmig angenommen, und auch im Nationalrat fand sie eine ganz grosse Mehrheit. 
+Anstatt die Motion jetzt jedoch zügig umzusetzen und eine klare Vorlage auszuarbeiten, hat das EJPD eine eigene Strategie, die sogenannte Asylstrategie 27, gestartet. Zusammen mit den Kantonen und Gemeinden sollen an runden Tischen und Arbeitsgruppen Strategien entwickelt werden. Das ist gut und recht. Aber so positiv, wie es die Berichterstatterin gesagt hat, kam es bei mir in der Kommission nicht an. Ich und meine Minderheit haben immer noch das Gefühl, dass man sich hier zu oft und zu fest, rund um Strategien, im Kreise dreht. Es fehlt die konkrete Umsetzung und dass man jetzt rasch Massnahmen ergreift. Meine Minderheit ist daher wirklich überzeugt, dass es nun eine zügige Umsetzung der Motion 24.4271 braucht, anstatt eine lange und weitere Strategiediskussion. 
+Mit der Strategie kann man noch weitere, über die vorliegende Motion hinausgehende Themen angehen. Aber die Beschleunigung der Verfahren, und ich glaube, darüber besteht eine breite Einigkeit, die muss jetzt rasch angegangen werden. Die Motion beinhaltet ja auch sehr viele klare Vorgaben. Ich bin sicher, mein Standeskollege und der Initiant der Motion, Kollege Würth, wird dazu auch noch selber Ausführungen machen. 
+Wichtig scheint mir zum Abschluss: Dass die Verfahren beschleunigt und verkürzt werden, entspricht, glaube ich, der Erwartung der Bürgerinnen und Bürger. Eine Beschleunigung würde die Akzeptanz für das Asylsystem massiv erhöhen und die Verwaltungen beim Bund, bei den Kantonen und Gemeinden und vor allem auch unsere Gerichte endlich entlasten. Damit werden eben auch Kosten gespart, deshalb kam diese Motion ursprünglich auch von der Finanzkommission. Vor allem würden wir mit einer Beschleunigung wieder auf den eigentlichen Kernbereich des Asylsystems fokussieren. Das System soll denen, die an Leib und Leben bedroht sind, helfen. Es soll nicht mit Wirtschaftsflüchtlingen und Kriminellen belastet werden. 
+Vor diesem Hintergrund bitte ich Sie, die vorliegende Motion anzunehmen und meine Minderheit zu unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zunächst möchte ich mich dafür bedanken, dass wir endlich über diese Asylstrategie diskutieren, und zwar ernsthaft. Ich möchte mich insbesondere bei der Kommission bedanken. Sie hat intensive Anhörungen gemacht, ich werde noch darauf zurückkommen. Diese waren sehr wichtig.
+Ich möchte ganz kurz zum Ausdruck bringen, warum der Bundesrat diese Motion ablehnt. Die erste hat er ja entgegengenommen, die Beschleunigung ist unbestritten. Dort leistet der Bundesrat den Teil, den er kann. Beim SEM haben w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zunächst möchte ich mich dafür bedanken, dass wir endlich über diese Asylstrategie diskutieren, und zwar ernsthaft. Ich möchte mich insbesondere bei der Kommission bedanken. Sie hat intensive Anhörungen gemacht, ich werde noch darauf zurückkommen. Diese waren sehr wichtig.
+Ich möchte ganz kurz zum Ausdruck bringen, warum der Bundesrat diese Motion ablehnt. Die erste hat er ja entgegengenommen, die Beschleunigung ist unbestritten. Dort leistet der Bundesrat den Teil, den er kann. Beim SEM haben wir die Pendenzen massiv abgebaut, da sind wir dran. Beim anderen Teil, bei den Gerichten, kann ich nichts machen, ich werde da nichts weiterverfolgen können. Ich bin froh, dass Sie das ernst nehmen.
+Der Grund, warum wir die Ablehnung der Motion beantragen, ist also nicht, dass uns das Beschleunigungspaket im Wege stehen würde, sondern dass Sie gleichzeitig die Asylstrategie aussetzen wollen. Das wäre kontraproduktiv, da sind wir wieder bei der Motion von vorhin. Damit entschleunigen Sie den Prozess - Sie beschleunigen ihn nicht -, und das macht doch keinen Sinn.
+Natürlich ist das Ziel der Asylstrategie und all der Workstreams, an denen im Moment intensiv gearbeitet wird, dass wir Ihnen ein Gesetzespaket vorlegen. Aber wenn wir die Asylstrategie aussetzen, dauert das länger, nicht kürzer. Denn der Absender der Asylstrategie, das ist mir wichtig, ist nicht nur der Bundesrat. Es sind auch die Kantone, es sind die Gemeinden, es sind die Städte. Diese braucht es zum Vollzug dieser Massnahmen. Sie werden sich bei dieser Gesetzgebung querstellen, wenn Sie sie vollständig übersteuern wollen. Denn sie insistieren, dass es keine Lastenverschiebung vom Bund zu den Kantonen geben darf, und diese Gefahr besteht natürlich.
+Ich muss es vielleicht nochmals erklären: Was ist eigentlich der Grund für die vielen Pendenzen? Warum sind wir auch bei den erweiterten Verfahren so viel langsamer, als wir es sein müssten? Ich muss es hier nochmals in aller Deutlichkeit sagen: Es ist der Angriff Russlands auf die Ukraine. Es kamen über hunderttausend zusätzliche Flüchtlinge in die Schweiz, sie mussten untergebracht, geschult werden usw. Wir waren darauf nicht genügend vorbereitet. Das Asylsystem kam an seine Grenzen, die Gemeinden kamen an ihre Grenzen. Deshalb haben wir so viele Pendenzen aufgebaut, das ist der Hauptgrund.
+Jetzt geht es darum, diese Pendenzen abzubauen, damit die Verfahren wieder schnell gehen. Sie haben es gesagt, Frau Friedli, es sind erstinstanzlich immer noch 7000 Pendenzen. Aber bitte respektieren Sie, dass es immer Verfahrenspendenzen gibt, es gibt immer laufende Verfahren; das sind etwa 5900. Es gibt aber auch solche, die in der Schublade liegen, um die sich niemand kümmert. Es verbleiben noch etwa 2000 Pendenzen, die in der Schublade sind, die wir noch nicht anpacken konnten. Bis Ende Jahr sind diese aber weg, dann hat das SEM seine Aufgaben gemacht, und das trotz dem Entlastungspaket. Auch wir müssen Personal einsparen, das möchte ich Ihnen sagen. Wir haben auch in diesem Bereich Personal abbauen müssen. Wir haben das aber hoch priorisiert; genau deshalb, weil Sie recht haben, wenn Sie sagen, wir müssten schneller werden, es sei kein Zustand, dass diese Entscheide so lange dauerten.
+Wie gesagt, bis Ende Jahr sollten wir das hinkriegen - wenn nicht wieder viel mehr Flüchtlinge kommen, als wir erwarten. Wir haben aber überhaupt keine Hinweise darauf, dass das der Fall sein könnte. Im Moment kommen im dritten Jahr in Folge weniger Flüchtlinge als zuvor. Das sollten wir also hinkriegen, dann sind die Pendenzen weg.
+Aber bei den Gerichten bitte ich Sie, dran zu bleiben und die entsprechenden Massnahmen zu ergreifen, damit das endlich schneller geht.
+Wir wollen beschleunigen, auch mit dieser Asylstrategie. Das ist mir wichtig. Die Kommission hat die KdK angehört, die SODK, die KKJPD, den Gemeindeverband, den Städteverband, und wir sind uns einig über den Handlungsbedarf. Wir haben uns darauf geeinigt, wo wir dringend Reformen brauchen. Diese gehen wir an; dort, wo wir können, ohne Gesetzesänderungen; dort, wo das nicht geht, kommen wir rasch mit Vorlagen. Wir haben zum Beispiel eine Taskforce zur Bekämpfung der Kriminalität eingesetzt. Sie lachen jeweils, wenn ich das sage. Aber darf ich Sie daran erinnern, dass diese Taskforce liefert: Sie hat einen Zwischenbericht gemacht und aufgezeigt, dass sie in allen Regionen aktiv ist und dass sie dank der Vernetzung der Institutionen auf kantonaler Ebene und auf Bundesebene, des Asylbereichs und der Polizei, bereits 50 renitente Kriminelle ins Gefängnis bringen konnte - 50! Bevor Sie also eine Gesetzesänderung beschlossen haben, hat sie geliefert. Jetzt müssen wir diese Zusammenarbeit etablieren und verbessern. Dort, wo die Taskforce noch weiteren Gesetzesänderungsbedarf sieht, wird sie die Vorschläge bald liefern, und dann werden wir mit den entsprechenden Entwürfen kommen. Aber ständig zu sagen, wir würden nichts machen, ist nicht in Ordnung. Vor allem im Zusammenhang mit diesen Pendenzen muss ich schon sagen, dass die Kritik nicht gerechtfertigt ist. 
+Was macht jetzt diese Asylstrategie? Warum ist es kontraproduktiv, sie zurückzuweisen? Weil sie das Ziel verfolgt, zu beschleunigen. Aktuell befinden wir uns bereits in der Umsetzungsphase. Ich sage nochmals, dass wir in der Umsetzungsphase sind, weil sie ganz konkrete Resultate bringt. Bund, Kantone, Städte und Gemeinden haben sich Ende letzten Jahres auf die Stossrichtung geeinigt. Wir haben das politische Mandat mit klaren Aufträgen definiert, und wir erarbeiten jetzt die konkreten Massnahmen. Die Arbeiten laufen gemäss Zeitplan, und die ersten Ergebnisse werden wir in der zweiten Jahreshälfte präsentieren. 
+Ein Kernelement der Asylstrategie ist ein vorgelagertes Zuständigkeitsverfahren. Dabei prüft das SEM in einem ersten Schritt, ob überhaupt ein Asylgesuch im Sinne des Asylgesetzes vorliegt. Nur, wenn das der Fall ist, wird die Person in die Asylstrukturen aufgenommen. Ziel ist es, Gesuche aus asylfremden Motiven frühzeitig zu erkennen - auch das wollen Sie ja mit verschiedenen Vorstössen erreichen -, damit wir die Asylstrukturen entlasten können. Gemäss Erfahrungen des SEM würde das bis zu 20 Prozent aller Asylgesuche betreffen. Liegt von einer Person kein Asylgesuch vor, gelten für sie die Bestimmungen des Ausländer- und Integrationsgesetzes. Hier tragen aber die Kantone die Hauptverantwortung. Aus diesem Grund ist es von zentraler Bedeutung, dieses Verfahren zwischen Bund, Kantonen und Gemeinden eng abzustimmen. Da müssen wir die Kantone an Bord haben. Ich bitte Sie, den Kantonen, insbesondere jeweils Ihrem Kanton, mit auf den Weg zu geben, dass sie dieses vorgelagerte Verfahren unterstützen und nicht bekämpfen sollen. Im Moment ist das ein bisschen mein Problem bei dieser Asylstrategie. Wir setzen Ihre Vorstösse um, indem wir sie mit den Kantonen und Gemeinden diskutieren und entsprechende Vorlagen machen, die dann auch mehrheitsfähig sein können. 
+Dieses Vorverfahren halte ich für absolut zentral und wichtig. Wenn es funktioniert, davon bin ich überzeugt, wird es dazu führen, dass viel weniger Leute in die Schweiz kommen, insbesondere aus Nordafrika, weil diese dann wissen, dass man bei uns im Asylzentrum nicht mehr gratis übernachten kann, wenn man im Herkunftsland nicht verfolgt wird. 
+Gleichzeitig überarbeiten wir das Konzept der sicheren Herkunftsstaaten. Das nimmt ein anderes Anliegen des Motionärs auf und gehört in das Beschleunigungspaket hinein.
+Ein weiteres Anliegen des Beschleunigungspaketes wurde bereits im Entlastungspaket 27 aufgenommen: Bei Mehrfach- und Wiedererwägungsgesuchen wird eine Karenzfrist von sechs Monaten gelten. 
+Schliesslich sorgt die Asylstrategie dafür, dass bereits überwiesene parlamentarische Vorstösse im Sicherheitsbereich durch die enge Zusammenarbeit von Bund, Kantonen, Städten und Gemeinden breit abgestützt und koordiniert umgesetzt werden. Mit der Asylstrategie sind wir hier eindeutig schneller am Ziel. 
+Der Einbezug des Parlamentes in die Asylstrategie ist mir wichtig. Deshalb haben wir die Asylstrategie inzwischen den Staatspolitischen Kommissionen beider Räte vorgestellt. Ich glaube, sie kommen auch deshalb zum Schluss, dass wir hier auf dem richtigen Weg sind und genauso griffige Instrumente erarbeiten können. 
+Der Bundesrat beantragt Ihnen, der Mehrheit Ihrer Kommission zu folgen und die Motion abzulehnen, weil er Ihren Auftrag ernst nimmt, die Sache zu beschleunigen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas trop rallonger le débat, parce que ce que je voulais dire a été dit tant par M. Maillard que par M. Sommaruga. Aujourd'hui, j'invite vraiment M. Müller à retirer sa motion, parce qu'elle n'a plus d'objectif, puisque depuis le 12 juin, comme cela a été rappelé, l'Italie s'est engagée à reprendre les cas Dublin. J'avais de la sympathie pour le contenu de la motion lorsqu'elle a été déposée, mais, avec la réponse apportée par le Conseil fédéral, je crois qu'on a les réponses aux ques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas trop rallonger le débat, parce que ce que je voulais dire a été dit tant par M. Maillard que par M. Sommaruga. Aujourd'hui, j'invite vraiment M. Müller à retirer sa motion, parce qu'elle n'a plus d'objectif, puisque depuis le 12 juin, comme cela a été rappelé, l'Italie s'est engagée à reprendre les cas Dublin. J'avais de la sympathie pour le contenu de la motion lorsqu'elle a été déposée, mais, avec la réponse apportée par le Conseil fédéral, je crois qu'on a les réponses aux questions qui sont soulevées et qui se heurtent à d'autres réalités. C'est vrai qu'à force de vouloir faire de la cogestion, si je peux faire un ajout aux propos tenus par M. Maillard, on va arriver à la congestion, de telle sorte que l'administration ne passera plus son temps qu'à répondre aux interventions plutôt que d'agir réellement sur le terrain pour aboutir à des solutions concrètes. C'est la raison pour laquelle, si M. Müller maintient sa motion, je la rejetterai. Si les problèmes qui étaient soulevés, comme je l'ai dit, attiraient ma sympathie, avec les réponses qui sont données aujourd'hui, la motion n'a plus lieu d'être.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stark Jakob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. Die Bundesverfassung hält in Artikel 29 Absatz 3 klar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. Die Bundesverfassung hält in Artikel 29 Absatz 3 klar fest, dass jede Person, die nicht über die erforderlichen Mittel verfügt, Anspruch darauf hat. Bei Asylsuchenden gehen wir davon aus, dass diese Voraussetzung erfüllt ist. Wäre das nicht der Fall, müssten wir das gesamte System infrage stellen und zunächst klären, Herr Zopfi, welche Asylsuchenden tatsächlich über ausreichende Mittel verfügen. Das heutige System basiert somit auf der Annahme der Mittellosigkeit und gewährt entsprechend einen Anspruch auf unentgeltliche Rechtspflege.
+Gleichzeitig verlangt die Verfassung, dass das Rechtsbegehren - ich zitiere - "nicht aussichtslos erscheint". Genau dieser Grundsatz gilt für alle Personen in unserem Land, die von einem Verfahren betroffen sind, und er soll selbstverständlich auch künftig für Asylsuchende gelten, jedoch nicht darüber hinaus. Meine Forderung zielt nicht darauf ab, die automatische Zuteilung einer kostenlosen Rechtsvertretung für jede neu asylsuchende Person aufzuheben; überhaupt nicht. Entscheidend ist vielmehr, dass die Rechtsvertretung in aussichtslosen Fällen früher endet als heute. Darin liegt der Kern meines Anliegens. Ich bin zudem überzeugt, dass eine frühere Beendigung zu deutlich weniger Beschwerden führen würde. Ich komme darauf zurück.
+Im geltenden Asylgesetz gehört es zu den ersten Aufgaben der Rechtsvertretung, die asylsuchende Person nach Teilnahme an der Erstbefragung und der Anhörung zu den Asylgründen über ihre Erfolgschancen im Verfahren zu informieren; hier verweise ich auf Artikel 102h Absatz 2 AsylG. Zu diesem Zeitpunkt liegt bereits ein umfassender Überblick über den Sachverhalt vor. Anschliessend begleitet die Rechtsvertretung das Verfahren bis zur Beschwerde und zum Entscheid des Bundesverwaltungsgerichtes. Heute endet die Rechtsvertretung - Herr Zopfi hat es gesagt - entweder mit der Rechtskraft eines Asylentscheides oder mit der Mitteilung der zugewiesenen Rechtsvertreterin oder des zugewiesenen Rechtsvertreters an die asylsuchende Person, dass wegen Aussichtslosigkeit keine Beschwerde eingereicht wird.
+Auffällig ist, dass rund 20 Prozent aller Fälle an das Bundesverwaltungsgericht weitergezogen werden, während lediglich 5 bis 6 Prozent dieser Beschwerden erfolgreich sind. Das bedeutet, dass 94 bis 95 Prozent der weitergezogenen Fälle mit einer Ablehnung enden. Der Spielraum ist somit erheblich. In der Praxis wägen Rechtsvertreter im Zweifel zugunsten der asylsuchenden Person ab und reichen eine Beschwerde ein, insbesondere wenn diese darauf beharrt. Daraus ergibt sich, dass eine beträchtliche Zahl von Entscheiden weitergezogen wird, obwohl die Erfolgsaussichten offensichtlich gering sind, und genau das ist der springende Punkt.
+Ich sage es nochmals: Der Kommissionsbericht zeigt, dass das neu strukturierte Asylverfahren nicht nur effizient, sondern auch sehr sorgfältig ist. Die Entscheidbeständigkeitsquote - auch das, Herr Zopfi, haben Sie gesagt - liegt bei 99 Prozent, was ausserordentlich hoch ist. Das bedeutet, dass rund 90 Prozent der erstinstanzlichen Entscheide des Staatssekretariates für Migration (SEM) am Ende rechtskräftig werden. Vor diesem Hintergrund kann man die Frage stellen, ob es trotz der verfassungsrechtlichen Vorgaben notwendig ist, allen Betroffenen in jedem Fall ein Rechtsmittel zur Verfügung zu stellen, wenn die Verfahren bereits mit hoher Sorgfalt durchgeführt werden. Aber - das Beschwerdeverfahren bleibt möglich.
+Nochmals: 20 Prozent der Entscheide werden weitergezogen und nur 5 bis 6 Prozent aller Beschwerden ans Bundesverwaltungsgericht dann gutgeheissen. Gleichzeitig, auch darauf wurde hingewiesen, stapeln sich beim Bundesverwaltungsgericht die Beschwerden zu Bergen und verzögern den Vollzug um Monate. Ja, wir haben aus der Finanzkommission interveniert. Es wurde uns beschieden, dass das in St. Gallen offenbar nicht möglich ist, die Abteilung die nötigen Kapazitäten nicht erhält und diese Berge eben Berge bleiben.
+Fazit: Wenn die Zahl dieser Beschwerden abnehmen würde, könnten wir den ganzen Effizienzgewinn behalten. Das könnte man machen, indem früher gesagt würde: Diese Fälle sind aussichtslos, wir brechen jetzt die Rechtsvertretung ab.
+Ich möchte zusammenfassen: Bei dieser Ausgangslage ist es aus Qualitätsgründen ohne Weiteres zulässig und aus Effizienzgründen auf jeden Fall notwendig, dass die Erfolgsaussichten von Asylgesuchen in einer ersten Phase, nach Erstbefragung und Anhörung, zwingend beurteilt werden und die Rechtsvertretung nur weitergeführt wird, wenn das Asylgesuch nicht aussichtslos erscheint - wie es auch in der Bundesverfassung steht. Wenn es nicht aussichtslos erscheint, soll die Beschwerde ergriffen und die Rechtsvertretung weiterhin gewährt werden können, aber ansonsten ist das Verfahren abzuschliessen.
+Damit würden sich erstens die Zahl der Beschwerden und die Kosten für die Rechtsvertretung deutlich reduzieren. Zweitens könnten die Asylverfahren - ich sage es nochmals: unter Beibehaltung der hohen Qualität - deutlich beschleunigt werden. Drittens würde die Verfahrensgarantie gemäss Bundesverfassung so gewährleistet, wie sie für alle Personen in der Schweiz gilt, die sich in irgendeinem rechtlichen Verfahren befinden.
+Ich bitte Sie deshalb, der Minderheit zuzustimmen und die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir haben letzte Woche ein hitziges Traktandum verhandelt, und meine Nachbarin rechts von mir hat von groben Fouls gesprochen. Sie ist deutlich die bessere Fussballerin als ich, ich habe zwei linke Füsse, aber ich möchte trotzdem auch hier einen Fussballvergleich bemühen. Wenn Sie nämlich diese Motion annehmen, dann schiessen Sie ein Eigentor. Um das zu begründen, möchte ich etwas in die Tiefe gehen und zuerst einmal mit drei Feststellungen starten: 
+Erstens, die Minderheit - Sie sehen das im sc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir haben letzte Woche ein hitziges Traktandum verhandelt, und meine Nachbarin rechts von mir hat von groben Fouls gesprochen. Sie ist deutlich die bessere Fussballerin als ich, ich habe zwei linke Füsse, aber ich möchte trotzdem auch hier einen Fussballvergleich bemühen. Wenn Sie nämlich diese Motion annehmen, dann schiessen Sie ein Eigentor. Um das zu begründen, möchte ich etwas in die Tiefe gehen und zuerst einmal mit drei Feststellungen starten: 
+Erstens, die Minderheit - Sie sehen das im schriftlichen Kommissionsbericht - stört sich daran, dass Asylbewerberinnen und Asylbewerber besser behandelt würden als Schweizerinnen und Schweizer, was die unentgeltliche Rechtspflege angeht. Lassen Sie mich klar festhalten, dass dem nicht so ist. In unserem Staat hat Anspruch auf unentgeltliche Rechtspflege, wer nicht in der Lage ist, das Verfahren zu bezahlen, gleichzeitig - wegen der Komplexität - anwaltliche Unterstützung benötigt sowie Erfolgsaussichten hat. Das ist überall so, und ich kann Ihnen als im Familienrecht tätiger Anwalt bestätigen, dass ich unzählige Verfahren über die unentgeltliche Rechtspflege führe. Zweitens, das SEM arbeitet im Bereich der Beschwerden sehr erfolgreich; das kann man sagen. Die Pendenzen konnten massiv reduziert werden, wir haben uns diese Zahlen zeigen lassen. Zudem - und das ist in diesem Kontext sehr interessant - sind die Entscheide des SEM insgesamt zu über 98 Prozent beständig. Was bedeutet das? Über 98 Prozent der Entscheide des SEM treten, weil sie nicht mit Beschwerden angefochten werden oder weil die Beschwerden abgewiesen werden, in Rechtskraft. Das ist eine beeindruckende Quote, die wahrscheinlich an wenigen Orten erreicht wird. Ich will damit nicht sagen, dass alles gut läuft, aber wir haben es hier konkret mit dem Beschwerdeverfahren zu tun, und ich würde sagen, dass man in diesem Bereich die Feststellung machen kann, dass es eigentlich nicht schlecht läuft. 
+Allerdings muss ich das auch wieder ein bisschen relativieren, denn meine dritte Feststellung lautet: Wir haben schon nicht einfach keine Probleme. Ein Problem, das wir haben, ist, dass sich am Bundesverwaltungsgericht die Pendenzen stapeln. Ende 2025 gab es 5795 Pendenzen; 253 davon stammten noch von 2022, 514 von 2023, 1864 von 2024 und 2834 von 2025. Es gibt leider eine steigende Zahl von Pendenzen. Und jetzt ist es so: Bei diesen Fällen geht es ja nicht einfach nur um Fälle, die am Gericht irgendwo in einer Schublade liegen und dann bearbeitet werden, sondern es geht um Menschen, die irgendwo in den Gemeinden einquartiert werden müssen, die finanziert werden müssen, usw. Diese Fälle kosten - also nicht die Fälle in der Schublade, sondern die Menschen, die in unserem Land bleiben, obwohl sie das Land dann vielleicht verlassen müssten, wenn der Entscheid rechtskräftig würde. Und wir reden hier nicht von kleinen Beträgen, wir reden von Dutzenden Millionen von Franken. Wenn wir Handlungsbedarf feststellen - und es ist, im Unterschied zu dem, was ich in Bezug auf meine zweite Feststellung gesagt habe, tatsächlich nicht alles gut -, dann ist es wichtig und zentral, dass wir das Beschwerdeverfahren beschleunigen und es auf keinen Fall ausbremsen. Wenn die Beschwerdeverfahren länger gehen, dann kostet uns das massiv mehr Geld. 
+Jetzt komme ich zu den Effekten dieser Motion und versuche Ihnen darzulegen, weshalb die Motion in diesem Kontext ein Eigentor wäre. 
+Der erste Effekt: Im Asylbereich funktioniert das System mit der unentgeltlichen Rechtsberatung gut. Die Personen, die diese Rechtsberatung machen, sind Juristinnen und Juristen; sie werden dafür angestellt, aber sie werden nicht pro Fall bezahlt, sondern - und das ist sehr entscheidend - sie werden pauschal bezahlt. Sie haben also keinen Anreiz, aussichtslose Beschwerden zu führen, da sie nicht für die einzelnen Beschwerden, die sie führen, einen Lohn oder eine Zahlung erhalten, sondern sie erhalten einfach eine grundsätzliche Pauschale. Und deshalb behandeln sie jene Fälle - das ist auch ihre Pflicht -, bei denen Aussicht auf Erfolg besteht. Sie haben die gesetzliche Aufgabe, die betroffenen Menschen über die Erfolgsaussichten zu informieren, und eben nur dort Beschwerde zu führen, wo es Aussichten auf Erfolg gibt. Dieser Grundsatz ist also bereits festgehalten. Und logisch, es ist klar, dass es sich um eine schwierige Einschätzung handelt. Die tiefe Gutheissungsquote von Beschwerden, die ich Ihnen vorher genannt habe, zeigt ja, dass das SEM seine Arbeit nicht schlecht macht und die Erfolgsaussichten deshalb meist relativ tief sind. Aber, und das ist zentral, es ist ein effizientes System. Wenn nämlich mit dieser Motion die unentgeltliche Prozessführung eingeschränkt und nur noch in Fällen gewährt würde, in denen ein Verfahren aussichtsreich ist - diese Prüfung bzw. Einschätzung wird heute eigentlich durch die Rechtsberatung vorgenommen -, dann müsste darüber ja neu entschieden werden. 
+Heute läuft es so, dass der Betroffene zur Rechtsvertretung geht. Diese berät ihn über die Erfolgsaussichten. Wenn gewisse Aussichten auf Erfolg bestehen - natürlich behandeln Sie als Anwalt nicht Fälle mit 100 Prozent Aussicht auf Erfolg, sondern vielmehr solche mit gewissen Aussichten - dann wird Beschwerde geführt. Das geschieht in ungefähr 20 Prozent der Fälle; ich werde nochmals darauf zurückkommen. In 80 Prozent der Fälle entscheidet die Rechtsvertretung also, dass es sich nicht lohnt, es zu probieren. Das ist eine hohe Quote. Stellen Sie sich vor, wie die Pendenzen beim Bundesverwaltungsgericht aussehen würden, wenn diese Quote tiefer wäre.
+Die Prozessaussichten werden also heute bereits geprüft, und zwar, und das ist auch ein wichtiger Punkt, innerhalb der Beschwerdefrist. Die Beschwerdefrist beginnt mit dem Entscheid des SEM zu laufen, und innerhalb dieser Frist wird entschieden, ob es aussichtsreich ist, eine Beschwerde zu machen. Wenn Sie das nun genauer überprüfen wollen, dann müssten Sie diesen Entscheid dem Gericht überlassen. Dann müsste das Gericht entscheiden, wie es der Motionär will, wie die Prozessaussichten sind, ob Aussicht auf Erfolg besteht. Dies müsste aber logischerweise nach der Beschwerdefrist gemacht werden. Denn das Gericht kann ja die Chancen erst beurteilen, wenn eine Beschwerde eingegangen ist. Vorher weiss es von diesem Fall gar nichts. Und, das ist ebenfalls klar, für diesen Entscheid braucht das Gericht Zeit. Es muss die Parteien anhören, es gibt rechtsstaatliche Pflichten und Garantien usw. Nehmen wir jetzt einmal an, dass das Bundesverwaltungsgericht für diese vielen Fälle, für 100 Prozent, nicht, wie heute für 20 Prozent, jeweils, sagen wir, zwei Wochen braucht, um die Frage zu entscheiden - und es wäre ein absolutes Turbogericht, wenn es das könnte. Das wäre schon deutlich teurer, als das, was die unentgeltliche Rechtsberatung überhaupt kostet, weil in diesen zwei Wochen viel mehr Menschen keinen Entscheid hätten und zwei Wochen länger im System bleiben würden. Wenn es einen Monat dauert, bleiben sie einen Monat länger im System, wenn es zwei Monate dauert, sind es zwei Monate länger, und während dieser Zeit verursachen sie jeden Tag Kosten. Es gibt Zahlen dazu, Sie können ausrechnen, was das kostet.
+Wenn dann noch mehr Personen als heute versuchen, eine Beschwerde zu machen, weil Sie die Erfolgsaussichten nicht mehr bei der Rechtsberatung analysiert bekommen, dann kippt es definitiv ins Kontraproduktive. Denn wenn dann nicht mehr 20 Prozent wie heute, sondern sagen wir 80 Prozent Beschwerde erheben, kann ich Ihnen sagen, was passiert. Das Bundesverwaltungsgericht würde von Beschwerden überschwemmt. Das Ziel muss aber sein, die Pendenzen am Bundesverwaltungsgericht zu senken, und nicht, sie zu steigern. Das können wir nicht tun, indem wir das Verfahren verlangsamen. Wir können es nur tun, indem wir beschleunigen. Die unentgeltliche Rechtsvertretung, ich will das klipp und klar sagen, beschleunigt das Verfahren, es bremst sie nicht. Diese Rechtsvertretenden haben keinen Anreiz, das System zu blockieren, weil sie pauschal bezahlt sind und nicht nach Stundensatz wie ein Anwalt üblicherweise.
+Damit komme ich zum zweiten Effekt. Denn auch der zweite Effekt wird klar, wenn man sich ein bisschen in die Statistik vertieft. Interessant wird es nämlich, wenn Sie die verschiedenen Herkunftsländer betrachten. Dort, wo die Rechtsvertretung über die unentgeltliche Rechtspflege läuft - das, was der Motionär infrage stellen will -, haben wir eine Beschwerdequote, ich habe es erwähnt, von etwa 20 Prozent. Von hundert Personen, die einen negativen Entscheid haben, führen dann also 20 Prozent Beschwerde. Das ist eigentlich eine recht tiefe Quote, denn es geht für diese Leute um einen für sie extrem einschneidenden Entscheid. Man würde eigentlich erwarten, dass die meisten probieren, eine Beschwerde zu machen. Aber es probieren es nur 20 Prozent. Das bedeutet umgekehrt, dass die Rechtsvertretungen in 80 von 100 Fällen raten, keine Beschwerde zu machen, und dass sie dies erfolgreich tun, denn es wird ja dann auch keine Beschwerde eingereicht. Die Aussichtslosigkeit oder die Prozessaussichten werden also bereits geprüft. Man könnte das Problem lösen, indem man sagt, es gibt einfach keine Beschwerde mehr. Aber dass man überhaupt Beschwerde machen kann, ist ein durch unsere Verfassung geschütztes Recht, und es führt ja gerade dazu, dass das SEM seine Arbeit speditiv machen kann. Sonst würden Sie die Verantwortung noch mehr zum SEM verlagern.
+Jetzt sehen Sie aber eine Auffälligkeit, und es ist wirklich eine Auffälligkeit, wenn Sie die Statistik anschauen. Bei gewissen Herkunftsländern ist es sehr verbreitet, dass nicht die unentgeltliche Rechtsvertretung beigezogen wird, sondern selbst, auf eigene Kosten, ein Anwalt mandatiert wird. Bezahlt wird das häufig aus den Kreisen der Diaspora. Zu beobachten ist dies sehr stark und sehr auffällig bei Menschen mit dem Herkunftsland Türkei. Die Beschwerdequote bei dieser Gruppe beträgt jetzt plötzlich, und das ist die Auffälligkeit, nicht mehr 20 Prozent wie bei den anderen, sondern 65 Prozent. Von 100 Betroffenen führen also nicht 20, sondern 65 Beschwerde. In absoluten Zahlen, ich habe das für 2024 nachgerechnet, führt es dazu, dass ungefähr 1200 Personen mehr Beschwerde führen als bei Personen aus den übrigen Herkunftsländern. Wenn man also diese 65 Prozent bei den Menschen mit dem Herkunftsland Türkei ausrechnet, gibt es 1200 Fälle am Bundesverwaltungsgericht mehr als bei den Menschen aus anderen Herkunftsländern. Ich habe Ihnen die Zahlen zu den Pendenzen am Bundesverwaltungsgericht genannt. Wenn Sie jetzt schauen, wie diese Zahl in Relation zu den Pendenzen steht, im Jahr 2025 waren es um die 2500, dann sehen Sie, dass 1200 Beschwerden recht einschenken.
+Was ist das Fazit? Das Fazit ist: Es führt nicht zu weniger Beschwerden, sondern es führt zu deutlich mehr Beschwerden, wenn Sie die unentgeltliche Rechtsvertretung nicht mehr, sondern weniger stark einschränken. Wahrscheinlich kann man wirklich sagen, dass das zu massiv mehr Beschwerden führt. Das lässt sich aus dem System auch erklären. Denn was würde passieren, wenn wir jetzt eingreifen? Das würde doch dazu führen, dass mehr Menschen einen Anwalt anstellen, da es für sie es um einen einschneidenden Entscheid geht. Das würde wahrscheinlich sogar durch die Diaspora finanziert, wie etwa bei der türkischen Diaspora, oder durch NGO und so weiter. Der Anreiz, keine aussichtslosen Beschwerden zu führen, würde wegfallen. Ehrlich gesagt: Ich habe nichts gegen Anwälte, ich bin selbst einer, aber wenn ein Anwalt den Kostenvorschuss bezahlt bekommt, von wem auch immer, dann wird er diese Beschwerde führen. Dies würde den Pendenzenberg am Bundesverwaltungsgericht anwachsen lassen, die Fälle verzögern, die anderen Fälle mitverzögern und massive Kosten verursachen. Wir reden von Dutzenden von Millionen Franken jährlich, wenn dieser Fall eintreten würde. Und ich sage Ihnen: Dieser Fall kann eintreten. Es ist unklar, wie viele Millionen es genau sind. Meine Schätzung wäre 100 Millionen Franken, aber behaften Sie mich nicht darauf. 
+Wenn Sie am Bundesverwaltungsgericht etwas zur Beschleunigung erreichen wollen, dann müssen Sie dort beschleunigen und nicht mit neuen Auflagen verlangsamen, mit der vermeintlich eingängigen Argumentation, die Schweizer müssten ja auch selber bezahlen. Mit dem EP 27 haben wir sogar Massnahmen getroffen. Diese sind damals aus der Subkommission 4 der Finanzkommission gekommen. Kollege Benedikt Würth, Kollege Benjamin Mühlemann, der gerade nicht hier ist, und ich haben uns mit diesen Zahlen eingehend beschäftigt. Ich will jetzt nicht sagen, dass wir alles gut machen, aber wir haben ein paar Massnahmen gefunden und Ihnen vorgeschlagen. Diese sind dann auch einstimmig durch diesen Rat gegangen. Diese Massnahmen führen wirklich dazu, dass beschleunigt werden kann. 
+All das, was ich Ihnen jetzt gesagt habe, hat dazu geführt, dass die Kommission Ihnen mit 10 zu 2 Stimmen, also deutlich, beantragt, diese Motion abzulehnen. 
+Vielleicht fragen Sie sich jetzt, wieso spricht der Mensch so lange, wenn es in der Kommission so klar war? Ich sage Ihnen, weshalb das so ist. Ich weiss, dass im Asylbereich die politische Unzufriedenheit gross ist. Vielleicht braucht es zwischendurch auch ein Zeichen. Aber ich sage Ihnen eines: In diesem Fall würden wir in ein System eingreifen, das nachweislich funktioniert. Wir würden wider besseres Wissen, wider diese Fakten und Zahlen hier eingreifen aus einer Unzufriedenheit und aus dem Gefühl, dass hier eine Ungleichbehandlung vorliegt. Ich bitte Sie, das nicht zu tun. Viele von Ihnen waren früher z. B. in Exekutiven, und Sie wissen, dass man manchmal justieren muss, aber nicht dort, wo es mehr schadet, als nützt. 
+Ich bitte Sie, hier dem Muster, gemäss dem die SPK sehr klar entscheidet und sich damit auseinandersetzt und der Rat nachher im Zweifel für Härte stimmt, nicht zu folgen und diese Motion aufgrund der Fakten abzulehnen. Sie ergibt keinen Sinn und ist definitiv ein Eigentor.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derrière la grande intervention de notre collègue Damian Müller sur la politique générale en matière d'asile, il y a une motion qui est extrêmement précise, qui charge le Conseil fédéral de négocier bilatéralement avec l'Italie pour que celle-ci reprenne les personnes relevant de sa responsabilité en vertu du règlement de Dublin. Le 12 juin, c'est-à-dire vendredi dernier, est entré en vigueur le Pacte sur la migration et l'asile de l'Union européenne. L'Italie a réagi en indiquant qu'elle allait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derrière la grande intervention de notre collègue Damian Müller sur la politique générale en matière d'asile, il y a une motion qui est extrêmement précise, qui charge le Conseil fédéral de négocier bilatéralement avec l'Italie pour que celle-ci reprenne les personnes relevant de sa responsabilité en vertu du règlement de Dublin. Le 12 juin, c'est-à-dire vendredi dernier, est entré en vigueur le Pacte sur la migration et l'asile de l'Union européenne. L'Italie a réagi en indiquant qu'elle allait reprendre les cas Dublin suisses. En d'autres termes, le problème n'existe plus puisque l'Italie, parce que ce mécanisme de solidarité au sein de l'Union européenne a été mis en place, a décidé de reprendre tous les cas Dublin et de faire fonctionner le système Dublin, ce qui s'applique également à la Suisse. Je vous invite simplement à relire la presse qui est sortie ce dimanche, voire ce lundi, en Suisse et en Italie.
+Dès lors, j'aurais attendu, cher collègue Damian Müller, que vous retiriez votre motion, parce que cette demande n'est plus d'actualité. Elle n'est plus d'actualité parce que l'Italie a annoncé qu'elle allait reprendre les cas Dublin dans le cadre de l'application du Pacte européen sur la migration et l'asile qui est entré en vigueur le 12 juin. En d'autres termes, comme cette motion doit encore être acceptée par le deuxième conseil, on arrivera de toute façon comme la pluie après la vendange et elle ne servira à rien. Ceci montre bien qu'aujourd'hui, si on maintient cette motion au vote, ce n'est pas le problème qui est exposé dans la motion qui est en jeu, mais c'est une volonté de s'attaquer de manière systématique au chef du Département fédéral de justice et police qui met en place la stratégie de traitement des cas d'asile qui nous a été expliquée tout à l'heure.
+J'espérais que vous seriez assez cohérent avec votre motion et que vous prendriez acte de la réalité politique telle qu'elle existe aujourd'hui en Italie et qui fait qu'il n'y a plus de nécessité d'agir au niveau du Conseil fédéral puisqu'il n'y a plus qu'à attendre que ce soit mis en pratique.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat beantragt, die Motion abzulehnen. Er hat sich die Mühe gemacht und in Ihrem Auftrag in einem Postulatsbericht im Detail aufgezeigt, wo die Probleme mit den "return hubs" liegen. Er hat aufgezeigt, dass sie mit enormen Kosten verbunden sind und dass es schlicht und einfach nicht möglich sein wird, die ganzen Rückkehr- oder Asylprobleme über die "return hubs" zu lösen. Er hat sich aber immer offen gezeigt, und das ist immer noch die Haltung des Bundesrates: Wenn sich ein Weg auftut, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat beantragt, die Motion abzulehnen. Er hat sich die Mühe gemacht und in Ihrem Auftrag in einem Postulatsbericht im Detail aufgezeigt, wo die Probleme mit den "return hubs" liegen. Er hat aufgezeigt, dass sie mit enormen Kosten verbunden sind und dass es schlicht und einfach nicht möglich sein wird, die ganzen Rückkehr- oder Asylprobleme über die "return hubs" zu lösen. Er hat sich aber immer offen gezeigt, und das ist immer noch die Haltung des Bundesrates: Wenn sich ein Weg auftut, dann sind wir dabei. 
+Mit dieser Motion verlangen Sie jetzt, dass wir das quasi als Priorität nehmen. Sie haben mir vorhin gesagt, ich müsse Prioritäten setzen, auf das Richtige und Wichtige setzen. Hier sagen Sie mir aber, ich müsse das beiseitestellen und dafür auf ein Pferd setzen, das noch nie ans Ziel gekommen ist. Es gibt bis heute keine funktionierenden "return hubs". Alle Staaten, die es versucht haben, sind bisher gescheitert. 
+Eine der Voraussetzungen ist die Rückkehrverordnung, die demnächst in Kraft treten soll. Das ist auch eine wichtige Voraussetzung, um entsprechende Verträge überhaupt aufsetzen und die Gesetzgebung in der Schweiz anpassen zu können. Wenn wir diese Rückkehrverordnung kennen und es gute Projekte gibt, dann können wir einen weiteren Schritt machen.
+Die Motion berücksichtigt einfach nicht, dass es drei Gründe gibt, warum diese "return hubs" die in sie gesetzten Hoffnungen nicht erfüllen werden. 
+Erstens geht es um die Kosten; sie sind sehr teuer. Zweitens ist die Umsetzung nicht möglich, denn bisher - ich sage es nochmals - ist sie nirgends erfolgreich gelungen. Drittens zur Wirkung: Selbst wenn wir es schaffen, gewisse Leute über "return hubs" wieder nach Afrika zu bringen, werden die grossen Herausforderungen im Asylwesen bleiben. 
+Deshalb ist der Bundesrat nach wie vor der Ansicht, dass wir die Prioritäten dort setzen sollen, wo wir den Handlungsbedarf gemeinsam mit Kantonen, Gemeinden und Städten erkannt haben. Wir werden ihnen bald Vorschläge unterbreiten, wir wählen dazu den Weg über die Asylstrategie.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich starte mit der Motion Chiesa 26.3229. Personen, die eine Gefahr für die öffentliche Sicherheit und Ordnung darstellen, sollen in der Schweiz keine Aufenthaltsbewilligung erhalten. Darüber sind wir uns einig. Die zuständigen Behörden können die Erteilung von Bewilligungen bereits heute konsequent verweigern, wenn Vorstrafen bekannt sind. Es handelt sich um bewährte Bestimmungen, sowohl im Ausländer- und Integrationsgesetz als auch im Freizügigkeitsabkommen. Und nun zu Ihrer Forderung nach dem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich starte mit der Motion Chiesa 26.3229. Personen, die eine Gefahr für die öffentliche Sicherheit und Ordnung darstellen, sollen in der Schweiz keine Aufenthaltsbewilligung erhalten. Darüber sind wir uns einig. Die zuständigen Behörden können die Erteilung von Bewilligungen bereits heute konsequent verweigern, wenn Vorstrafen bekannt sind. Es handelt sich um bewährte Bestimmungen, sowohl im Ausländer- und Integrationsgesetz als auch im Freizügigkeitsabkommen. Und nun zu Ihrer Forderung nach dem systematischen Verlangen eines Strafregisterauszugs: Bei Drittstaatsangehörigen können die Behörden bereits heute einen Strafregisterauszug aus dem Herkunftsland verlangen, und zwar auch systematisch. Im Anwendungsbereich des Freizügigkeitsabkommens ist es rechtlich anders geregelt. Das systematische Einholen von Strafregisterauszügen würde das Freizügigkeitsabkommen und die völkerrechtlichen Pflichten der Schweiz verletzen. Bei Verdachtsmomenten dürfen die Kantone aber jederzeit einen Strafregisterauszug einfordern. Die Kantone sollen weiterhin entscheiden, wann das Einholen eines Strafregisterauszugs aus dem Herkunftsland sinnvoll erscheint. Und tatsächlich verlangen viele Kantone bereits heute vor der Erteilung einer Bewilligung einen Strafregisterauszug. Das macht ja auch Ihr Kanton, geschätzter Herr Ständerat Chiesa. Es ist also möglich. Eine Anpassung der gesetzlichen Grundlagen ist deshalb nicht nötig. Der Bundesrat beantragt, die Motion Chiesa abzulehnen. 
+Ich komme zur Motion Schwander 26.3407. Keiner der fünf genannten Staaten erfüllt zurzeit die genannten Bedingungen zur Bezeichnung als Safe Country nach Schweizer Kriterien; das ist so. Aber das Safe-Country-Konzept der Schweiz und das Safe-Country-Konzept der EU unterscheiden sich voneinander. Die Mitgliedschaft im Europarat oder eine Bezeichnung durch die EU als sicherer Herkunftsstaat reichen nach Schweizer Kriterien tatsächlich nicht aus. Für uns ist relevant, ob in einem Staat tatsächlich die gesamte Bevölkerung vor unrechtmässiger Verfolgung geschützt ist. Dies ist in diesen Staaten nicht der Fall. In der EU hat die Bezeichnung als Safe Country andere Folgen als in der Schweiz. In der EU können Asylgesuche nur dann in einem beschleunigten Verfahren behandelt werden, wenn die Gesuchstellenden aus einem Safe Country stammen. Im Gegensatz dazu können wir in der Schweiz Asylgesuche aus allen Herkunftsländern in beschleunigten Verfahren behandeln. Die Auswirkungen einer Bezeichnung eines Landes als Safe Country sind in der Schweiz also aktuell gering. Wenn wir nun die Liste der sicheren Herkunftsländer nach Belieben erweitern, verletzen wir damit nicht nur das geltende Asylgesetz, sondern täuschen auch eine Wirkung vor, die eine solche Bezeichnung in der Realität nicht hat. 
+Was wir aber tun müssen, ist, unser Safe-Country-Konzept so anzupassen, dass es zu einem griffigen Instrument wird. Diese Arbeiten hat das EJPD bereits eingeleitet. Im Rahmen der Asylstrategie 27 werden Anpassungen und Alternativen geprüft. 
+Der Bundesrat beantragt Ihnen deshalb, die Motion Schwander abzulehnen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le 12 juin est entré en vigueur le pacte européen sur la migration. Ce pacte prévoit la création possible de "hubs" de retour à l'extérieur de l'Union européenne. C'est malheureusement un choix politique qui a été fait. Je conteste cette possibilité sur le principe, mais c'est la réalité qui a été voulue par la majorité des États au Conseil européen, à la Commission européenne et au Parlement européen. On va donc assister à la création de ces "hubs" et les premières propositions sont déjà tombée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le 12 juin est entré en vigueur le pacte européen sur la migration. Ce pacte prévoit la création possible de "hubs" de retour à l'extérieur de l'Union européenne. C'est malheureusement un choix politique qui a été fait. Je conteste cette possibilité sur le principe, mais c'est la réalité qui a été voulue par la majorité des États au Conseil européen, à la Commission européenne et au Parlement européen. On va donc assister à la création de ces "hubs" et les premières propositions sont déjà tombées de la part de pays européens pour les créer au Rwanda, en Ouganda ou au Sénégal, voire dans d'autres pays où la situation en matière de gestion de l'administration et de droits de l'homme est particulièrement difficile.
+Bien. On aurait pu être membre du pacte européen sur la migration, puisqu'il nous était proposé d'y adhérer. Ce Parlement n'a pas voulu de cette adhésion pour avoir une solution qui soit une solution nationale. consistant à adhérer de manière ponctuelle, là où il y a des nécessités, sur la base des choix que nous faisons. Donc, le fait que l'on ait aujourd'hui une réflexion sur la base du droit suisse est la conséquence logique du fait que la Suisse ne participe pas au pacte sur la migration qui comporte déjà un certain nombre de règles.
+Le fait de dire qu'il faut d'abord vérifier au niveau suisse si cela est possible, je pense que c'est fondamental. Cela correspond même à la volonté de ce Parlement, de garder notre souveraineté. On ne peut pas simplement déléguer cela à des États tiers. L'un dans l'autre, on verra malheureusement ces "hubs", mais, en l'état, je pense que la position expliquée par le Conseil fédéral est juste et devra naturellement être actualisée en fonction des développements en cours dans l'Union européenne.
+Je rappelle encore une chose : il y a d'autres instruments qui sont à disposition. Il y a notamment les renvois par avion, qui sont mutualisés entre les pays européens et qui permettent de faire des expulsions forcées, notamment de personnes qui peuvent avoir commis des actes criminels ou qui posent problème. Or, les "hubs" de retour qui sont prévus par l'Union européenne, et il faut s'en souvenir, concernent les personnes qui, en Suisse, ont un permis F, à savoir des personnes qui demandaient l'asile, qui ont été déboutées et qui ne peuvent pas revenir dans leur pays en raison de la situation dans ce pays - cela peut être à cause de la guerre, à cause de situations climatiques insupportables, à cause de la répression générale, etc. - même si les conditions personnelles sont remplies. C'est par exemple le cas pour le renvoi des femmes en Afghanistan. Ce sont des choses de ce genre-là. Mais ça ne concerne pas des personnes qui commettent des infractions. Ce sont aussi des familles. L'Union européenne a ouvert les "hubs" de retour également aux familles, c'est-à-dire même à des mineurs. Et qu'est-ce qui se passera lorsqu'ils seront dans ces hubs ? Ils n'y resteront pas seulement pendant 15 jours, pendant 12 mois ou 24 mois.
+Je termine donc avec cela : on pourrait renvoyer des familles dans ces centres de retour et ce sera une détention, une détention administrative, qui durera pendant des années, parce qu'il n'y a pas de limite prévue. Il est donc vrai que cela interpelle et qu'il est nécessaire de voir si cela est compatible ou pas avec le droit suisse, même si cela a été adopté par l'Union européenne, même si cela a été adopté par nos pays voisins. Je pense qu'il faut donc aller dans le sens que propose le Conseil fédéral qui est de rejeter la motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Würth Benedikt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorher bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorher bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staatsrechnung 2025 festgestellt, dass wir bei den erweiterten Verfahren mittlerweile bei 571 Tagen sind, 571 Tage. Das Ziel mit der Asylreform war ursprünglich 90 Tage; wir überschiessen also um den Faktor 6 und das mit einer ungebrochenen Dynamik. 
+Wenn man einen solchen Befund hat, dann müsste man eigentlich alle Ressourcen in dieses Thema stecken. Wir machen aber umgekehrt eine Strategie, indem wir alles möglichst öffnen, und nicht nur Kantone und Gemeinden einladen, sondern es können logischerweise auch NGO mitmachen. Man geht in die Papiere, die im Netz abrufbar sind und macht eine Grossgruppenveranstaltungen, anstatt dass man die Ressourcen hier, wo es wirklich dringlich und nötig ist, fokussiert. Das verstehe ich einfach nicht mehr. 
+Es ist nicht so, dass man von der Strategie- in die Umsetzungsphase gekommen ist. Umsetzen, was heisst umsetzen? Umsetzen können wir erst dann, wenn wir konkrete Vorlagen auf dem Tisch haben. Ich habe die Motionen, die wir überwiesen haben, nicht gezählt; besten Dank, Kollegin Friedli, offenbar sind es zwanzig. Das heisst doch konkret, dass der Bundesrat eine Vorlage unterbreiten muss, im Grunde genommen eine grössere Teilrevision des Asylgesetzes. Dann rede ich von Umsetzung, aber doch nicht, wenn irgendwie Konzeptpapiere hin- und hergeschoben werden. Dann beginnt die Umsetzung, bei der konkreten Imvollzugsetzung. 
+Darum erstaunt es mich, wenn die SPK sagt, wir seien in einer Umsetzungsphase - Mitnichten, mitnichten! Wenn Sie schauen, wie diese Übung aufgegleist wurde - ich bin etwas kritisch, weil ich die Unterlagen en détail angeschaut habe: Wenn man in Bern eine Strategie startet, wird zuerst einmal ein Büro beauftragt; in diesem Fall ist das Ecoplan; es gibt weitere bekannte. Ecoplan macht einen grossen Bericht. Dann gibt es eine politische Synthese, eine Asylkonferenz - das war in den Jahren 2024, 2025. Im Jahr 2026 wird in verschiedenen Workstreams und Workshops gearbeitet - schön und gut. Im Jahr 2027, so die Medienmitteilung der Asylkonferenz von Ende November 2025, gibt es dann vielleicht, vielleicht auch nicht, eine Vorlage. Bei der Frage der asylsuchenden Kriminaltouristen haben wir beispielsweise überwiesene Motionen verschiedener Herkunft. Auch Kollegin Moser hat einen konkreten Vorschlag überwiesen. Hier wird einerseits gesagt, wir prüfen, andererseits wird gesagt, dass man gesetzliche Grundlagen brauche. Das schafft einfach kein Vertrauen. Ich habe mir überlegt, wann wir in den letzten zwei, drei Jahren überhaupt eine Asylgesetzrevision auf dem Tisch gehabt haben. Wir haben sie im Zusammenhang mit der Umsetzung des EU-Migrationspaktes auf dem Tisch gehabt. Da hätte man eine konkrete Umsetzung machen können. Wenn die Kommissionssprecherin sagt, wir seien in der Umsetzung: Wieso hat man dort nicht konkrete Vorlagen gebracht, die die Vorstösse des Parlamentes umgesetzt hätten? Oder wir haben das EP 27 auf dem Tisch gehabt. Dort hat sogar das Parlament selbst, Kollege Zopfi hat es erwähnt, aus der Finanzkommission heraus das Asylgesetz angepasst, hat für Mehrfachgesuche und Wiedererwägungsgesuche eine Karenzfrist eingebaut. Das können wir als Parlament schon machen, aber ich hätte eigentlich erwartet, dass das der Bundesrat macht, wenn er schon einen konkret überwiesenen Vorstoss hat, der in Richtung Beschleunigung geht, und wenn er schon den Befund sieht, dass wir komplett aus dem Ruder laufen, was die Verfahrensdauern anbelangt.
+Ich meine, so kann man natürlich kein Vertrauen aufbauen, und so muss man sich auch nicht wundern, dass laufend Vorstösse überwiesen werden. Kollegin Z'graggen, die Berichterstatterin, sagte, dass es sein könnte, dass diese Motion die Asylstrategie übersteuere. Ich bin institutionell an einem völlig anderen Ort: Ich muss sagen, die Asylstrategie kann nicht das Parlament übersteuern, denn das Parlament erteilt die Aufträge. Man kann doch nicht sagen, okay, wir machen einen dreijährigen Prozess, die Asylstrategie 2027, und das, was im Parlament läuft, das nehmen wir einfach laufend entgegen und schauen dann, wie und in welchem Rahmen auch immer wir es abarbeiten. So geht das doch nicht. Klar, kann man auch so eine Legislatur absolvieren. So geht es aber eigentlich nicht, das ist nicht mein Verständnis vom Zusammenspiel zwischen Parlament und Regierung.
+Und dann lese ich in diesem Papier zur Asylstrategie 2027 - hören Sie gut zu -, dass jetzt tatsächlich überlegt wird, wie man eine neue Festlegung für den Zielwert im Bereich der erweiterten Verfahren machen könne. Wir haben also den Befund, dass wir die Zielsetzung aus der Asylstrategie 2016 überschiessen, und wir überlegen, wie wir die Verfahren beschleunigen können, aber wir überlegen auch noch, wie wir einen neuen Zielwert setzen können. Das ist falsch angedacht. So kann es meines Erachtens nicht gehen.
+Es wird offensichtlich, wenn man diese Papiere liest - und das bestreite ich ja gar nicht -, dass es Konzepte für ausreichende und rasch aktivierbare Unterbringungsstrukturen für ein abgestimmtes Krisenmanagement, für ein schwankungstaugliches Asylsystem braucht; so weit, so gut. Woran erinnern wir uns? Natürlich an die seinerzeitige Diskussion um die Asylcontainer. Ich kann auch zwischen den Zeilen lesen. Wieso sind die Kantone hier so motiviert? Wahrscheinlich, weil sie nochmals eine Erwartung in diese Richtung haben. Aber der Ständerat hat hier viermal Nein gesagt. Wir müssen beschleunigen und nicht Strukturen und Prozesse und Ressourcen aufbauen. Da liegt die Hauptpriorität, und darum ist diese Motion eben nach wie vor wichtig. Nicht als Zeichen, das möchte ich betonen, es ist nicht eine Zeichensetzung, die wir hier machen, sondern die Motion ist materiell richtig und wichtig, damit uns der Bundesrat nun konkret die Vorlagen bringt, die er eigentlich auch im Zuge der Umsetzung bereits überwiesener Vorstösse unterbreiten müsste.
+Das sind meine Überlegungen, wieso diese Motion nach wie vor richtig und wichtig ist, wieso sie nach wie vor aktuell ist und wieso ich mit dieser Motion auch klar die Erwartung verbinde, Herr Bundesrat, dass man zur Umsetzung der überwiesenen Vorstösse nun endlich eine grössere Teilrevision des Asylgesetzes bringt. Unser Parlament kann letztlich nur Recht setzen, wenn wir eine Vorlage auf dem Tisch haben - mit Motionen erteilen wir nur Aufträge, aber Rechtsetzung passiert dann, wenn wir eine Vorlage haben. Und hier haben wir keine Vorlage, das ist doch das Problem, ausser eben im Zusammenhang mit dem EP 27 und dem EU-Migrations- und Asylpakt.
+In diesem Sinne bin ich dezidiert der Auffassung, dass die Motion nach wie vor richtig und wichtig ist. Die Kantone, Gemeinden und der Bund können weiterhin gut zusammenarbeiten. Aber einfach eine Strategie vorzuschieben und gleichzeitig die Bearbeitung und Umsetzung von Vorstössen auf die lange Bank zu schieben, das möchte ich persönlich, das muss ich klar sagen, nicht mehr akzeptieren.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen haben Sie im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Was Sie aber nicht können, ist in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Von dem her finde ich die Frage, die aufgew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen haben Sie im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Was Sie aber nicht können, ist in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Von dem her finde ich die Frage, die aufgeworfen wird, im Sinne der Zuständigkeit, der Rechtssicherheit und der Weiterentwicklung in diesem Gebiet durchaus interessant. 
+Ich sehe aber auch Punkte, die sehr genau geprüft werden müssen. Einerseits, was würde das für die Verfahrensbelastung oder für die Belastung, die Pendenzen am Bundesverwaltungsgericht bedeuten? Wir haben uns schon bei zwei Traktanden darüber unterhalten. Was würde das staatsorganisatorisch bedeuten? Hätten die Kantone plötzlich eine Aufsicht über eine Bundesbehörde - dieses Problem spricht der Bundesrat an - und letztlich, welcher Qualitätsgewinn oder Erkenntnisgewinn wäre daraus zu erwarten? In diesem Sinn scheint es mir angezeigt, dass sich die Kommission damit befasst, auch prüft, ob es allenfalls Alternativen gäbe, um das, was der Motionär will, zu gewährleisten. Ich bin deshalb der Ansicht, dass die Kommission sich hier vertiefen soll, habe dies auch mit dem Motionär abgesprochen und gehe davon aus, dass er sich damit einverstanden erklären kann.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müller Damian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich danke dem Bundesrat für seine Antwort, auch wenn ich feststelle, dass er sich - wie allzu oft, wenn es um Rückführungen geht - auf das absolute Minimum beschränkt. Die Suche nach funktionierenden Lösungen scheint vom EJPD mittlerweile als unverhältnismässiger Aufwand angesehen zu werden. Der einfachste Weg besteht offenbar darin, die bisherige Praxis fortzusetzen und Asylsuchende in der Schweiz zu behalten, die eigentlich nicht in die Zuständigkeit unseres Landes fallen. Von innovativen Idee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich danke dem Bundesrat für seine Antwort, auch wenn ich feststelle, dass er sich - wie allzu oft, wenn es um Rückführungen geht - auf das absolute Minimum beschränkt. Die Suche nach funktionierenden Lösungen scheint vom EJPD mittlerweile als unverhältnismässiger Aufwand angesehen zu werden. Der einfachste Weg besteht offenbar darin, die bisherige Praxis fortzusetzen und Asylsuchende in der Schweiz zu behalten, die eigentlich nicht in die Zuständigkeit unseres Landes fallen. Von innovativen Ideen habe ich keine Spur gefunden.
+Herr Bundesrat, Sie liessen sich zum Amtsantritt prominent mit der Aussage zitieren, wer denke, linke Politik heisse Wegschauen von Problemen, irre sich. Ich muss Ihnen ganz offen sagen, dass ich diese Aussage mit Ihrer Stellungnahme zu diesem Vorstoss nicht in Einklang bringen kann.
+Die Umsetzung der Punkte 1 und 2 fordert vor allem guten Willen und eine gewisse Aufgeschlossenheit. Diese beiden Punkte beinhalten keinerlei Ergebnisverpflichtung. Sie zielen lediglich darauf ab, Verhandlungen mit Italien aufzunehmen. Ich bin nicht naiv und bin mir bewusst, dass diese Gespräche komplex werden und möglicherweise sogar scheitern können. Wenn wir es aber gar nicht erst versuchen, wird genau gar nichts passieren. Und das geht dann halt schon in Richtung Wegschauen von Problemen.
+Der Bundesrat erklärt lieber, warum Schritte scheitern könnten, anstatt sie zu unternehmen. Diese Haltung bedauere ich, zumal ich durchaus der Absicht bin, dass Italien ein Interesse an einer Zusammenarbeit mit der Schweiz hat, insbesondere, wenn diese eine finanzielle Unterstützung für seine Zentren in Albanien beinhaltet. Im Rahmen der Anwendung der Dublin-Verordnung kann Italien genau festlegen, wohin die Dublin-Fälle, für die es zuständig ist, zurückgeschickt werden sollen. Das kann Rom, Mailand oder ein anderer Ort sein. Grundsätzlich ist es also möglich, dass Italien die Schweiz bittet, bestimmte Fälle an Zentren in Albanien zurückzuschicken. Angesichts der engen Beziehung zwischen den Staaten könnte Italien sogar eine Anpassung des mit Albanien abgeschlossenen Abkommens in Betracht ziehen.
+Was Punkt 3 betrifft: Wenn ich die Antwort richtig interpretiere, schliesst der Bundesrat aufgrund einer Auslegeordnung im Rahmen des in der Antwort erwähnten Postulates Caroni aus, dass ein solches Modell mit einer Rückkehr das Schweizer System entlasten könnte.
+Jüngst wurde zwischen dem Rat der Europäischen Union und dem Europäischen Parlament eine Einigung über eine neue EU-Verordnung zur Weiterentwicklung der Rückführungsrichtlinie erzielt, die unter anderem die Schaffung von Rückführungszentren in Drittstaaten vorsieht. Herr Bundesrat, wie gedenken Sie, gestützt darauf die künftige Zusammenarbeit der Schweiz in diesem Bereich konkret auszugestalten? Und an welche Drittstaaten könnte sich die Schweiz bereits wenden?
+Es ist nun die Aufgabe des Parlaments, den Bundesrat dazu anzuhalten, Gespräche mit Italien aufzunehmen und die Möglichkeit einer Zusammenarbeit mit Rom konkret zu prüfen. Auch hier besteht keine Verpflichtung, ein bestimmtes Ergebnis zu erzielen, sondern lediglich die Verpflichtung, Gespräche mit Italien aufzunehmen, um dessen Interesse an einer Zusammenarbeit mit der Schweiz im Bereich der Rückführung auszuloten. Aus all diesen Gründen bitte ich Sie, diese Motion anzunehmen.
+Herr Bundesrat, ich gebe es offen zu, ich beneide Sie nicht. Die letzten Wochen und Monate haben deutlich gezeigt, welche Sorgen die Menschen in unserem Land haben. Die Bevölkerung spricht über Migration, über Asyl, über Sicherheit und über die Frage, ob unser Staat die Situation noch unter Kontrolle hat. Gerade deshalb erstaunt mich die Haltung Ihres Departements. Bei der Überarbeitung der Lex Koller geht alles sehr schnell. Dafür werden in kürzester Zeit Berichte erstellt, Varianten geprüft und Gesetzesänderungen vorbereitet. Wenn es aber um Rückführungen von Personen geht, die kein Bleiberecht in der Schweiz haben, höre ich immer wieder, weshalb etwas nicht möglich sein soll. Ich spreche hier nicht von Flüchtlingen.
+Was mich zunehmend stört: Wir sprechen ständig über Strategien, Konzepte und auch über Prüfaufträge. Die Bevölkerung erwartet etwas anderes. Sie erwartet Resultate, sie erwartet Taten, und sie erwartet Lösungen. Niemand verlangt Wunder, niemand verlangt, dass jede Verhandlung erfolgreich endet. Aber die Menschen dürfen erwarten, dass der Bundesrat aktiv Möglichkeiten auslotet, Partner sucht und neue Wege prüft, anstatt bereits zu Beginn zu erklären, weshalb etwas nicht funktionieren könnte. Genau das verlangt diese Motion, nicht mehr und nicht weniger. Sie verpflichtet den Bundesrat nicht zu einem bestimmten Ergebnis, sie verpflichtet ihn lediglich dazu, aktiv zu werden. Genau deshalb bitte ich Sie, die Motion zu unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gössi Petra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um es gleich vorwegzunehmen: Die Stellungnahme des Bundesrates hat mich enttäuscht, aber nicht einfach deshalb, weil er die Ablehnung meiner Motion beantragt hat; ich erkläre Ihnen das gerne. Bei einem Antrag auf Ablehnung hätte ich erwartet, dass der Bundesrat das mit dem Hinweis tut, das SEM sei solche Projekte bereits am Aufgleisen und die Motion genau deshalb gar nicht mehr notwendig. Die Stellungnahme sagt aber etwas ganz anderes aus. Sie lässt nämlich offen, ob der Bundesrat die Einrichtun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um es gleich vorwegzunehmen: Die Stellungnahme des Bundesrates hat mich enttäuscht, aber nicht einfach deshalb, weil er die Ablehnung meiner Motion beantragt hat; ich erkläre Ihnen das gerne. Bei einem Antrag auf Ablehnung hätte ich erwartet, dass der Bundesrat das mit dem Hinweis tut, das SEM sei solche Projekte bereits am Aufgleisen und die Motion genau deshalb gar nicht mehr notwendig. Die Stellungnahme sagt aber etwas ganz anderes aus. Sie lässt nämlich offen, ob der Bundesrat die Einrichtung von Rückkehrzentren tatsächlich unterstützen wird, wie dies verschiedene Medien Anfang Monat berichtet haben. 
+Beim Lesen der Stellungnahme des Bundesrates habe ich den Eindruck erhalten, dass der Bundesrat solche Zentren nur unterstützen will, solange die EU die Richtung vorgibt. Natürlich sind solche Projekte riskant, und natürlich können sie scheitern, und natürlich wird uns das Geld kosten. Die Stellungnahme des Bundesrates erweckt aber den Eindruck, als wäre blosses Abwarten ausreichend, und da bin ich nun ganz klar anderer Meinung. Wir sind ein eigenständiges Land mit einer eigenständigen Politik, und deshalb müssen wir auch in der Asylpolitik eigene Pflöcke einschlagen. 
+Unser Asylsystem ist am Anschlag. Das hören wir regelmässig aus den Kantonen, aus den Gemeinden. Das haben wir nun auch heute Vormittag wieder diskutiert. Der Druck ist massiv, das haben uns auch die Debatten der vergangenen Monate im Zusammenhang mit der Diskussion über die Volksinitiative "Keine 10-Millionen-Schweiz!" aufgezeigt. Wir haben Pendenzen, überlastete Strukturen, Wegweisungen, die nicht vollzogen werden. Das alles ist heute leider Alltag. Wenn Sie nun ernsthaft sagen, dass wir in der Asylpolitik keine zusätzlichen Instrumente brauchen, dann blenden Sie meines Erachtens diese Realität schlicht und einfach aus. "Return hubs" können ein solches Instrument sein. Denn mit der Motion verlange ich ja nur, dass endlich Schluss ist mit dem Zuwarten. Wir müssen zusätzliche Instrumente schaffen, damit ausreisepflichtige Personen die Schweiz auch tatsächlich verlassen und nicht jahrelang im Land bleiben. 
+Die EU hat mit der neuen Rückführungsverordnung eine Kursänderung vorgenommen. Die Verordnung bietet die Rechtsgrundlage, um Ausreisepflichtige in Rückführungszentren in Drittstaaten ausserhalb der EU zu bringen. Und was macht der Bundesrat? Er bringt im Wesentlichen drei Argumente vor, weshalb die Schweiz vorerst im Beobachterstatus verbleiben soll. Im Klartext heisst das: Europa beginnt zu handeln, und wir schauen zu. Damit machen wir uns aber zu einer attraktiven Ausweichdestination für Asylsuchende, weil wir weniger strenge Regeln haben. 
+Nun aber zu den drei Argumenten, die der Bundesrat gegen die Motion vorbringt. 
+Das erste Argument sind Misserfolge in der Vergangenheit. Ja, natürlich gab es Projekte, die nicht funktioniert haben. Das bestreite ich nicht. Aber die richtige Reaktion darauf ist doch nicht zu sagen: dann machen wir gar nichts und beobachten. Die Reaktion muss vielmehr sein: dann machen wir es besser. Sich auf alte Beispiele zu berufen, um neue Möglichkeiten gar nicht erst anzugehen, ist defensiv. Das genügt dem Anspruch an eine vorausschauende Politik nicht.
+Zum zweiten Argument, den Risiken und Abhängigkeiten von Rechtsstaaten: Abhängigkeiten und Risiken kennen wir aus jedem Migrationsabkommen und aus jeder Rückübernahmevereinbarung. Gerade deshalb ist es die Aufgabe des Bundesrates, die Rahmenbedingungen so zu gestalten, dass diese Risiken begrenzt sind, mit klaren Verträgen, mit der Verknüpfung von Bedingungen und Leistungen und zum Beispiel auch mit Ausstiegsklauseln.
+Dann komme ich noch zum dritten Argument, dass die Externalisierung das nationale System nicht ersetzt. Natürlich ist es richtig, dass Rückkehrzentren unser nationales System nicht ersetzen, sondern nur ergänzen. Daraus lässt sich aber nicht ableiten, dass auf dieses Instrument zu verzichten ist. Rückkehrzentren sind ein zusätzliches Werkzeug für besonders schwierige Fälle, in denen der Vollzug im Herkunftsstaat blockiert ist. Wer dieses Werkzeug nicht einmal vorbereiten will, nimmt Vollzugsdefizite in Kauf und schwächt damit die Glaubwürdigkeit unseres Asylsystems.
+Für mich stehen bei der vorliegenden Motion drei Punkte im Zentrum: erstens Ordnung, zweitens Glaubwürdigkeit und drittens Sicherheit.
+Der erste Punkt, die Ordnung, ist zentral, weil ein Rechtsstaat seine Entscheide - vorliegend die rechtskräftigen Wegweisungen - durchsetzen können muss. Es braucht, zweitens, Glaubwürdigkeit, weil die Akzeptanz des Asylsystems davon abhängt, dass die Hilfe bei den wirklich Schutzbedürftigen ankommt. Wenn Wegweisungen faktisch nicht vollzogen werden können, kippt die Stimmung letztlich zulasten derjenigen, die unseren Schutz am dringendsten brauchen.
+Drittens geht es um die Sicherheit. Innere Sicherheit setzt klare Verhältnisse voraus. Je länger abgewiesene Personen ohne Perspektive in unserem Land verbleiben, desto grösser werden Spannungen, Unsicherheit und mögliche Risiken.
+Ich erinnere Sie noch an einen letzten Punkt. Diese Motion ist kein Blankocheck. Jede konkrete Umsetzung, jede Gesetzesänderung kommt wieder in dieses Parlament, mit allen Kontroll- und Referendumsrechten. Ich bitte Sie deshalb um Unterstützung dieser Motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundesrats-Bashing auszuhalten ist Teil meines Jobbeschriebs. Damit habe ich kein Problem, ebenso wenig mit Motionen, die ein Zeichen setzen wollen; solche Motionen nehme ich gerne entgegen. Ich erwarte aber, dass man die Leistungen, die die Administration erbringt, anerkennt. Wenn Sie diese Motion annehmen, machen Sie eigentlich nur Folgendes: Sie anerkennen die Leistungen, die vollbracht werden, ohne irgendeinen konstruktiven Beitrag zu leisten, nicht. Ich möchte Ihnen das anhand der drei Punk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bundesrats-Bashing auszuhalten ist Teil meines Jobbeschriebs. Damit habe ich kein Problem, ebenso wenig mit Motionen, die ein Zeichen setzen wollen; solche Motionen nehme ich gerne entgegen. Ich erwarte aber, dass man die Leistungen, die die Administration erbringt, anerkennt. Wenn Sie diese Motion annehmen, machen Sie eigentlich nur Folgendes: Sie anerkennen die Leistungen, die vollbracht werden, ohne irgendeinen konstruktiven Beitrag zu leisten, nicht. Ich möchte Ihnen das anhand der drei Punkte Ihrer Motion kurz erklären:
+1. Ich gehe mit Ihnen einig, Herr Müller, die Wiederaufnahme der Dublin-Überstellung nach Italien ist eine Priorität. Das haben Bundesrat und die Administration mit grossem Engagement verfolgt, es ist mittlerweile in Umsetzung. Seit letztem Freitag, also dem 12. Juni, ist der EU-Migrations- und Asylpakt in Kraft. Diese Reform war eine Voraussetzung für Italien, damit es Dublin-Überstellungen aus ganz Europa wieder akzeptiert, sie ist jetzt in Kraft. Die Schweiz gehört laut der italienischen Seite zu den prioritären Ländern, mit denen die Überstellungen wieder aufgenommen werden sollen. Das SEM hat die italienischen Behörden darüber informiert, dass es die Überstellungen im Rahmen der Dublin-Verordnung ab dem 12. Juni schrittweise wieder aufnehmen werde.
+2. Zur Rückführung von Dublin-Fällen in die Zentren in Albanien: Die Dublin-Regeln sehen keine Wegweisung von Dublin-Fällen in Drittstaaten vor, Herr Müller. Wir haben also keine Rechtsgrundlage, die uns ein solches Vorgehen überhaupt erlauben würde, und auf EU-Ebene ist dies auch nicht möglich. Das können wir auch nicht im Schweizer Recht oder mit einem Abkommen mit Italien ändern. Übrigens schickt nicht einmal Italien selbst Dublin-Fälle nach Albanien.
+3. Zur Mitnutzung der Zentren in Albanien durch die Schweiz als Rückkehrzentren: Ein solches Vorhaben bedingt, dass zuerst auf Ebene EU die Rechtsgrundlage für solche Rückkehrzentren verabschiedet wird. Das wird vermutlich bis im Sommer der Fall sein. Anschliessend wird die Schweiz diesen Schengen-Rechtsakt in ihr Recht übernehmen. Daneben müsste eine trilaterale Vereinbarung mit Italien und Albanien abgeschlossen werden. Ob dazu seitens der beiden Partner ein politischer Wille besteht, ist mehr als fraglich, es ist illusorisch. Italien hat selbst ein Interesse, die Plätze vollumfänglich zu nutzen, und Albanien hat seinerzeit mehrmals betont, dass es dieses Abkommen geschlossen habe, um einem befreundeten Land wie Italien zu helfen. Es hat aber auch klar gesagt, dass es dieses Abkommen nicht auf andere Länder ausweiten wolle; auch mir gegenüber hat Albanien das zum Ausdruck gebracht. Zudem hat der albanische Aussenminister kürzlich in Frage gestellt, ob das Abkommen mit Italien überhaupt über 2029 hinaus verlängert werden wird, weil es in Albanien nicht beliebt ist. 
+An diesem Beispiel sehen wir gut, in welche Abhängigkeiten man sich bei solchen Modellen begeben kann. Das Risiko hat der Bundesrat auch in einem Bericht in Erfüllung des Postulates Caroni festgestellt. Er kommt daher zum Schluss, dass sich die Zentren in Albanien weder für die Rückführung von Dublin-Fällen noch für die Mitnutzung als Rückführungszentren eignen. Der Bundesrat beantragt Ihnen deshalb, die Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillard Pierre-Yves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a compté notre collègue Friedli - j'avais aussi fait ce décompte pendant une autre session -, on doit probablement être à plus d'une vingtaine de motions et d'interventions parlementaires concernant l'asile en moins d'un an. On vient même maintenant d'adopter une motion pour dire au Conseil fédéral dans quel ordre il doit traiter les motions ; c'est ce qu'on vient de faire avec la motion de M. Würth. Chères et chers collègues, ce que l'on est en train d'essayer de faire, c'est simplement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comme l'a compté notre collègue Friedli - j'avais aussi fait ce décompte pendant une autre session -, on doit probablement être à plus d'une vingtaine de motions et d'interventions parlementaires concernant l'asile en moins d'un an. On vient même maintenant d'adopter une motion pour dire au Conseil fédéral dans quel ordre il doit traiter les motions ; c'est ce qu'on vient de faire avec la motion de M. Würth. Chères et chers collègues, ce que l'on est en train d'essayer de faire, c'est simplement de la cogestion. On voit maintenant des motions porter sur les contacts que doit prendre le Conseil fédéral avec quel pays. On l'encourage à négocier, alors qu'en principe, une motion vise à changer une base légale. On commence à vouloir faire du pilotage automatique du Conseil fédéral pour savoir avec qui il doit discuter et comment il doit négocier. S'il le fait, mais qu'il n'a pas de résultat, on vient lui faire des commentaires un peu faciles, pour dire qu'il y met de la mauvaise volonté.
+Je pense que notre Parlement, sur ce thème, perd un peu ses repères. Il perd un peu même parfois la décence politique de base, qui consiste à respecter la séparation des pouvoirs et à respecter le travail des autres. Si c'était tellement facile, il y aurait une concurrence débordante pour entrer au Conseil fédéral. On a eu, lors d'une vacance récente, une liste de renoncements à la candidature qui était quand même assez spectaculaire. Manifestement, ce rôle n'attire pas exagérément, y compris les membres de ce Parlement. Si c'était si facile, il y aurait une concurrence féroce pour prendre ce département lors de la répartition des départements. Or, comme le on sait, les groupes qui déposent des motions à peu près lors de toutes les sessions ne sont pas pressés de prendre la responsabilité exécutive de ce dossier. Je trouve donc qu'il y a beaucoup d'hypocrisie dans ce dossier, et parfois même un petit peu de facilité à critiquer toujours celles et ceux qui essayent de faire des choses.
+La réalité pragmatique, c'est que le nombre de demandes d'asile baisse, c'est que le nombre de renvois augmente, c'est que le nombre de cas pendants se réduit, comme nous l'explique à longueur de session le conseiller fédéral. Certains peuvent se désoler de cela. Je trouve que c'est plutôt le résultat d'un travail qui est fait par l'exécutif. On est un certain nombre dans ce conseil à avoir été membres d'un exécutif. On sait que la critique est facile, mais que l'art est difficile.
+En raison de ce bon vieux principe, je vous invite à rejeter cette motion, qui me paraît enfoncer des portes ouvertes. À part cela, les réponses du Conseil fédéral sont éloquentes : si l'Italie ne reprend pas ses ressortissants, elle ne va pas davantage les reprendre si on les met en Albanie. Cela me semble être assez clairement expliqué dans l'avis du Conseil fédéral, donc je ne vois pas ce que cette proposition amènerait concrètement. Je vous remercie donc de rejeter cette proposition. Je ne répéterai pas la même chose tout à l'heure sur les autres motions, mais mon avis est le même.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Pierre-André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avant de passer aux élections prévues à l'ordre du jour, nous allons prendre congé du juge Jean-Luc Baechler, ancien président du Tribunal administratif fédéral, et du juge fédéral Christian Herrmann. 
+Diplômé de l'Université de Fribourg, Jean-Luc Baechler a obtenu son brevet d'avocat alors qu'il était assistant bilingue à la faculté de droit et à la chaire de droit romain de cette même université. De 1990 à 1991, il a dirigé la section Afrique-Roumanie de l'Office fédéral des réfugiés à Berne. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avant de passer aux élections prévues à l'ordre du jour, nous allons prendre congé du juge Jean-Luc Baechler, ancien président du Tribunal administratif fédéral, et du juge fédéral Christian Herrmann. 
+Diplômé de l'Université de Fribourg, Jean-Luc Baechler a obtenu son brevet d'avocat alors qu'il était assistant bilingue à la faculté de droit et à la chaire de droit romain de cette même université. De 1990 à 1991, il a dirigé la section Afrique-Roumanie de l'Office fédéral des réfugiés à Berne. S'en sont suivies de nombreuses années d'activité à Estavayer-le-lac, en qualité de préfet du district de la Broye, juge administratif puis président du Tribunal d'arrondissement à partir de 2002, et président de la Chambre des prud'hommes et de la Chambre des tutelles de la Broye. Parallèlement à son activité judiciaire, M. Baechler a oeuvré au sein de la Commission des sanctions de la Fédération suisse des sports équestres de 1992 à 1999 et rejoint en 1998 l'état-major de l'armée comme spécialiste en droit des gens, avec le grade de lieutenant-colonel.
+C'est en juin 2006 que Jean-Luc Baechler a été élu par notre assemblée pour siéger auprès du futur Tribunal administratif fédéral, qui est entré en fonction en 2007. S'il est resté fidèle à la Cour II durant toute sa carrière, le juge Baechler s'est également engagé pour le tribunal dans son ensemble, puisqu'il a exercé les fonctions de vice-président de 2013 à 2014, et de président de 2015 à 2018. Son autorité naturelle et sa parfaite connaissance de l'institution lui ont permis d'assumer parfaitement ce mandat.
+Au sein de la Cour II, Jean-Luc Baechler était le seul juge francophone pour les affaires relevant de la surveillance des marchés financiers. Autant dire qu'il y a acquis la maîtrise de ces dossiers volumineux et particulièrement exigeants. Cependant, son domaine de compétence judiciaire a toujours été diversifié, tout comme ses activités accessoires et centres d'intérêt, car le juge Baechler est aussi un homme de culture qui aime à s'investir pour les autres. J'en veux pour preuve son engagement de 33 années à la tête du conseil de la fondation pour personnes en situation de handicap "La Rosière" à Estavayer-le-Lac.
+C'est donc avec tristesse et regret que le Tribunal administratif fédéral voit aujourd'hui partir en la personne de Jean-Luc Baechler un ancien président dévoué, un juge expérimenté rompu aux dossiers complexes et un collègue aussi bienveillant qu'attentif aux autres.
+Nous prenons également congé ce matin du juge fédéral Christian Herrmann, diplômé de l'Université de Neuchâtel et titulaire du brevet d'avocat du canton de Berne. Après un début de carrière au sein du commandement de la police municipale de Bienne, M. Herrmann a exercé les fonctions de juge d'instruction puis de juge d'appel à la Cour suprême du canton de Berne. C'est en septembre 2009 qu'il a été élu au Tribunal fédéral, où il a rejoint la deuxième Cour de droit civil, dont il a assumé la présidence de 2019 à 2024.
+Tout au long de son parcours, le juge Herrmann s'est distingué par l'étendue de son expérience et la sûreté de son jugement ; il n'a eu de cesse de défendre une conception élevée de la justice, fondée sur la responsabilité, la discipline et le respect des institutions.
+Dans l'exercice de ses fonctions présidentielles, M. Herrmann a fait preuve d'un sens éminent de l'organisation, garantissant une conduite méthodique et ordonnée des travaux de la deuxième Cour de droit civil. Par une gestion maîtrisée des affaires, une répartition équilibrée des tâches et une anticipation constante des besoins, il a assuré un fonctionnement efficace et harmonieux de la cour. C'est avec cette maîtrise unanimement reconnue qu'il a assumé la présidence de la Conférence des présidents en 2023 et 2024.
+Animé par un souci constant d'équilibre et de mesure, le juge Herrmann a su privilégier une approche marquée par la justesse de l'appréciation, tout en demeurant attentif aux intérêts en présence et aux personnes concernées. Cette attitude, conjuguée au traitement efficace des dossiers, témoigne d'une pratique du droit à la fois rigoureuse et profondément humaine.
+Enfin, l'engagement de M. Herrmann s'est accompagné d'un sens élevé du collectif et d'une attention constante portée à ses collègues et collaborateurs. Par son autorité sereine, sa disponibilité et sa loyauté, il a contribué à instaurer un climat de confiance et de respect au sein de la cour, tout en cultivant la convivialité.
+L'empreinte laissée par l'action des juges Baechler et Herrmann appelle, au moment de leur départ à la retraite, l'expression d'une reconnaissance institutionnelle appuyée. Aussi, au nom des deux Chambres réunies ce matin, je tiens à vous adresser, Messieurs les juges, nos sincères remerciements pour votre engagement et votre précieuse contribution à la jurisprudence de notre pays. Nous vous souhaitons de profiter longuement et en pleine santé d'une retraite amplement méritée ! (Standing ovation)
+[VS]
+[VS]
+Wahl von drei Mitgliedern (anstelle von Herrn Jean-Luc Baechler, Herrn Maurizio Greppi und Herrn Markus König)[GZ]
+Election de trois membres (en remplacement de MM. Jean-Luc Baechler, Maurizio Greppi et Markus König)[GZ]
+[VS][GZ]
+Le président (Page Pierre-André, président): En raison du départ à la retraite des juges Jean-Luc Baechler, Maurizio Greppi et Markus König, trois postes sont à pourvoir au Tribunal administratif fédéral. Avec le soutien de tous les groupes parlementaires, la Commission judiciaire vous propose d'y élire M. Jonas Attenhofer, Mme Eva Hostettler et M. Julien Theubet. Vous avez reçu un rapport de la commission.
+[VS]
+Ergebnis der Wahl - Résultat du scrutin[GZ]
+Ausgeteilte Wahlzettel - Bulletins délivrés ... 224[GZ]
+eingelangt - rentrés ... 224[GZ]
+leer - blancs ... 2[GZ]
+ungültig - nuls ... 0[GZ]
+gültig - valables ... 222[GZ]
+absolutes Mehr - Majorité absolue ... 112[GZ]
+[VS][GZ]
+Es werden gewählt - Sont élus[GZ]
+Attenhofer Jonas ... mit 191 Stimmen[GZ]
+Hostettler Eva ... mit 198 Stimmen[GZ]
+Theubet Julien ... mit 209 Stimmen[GZ]
+[VS]
+Ferner haben Stimmen erhalten-Ont en outre obtenu des voix[GZ]
+Verschiedene - Divers ... 3
+[VS]
+Le président (Page Pierre-André, président): J'adresse toutes mes félicitations à M. Attenhofer, Mme Hostettler et M. Theubet pour leur élection et leur souhaite plein succès dans l'exercice de leur nouvelle fonction. (Standing ovation)
 </t>
   </si>
 </sst>
@@ -1154,8 +1634,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I50" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I75" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I75"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2881,6 +3361,719 @@
         <v>222</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>223</v>
+      </c>
+      <c r="B51" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" t="s">
+        <v>74</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>225</v>
+      </c>
+      <c r="I51" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>229</v>
+      </c>
+      <c r="I52" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53"/>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>232</v>
+      </c>
+      <c r="I53" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>234</v>
+      </c>
+      <c r="B54" t="s">
+        <v>224</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>235</v>
+      </c>
+      <c r="I54" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>238</v>
+      </c>
+      <c r="E55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" t="s">
+        <v>239</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>240</v>
+      </c>
+      <c r="I55" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>242</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
+        <v>140</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>243</v>
+      </c>
+      <c r="I56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>65</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>247</v>
+      </c>
+      <c r="I57" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>249</v>
+      </c>
+      <c r="B58" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58" t="s">
+        <v>251</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>252</v>
+      </c>
+      <c r="I58" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>255</v>
+      </c>
+      <c r="E59" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" t="s">
+        <v>209</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>256</v>
+      </c>
+      <c r="I59" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>258</v>
+      </c>
+      <c r="B60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>259</v>
+      </c>
+      <c r="E60" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>260</v>
+      </c>
+      <c r="I60" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>263</v>
+      </c>
+      <c r="I61" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>265</v>
+      </c>
+      <c r="B62" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>266</v>
+      </c>
+      <c r="I62" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>269</v>
+      </c>
+      <c r="E63" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" t="s">
+        <v>177</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>270</v>
+      </c>
+      <c r="I63" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>272</v>
+      </c>
+      <c r="B64" t="s">
+        <v>224</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>255</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>273</v>
+      </c>
+      <c r="I64" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>275</v>
+      </c>
+      <c r="B65" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>246</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>276</v>
+      </c>
+      <c r="I65" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>165</v>
+      </c>
+      <c r="E66"/>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>279</v>
+      </c>
+      <c r="I66" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>281</v>
+      </c>
+      <c r="B67" t="s">
+        <v>224</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67"/>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>282</v>
+      </c>
+      <c r="I67" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>284</v>
+      </c>
+      <c r="B68" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>246</v>
+      </c>
+      <c r="E68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>285</v>
+      </c>
+      <c r="I68" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>287</v>
+      </c>
+      <c r="B69" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>288</v>
+      </c>
+      <c r="E69" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" t="s">
+        <v>44</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>289</v>
+      </c>
+      <c r="I69" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>291</v>
+      </c>
+      <c r="B70" t="s">
+        <v>224</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>255</v>
+      </c>
+      <c r="E70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" t="s">
+        <v>209</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>292</v>
+      </c>
+      <c r="I70" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>295</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>296</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>297</v>
+      </c>
+      <c r="I71" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>300</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>239</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>301</v>
+      </c>
+      <c r="I72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>303</v>
+      </c>
+      <c r="B73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73"/>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>304</v>
+      </c>
+      <c r="I73" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>306</v>
+      </c>
+      <c r="B74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>307</v>
+      </c>
+      <c r="E74" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" t="s">
+        <v>55</v>
+      </c>
+      <c r="G74" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" t="s">
+        <v>308</v>
+      </c>
+      <c r="I74" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>310</v>
+      </c>
+      <c r="B75" t="s">
+        <v>224</v>
+      </c>
+      <c r="C75" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" t="s">
+        <v>311</v>
+      </c>
+      <c r="E75" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" t="s">
+        <v>312</v>
+      </c>
+      <c r="I75" t="s">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -355,14 +355,14 @@
   </si>
   <si>
     <t xml:space="preserve">Avec son rapport de gestion 2025, le Conseil fédéral analyse dans quelle mesure les objectifs fixés pour l'année en question ont été atteints. Il fournit de plus des explications concernant les écarts par rapport aux objectifs et présente les principaux objets non planifiés. En 2025, les droits de douane introduits en août sur les exportations suisses vers les États-Unis ont fortement mobilisé le Conseil fédéral. Par ailleurs, les questions de compétitivité de l'économie suisse, les oeuvres sociales et les sujets de sécurité ont figuré au premier plan. Comme chaque année, le rapport de gestion offre une très bonne opportunité de dialogue entre le Parlement et le Conseil fédéral. J'aimerais remercier les Commissions de gestion et les rapporteurs qui se sont exprimés sur ce rapport.
-Je vais maintenant rappeler brièvement le cadre de la politique du Conseil fédéral, à savoir les quatre lignes directrices de la législature 2023 à 2027. Je vous exposerai ensuite les points essentiels du travail accompli par le gouvernement l'année passée, soit la deuxième année de la législature. Les lignes directrices sont les suivantes : 1. "la Suisse assure durablement sa prospérité et saisit les chances qu'offre le numérique" ; 2. "elle encourage la cohésion nationale et intergénérationnelle" ; 3. "elle assure la sécurité, oeuvre en faveur de la paix et agit de manière cohérente et fiable sur le plan international" ; 4. "elle protège le climat et prend soin des ressources naturelles."
+Je vais maintenant rappeler brièvement le cadre de la politique du Conseil fédéral, à savoir les quatre lignes directrices de la législature 2023 à 2027. Je vous exposerai ensuite les points essentiels du travail accompli par le gouvernement l'année passée, soit la deuxième année de la législature. Les lignes directrices sont les suivantes[NB]: 1. "la Suisse assure durablement sa prospérité et saisit les chances qu'offre le numérique"[NB]; 2. "elle encourage la cohésion nationale et intergénérationnelle"[NB]; 3. "elle assure la sécurité, oeuvre en faveur de la paix et agit de manière cohérente et fiable sur le plan international"[NB]; 4. "elle protège le climat et prend soin des ressources naturelles."
 Ces lignes directrices sont divisées en 25 objectifs et regroupent un total de 148 mesures pour l'année 2025. Le Conseil fédéral a entièrement mis en oeuvre 88 de ces objets, et 9 ont été partiellement réalisés.
-J'aborde maintenant les points forts de l'année dernière et, pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices. La première ligne directrice concerne la prospérité et le numérique. En matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur 2 axes principaux : l'amélioration des conditions-cadres de l'ensemble des entreprises et la réduction de la charge réglementaire.
+J'aborde maintenant les points forts de l'année dernière et, pour ce faire, je vais me concentrer sur certaines priorités des lignes directrices. La première ligne directrice concerne la prospérité et le numérique. En matière d'économie, le Conseil fédéral a adopté un paquet de mesures pour la compétitivité de l'économie suisse. Ces mesures reposent sur 2 axes principaux[NB]: l'amélioration des conditions-cadres de l'ensemble des entreprises et la réduction de la charge réglementaire.
 En ce qui concerne les finances, l'année 2025 a été notamment marquée par l'adoption du message concernant le programme d'allègement budgétaire 2027. Ce programme est essentiel pour rétablir l'équilibre entre les recettes et les dépenses de la Confédération dans les années à venir.
 S'agissant de la place financière suisse, le Conseil fédéral a défini les grandes lignes des révisions de lois et autres ordonnances dans le secteur bancaire.
-En matière d'infrastructures et de transports, le Conseil fédéral a pris connaissance du rapport d'expertise "DETEC : Transports 2045" de l'École polytechnique fédérale de Zurich sur l'aménagement des infrastructures de transport. Cette analyse indépendante présente les projets à réaliser en priorité du point de vue technique d'ici 2045.
+En matière d'infrastructures et de transports, le Conseil fédéral a pris connaissance du rapport d'expertise "DETEC[NB]: Transports 2045" de l'École polytechnique fédérale de Zurich sur l'aménagement des infrastructures de transport. Cette analyse indépendante présente les projets à réaliser en priorité du point de vue technique d'ici 2045.
 Dans le domaine du numérique, en 2025, le Conseil fédéral a approuvé le message concernant la nouvelle loi fédérale sur le dossier électronique de santé. Ce dossier est automatiquement mis à la disposition de toute la population. Il renforce le système de santé en réunissant en un seul endroit toutes les informations de santé pertinentes de son titulaire.
-Consacrons-nous maintenant à la deuxième ligne directrice : la cohésion nationale et intergénérationnelle. Pour ce qui est des affaires sociales, le Conseil fédéral a décidé des lignes directrices de la prochaine réforme de l'AVS. La réforme AVS 2030 vise à stabiliser et moderniser l'AVS. Elle prévoit des mesures visant à rendre le système plus équitable et à prolonger la vie active.
+Consacrons-nous maintenant à la deuxième ligne directrice[NB]: la cohésion nationale et intergénérationnelle. Pour ce qui est des affaires sociales, le Conseil fédéral a décidé des lignes directrices de la prochaine réforme de l'AVS. La réforme AVS 2030 vise à stabiliser et moderniser l'AVS. Elle prévoit des mesures visant à rendre le système plus équitable et à prolonger la vie active.
 En matière de santé, en 2025, le Conseil fédéral a approuvé le message concernant la révision partielle de la loi sur les épidémies. Le but est d'améliorer la gestion des crises de santé publique et de mieux protéger la population contre de futures pandémies.
 Concernant le système de santé, le Conseil fédéral a approuvé Tardoc, le nouveau système tarifaire global pour les prestations médicales ambulatoires. Celui-ci tient mieux compte des besoins de la médecine de famille, simplifie la facturation et limite les incitations à accroître les quantités de prestations facturées.
 Je passe maintenant à la troisième ligne directrice, relative à la sécurité et à l'action sur le plan international. Sur les plans de la politique extérieure et de la coopération internationale, le Conseil fédéral a défini les priorités thématiques pour la présidence suisse de l'OSCE en 2026. Ces priorités incluent, entre autres, le renforcement du dialogue inclusif entre les 57 États participants.
@@ -382,17 +382,17 @@
     <t xml:space="preserve">de Montmollin Simone</t>
   </si>
   <si>
-    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités né</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire !", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités nécessaires à cet effet. Selon les initiants, cet objectif implique notamment de pouvoir recourir à toutes les technologies de production disponibles, y compris le nucléaire. Ils soulèvent ainsi à la fois la question de la sécurité d'approvisionnement et remettent en question la répartition des compétences entre Confédération, cantons et acteurs du secteur électrique. L'objectif du contre-projet est de rétablir l'ouverture technologique en supprimant l'interdiction légale du nucléaire tout en refusant la modification constitutionnelle proposée dans l'initiative.
+    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire[NB]!", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors de sa séance des 20 et 21 avril dernier, la commission a examiné l'initiative populaire "De l'électricité pour tous en tout temps (Stop au blackout)", son contre-projet indirect ainsi que deux pétitions, 26.2007, "Non au retour du nucléaire[NB]!", et 26.2008, "Non à de nouvelles centrales nucléaires". L'initiative populaire vise à inscrire dans la Constitution que l'approvisionnement électrique doit être garanti en tout temps et à confier à la Confédération la définition des responsabilités nécessaires à cet effet. Selon les initiants, cet objectif implique notamment de pouvoir recourir à toutes les technologies de production disponibles, y compris le nucléaire. Ils soulèvent ainsi à la fois la question de la sécurité d'approvisionnement et remettent en question la répartition des compétences entre Confédération, cantons et acteurs du secteur électrique. L'objectif du contre-projet est de rétablir l'ouverture technologique en supprimant l'interdiction légale du nucléaire tout en refusant la modification constitutionnelle proposée dans l'initiative.
 Dans le cadre de ses travaux préparatoires, la commission a procédé à de nombreuses auditions et notamment entendu des représentants de l'Inspection fédérale de la sécurité nucléaire, de l'Association des entreprises électriques suisses, de Swissgrid, de la Conférence des directeurs cantonaux de l'énergie ainsi que de l'industrie électrique, du monde scientifique et d'organisations concernées.
 En outre, lors de sa séance du 30 mars dernier, elle a chargé l'administration d'établir huit rapports complémentaires, notamment sur la rentabilité des projets hydroélectriques, sur les conséquences militaires et sécuritaires liées aux installations nucléaires, sur les questions de responsabilité civile et de couverture des dommages, sur les chaînes d'approvisionnement en combustible nucléaire, sur les réacteurs de quatrième génération, sur les besoins éventuels en centrales à gaz ainsi que sur le développement des énergies renouvelables.
 Les auditions ont montré un consensus sur la nécessité de poursuivre le développement des énergies renouvelables, de renforcer les réseaux électriques et de garantir la sécurité d'approvisionnement à long terme. Les besoins futurs en électricité seront vraisemblablement plus élevés que ceux évalués en 2017 lors de l'adoption de la stratégie énergétique 2050, notamment en raison de l'électrification croissante des usages, des centres de données et du développement de l'intelligence artificielle. Une réévaluation de ces besoins est en cours. La commission a d'ailleurs déposé les deux postulats 26.3019 et 26.3020 pour lesquels des réponses sont attendues d'ici fin 2027 dans le cadre des nouvelles perspectives énergétiques 2060 en cours d'élaboration, qui devront permettre des analyses actualisées de l'approvisionnement futur en électricité. À cet égard, les auditions ont fait apparaître des appréciations divergentes quant au rôle du nucléaire.
 La Conférence des directeurs cantonaux de l'énergie a indiqué que si les cantons rejetaient très largement l'initiative populaire, les positions sont plus nuancées sur le contre-projet indirect. Dix cantons demandent des analyses complémentaires, sept le soutiennent sous réserve du maintien du soutien aux énergies renouvelables et à l'hydraulique, tandis que huit s'y opposent. Les cantons ont demandé une actualisation des perspectives énergétiques et des précisions concernant les coûts, le financement, l'intégration d'éventuelles nouvelles centrales dans le système électrique suisse ainsi que la gestion à long terme des déchets radioactifs. Ils ont en revanche confirmé leur soutien à la poursuite de l'exploitation des centrales existantes, aussi longtemps que les exigences de sécurité sont remplies.
 Ces appréciations ont émaillé également le débat d'entrée en matière de la commission. Plusieurs membres ont demandé le renvoi du projet au Conseil fédéral, estimant que les bases décisionnelles demeuraient insuffisantes, notamment en ce qui concerne les coûts, le financement, les risques résiduels, les conséquences sur le développement des énergies renouvelables et la gestion des déchets radioactifs. La majorité de la commission a toutefois considéré que ces interrogations, bien que légitimes, ne justifiaient pas un renvoi. D'une part, le contre-projet ne préjuge pas d'une future décision de construire de nouvelles centrales et, d'autre part, il ne remet pas en cause la stratégie énergétique 2050 ni les lois votées par le peuple en la matière ces dernières années. Le contre-projet vise uniquement à supprimer une interdiction générale afin de préserver toutes les options susceptibles de contribuer à la sécurité d'approvisionnement dans un contexte marqué par des incertitudes géopolitiques et une demande d'électricité en hausse. Maintenir une interdiction revient à donner un signal paradoxal qui consiste à vouloir garantir notre approvisionnement sans intégrer toutes les technologies dans la réflexion.
 La commission est entrée en matière, par 13 voix contre 12. Elle a ensuite refusé la proposition de renvoi du contre-projet au Conseil fédéral, par 13 voix contre 11.
-Ces demandes de précision, bien que légitimes, sont prématurées. Elles ne pourront trouver de réponse cohérente qu'en cas de projet concret, et non de manière théorique. Il y a quatre minorités à cet égard : les minorités I (Wismer Priska), II (Masshardt), III (Bäumle) et IV (Schlatter).
+Ces demandes de précision, bien que légitimes, sont prématurées. Elles ne pourront trouver de réponse cohérente qu'en cas de projet concret, et non de manière théorique. Il y a quatre minorités à cet égard[NB]: les minorités I (Wismer Priska), II (Masshardt), III (Bäumle) et IV (Schlatter).
 La commission a ensuite procédé à la discussion par article de la modification de la loi sur l'énergie nucléaire, soit du contre-projet à l'initiative, et s'est ralliée en tous points à la position du Conseil des États en refusant plusieurs propositions.
 À l'article 12a, la minorité Wismer Priska vise à limiter la levée de l'interdiction aux seules centrales de quatrième génération. La majorité relève qu'une telle restriction reviendrait pratiquement à maintenir l'interdiction actuelle, car il existe actuellement plus de 90 concepts différents dans le monde, aucune définition n'existant pour qualifier ce que sera une centrale de quatrième génération. Cette proposition a été rejetée, par 13 voix contre 12.
 À l'article 12b, la minorité Bäumle porte sur la responsabilité civile et les conséquences financières d'un accident nucléaire majeur. L'auteur considère que toute nouvelle centrale devrait être soumise à des exigences de couverture financière plus élevées. Pour la majorité, augmenter substantiellement les règles de couverture reviendrait à imposer des exigences plus élevées aux installations futures qu'aux centrales existantes, alors que celles-ci devraient être plus sûres. De tels coûts empêcheraient de facto tout nouveau projet. Cette proposition a été rejetée, par 13 voix contre 11.
@@ -1188,11 +1188,11 @@
   </si>
   <si>
     <t xml:space="preserve">Ich bitte Sie, dieser Motion zuzustimmen. Ich halte mich kurz, ich gehe davon aus, dass der Motionär auch noch sprechen wird.
-Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese, in der Bundesverfassung verankerte Rechtsweggarantie, im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshal</t>
+Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese in der Bundesverfassung verankerte Rechtsweggarantie im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshalb </t>
   </si>
   <si>
     <t xml:space="preserve">Ich bitte Sie, dieser Motion zuzustimmen. Ich halte mich kurz, ich gehe davon aus, dass der Motionär auch noch sprechen wird.
-Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese, in der Bundesverfassung verankerte Rechtsweggarantie, im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshalb diese Rechtsweggarantie nicht überall gleich umgesetzt werden soll. Das ist die Kernfrage. Ich glaube, wir müssen hier besonders diese Fragen stellen.
+Ich habe jetzt sehr gut zugehört, aber es geht um die in der Bundesverfassung verankerte Rechtsweggarantie. Und diesbezüglich geht es um die Frage, warum genau diese in der Bundesverfassung verankerte Rechtsweggarantie im Asylverfahren anders geregelt werden soll als in anderen Gesetzen. Das ist die Kernfrage, und das ist eine Prinzipfrage. Ich sehe es nicht ein, weshalb diese Rechtsweggarantie nicht überall gleich umgesetzt werden soll. Das ist die Kernfrage. Ich glaube, wir müssen hier besonders diese Fragen stellen.
 Es geht ja - entgegen dem Titel - nicht um die unentgeltliche Rechtspflege als Ganzes, sondern es geht um einen Teilbereich, nämlich um die unentgeltliche Rechtsvertretung. Hierzu steht in Artikel 29 Absatz 3 der Bundesverfassung, jede Person habe ausserdem Anspruch auf unentgeltlichen Rechtsbeistand, soweit dies zur Wahrung ihrer Rechte notwendig sei. Sie haben das angeschnitten mit der Frage der Komplexität. "Soweit es zur Wahrung ihrer Rechte notwendig ist" - und meine Erfahrung in der Praxis, in der Umsetzung ist, dass die Hürden sehr hoch sind. Die Gerichte sagen: Ja, du kannst dich ja selber vertreten, es ist nicht so komplex. Und dann bekommen Sie eben keine unentgeltliche Rechtsvertretung.
 Die Problematik bei den Bürgerinnen und Bürgern ist, dass sie diese Frage erst im Hauptverfahren beantwortet bekommen, Herr Kollege Zopfi, erst im Hauptverfahren. Sie wissen also das ganze Verfahren hindurch nicht, ob Sie tatsächlich diese unentgeltliche Rechtsvertretung bekommen. Gegebenenfalls müssen Sie den Anwalt am Schluss doch selbst bezahlen. Ein konkretes Beispiel: Eine Familie mit zwei Kindern wollte eben eine unentgeltliche Rechtsvertretung, hatte aber 8000 Franken auf einem Sparkonto. Das Gericht sagte, dass von den 8000 Franken die 5000 Franken für den Anwalt selbst bezahlt werden können. Das ist die Problematik, die Bürger sehen diese Vergleiche. Das ist nicht ein Einzelfall, das sehe ich ständig, fast wöchentlich, bezüglich unentgeltlicher Rechtsvertretung und nicht bezüglich genereller Rechtspflege.
 Deshalb glaube ich, dass wir hier gut daran tun, wenn wir die in der Bundesverfassung verankerte Rechtsweggarantie in allen Gesetzen gleich anwenden. Ich bitte Sie daher, die Motion anzunehmen.
@@ -1209,7 +1209,7 @@
   <si>
     <t xml:space="preserve">Ich möchte Sie in aller Kürze bitten, der Mehrheit zu folgen. 
 Herr Zopfi hat dargelegt, warum das heutige System funktioniert. Die Rechtsvertreter haben die richtigen Anreize und sorgen in 80 Prozent der Fälle dafür, dass keine Beschwerde erhoben wird. Zudem ist die Alternative, dass entweder das Ganze später verzögert geprüft wird oder aber die Leute selber einen Rechtsbeistand nehmen, Stichwort "türkische Verhältnisse". Also: Das heutige System funktioniert und würde sonst verschlechtert. 
-Die Kernfrage von Herrn Schwander ist ja: Warum wird im allgemeinen Recht die Frage des Rechtsbeistands anders behandelt? Wir sind hier in einer ganz besonderen Konstellation, im Asylverfahren, in dem wir in möglichst kurzer Frist über ganz existenzielle Fragen entscheiden; also im Extremfall darüber, ob jemand in einen angeblichen Folterstaat zurückgehen muss oder nicht. Das wollen wir eben möglichst schnell entscheiden. Weil es immer um diese spezielle Konstellation geht, hat der Gesetzgeber gesagt, in diesem Sonderfall werde eine allgemeine Entscheidung getroffen. Hier ist der Rechtsbeistand fast in jedem Fall angemessen. Schweizerinnen und Schweizer kommen zum Glück gar nicht in diese Situation, aber auch sie würden ihn in dieser Situation natürlich erhalten. Also: Man hat für eine Standortkonstellation unter besonderen Verhältnissen diese besondere Lösung gefunden. Das ist eigentlich kein Ausbruch aus dem System.
+Die Kernfrage von Herrn Schwander ist ja: Warum wird im allgemeinen Recht die Frage des Rechtsbeistands anders behandelt? Wir sind hier in einer ganz besonderen Konstellation, im Asylverfahren, in dem wir in möglichst kurzer Frist über ganz existenzielle Fragen entscheiden; also im Extremfall darüber, ob jemand in einen angeblichen Folterstaat zurückgehen muss oder nicht. Das wollen wir eben möglichst schnell entscheiden. Weil es immer um diese spezielle Konstellation geht, hat der Gesetzgeber gesagt, in diesem Sonderfall werde eine allgemeine Entscheidung getroffen. Hier ist der Rechtsbeistand fast in jedem Fall angemessen. Schweizerinnen und Schweizer kommen zum Glück gar nicht in diese Situation, aber auch sie würden ihn in dieser Situation natürlich erhalten. Also: Man hat für eine Standardkonstellation unter besonderen Verhältnissen diese besondere Lösung gefunden. Das ist eigentlich kein Ausbruch aus dem System.
 Ich bitte Sie, mit der klaren Mehrheit zu stimmen.
 </t>
   </si>
@@ -1239,18 +1239,19 @@
     <t xml:space="preserve">UR</t>
   </si>
   <si>
-    <t xml:space="preserve">Diese Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Dabtte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspaketeds sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diese Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Dabtte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspaketeds sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbeit zwischen Bund, Kantonen, Städten und Gemeinden vereinbar ist. 
-Die Kommission hat zur Asylstrategie und der nun laufenden Umsetzung eine allgemeine, nicht nur gestützt auf diese Motion umfassende Anhörung durchgeführt. Sie hat den Bundesrat, das Staatssekretariat für Migration, die Konferenz der Kantonsregierungen, die KKJPD, die SODK angehört. Ebenfalls einbezogen wurden weitere Kantone, so zum Beispiel der Kanton St. Gallen und der Kanton Waadt sowie Vertreterinnen und Vertreter der Städte und Gemeinden. Im Rahmen dieser Anhörungen wurde der aktuelle Stand der Arbeiten im Asylbereich sowie die Umsetzung der Asylstrategie 2027 diskutiert. Dabei wurde deutlich, dass Bund, Kantone, Städte und Gemeinden in enger Abstimmung zusammenarbeiten und dass die Beschleunigung der Verfahren ein zentrales Anliegen aller beteiligten Akteure ist.
+    <t xml:space="preserve">Die Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Debatte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspakets sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbeit z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion wurde nach ihrer Zuweisung an die Kommission auch dort vertieft beraten. Die Kommission erhielt nach einer kurzen Debatte zur Zuweisung den Auftrag, den Zusammenhang zwischen der Motion der Asylstrategie 2027 sowie den bereits laufenden Umsetzungsarbeiten im Asylbereich zu prüfen. Es ging um die Frage, ob die in der Motion geforderte Priorisierung eines Beschleunigungspakets sowie die Zurückstellung der Asylstrategie 2027 mit den laufenden Umsetzungsarbeiten sowie der Zusammenarbeit zwischen Bund, Kantonen, Städten und Gemeinden vereinbar ist. 
+Die Kommission hat zur Asylstrategie und der nun laufenden Umsetzung eine allgemeine, nicht nur gestützt auf diese Motion umfassende Anhörung durchgeführt. Sie hat den Bundesrat, das Staatssekretariat für Migration, die Konferenz der Kantonsregierungen, die KKJPD, die SODK angehört. Ebenfalls einbezogen wurden weitere Kantone, so zum Beispiel der Kanton St. Gallen und der Kanton Waadt, sowie Vertreterinnen und Vertreter der Städte und Gemeinden. Im Rahmen dieser Anhörungen wurde der aktuelle Stand der Arbeiten im Asylbereich sowie die Umsetzung der Asylstrategie 2027 diskutiert. Dabei wurde deutlich, dass Bund, Kantone, Städte und Gemeinden in enger Abstimmung zusammenarbeiten und dass die Beschleunigung der Verfahren ein zentrales Anliegen aller beteiligten Akteure ist.
 Ihre Kommission hält fest, dass das Asylwesen nur gemeinsam, im Verbund von Bund, Kantonen, Städten und Gemeinden, bei der Planung, der Steuerung und vor allem dann in der Umsetzung gemeinsam erfolgen kann. Nach den Anhörungen wurde festgestellt, dass die Motion in ihrer aktuellen Form die Gefahr einer Übersteuerung der laufenden Arbeiten zwischen Bund und Kantonen und Gemeinden beinhalten könnte und dass bei einer wörtlichen Umsetzung der Forderung der Motion insbesondere im Hinblick auf die Zurückstellung der Asylstrategie laufende Arbeiten faktisch neu priorisiert oder unterbrochen werden müssten, was nicht im Sinne der geforderten Beschleunigung wäre.
 Wir haben in der Kommission weiter festgestellt, dass zum Zeitpunkt der Einreichung der Motion unseres Kollegen die Ausgestaltung der Asylstrategie 2027 noch nicht in der heutigen Form bekannt war, sodass die Motion mit einer anderen Ausgangslage allenfalls politisch anders zu beurteilen gewesen wäre. 
-Der Bundesrat hat in der Kommission in seinen Ausführungen im Kern betont, dass der Beschleunigungsauftrag bereits aufgenommen wurde und das im Rahmen der Motion 24.4171 und die Umsetzung bereits läuft. Bundesrat und Staatssekretär haben in der Kommission zudem darauf hingewiesen, Bundesrat oder Staatssekretär für Migration darauf hingewiesen, dass sich die Arbeiten inzwischen in einer Umsetzungsphase und nicht mehr in einer Strategiephase befinden. Das heisst: Die Strategiephase ist abgeschlossen, jetzt laufen die Umsetzungsarbeiten in Zusammenarbeit Bund, Kantone, Städte, Gemeinden.
-Weiter wurde in der Kommission festgehalten, dass die Motion ja in zwei Elemente aufgeteilt ist. Zum einen enthält sie die Forderung nach prioritärer Umsetzung des Beschleunigungsauftrages, zum anderen verlangt sie die Zurückstellung der Asylstrategie 2027. Die Kommission hat im Besonderen den zweiten Punkt in der aktuellen Umsetzungspraxis als nichtzielführend beurteilt, weil ja die Umsetzungsmassnahmen laufen und die Asylstrategie in dem Sinn als Grundlagenarbeit abgeschlossen ist.
-Die Kommission vertritt deshalb die Auffassung, dass die Beschleunigung im Rahmen der bestehenden Strategie - die eigentliche Stossrichtung des Vorstosses, die auch gut ist und in der Kommission geteilt wird - stärker zu gewichten ist und die bereits überwiesenen parlamentarischen Aufträge konsequent umzusetzen sind, parallel laufende Arbeiten jetzt jedoch nicht zu unterbrechen seien. Wir haben in der Kommission überlegt, ob eine Anpassung des Vorstosses im Sinne einer stärkeren Integration in die laufenden Arbeiten naheliegend gewesen wäre. Es ist uns aber - das wissen Sie - gemäss Parlamentsrecht nicht möglich, eine Anpassung der Motion vorzunehmen. In der Kommission haben wir den angehörten Stellen gegenüber - Kantonen und Gemeinden, aber natürlich auch dem Bund - auf jeden Fall deutlich gemacht, dass im Parlament eine gewisse Ungeduld in Bezug auf die Umsetzungen der überwiesenen Motionen und Postulate im Asylbereich besteht und die laufenden Arbeiten an bereits überwiesenen Vorstössen des Parlamentes und weiteren politischen Aufträgen zwingend in die Umsetzung der Massnahmen der Asylstrategie einzuschliessen sind.
-Zusammenfassend lässt sich sagen: Die Anliegen der Motion sind im Grundsatz bereits in die laufenden Arbeiten zur Umsetzung der Asylstrategie 2027 integriert. Die entsprechenden Prozesse sind aufeinander abgestimmt und werden gemeinsam weitergeführt. Eine zusätzliche Priorisierung oder eine Zurückstellung der laufenden Strategiearbeiten würde, je nach Ausgestaltung, Auswirkungen auf die bestehende Koordination zwischen den Staatsebenen haben. Damit befürchtet die Kommission das Gegenteil einer Beschleunigung. Aus diesen Gründen beantragt Ihre Kommission mit 7 zu 3 Stimmen bei 3 Enthaltungen, die Motion nicht anzunehmen. Das zentrale Anliegen der Motion, die Beschleunigung der Verfahren und die Weiterentwicklung der Systemsteuerung, wird von allen Seiten und auch von Ihrer Kommission geteilt, ist aber bereits Gegenstand der laufenden Arbeiten.
-Eine Minderheit der Kommission beantragt die Annahme der Motion. Sie ist der Auffassung, dass eine zusätzliche politische Priorisierung in einzelnen Bereichen angezeigt ist, um die laufenden Arbeiten gezielt zu verstärken. Sie verweist dabei insbesondere auf klar identifizierte Problemfelder wie Mehrfachgesuche oder vergleichbare Konstellationen. Aus Sicht der Minderheit ergänzt die Motion die Asylstrategie, indem sie den Fokus auf einzelne prioritäre Bereiche lege und verstärke, ohne die laufenden Arbeiten grundsätzlich infrage zu stellen. Sie beantragt daher die Annahme der Motion. Ich gehe davon aus, dass die Minderheitssprecherin, Frau Ständerätin Friedli, das selbst noch im Detail ausführen wird.
+Der Bundesrat hat in seinen Ausführungen in der Kommission im Kern betont, dass der Beschleunigungsauftrag im Rahmen der Behandlung der Motion 24.4271 bereits aufgenommen wurde und dass die Umsetzung bereits läuft. Der Bundesrat bzw. der Staatssekretär für Migration hat zudem in der Kommission darauf hingewiesen, dass sich die Arbeiten inzwischen in einer Umsetzungsphase und nicht mehr in einer Strategiephase befinden. Das heisst: Die Strategiephase ist abgeschlossen; jetzt laufen die Umsetzungsarbeiten in der Zusammenarbeit zwischen Bund, Kantonen, Städten und Gemeinden.
+Weiter wurde in der Kommission festgehalten, dass die Motion ja in zwei Elemente aufgeteilt ist. Zum einen enthält sie die Forderung nach einer prioritären Umsetzung des Beschleunigungsauftrags, zum anderen verlangt sie die Zurückstellung der Asylstrategie 2027. Die Kommission hat insbesondere den zweiten Punkt in der aktuellen Umsetzungspraxis als nicht zielführend beurteilt, weil ja die Umsetzungsmassnahmen laufen und die Asylstrategie in diesem Sinne als Grundlagenarbeit abgeschlossen ist.
+Die Kommission vertritt deshalb die Auffassung, dass die Beschleunigung im Rahmen der bestehenden Strategie - die eigentliche Stossrichtung des Vorstosses, die gut ist und von der Kommission unterstützt wird - stärker zu gewichten ist. Die bereits überwiesenen parlamentarischen Aufträge sind konsequent umzusetzen, parallel laufende Arbeiten sind jedoch nicht zu unterbrechen. 
+Wir haben in der Kommission überlegt, ob eine Anpassung des Vorstosses im Sinne einer stärkeren Integration in die laufenden Arbeiten naheliegend gewesen wäre. Es ist uns aber - das wissen Sie - gemäss Parlamentsrecht nicht möglich, eine Anpassung der Motion vorzunehmen. In der Kommission haben wir den angehörten Stellen gegenüber - Kantonen und Gemeinden, aber natürlich auch dem Bund - auf jeden Fall deutlich gemacht, dass im Parlament eine gewisse Ungeduld in Bezug auf die Umsetzungen der überwiesenen Motionen und Postulate im Asylbereich besteht, und dass die bereits überwiesenen Vorstössen des Parlamentes und weitere politische Aufträge zwingend in die laufenden Arbeiten zur Umsetzung der Massnahmen der Asylstrategie einzuschliessen sind.
+Zusammenfassend lässt sich sagen: Die Anliegen der Motion sind im Grundsatz bereits in die laufenden Arbeiten zur Umsetzung der Asylstrategie 2027 integriert. Die entsprechenden Prozesse sind aufeinander abgestimmt und werden gemeinsam weitergeführt. Eine zusätzliche Priorisierung oder eine Zurückstellung der laufenden Strategiearbeiten hätte, je nach Ausgestaltung, Auswirkungen auf die bestehende Koordination zwischen den Staatsebenen. Damit befürchtet die Kommission das Gegenteil einer Beschleunigung. Aus diesen Gründen beantragt Ihre Kommission mit 7 zu 3 Stimmen bei 3 Enthaltungen, die Motion nicht anzunehmen. Das zentrale Anliegen der Motion - die Beschleunigung der Verfahren und die Weiterentwicklung der Systemsteuerung - wird von allen Seiten und auch von Ihrer Kommission geteilt, ist aber bereits Gegenstand der laufenden Arbeiten.
+Eine Minderheit der Kommission beantragt die Annahme der Motion. Sie ist der Auffassung, dass eine zusätzliche politische Priorisierung in einzelnen Bereichen angezeigt ist, um die laufenden Arbeiten gezielt zu verstärken. Sie verweist dabei insbesondere auf klar identifizierte Problemfelder wie Mehrfachgesuche oder vergleichbare Konstellationen. Aus Sicht der Minderheit ergänzt die Motion die Asylstrategie, indem sie den Fokus auf einzelne prioritäre Bereiche legt und verstärkt, ohne die laufenden Arbeiten grundsätzlich infrage zu stellen. Sie beantragt daher die Annahme der Motion. Ich gehe davon aus, dass die Minderheitssprecherin, Frau Ständerätin Friedli, das selbst noch im Detail ausführen wird.
 </t>
   </si>
   <si>
@@ -1260,15 +1261,17 @@
     <t xml:space="preserve">Zopfi Mathias</t>
   </si>
   <si>
-    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt. Nicht irgendein Gefühl im Einzelfall, sondern ob wir diese Pendenzen senken können, wird einschenken. Es mag eine Wiederholung se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt. Nicht irgendein Gefühl im Einzelfall, sondern ob wir diese Pendenzen senken können, wird einschenken. Es mag eine Wiederholung sein, aber lassen Sie mich noch konkret auf das, was Sie gesagt haben, Kollege Stark, reagieren. 
-Wenn die Kommission sich mit diesen Rädchen und mit diesem System auseinandergesetzt hat und mit 10 zu 2 Stimmen zum Schluss kommt, dass es eben nicht funktioniert - und Ihre Überlegungen kann ich zu 100 Prozent nachvollziehen -, dann frage ich Sie, ob es klug ist, dass der Rat das hier übersteuert aus dem Gefühl heraus, dass man hier vielleicht optimieren könnte. 
+    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt; es ist nicht irgendein Gefühl im Einzelfall. Vielmehr ist von Belang, dass wir diese Pendenzen senken können. 
+Es mag eine Wieder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kollege Stark hat komplexe Fragen geschildert. Es sind Fragen, die man sich stellen kann und stellen muss, wenn man dieses Verfahren anschaut. Gibt es Optimierungspotenzial? An welchem Rädchen müssen wir drehen, damit es schneller geht? Ich glaube, unser aller Ziel ist es, dass wir die Pendenzen beim Bundesverwaltungsgericht senken können. Das ist das, was einschenkt; es ist nicht irgendein Gefühl im Einzelfall. Vielmehr ist von Belang, dass wir diese Pendenzen senken können. 
+Es mag eine Wiederholung sein, aber lassen Sie mich noch konkret auf das, was Sie gesagt haben, Kollege Stark, reagieren. Wenn die Kommission sich mit diesen Rädchen und mit diesem System auseinandergesetzt hat und mit 10 zu 2 Stimmen zum Schluss kommt, dass es eben nicht funktioniert - und Ihre Überlegungen kann ich zu 100 Prozent nachvollziehen -, dann frage ich Sie, ob es klug ist, dass der Rat das hier aus dem Gefühl heraus, dass man hier vielleicht optimieren könnte, übersteuert. 
 Tatsache ist, Kollege Stark: Sie haben gesagt, dass man diesen Entscheid, ob eine unentgeltliche Rechtsvertretung gewährt wird oder nicht, schnell treffen muss. Und Kollege Schwander hat gesagt, dass diese Frage im normalen Verfahren einer Schweizerin oder eines Schweizers vor einem Gericht erst im Laufe des Verfahrens geklärt wird. Ich sage Ihnen nochmals, und das ist das Entscheidende: Sie können es doch nicht schneller klären als die zuständige Person, die es innerhalb der Beschwerdefrist klärt - und die ist kurz. Und sie ist deshalb kurz, weil wir diese Rechtsvertretung gewähren. Deshalb können Sie die Frist so kurz machen. Innerhalb dieser Frist wird das heute geklärt. 
-Und 80 Prozent der Fälle fallen einfach weg. Das ist eine sagenhafte Quote, denn ich sage Ihnen, Anwälte führen gerne Beschwerde. Das ist ihr Beruf. 80 Prozent fallen weg. Und irgendjemand muss es ja klären. Sie können ja nicht sagen, die betroffene Person klärt das. Sie wird zu 100 Prozent Beschwerde erheben. Mein Fall ist immer der wichtigste für mich. Irgendjemand muss es klären. Sie können es in keinem Fall schneller klären als durch das heutige System. Wenn es neu ein Gericht klären muss, dauert es Wochen, wenn nicht Monate. Und ich sage Ihnen, das kostet. 
+Und 80 Prozent der Fälle fallen einfach weg. Das ist eine sagenhafte Quote, denn ich sage Ihnen, Anwälte führen gerne Beschwerde. Das ist ihr Beruf. 80 Prozent fallen weg. Und irgendjemand muss es ja klären. Sie können ja nicht sagen, die betroffene Person klärt das. Sie wird auf jeden Fall Beschwerde erheben. Mein Fall ist immer der wichtigste für mich. Irgendjemand muss es klären. Sie können es in keinem Fall schneller klären als durch das heutige System. Wenn es neu ein Gericht klären muss, dauert es Wochen, wenn nicht Monate. Und ich sage Ihnen, das kostet. 
 Sie operieren hier am offenen Herzen eines Systems, in dem dieser Teil funktioniert. Der Teil Pendenzen funktioniert nicht. Ich möchte eigentlich, Kollege Stark, dass Sie Ihre Energie und Ihren Willen, das zu verbessern, auf das Bundesverwaltungsgericht richten und schauen, wie man dort beschleunigen kann. Dort muss man beschleunigen. Indem dort Verfahrensrechte geprüft und nochmals geprüft werden, indem es noch einmal und noch einmal einen Schriftenwechsel gibt, wird verzögert, und die Fälle stapeln sich. 
-Schnelles Recht ist gutes Recht. Ein schneller Entscheid ist ein guter Entscheid. Der Entscheid über die unentgeltliche Rechtsvertretung wird innerhalb von wenigen Tagen durch die zuständigen Personen gefällt und führt zu deutlich tieferen Kosten. Ich bitte Sie, sich die Überlegungen, die die SPK mit 10 zu 2 Stimmen zu diesem Entscheid geführt haben, wirklich zu überlegen und hier nicht aus dem Gefühl heraus, dass es eine Ungleichbehandlung sei - die es nicht ist -, diese Motion gutzuheissen. Sie würden nicht dem SEM einen Denkzettel verpassen, sondern Ihrer Kommission, die sich damit wirklich vertieft auseinandergesetzt hat.
+Schnelles Recht ist gutes Recht. Ein schneller Entscheid ist ein guter Entscheid. Der Entscheid über die unentgeltliche Rechtsvertretung wird innerhalb von wenigen Tagen durch die zuständigen Personen gefällt und führt zu deutlich tieferen Kosten. 
+Ich bitte Sie, diese Überlegungen, die die SPK zu diesem Entscheid geführt haben - sie hat mit 10 zu 2 Stimmen beschlossen -, zu berücksichtigen und hier nicht aus dem Gefühl heraus, dass es eine Ungleichbehandlung sei - die es nicht ist -, diese Motion anzunehmen. Sie würden nicht dem SEM einen Denkzettel verpassen, sondern Ihrer Kommission, die sich damit wirklich vertieft auseinandergesetzt hat.
 </t>
   </si>
   <si>
@@ -1281,14 +1284,14 @@
     <t xml:space="preserve">Die Asylpolitik beschäftigt unseren Rat, aber auch die Bürgerinnen und Bürger in diesem Land sehr. Das haben wir auch bei der Abstimmung vom letzten Sonntag bemerkt. Es kommen zu viele Menschen über die Asylschiene in unser Land, die gar nicht an Leib und Leben bedroht sind und daher eigentlich auch kein Asylgesuch stellen sollten. Sie kommen zu uns mit der Aussicht auf eine bessere Zukunft, erfüllen jedoch den Asyltatbestand nicht. Diese Personen belasten unser System, denn sind sie einmal im L</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Asylpolitik beschäftigt unseren Rat, aber auch die Bürgerinnen und Bürger in diesem Land sehr. Das haben wir auch bei der Abstimmung vom letzten Sonntag bemerkt. Es kommen zu viele Menschen über die Asylschiene in unser Land, die gar nicht an Leib und Leben bedroht sind und daher eigentlich auch kein Asylgesuch stellen sollten. Sie kommen zu uns mit der Aussicht auf eine bessere Zukunft, erfüllen jedoch den Asyltatbestand nicht. Diese Personen belasten unser System, denn sind sie einmal im Land und im Asylsystem, ist eine Rückkehr schwierig. Die Verfahren dauern lange, können verzögert und mit vielen Rechtsmitteln verlängert werden. Das bringt viel Sand ins Getriebe und belastet vor allem auch die Kantone und die Gemeinden. Zudem gibt es einen Teil der Personen im Asylsystem, welche mit den Behörden nicht kooperieren oder gar kriminell werden. Diese Personen missbrauchen unser Asylsystem, und das führt dazu, dass die Glaubwürdigkeit und Akzeptanz sinken.
-Bis jetzt ist es dem Bundesrat und dem Staatssekretariat für Migration nicht gelungen, diese, ich nenne es Grossbaustelle, anzugehen und vor allem nicht, griffige Massnahmen gegen Missbräuche zu ergreifen. Wir hören immer wieder: Wir sind daran, wir haben eine Strategie, wir sind am Arbeiten. Das reicht jedoch nicht mehr, und das führt eben dazu, dass praktisch in jeder Session mehrere Vorstösse zum Asylbereich eingereicht werden. Ich habe gezählt; wir haben über zwanzig überwiesene Vorstösse im Asylbereich, die der Bundesrat in Gesetzesvorlagen umsetzen sollte. Die Themen kreisen eigentlich immer um die Beschleunigung der Verfahren, Massnahmen für mehr Ausschaffungen und eine härtere Gangart gegenüber Kriminellen. Und wie ich gesagt habe, haben wir bis jetzt weder vom EJPD noch vom Bundesrat gehört, wann diese Vorstösse konkret umgesetzt werden und wann wir eine Botschaft ans Parlament erwarten können.
-Um all diese Massnahmen zu bündeln, hat die Finanzkommission des Ständerates im Rahmen der Erarbeitung des Voranschlages 2025 eine Motion für ein sogenanntes Beschleunigungspaket für das Asylwesen eingereicht. Es ist eigentlich dazu gekommen, weil die Kosten im Asylbereich laufend steigen. Der Bundeshaushalt wird damit immer mehr belastet. Man hat damals festgestellt, dass sich die Anzahl der Gesuche zwar immer wieder verändert oder auch zurückgeht, aber aufgrund der langen Verfahren sich der Pendenzenberg nicht wirklich abbaut. Das SEM sagt immer wieder, der Pendenzenberg sinke. Aber per 30. April dieses Jahres waren immer noch 7881 Asylgesuche sowie 3642 Gesuche um den Schutzstatus S erstinstanzlich pendent. Insgesamt warten nach wie vor über 20 000 Personen auf einen Entscheid. Im Jahr 2025 betrug die durchschnittliche erstinstanzliche Verfahrensdauer 571 Tage. Der Zielwert liegt bei 90 Tagen. Das zeigt: Es besteht dringender Handlungsbedarf. Das hat man mit der Motion 24.4271 gesehen und daher ein Paket mit gezielten regulatorischen und technischen Massnahmen angestossen, welche zur Beschleunigung und damit zum Pendenzenabbau beitragen.
-Ich erlaube mir einfach nochmals, auch zu erwähnen, welche ganz konkreten Massnahmen in dieser Motion erwähnt wurden. Beispiele sind: Vorverfahren: Länder mit einer Bleibequote unter 5 Prozent werden als Safe Countries eingestuft. Oder Angehörige von EU-/EFTA Staaten und Angehörige von Staaten, denen die EU den offiziellen Status "Beitrittskandidat" vergeben hat, können kein Begehren auf vorläufige Aufnahme infolge Unzumutbarkeit geltend machen. Der Status S bleibt vorbehalten. Oder Mehrfachgesuchen um Asyl soll die aufschiebende Wirkung entzogen werden. Oder bei Personen, die ihre Mitwirkungspflicht grob verletzen, soll das Asylgesuch in einem raschen Verfahren abgeschrieben werden. Oder stärkere Verbindlichkeit und Durchsetzung der geltenden Behandlungsfristen des Asylgesetzes mit entsprechenden Instrumenten. Oder generell Verkürzung der Fristen. Oder Einschränkung des Umfangs der Begründungspflicht im Beschwerdeverfahren.
-Kollege Zopfi hat beim vorangehenden Geschäft gesagt, schnelles Recht ist gutes Recht. Das sollten wir uns hier als Vorbild nehmen. Und Sie sehen, die Motion schlägt einen ganzen Strauss von Massnahmen vor. Auch der Bundesrat hat ja damals die Annahme dieser Motion beantragt. Unser Rat hat sie einstimmig angenommen, und auch im Nationalrat fand sie eine ganz grosse Mehrheit. 
-Anstatt die Motion jetzt jedoch zügig umzusetzen und eine klare Vorlage auszuarbeiten, hat das EJPD eine eigene Strategie, die sogenannte Asylstrategie 27, gestartet. Zusammen mit den Kantonen und Gemeinden sollen an runden Tischen und Arbeitsgruppen Strategien entwickelt werden. Das ist gut und recht. Aber so positiv, wie es die Berichterstatterin gesagt hat, kam es bei mir in der Kommission nicht an. Ich und meine Minderheit haben immer noch das Gefühl, dass man sich hier zu oft und zu fest, rund um Strategien, im Kreise dreht. Es fehlt die konkrete Umsetzung und dass man jetzt rasch Massnahmen ergreift. Meine Minderheit ist daher wirklich überzeugt, dass es nun eine zügige Umsetzung der Motion 24.4271 braucht, anstatt eine lange und weitere Strategiediskussion. 
-Mit der Strategie kann man noch weitere, über die vorliegende Motion hinausgehende Themen angehen. Aber die Beschleunigung der Verfahren, und ich glaube, darüber besteht eine breite Einigkeit, die muss jetzt rasch angegangen werden. Die Motion beinhaltet ja auch sehr viele klare Vorgaben. Ich bin sicher, mein Standeskollege und der Initiant der Motion, Kollege Würth, wird dazu auch noch selber Ausführungen machen. 
-Wichtig scheint mir zum Abschluss: Dass die Verfahren beschleunigt und verkürzt werden, entspricht, glaube ich, der Erwartung der Bürgerinnen und Bürger. Eine Beschleunigung würde die Akzeptanz für das Asylsystem massiv erhöhen und die Verwaltungen beim Bund, bei den Kantonen und Gemeinden und vor allem auch unsere Gerichte endlich entlasten. Damit werden eben auch Kosten gespart, deshalb kam diese Motion ursprünglich auch von der Finanzkommission. Vor allem würden wir mit einer Beschleunigung wieder auf den eigentlichen Kernbereich des Asylsystems fokussieren. Das System soll denen, die an Leib und Leben bedroht sind, helfen. Es soll nicht mit Wirtschaftsflüchtlingen und Kriminellen belastet werden. 
+    <t xml:space="preserve">Die Asylpolitik beschäftigt unseren Rat, aber auch die Bürgerinnen und Bürger in diesem Land sehr. Das haben wir auch bei der Abstimmung vom letzten Sonntag bemerkt. Es kommen zu viele Menschen über die Asylschiene in unser Land, die gar nicht an Leib und Leben bedroht sind und daher eigentlich auch kein Asylgesuch stellen sollten. Sie kommen zu uns mit der Aussicht auf eine bessere Zukunft, erfüllen jedoch den Asyltatbestand nicht. Diese Personen belasten unser System, denn sind sie einmal im Land und im Asylsystem, ist eine Rückkehr schwierig. Die Verfahren dauern lange, können verzögert und mit vielen Rechtsmitteln verlängert werden. Das bringt viel Sand ins Getriebe und belastet vor allem auch die Kantone und die Gemeinden. Zudem gibt es einen Teil an Personen im Asylsystem, welcher mit den Behörden nicht kooperiert oder gar kriminell wird. Diese Personen missbrauchen unser Asylsystem. Das führt dazu, dass die Glaubwürdigkeit und Akzeptanz sinken.
+Bis jetzt ist es dem Bundesrat und dem Staatssekretariat für Migration nicht gelungen, diese Grossbaustelle, wie ich es nenne, anzugehen. Vor allem ist es nicht gelungen, griffige Massnahmen gegen Missbräuche zu treffen. Wir hören immer wieder: Wir sind daran, wir haben eine Strategie, wir sind am Arbeiten. Das reicht jedoch nicht mehr. Das führt dazu, dass praktisch in jeder Session mehrere Vorstösse zum Asylbereich eingereicht werden. Ich habe gezählt: Wir haben über zwanzig überwiesene Vorstösse im Asylbereich, die der Bundesrat in Gesetzesvorlagen umsetzen sollte. Die Themen kreisen eigentlich immer um die Beschleunigung der Verfahren, Massnahmen für mehr Ausschaffungen und eine härtere Gangart gegenüber Kriminellen. Wie ich gesagt habe, haben wir bis jetzt weder vom EJPD noch vom Bundesrat gehört, wann diese Vorstösse konkret umgesetzt werden und wann wir eine Botschaft ans Parlament erwarten können.
+Um all diese Massnahmen zu bündeln, hat die Finanzkommission des Ständerates im Rahmen der Erarbeitung des Voranschlages 2025 eine Motion für ein sogenanntes Beschleunigungspaket für das Asylwesen eingereicht. Es ist eigentlich dazu gekommen, weil die Kosten im Asylbereich laufend steigen. Der Bundeshaushalt wird damit immer mehr belastet. Man hat damals festgestellt, dass sich die Anzahl der Gesuche zwar immer wieder verändert oder auch zurückgeht, aber aufgrund der langen Verfahren sich der Pendenzenberg nicht wirklich abbaut. Das SEM sagt immer wieder, der Pendenzenberg sinke. Aber per 30. April dieses Jahres waren immer noch 7881 Asylgesuche sowie 3642 Gesuche um den Schutzstatus S erstinstanzlich pendent. Insgesamt warten nach wie vor über 20 000 Personen auf einen Entscheid. Im Jahr 2025 betrug die durchschnittliche erstinstanzliche Verfahrensdauer 571 Tage. Der Zielwert liegt bei 90 Tagen. Das zeigt: Es besteht dringender Handlungsbedarf. Das hat man mit der Motion 24.4271 gesehen und daher ein Paket mit gezielten regulatorischen und technischen Massnahmen angestossen, welche zur Beschleunigung und damit zum Pendenzenabbau beitragen sollen.
+Ich erlaube mir einfach nochmals zu erwähnen, welche ganz konkreten Massnahmen in dieser Motion erwähnt wurden. Beispiele sind: Vorverfahren: Länder mit einer Bleibequote unter 5 Prozent werden als Safe Countries eingestuft. Oder Angehörige von EU/EFTA-Staaten und Angehörige von Staaten, denen die EU den offiziellen Status "Beitrittskandidat" vergeben hat, können kein Begehren auf vorläufige Aufnahme infolge Unzumutbarkeit geltend machen. Der Status S bleibt vorbehalten. Oder Mehrfachgesuchen um Asyl soll die aufschiebende Wirkung entzogen werden. Oder bei Personen, die ihre Mitwirkungspflicht grob verletzen, soll das Asylgesuch in einem raschen Verfahren abgeschrieben werden; oder stärkere Verbindlichkeit und Durchsetzung der geltenden Behandlungsfristen des Asylgesetzes mit entsprechenden Instrumenten; oder generelle Verkürzung der Fristen; oder Einschränkung des Umfangs der Begründungspflicht im Beschwerdeverfahren.
+Kollege Zopfi hat beim vorangehenden Geschäft gesagt, schnelles Recht sei gutes Recht. Das sollten wir uns hier zum Vorbild nehmen. Und Sie sehen, die Motion schlägt einen ganzen Strauss von Massnahmen vor. Auch der Bundesrat hat ja damals die Annahme dieser Motion beantragt. Unser Rat hat sie einstimmig angenommen, und auch im Nationalrat fand sie eine ganz grosse Mehrheit. 
+Anstatt die Motion jetzt jedoch zügig umzusetzen und eine klare Vorlage auszuarbeiten, hat das EJPD eine eigene Strategie, die sogenannte Asylstrategie 27, gestartet. Zusammen mit den Kantonen und Gemeinden sollen an runden Tischen und in Arbeitsgruppen Strategien entwickelt werden. Das ist gut und recht. Aber so positiv, wie es die Berichterstatterin gesagt hat, kam es bei mir in der Kommission nicht an. Ich und meine Minderheit haben immer noch das Gefühl, dass man sich hier zu oft und zu fest, rund um Strategien, im Kreise dreht. Es fehlt die konkrete Umsetzung und dass man jetzt rasch Massnahmen ergreift. Meine Minderheit ist daher wirklich überzeugt, dass es nun eine zügige Umsetzung der Motion 24.4271 braucht, anstatt eine weitere lange Strategiediskussion. 
+Mit der Strategie kann man noch weitere, über die vorliegende Motion hinausgehende Themen angehen. Aber die Beschleunigung der Verfahren, und ich glaube, darüber besteht eine breite Einigkeit, muss jetzt rasch angegangen werden. Die Motion beinhaltet ja auch sehr viele klare Vorgaben. Ich bin sicher, mein Standeskollege und der Initiant der Motion, Kollege Würth, wird dazu auch noch selber Ausführungen machen. 
+Wichtig scheint mir zum Abschluss: Dass die Verfahren beschleunigt und verkürzt werden, entspricht, glaube ich, der Erwartung der Bürgerinnen und Bürger. Eine Beschleunigung würde die Akzeptanz für das Asylsystem massiv erhöhen und die Verwaltungen beim Bund, bei den Kantonen und Gemeinden und vor allem auch unsere Gerichte endlich entlasten. Damit werden eben auch Kosten gespart, deshalb kam diese Motion ursprünglich auch von der Finanzkommission. Vor allem würden wir mit einer Beschleunigung wieder auf den eigentlichen Kernbereich des Asylsystems fokussieren. Das System soll denen, die an Leib und Leben bedroht sind, helfen. Es soll nicht mit Wirtschaftsflüchtlingen und Kriminellen belastet werden.
 Vor diesem Hintergrund bitte ich Sie, die vorliegende Motion anzunehmen und meine Minderheit zu unterstützen.
 </t>
   </si>
@@ -1336,17 +1339,19 @@
     <t xml:space="preserve">Stark Jakob</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. Die Bundesverfassung hält in Artikel 29 Absatz 3 klar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. Die Bundesverfassung hält in Artikel 29 Absatz 3 klar fest, dass jede Person, die nicht über die erforderlichen Mittel verfügt, Anspruch darauf hat. Bei Asylsuchenden gehen wir davon aus, dass diese Voraussetzung erfüllt ist. Wäre das nicht der Fall, müssten wir das gesamte System infrage stellen und zunächst klären, Herr Zopfi, welche Asylsuchenden tatsächlich über ausreichende Mittel verfügen. Das heutige System basiert somit auf der Annahme der Mittellosigkeit und gewährt entsprechend einen Anspruch auf unentgeltliche Rechtspflege.
-Gleichzeitig verlangt die Verfassung, dass das Rechtsbegehren - ich zitiere - "nicht aussichtslos erscheint". Genau dieser Grundsatz gilt für alle Personen in unserem Land, die von einem Verfahren betroffen sind, und er soll selbstverständlich auch künftig für Asylsuchende gelten, jedoch nicht darüber hinaus. Meine Forderung zielt nicht darauf ab, die automatische Zuteilung einer kostenlosen Rechtsvertretung für jede neu asylsuchende Person aufzuheben; überhaupt nicht. Entscheidend ist vielmehr, dass die Rechtsvertretung in aussichtslosen Fällen früher endet als heute. Darin liegt der Kern meines Anliegens. Ich bin zudem überzeugt, dass eine frühere Beendigung zu deutlich weniger Beschwerden führen würde. Ich komme darauf zurück.
+    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. 
+Die Bundesverfassung hält in Artikel 29 Absatz 3 klar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte vorausschicken, dass es mir keineswegs darum geht, das heutige System infrage zu stellen. Ich lege dar, weshalb ich überzeugt bin, dass sich dieses System verbessern lässt und dass gewisse Missstände bestehen. Wenn Sie, Herr Zopfi, darauf hinweisen, dass bei Umsetzung meiner Idee mehr Asylpersonen die Kosten selbst tragen würden, stellt sich die grundsätzliche Frage, weshalb wir überhaupt eine unentgeltliche Rechtspflege vorsehen. 
+Die Bundesverfassung hält in Artikel 29 Absatz 3 klar fest, dass jede Person, die nicht über die erforderlichen Mittel verfügt, Anspruch darauf hat. Bei Asylsuchenden gehen wir davon aus, dass diese Voraussetzung erfüllt ist. Wäre das nicht der Fall, müssten wir das gesamte System infrage stellen und zunächst klären, Herr Zopfi, welche Asylsuchenden tatsächlich über ausreichende Mittel verfügen. Das heutige System basiert somit auf der Annahme der Mittellosigkeit und gewährt entsprechend einen Anspruch auf unentgeltliche Rechtspflege.
+Gleichzeitig verlangt die Bundesverfassung, dass das Rechtsbegehren - ich zitiere - "nicht aussichtslos erscheint". Genau dieser Grundsatz gilt für alle Personen in unserem Land, die von einem Verfahren betroffen sind, und er soll selbstverständlich auch künftig für Asylsuchende gelten, jedoch nicht darüber hinaus. Meine Forderung zielt nicht darauf ab, die automatische Zuteilung einer kostenlosen Rechtsvertretung für jede neu asylsuchende Person aufzuheben; überhaupt nicht. Entscheidend ist vielmehr, dass die Rechtsvertretung in aussichtslosen Fällen früher endet als heute. Darin liegt der Kern meines Anliegens. Ich bin zudem überzeugt, dass eine frühere Beendigung zu deutlich weniger Beschwerden führen würde. Ich komme darauf zurück.
 Im geltenden Asylgesetz gehört es zu den ersten Aufgaben der Rechtsvertretung, die asylsuchende Person nach Teilnahme an der Erstbefragung und der Anhörung zu den Asylgründen über ihre Erfolgschancen im Verfahren zu informieren; hier verweise ich auf Artikel 102h Absatz 2 AsylG. Zu diesem Zeitpunkt liegt bereits ein umfassender Überblick über den Sachverhalt vor. Anschliessend begleitet die Rechtsvertretung das Verfahren bis zur Beschwerde und zum Entscheid des Bundesverwaltungsgerichtes. Heute endet die Rechtsvertretung - Herr Zopfi hat es gesagt - entweder mit der Rechtskraft eines Asylentscheides oder mit der Mitteilung der zugewiesenen Rechtsvertreterin oder des zugewiesenen Rechtsvertreters an die asylsuchende Person, dass wegen Aussichtslosigkeit keine Beschwerde eingereicht wird.
 Auffällig ist, dass rund 20 Prozent aller Fälle an das Bundesverwaltungsgericht weitergezogen werden, während lediglich 5 bis 6 Prozent dieser Beschwerden erfolgreich sind. Das bedeutet, dass 94 bis 95 Prozent der weitergezogenen Fälle mit einer Ablehnung enden. Der Spielraum ist somit erheblich. In der Praxis wägen Rechtsvertreter im Zweifel zugunsten der asylsuchenden Person ab und reichen eine Beschwerde ein, insbesondere wenn diese darauf beharrt. Daraus ergibt sich, dass eine beträchtliche Zahl von Entscheiden weitergezogen wird, obwohl die Erfolgsaussichten offensichtlich gering sind, und genau das ist der springende Punkt.
 Ich sage es nochmals: Der Kommissionsbericht zeigt, dass das neu strukturierte Asylverfahren nicht nur effizient, sondern auch sehr sorgfältig ist. Die Entscheidbeständigkeitsquote - auch das, Herr Zopfi, haben Sie gesagt - liegt bei 99 Prozent, was ausserordentlich hoch ist. Das bedeutet, dass rund 90 Prozent der erstinstanzlichen Entscheide des Staatssekretariates für Migration (SEM) am Ende rechtskräftig werden. Vor diesem Hintergrund kann man die Frage stellen, ob es trotz der verfassungsrechtlichen Vorgaben notwendig ist, allen Betroffenen in jedem Fall ein Rechtsmittel zur Verfügung zu stellen, wenn die Verfahren bereits mit hoher Sorgfalt durchgeführt werden. Aber - das Beschwerdeverfahren bleibt möglich.
-Nochmals: 20 Prozent der Entscheide werden weitergezogen und nur 5 bis 6 Prozent aller Beschwerden ans Bundesverwaltungsgericht dann gutgeheissen. Gleichzeitig, auch darauf wurde hingewiesen, stapeln sich beim Bundesverwaltungsgericht die Beschwerden zu Bergen und verzögern den Vollzug um Monate. Ja, wir haben aus der Finanzkommission interveniert. Es wurde uns beschieden, dass das in St. Gallen offenbar nicht möglich ist, die Abteilung die nötigen Kapazitäten nicht erhält und diese Berge eben Berge bleiben.
+Nochmals: 20 Prozent der Entscheide werden weitergezogen und nur 5 bis 6 Prozent aller Beschwerden ans Bundesverwaltungsgericht dann gutgeheissen. Gleichzeitig, auch darauf wurde hingewiesen, stapeln sich beim Bundesverwaltungsgericht die Beschwerden zu Bergen und verzögern den Vollzug um Monate. Ja, wir haben aus der Finanzkommission interveniert. Es wurde uns beschieden, dass das in St. Gallen offenbar nicht möglich ist, dass die Abteilung die nötigen Kapazitäten nicht erhält und dass diese Berge eben Berge bleiben.
 Fazit: Wenn die Zahl dieser Beschwerden abnehmen würde, könnten wir den ganzen Effizienzgewinn behalten. Das könnte man machen, indem früher gesagt würde: Diese Fälle sind aussichtslos, wir brechen jetzt die Rechtsvertretung ab.
-Ich möchte zusammenfassen: Bei dieser Ausgangslage ist es aus Qualitätsgründen ohne Weiteres zulässig und aus Effizienzgründen auf jeden Fall notwendig, dass die Erfolgsaussichten von Asylgesuchen in einer ersten Phase, nach Erstbefragung und Anhörung, zwingend beurteilt werden und die Rechtsvertretung nur weitergeführt wird, wenn das Asylgesuch nicht aussichtslos erscheint - wie es auch in der Bundesverfassung steht. Wenn es nicht aussichtslos erscheint, soll die Beschwerde ergriffen und die Rechtsvertretung weiterhin gewährt werden können, aber ansonsten ist das Verfahren abzuschliessen.
+Ich möchte zusammenfassen: Bei dieser Ausgangslage ist es aus Qualitätsgründen ohne Weiteres zulässig und aus Effizienzgründen auf jeden Fall notwendig, dass die Erfolgsaussichten von Asylgesuchen in einer ersten Phase, nach Erstbefragung und Anhörung, zwingend beurteilt werden und dass die Rechtsvertretung nur weitergeführt wird, wenn das Asylgesuch nicht aussichtslos erscheint - wie es auch in der Bundesverfassung steht. Wenn es nicht aussichtslos erscheint, soll die Beschwerde ergriffen und die Rechtsvertretung weiterhin gewährt werden können, aber ansonsten ist das Verfahren abzuschliessen.
 Damit würden sich erstens die Zahl der Beschwerden und die Kosten für die Rechtsvertretung deutlich reduzieren. Zweitens könnten die Asylverfahren - ich sage es nochmals: unter Beibehaltung der hohen Qualität - deutlich beschleunigt werden. Drittens würde die Verfahrensgarantie gemäss Bundesverfassung so gewährleistet, wie sie für alle Personen in der Schweiz gilt, die sich in irgendeinem rechtlichen Verfahren befinden.
 Ich bitte Sie deshalb, der Minderheit zuzustimmen und die Motion anzunehmen.
 </t>
@@ -1360,19 +1365,20 @@
   </si>
   <si>
     <t xml:space="preserve">Wir haben letzte Woche ein hitziges Traktandum verhandelt, und meine Nachbarin rechts von mir hat von groben Fouls gesprochen. Sie ist deutlich die bessere Fussballerin als ich, ich habe zwei linke Füsse, aber ich möchte trotzdem auch hier einen Fussballvergleich bemühen. Wenn Sie nämlich diese Motion annehmen, dann schiessen Sie ein Eigentor. Um das zu begründen, möchte ich etwas in die Tiefe gehen und zuerst einmal mit drei Feststellungen starten: 
-Erstens, die Minderheit - Sie sehen das im schriftlichen Kommissionsbericht - stört sich daran, dass Asylbewerberinnen und Asylbewerber besser behandelt würden als Schweizerinnen und Schweizer, was die unentgeltliche Rechtspflege angeht. Lassen Sie mich klar festhalten, dass dem nicht so ist. In unserem Staat hat Anspruch auf unentgeltliche Rechtspflege, wer nicht in der Lage ist, das Verfahren zu bezahlen, gleichzeitig - wegen der Komplexität - anwaltliche Unterstützung benötigt sowie Erfolgsaussichten hat. Das ist überall so, und ich kann Ihnen als im Familienrecht tätiger Anwalt bestätigen, dass ich unzählige Verfahren über die unentgeltliche Rechtspflege führe. Zweitens, das SEM arbeitet im Bereich der Beschwerden sehr erfolgreich; das kann man sagen. Die Pendenzen konnten massiv reduziert werden, wir haben uns diese Zahlen zeigen lassen. Zudem - und das ist in diesem Kontext sehr interessant - sind die Entscheide des SEM insgesamt zu über 98 Prozent beständig. Was bedeutet das? Über 98 Prozent der Entscheide des SEM treten, weil sie nicht mit Beschwerden angefochten werden oder weil die Beschwerden abgewiesen werden, in Rechtskraft. Das ist eine beeindruckende Quote, die wahrscheinlich an wenigen Orten erreicht wird. Ich will damit nicht sagen, dass alles gut läuft, aber wir haben es hier konkret mit dem Beschwerdeverfahren zu tun, und ich würde sagen, dass man in diesem Bereich die Feststellung machen kann, dass es eigentlich nicht schlecht läuft. 
-Allerdings muss ich das auch wieder ein bisschen relativieren, denn meine dritte Feststellung lautet: Wir haben schon nicht einfach keine Probleme. Ein Problem, das wir haben, ist, dass sich am Bundesverwaltungsgericht die Pendenzen stapeln. Ende 2025 gab es 5795 Pendenzen; 253 davon stammten noch von 2022, 514 von 2023, 1864 von 2024 und 2834 von 2025. Es gibt leider eine steigende Zahl von Pendenzen. Und jetzt ist es so: Bei diesen Fällen geht es ja nicht einfach nur um Fälle, die am Gericht irgendwo in einer Schublade liegen und dann bearbeitet werden, sondern es geht um Menschen, die irgendwo in den Gemeinden einquartiert werden müssen, die finanziert werden müssen, usw. Diese Fälle kosten - also nicht die Fälle in der Schublade, sondern die Menschen, die in unserem Land bleiben, obwohl sie das Land dann vielleicht verlassen müssten, wenn der Entscheid rechtskräftig würde. Und wir reden hier nicht von kleinen Beträgen, wir reden von Dutzenden Millionen von Franken. Wenn wir Handlungsbedarf feststellen - und es ist, im Unterschied zu dem, was ich in Bezug auf meine zweite Feststellung gesagt habe, tatsächlich nicht alles gut -, dann ist es wichtig und zentral, dass wir das Beschwerdeverfahren beschleunigen und es auf keinen Fall ausbremsen. Wenn die Beschwerdeverfahren länger gehen, dann kostet uns das massiv mehr Geld. 
-Jetzt komme ich zu den Effekten dieser Motion und versuche Ihnen darzulegen, weshalb die Motion in diesem Kontext ein Eigentor wäre. 
-Der erste Effekt: Im Asylbereich funktioniert das System mit der unentgeltlichen Rechtsberatung gut. Die Personen, die diese Rechtsberatung machen, sind Juristinnen und Juristen; sie werden dafür angestellt, aber sie werden nicht pro Fall bezahlt, sondern - und das ist sehr entscheidend - sie werden pauschal bezahlt. Sie haben also keinen Anreiz, aussichtslose Beschwerden zu führen, da sie nicht für die einzelnen Beschwerden, die sie führen, einen Lohn oder eine Zahlung erhalten, sondern sie erhalten einfach eine grundsätzliche Pauschale. Und deshalb behandeln sie jene Fälle - das ist auch ihre Pflicht -, bei denen Aussicht auf Erfolg besteht. Sie haben die gesetzliche Aufgabe, die betroffenen Menschen über die Erfolgsaussichten zu informieren, und eben nur dort Beschwerde zu führen, wo es Aussichten auf Erfolg gibt. Dieser Grundsatz ist also bereits festgehalten. Und logisch, es ist klar, dass es sich um eine schwierige Einschätzung handelt. Die tiefe Gutheissungsquote von Beschwerden, die ich Ihnen vorher genannt habe, zeigt ja, dass das SEM seine Arbeit nicht schlecht macht und die Erfolgsaussichten deshalb meist relativ tief sind. Aber, und das ist zentral, es ist ein effizientes System. Wenn nämlich mit dieser Motion die unentgeltliche Prozessführung eingeschränkt und nur noch in Fällen gewährt würde, in denen ein Verfahren aussichtsreich ist - diese Prüfung bzw. Einschätzung wird heute eigentlich durch die Rechtsberatung vorgenommen -, dann müsste darüber ja neu entschieden werden. 
+Erstens, die Minderheit - Sie sehen das im schriftlichen Kommissionsbericht - stört sich daran, dass Asylbewerberinnen und Asylbewerber besser behandelt würden als Schweizerinnen und Schweizer, was die unentgeltliche Rechtspflege angeht. Lassen Sie mich klar festhalten, dass dem nicht so ist. In unserem Staat hat Anspruch auf unentgeltliche Rechtspflege, wer nicht in der Lage ist, das Verfahren zu bezahlen, gleichzeitig - wegen der Komplexität - anwaltliche Unterstützung benötigt sowie Erfolgsaussichten hat. Das ist überall so, und ich kann Ihnen als im Familienrecht tätiger Anwalt bestätigen, dass ich unzählige Verfahren über die unentgeltliche Rechtspflege führe. 
+Zweitens, das SEM arbeitet im Bereich der Beschwerden sehr erfolgreich; das kann man sagen. Die Pendenzen konnten massiv reduziert werden, wir haben uns diese Zahlen zeigen lassen. Zudem - und das ist in diesem Kontext sehr interessant - sind die Entscheide des SEM insgesamt zu über 98 Prozent beständig. Was bedeutet das? Über 98 Prozent der Entscheide des SEM treten, weil sie nicht mit Beschwerden angefochten werden oder weil die Beschwerden abgewiesen werden, in Rechtskraft. Das ist eine beeindruckende Quote, die wahrscheinlich an wenigen Orten erreicht wird. Ich will damit nicht sagen, dass alles gut läuft, aber wir haben es hier konkret mit dem Beschwerdeverfahren zu tun, und ich würde sagen, dass man in diesem Bereich die Feststellung machen kann, dass es eigentlich nicht schlecht läuft. 
+Drittens, allerdings muss ich das auch wieder ein bisschen relativieren, denn meine Feststellung lautet: Wir haben schon nicht einfach keine Probleme. Ein Problem, das wir haben, ist, dass sich am Bundesverwaltungsgericht die Pendenzen stapeln. Ende 2025 gab es 5795 Pendenzen; 253 davon stammten noch von 2022, 514 von 2023, 1864 von 2024 und 2834 von 2025. Es gibt leider eine steigende Zahl von Pendenzen. Und jetzt ist es so: Bei diesen Fällen geht es ja nicht einfach nur um Fälle, die am Gericht irgendwo in einer Schublade liegen und dann bearbeitet werden, sondern es geht um Menschen, die irgendwo in den Gemeinden einquartiert werden müssen, die finanziert werden müssen, usw. Diese Fälle kosten - also nicht die Fälle in der Schublade, sondern die Menschen, die in unserem Land bleiben, obwohl sie das Land dann vielleicht verlassen müssten, wenn der Entscheid rechtskräftig würde. Wir reden hier nicht von kleinen Beträgen, wir reden von Dutzenden Millionen von Franken. Wenn wir Handlungsbedarf feststellen - und es ist, im Unterschied zu dem, was ich in Bezug auf meine zweite Feststellung gesagt habe, tatsächlich nicht alles gut -, dann ist es wichtig und zentral, dass wir das Beschwerdeverfahren beschleunigen und es auf keinen Fall ausbremsen. Wenn die Beschwerdeverfahren länger gehen, dann kostet uns das massiv mehr Geld. 
+Ich komme zu den Effekten dieser Motion und versuche Ihnen darzulegen, weshalb die Motion in diesem Kontext ein Eigentor wäre. 
+Der erste Effekt: Im Asylbereich funktioniert das System mit der unentgeltlichen Rechtsberatung gut. Die Personen, die diese Rechtsberatung machen, sind Juristinnen und Juristen; sie werden dafür angestellt, aber sie werden nicht pro Fall bezahlt, sondern - und das ist sehr entscheidend - sie werden pauschal bezahlt. Sie haben also keinen Anreiz, aussichtslose Beschwerden zu führen, da sie nicht für die einzelnen Beschwerden, die sie führen, einen Lohn oder eine Zahlung erhalten, sondern sie erhalten einfach eine grundsätzliche Pauschale. Deshalb behandeln sie jene Fälle - das ist auch ihre Pflicht -, bei denen Aussicht auf Erfolg besteht. Sie haben die gesetzliche Aufgabe, die betroffenen Menschen über die Erfolgsaussichten zu informieren, und nur dort Beschwerde zu führen, wo es Aussichten auf Erfolg gibt. Dieser Grundsatz ist also bereits festgehalten. Und logisch, es ist klar, dass es sich um eine schwierige Einschätzung handelt. Die tiefe Gutheissungsquote von Beschwerden, die ich Ihnen vorher genannt habe, zeigt, dass das SEM seine Arbeit nicht schlecht macht und die Erfolgsaussichten deshalb meist relativ tief sind. Aber, und das ist zentral, es ist ein effizientes System. Wenn nämlich mit dieser Motion die unentgeltliche Prozessführung eingeschränkt und nur noch in Fällen gewährt würde, in denen ein Verfahren aussichtsreich ist - das passiert heute bei der Prüfung -, dann müssten Sie das neu entscheiden.
 Heute läuft es so, dass der Betroffene zur Rechtsvertretung geht. Diese berät ihn über die Erfolgsaussichten. Wenn gewisse Aussichten auf Erfolg bestehen - natürlich behandeln Sie als Anwalt nicht Fälle mit 100 Prozent Aussicht auf Erfolg, sondern vielmehr solche mit gewissen Aussichten - dann wird Beschwerde geführt. Das geschieht in ungefähr 20 Prozent der Fälle; ich werde nochmals darauf zurückkommen. In 80 Prozent der Fälle entscheidet die Rechtsvertretung also, dass es sich nicht lohnt, es zu probieren. Das ist eine hohe Quote. Stellen Sie sich vor, wie die Pendenzen beim Bundesverwaltungsgericht aussehen würden, wenn diese Quote tiefer wäre.
 Die Prozessaussichten werden also heute bereits geprüft, und zwar, und das ist auch ein wichtiger Punkt, innerhalb der Beschwerdefrist. Die Beschwerdefrist beginnt mit dem Entscheid des SEM zu laufen, und innerhalb dieser Frist wird entschieden, ob es aussichtsreich ist, eine Beschwerde zu machen. Wenn Sie das nun genauer überprüfen wollen, dann müssten Sie diesen Entscheid dem Gericht überlassen. Dann müsste das Gericht entscheiden, wie es der Motionär will, wie die Prozessaussichten sind, ob Aussicht auf Erfolg besteht. Dies müsste aber logischerweise nach der Beschwerdefrist gemacht werden. Denn das Gericht kann ja die Chancen erst beurteilen, wenn eine Beschwerde eingegangen ist. Vorher weiss es von diesem Fall gar nichts. Und, das ist ebenfalls klar, für diesen Entscheid braucht das Gericht Zeit. Es muss die Parteien anhören, es gibt rechtsstaatliche Pflichten und Garantien usw. Nehmen wir jetzt einmal an, dass das Bundesverwaltungsgericht für diese vielen Fälle, für 100 Prozent, nicht, wie heute für 20 Prozent, jeweils, sagen wir, zwei Wochen braucht, um die Frage zu entscheiden - und es wäre ein absolutes Turbogericht, wenn es das könnte. Das wäre schon deutlich teurer, als das, was die unentgeltliche Rechtsberatung überhaupt kostet, weil in diesen zwei Wochen viel mehr Menschen keinen Entscheid hätten und zwei Wochen länger im System bleiben würden. Wenn es einen Monat dauert, bleiben sie einen Monat länger im System, wenn es zwei Monate dauert, sind es zwei Monate länger, und während dieser Zeit verursachen sie jeden Tag Kosten. Es gibt Zahlen dazu, Sie können ausrechnen, was das kostet.
-Wenn dann noch mehr Personen als heute versuchen, eine Beschwerde zu machen, weil Sie die Erfolgsaussichten nicht mehr bei der Rechtsberatung analysiert bekommen, dann kippt es definitiv ins Kontraproduktive. Denn wenn dann nicht mehr 20 Prozent wie heute, sondern sagen wir 80 Prozent Beschwerde erheben, kann ich Ihnen sagen, was passiert. Das Bundesverwaltungsgericht würde von Beschwerden überschwemmt. Das Ziel muss aber sein, die Pendenzen am Bundesverwaltungsgericht zu senken, und nicht, sie zu steigern. Das können wir nicht tun, indem wir das Verfahren verlangsamen. Wir können es nur tun, indem wir beschleunigen. Die unentgeltliche Rechtsvertretung, ich will das klipp und klar sagen, beschleunigt das Verfahren, es bremst sie nicht. Diese Rechtsvertretenden haben keinen Anreiz, das System zu blockieren, weil sie pauschal bezahlt sind und nicht nach Stundensatz wie ein Anwalt üblicherweise.
-Damit komme ich zum zweiten Effekt. Denn auch der zweite Effekt wird klar, wenn man sich ein bisschen in die Statistik vertieft. Interessant wird es nämlich, wenn Sie die verschiedenen Herkunftsländer betrachten. Dort, wo die Rechtsvertretung über die unentgeltliche Rechtspflege läuft - das, was der Motionär infrage stellen will -, haben wir eine Beschwerdequote, ich habe es erwähnt, von etwa 20 Prozent. Von hundert Personen, die einen negativen Entscheid haben, führen dann also 20 Prozent Beschwerde. Das ist eigentlich eine recht tiefe Quote, denn es geht für diese Leute um einen für sie extrem einschneidenden Entscheid. Man würde eigentlich erwarten, dass die meisten probieren, eine Beschwerde zu machen. Aber es probieren es nur 20 Prozent. Das bedeutet umgekehrt, dass die Rechtsvertretungen in 80 von 100 Fällen raten, keine Beschwerde zu machen, und dass sie dies erfolgreich tun, denn es wird ja dann auch keine Beschwerde eingereicht. Die Aussichtslosigkeit oder die Prozessaussichten werden also bereits geprüft. Man könnte das Problem lösen, indem man sagt, es gibt einfach keine Beschwerde mehr. Aber dass man überhaupt Beschwerde machen kann, ist ein durch unsere Verfassung geschütztes Recht, und es führt ja gerade dazu, dass das SEM seine Arbeit speditiv machen kann. Sonst würden Sie die Verantwortung noch mehr zum SEM verlagern.
+Wenn dann noch mehr Personen als heute versuchen, eine Beschwerde zu machen, weil Sie die Erfolgsaussichten nicht mehr bei der Rechtsberatung analysiert bekommen, dann kippt es definitiv ins Kontraproduktive. Denn wenn dann nicht mehr 20 Prozent wie heute, sondern sagen wir 80 Prozent Beschwerde erheben, kann ich Ihnen sagen, was passiert. Das Bundesverwaltungsgericht würde von Beschwerden überschwemmt. Das Ziel muss aber sein, die Pendenzen am Bundesverwaltungsgericht zu senken, und nicht, sie zu steigern. Das können wir nicht tun, indem wir das Verfahren verlangsamen. Wir können es nur tun, indem wir beschleunigen. Die unentgeltliche Rechtsvertretung, ich will das klipp und klar sagen, beschleunigt das Verfahren, sie bremst es nicht. Diese Rechtsvertretenden haben keinen Anreiz, das System zu blockieren, weil sie pauschal bezahlt sind und nicht nach Stundensatz wie ein Anwalt üblicherweise.
+Damit komme ich zum zweiten Effekt. Denn auch der zweite Effekt wird klar, wenn man sich ein bisschen in die Statistik vertieft. Interessant wird es nämlich, wenn Sie die verschiedenen Herkunftsländer betrachten. In Fällen, wo die Rechtsvertretung über die unentgeltliche Rechtspflege läuft - das, was der Motionär infrage stellen will -, haben wir eine Beschwerdequote, ich habe es erwähnt, von etwa 20 Prozent. Von hundert Personen, die einen negativen Entscheid haben, führen dann also 20 Prozent Beschwerde. Das ist eigentlich eine recht tiefe Quote, denn es geht für diese Leute um einen für sie extrem einschneidenden Entscheid. Man würde eigentlich erwarten, dass die meisten probieren, eine Beschwerde zu machen. Aber es probieren es nur 20 Prozent. Das bedeutet umgekehrt, dass die Rechtsvertretungen in 80 von 100 Fällen raten, keine Beschwerde zu machen, und dass sie dies erfolgreich tun, denn es wird ja dann auch keine Beschwerde eingereicht. Die Aussichtslosigkeit oder die Prozessaussichten werden also bereits geprüft. Man könnte das Problem lösen, indem man sagt, es gibt einfach keine Beschwerde mehr. Aber dass man überhaupt Beschwerde machen kann, ist ein durch unsere Verfassung geschütztes Recht, und es führt ja gerade dazu, dass das SEM seine Arbeit speditiv machen kann. Sonst würden Sie die Verantwortung noch mehr zum SEM verlagern.
 Jetzt sehen Sie aber eine Auffälligkeit, und es ist wirklich eine Auffälligkeit, wenn Sie die Statistik anschauen. Bei gewissen Herkunftsländern ist es sehr verbreitet, dass nicht die unentgeltliche Rechtsvertretung beigezogen wird, sondern selbst, auf eigene Kosten, ein Anwalt mandatiert wird. Bezahlt wird das häufig aus den Kreisen der Diaspora. Zu beobachten ist dies sehr stark und sehr auffällig bei Menschen mit dem Herkunftsland Türkei. Die Beschwerdequote bei dieser Gruppe beträgt jetzt plötzlich, und das ist die Auffälligkeit, nicht mehr 20 Prozent wie bei den anderen, sondern 65 Prozent. Von 100 Betroffenen führen also nicht 20, sondern 65 Beschwerde. In absoluten Zahlen, ich habe das für 2024 nachgerechnet, führt es dazu, dass ungefähr 1200 Personen mehr Beschwerde führen als bei Personen aus den übrigen Herkunftsländern. Wenn man also diese 65 Prozent bei den Menschen mit dem Herkunftsland Türkei ausrechnet, gibt es 1200 Fälle am Bundesverwaltungsgericht mehr als bei den Menschen aus anderen Herkunftsländern. Ich habe Ihnen die Zahlen zu den Pendenzen am Bundesverwaltungsgericht genannt. Wenn Sie jetzt schauen, wie diese Zahl in Relation zu den Pendenzen steht, im Jahr 2025 waren es um die 2500, dann sehen Sie, dass 1200 Beschwerden recht einschenken.
-Was ist das Fazit? Das Fazit ist: Es führt nicht zu weniger Beschwerden, sondern es führt zu deutlich mehr Beschwerden, wenn Sie die unentgeltliche Rechtsvertretung nicht mehr, sondern weniger stark einschränken. Wahrscheinlich kann man wirklich sagen, dass das zu massiv mehr Beschwerden führt. Das lässt sich aus dem System auch erklären. Denn was würde passieren, wenn wir jetzt eingreifen? Das würde doch dazu führen, dass mehr Menschen einen Anwalt anstellen, da es für sie es um einen einschneidenden Entscheid geht. Das würde wahrscheinlich sogar durch die Diaspora finanziert, wie etwa bei der türkischen Diaspora, oder durch NGO und so weiter. Der Anreiz, keine aussichtslosen Beschwerden zu führen, würde wegfallen. Ehrlich gesagt: Ich habe nichts gegen Anwälte, ich bin selbst einer, aber wenn ein Anwalt den Kostenvorschuss bezahlt bekommt, von wem auch immer, dann wird er diese Beschwerde führen. Dies würde den Pendenzenberg am Bundesverwaltungsgericht anwachsen lassen, die Fälle verzögern, die anderen Fälle mitverzögern und massive Kosten verursachen. Wir reden von Dutzenden von Millionen Franken jährlich, wenn dieser Fall eintreten würde. Und ich sage Ihnen: Dieser Fall kann eintreten. Es ist unklar, wie viele Millionen es genau sind. Meine Schätzung wäre 100 Millionen Franken, aber behaften Sie mich nicht darauf. 
-Wenn Sie am Bundesverwaltungsgericht etwas zur Beschleunigung erreichen wollen, dann müssen Sie dort beschleunigen und nicht mit neuen Auflagen verlangsamen, mit der vermeintlich eingängigen Argumentation, die Schweizer müssten ja auch selber bezahlen. Mit dem EP 27 haben wir sogar Massnahmen getroffen. Diese sind damals aus der Subkommission 4 der Finanzkommission gekommen. Kollege Benedikt Würth, Kollege Benjamin Mühlemann, der gerade nicht hier ist, und ich haben uns mit diesen Zahlen eingehend beschäftigt. Ich will jetzt nicht sagen, dass wir alles gut machen, aber wir haben ein paar Massnahmen gefunden und Ihnen vorgeschlagen. Diese sind dann auch einstimmig durch diesen Rat gegangen. Diese Massnahmen führen wirklich dazu, dass beschleunigt werden kann. 
+Was ist das Fazit? Das Fazit ist: Es führt nicht zu weniger Beschwerden, sondern es führt zu deutlich mehr Beschwerden, wenn Sie die unentgeltliche Rechtsvertretung nicht mehr, sondern weniger stark einschränken. Wahrscheinlich kann man wirklich sagen, dass das zu massiv mehr Beschwerden führt. Das lässt sich aus dem System auch erklären. Denn was würde passieren, wenn wir jetzt eingreifen? Das würde doch dazu führen, dass mehr Menschen einen Anwalt anstellen, da es für sie um einen einschneidenden Entscheid geht. Das würde wahrscheinlich sogar durch die Diaspora finanziert, wie etwa bei der türkischen Diaspora, oder durch NGO und so weiter. Der Anreiz, eine aussichtslose Beschwerde nicht zu führen, würde wegfallen. Ehrlich gesagt: Ich habe nichts gegen Anwälte, ich bin selbst einer, aber wenn ein Anwalt den Kostenvorschuss bezahlt bekommt, von wem auch immer, dann wird er diese Beschwerde führen. Dies würde den Pendenzenberg am Bundesverwaltungsgericht anwachsen lassen, die Fälle verzögern, die anderen Fälle mitverzögern und massive Kosten verursachen. Wir reden von Dutzenden von Millionen Franken jährlich, wenn dies eintreten würde. Und ich sage Ihnen: Dies kann eintreten. Es ist unklar, wie viele Millionen es genau sind. Meine Schätzung wäre 100 Millionen Franken, aber behaften Sie mich nicht darauf. 
+Wenn Sie erreichen wollen, dass es am Bundesverwaltungsgericht zu einer Beschleunigung kommt, dann müssen Sie dort beschleunigen und nicht mit neuen Auflagen verlangsamen, mit der vermeintlich eingängigen Argumentation, die Schweizer müssten ja auch selber bezahlen. Mit dem EP 27 haben wir sogar Massnahmen getroffen. Diese sind damals aus der Subkommission 4 der Finanzkommission gekommen. Kollege Benedikt Würth, Kollege Benjamin Mühlemann, der gerade nicht hier ist, und ich haben uns mit diesen Zahlen eingehend beschäftigt. Ich will jetzt nicht sagen, dass wir alles gut machen, aber wir haben ein paar Massnahmen gefunden und Ihnen vorgeschlagen. Diese sind dann auch einstimmig durch diesen Rat gegangen. Diese Massnahmen führen wirklich dazu, dass beschleunigt werden kann. 
 All das, was ich Ihnen jetzt gesagt habe, hat dazu geführt, dass die Kommission Ihnen mit 10 zu 2 Stimmen, also deutlich, beantragt, diese Motion abzulehnen. 
-Vielleicht fragen Sie sich jetzt, wieso spricht der Mensch so lange, wenn es in der Kommission so klar war? Ich sage Ihnen, weshalb das so ist. Ich weiss, dass im Asylbereich die politische Unzufriedenheit gross ist. Vielleicht braucht es zwischendurch auch ein Zeichen. Aber ich sage Ihnen eines: In diesem Fall würden wir in ein System eingreifen, das nachweislich funktioniert. Wir würden wider besseres Wissen, wider diese Fakten und Zahlen hier eingreifen aus einer Unzufriedenheit und aus dem Gefühl, dass hier eine Ungleichbehandlung vorliegt. Ich bitte Sie, das nicht zu tun. Viele von Ihnen waren früher z. B. in Exekutiven, und Sie wissen, dass man manchmal justieren muss, aber nicht dort, wo es mehr schadet, als nützt. 
+Vielleicht fragen Sie sich jetzt, wieso spricht der Mensch so lange, wenn es in der Kommission so klar war? Ich sage Ihnen, weshalb das so ist. Ich weiss, dass im Asylbereich die politische Unzufriedenheit gross ist. Vielleicht braucht es zwischendurch auch ein Zeichen. Aber ich sage Ihnen eines: In diesem Fall würden wir in ein System eingreifen, das nachweislich funktioniert. Wir würden wider besseres Wissen, wider diese Fakten und Zahlen hier aus einer Unzufriedenheit und aus dem Gefühl, dass hier eine Ungleichbehandlung vorliegt, eingreifen. Ich bitte Sie, das nicht zu tun. Viele von Ihnen waren früher z. B. in Exekutiven, und Sie wissen, dass man manchmal justieren muss, aber nicht dort, wo es mehr schadet, als nützt. 
 Ich bitte Sie, hier dem Muster, gemäss dem die SPK sehr klar entscheidet und sich damit auseinandersetzt und der Rat nachher im Zweifel für Härte stimmt, nicht zu folgen und diese Motion aufgrund der Fakten abzulehnen. Sie ergibt keinen Sinn und ist definitiv ein Eigentor.
 </t>
   </si>
@@ -1437,29 +1443,29 @@
     <t xml:space="preserve">Würth Benedikt</t>
   </si>
   <si>
-    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorher bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorher bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staatsrechnung 2025 festgestellt, dass wir bei den erweiterten Verfahren mittlerweile bei 571 Tagen sind, 571 Tage. Das Ziel mit der Asylreform war ursprünglich 90 Tage; wir überschiessen also um den Faktor 6 und das mit einer ungebrochenen Dynamik. 
-Wenn man einen solchen Befund hat, dann müsste man eigentlich alle Ressourcen in dieses Thema stecken. Wir machen aber umgekehrt eine Strategie, indem wir alles möglichst öffnen, und nicht nur Kantone und Gemeinden einladen, sondern es können logischerweise auch NGO mitmachen. Man geht in die Papiere, die im Netz abrufbar sind und macht eine Grossgruppenveranstaltungen, anstatt dass man die Ressourcen hier, wo es wirklich dringlich und nötig ist, fokussiert. Das verstehe ich einfach nicht mehr. 
-Es ist nicht so, dass man von der Strategie- in die Umsetzungsphase gekommen ist. Umsetzen, was heisst umsetzen? Umsetzen können wir erst dann, wenn wir konkrete Vorlagen auf dem Tisch haben. Ich habe die Motionen, die wir überwiesen haben, nicht gezählt; besten Dank, Kollegin Friedli, offenbar sind es zwanzig. Das heisst doch konkret, dass der Bundesrat eine Vorlage unterbreiten muss, im Grunde genommen eine grössere Teilrevision des Asylgesetzes. Dann rede ich von Umsetzung, aber doch nicht, wenn irgendwie Konzeptpapiere hin- und hergeschoben werden. Dann beginnt die Umsetzung, bei der konkreten Imvollzugsetzung. 
-Darum erstaunt es mich, wenn die SPK sagt, wir seien in einer Umsetzungsphase - Mitnichten, mitnichten! Wenn Sie schauen, wie diese Übung aufgegleist wurde - ich bin etwas kritisch, weil ich die Unterlagen en détail angeschaut habe: Wenn man in Bern eine Strategie startet, wird zuerst einmal ein Büro beauftragt; in diesem Fall ist das Ecoplan; es gibt weitere bekannte. Ecoplan macht einen grossen Bericht. Dann gibt es eine politische Synthese, eine Asylkonferenz - das war in den Jahren 2024, 2025. Im Jahr 2026 wird in verschiedenen Workstreams und Workshops gearbeitet - schön und gut. Im Jahr 2027, so die Medienmitteilung der Asylkonferenz von Ende November 2025, gibt es dann vielleicht, vielleicht auch nicht, eine Vorlage. Bei der Frage der asylsuchenden Kriminaltouristen haben wir beispielsweise überwiesene Motionen verschiedener Herkunft. Auch Kollegin Moser hat einen konkreten Vorschlag überwiesen. Hier wird einerseits gesagt, wir prüfen, andererseits wird gesagt, dass man gesetzliche Grundlagen brauche. Das schafft einfach kein Vertrauen. Ich habe mir überlegt, wann wir in den letzten zwei, drei Jahren überhaupt eine Asylgesetzrevision auf dem Tisch gehabt haben. Wir haben sie im Zusammenhang mit der Umsetzung des EU-Migrationspaktes auf dem Tisch gehabt. Da hätte man eine konkrete Umsetzung machen können. Wenn die Kommissionssprecherin sagt, wir seien in der Umsetzung: Wieso hat man dort nicht konkrete Vorlagen gebracht, die die Vorstösse des Parlamentes umgesetzt hätten? Oder wir haben das EP 27 auf dem Tisch gehabt. Dort hat sogar das Parlament selbst, Kollege Zopfi hat es erwähnt, aus der Finanzkommission heraus das Asylgesetz angepasst, hat für Mehrfachgesuche und Wiedererwägungsgesuche eine Karenzfrist eingebaut. Das können wir als Parlament schon machen, aber ich hätte eigentlich erwartet, dass das der Bundesrat macht, wenn er schon einen konkret überwiesenen Vorstoss hat, der in Richtung Beschleunigung geht, und wenn er schon den Befund sieht, dass wir komplett aus dem Ruder laufen, was die Verfahrensdauern anbelangt.
-Ich meine, so kann man natürlich kein Vertrauen aufbauen, und so muss man sich auch nicht wundern, dass laufend Vorstösse überwiesen werden. Kollegin Z'graggen, die Berichterstatterin, sagte, dass es sein könnte, dass diese Motion die Asylstrategie übersteuere. Ich bin institutionell an einem völlig anderen Ort: Ich muss sagen, die Asylstrategie kann nicht das Parlament übersteuern, denn das Parlament erteilt die Aufträge. Man kann doch nicht sagen, okay, wir machen einen dreijährigen Prozess, die Asylstrategie 2027, und das, was im Parlament läuft, das nehmen wir einfach laufend entgegen und schauen dann, wie und in welchem Rahmen auch immer wir es abarbeiten. So geht das doch nicht. Klar, kann man auch so eine Legislatur absolvieren. So geht es aber eigentlich nicht, das ist nicht mein Verständnis vom Zusammenspiel zwischen Parlament und Regierung.
-Und dann lese ich in diesem Papier zur Asylstrategie 2027 - hören Sie gut zu -, dass jetzt tatsächlich überlegt wird, wie man eine neue Festlegung für den Zielwert im Bereich der erweiterten Verfahren machen könne. Wir haben also den Befund, dass wir die Zielsetzung aus der Asylstrategie 2016 überschiessen, und wir überlegen, wie wir die Verfahren beschleunigen können, aber wir überlegen auch noch, wie wir einen neuen Zielwert setzen können. Das ist falsch angedacht. So kann es meines Erachtens nicht gehen.
-Es wird offensichtlich, wenn man diese Papiere liest - und das bestreite ich ja gar nicht -, dass es Konzepte für ausreichende und rasch aktivierbare Unterbringungsstrukturen für ein abgestimmtes Krisenmanagement, für ein schwankungstaugliches Asylsystem braucht; so weit, so gut. Woran erinnern wir uns? Natürlich an die seinerzeitige Diskussion um die Asylcontainer. Ich kann auch zwischen den Zeilen lesen. Wieso sind die Kantone hier so motiviert? Wahrscheinlich, weil sie nochmals eine Erwartung in diese Richtung haben. Aber der Ständerat hat hier viermal Nein gesagt. Wir müssen beschleunigen und nicht Strukturen und Prozesse und Ressourcen aufbauen. Da liegt die Hauptpriorität, und darum ist diese Motion eben nach wie vor wichtig. Nicht als Zeichen, das möchte ich betonen, es ist nicht eine Zeichensetzung, die wir hier machen, sondern die Motion ist materiell richtig und wichtig, damit uns der Bundesrat nun konkret die Vorlagen bringt, die er eigentlich auch im Zuge der Umsetzung bereits überwiesener Vorstösse unterbreiten müsste.
+    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorhin bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielen Dank für die Darlegung aus der Kommission, das war sehr interessant, ich glaube, für alle Beteiligten. Wir sind uns einig, Beschleunigung ist wichtig, Herr Zopfi hat es vorhin bei der Motion Stark gesagt. Sie können es auch im Geschäftsbericht des Bundesgerichts 2025, den wir heute Morgen gelesen bzw. angehört haben, nachlesen. Auf Seite 75 sehen Sie, wie die Anzahl der Pendenzen bei den Abteilungen IV und V wächst. Konkret haben wir auch in der Finanzkommission im Zusatzbericht zur Staatsrechnung 2025 festgestellt, dass wir bei den erweiterten Verfahren mittlerweile bei 571 Tagen sind, 571 Tage. Das Ziel mit der Asylreform waren ursprünglich 90 Tage; wir überschiessen also um den Faktor 6 - und das mit einer ungebrochenen Dynamik. 
+Wenn man einen solchen Befund hat, dann müsste man eigentlich alle Ressourcen in dieses Thema stecken. Wir machen aber umgekehrt eine Strategie, indem wir alles möglichst öffnen, und nicht nur Kantone und Gemeinden einladen, sondern es können logischerweise auch NGO mitmachen. Man geht in die Papiere, die im Netz abrufbar sind und macht Grossgruppenveranstaltungen, anstatt dass man die Ressourcen hier, wo es wirklich dringlich und nötig ist, fokussiert. Das verstehe ich einfach nicht mehr. 
+Es ist nicht so, dass man von der Strategie- in die Umsetzungsphase gekommen ist. Umsetzen, was heisst umsetzen? Umsetzen können wir erst dann, wenn wir konkrete Vorlagen auf dem Tisch haben. Ich habe die Motionen, die wir überwiesen haben, nicht gezählt; besten Dank, Kollegin Friedli, offenbar sind es zwanzig. Das heisst doch konkret, dass der Bundesrat eine Vorlage unterbreiten muss, im Grunde genommen eine grössere Teilrevision des Asylgesetzes. Dann rede ich von Umsetzung, aber doch nicht, wenn irgendwie Konzeptpapiere hin- und hergeschoben werden. Dann beginnt die Umsetzung, bei der konkreten Invollzugsetzung. 
+Darum erstaunt es mich, wenn die SPK sagt, wir seien in einer Umsetzungsphase. Mitnichten, mitnichten! Wenn Sie schauen, wie diese Übung aufgegleist wurde - ich bin etwas kritisch, weil ich die Unterlagen en détail angeschaut habe: Wenn man in Bern eine Strategie startet, wird zuerst einmal ein Büro beauftragt; in diesem Fall ist das Ecoplan; es gibt weitere bekannte. Ecoplan macht einen grossen Bericht. Dann gibt es eine politische Synthese, eine Asylkonferenz - das war in den Jahren 2024, 2025. Im Jahr 2026 wird in verschiedenen Workstreams und Workshops gearbeitet - schön und gut. Im Jahr 2027, so die Medienmitteilung der Asylkonferenz von Ende November 2025, gibt es dann vielleicht eine Vorlage, vielleicht auch nicht. Bei der Frage der asylsuchenden Kriminaltouristen haben wir beispielsweise überwiesene Motionen verschiedener Herkunft. Auch Kollegin Moser hat einen konkreten Vorschlag überwiesen. Hier wird einerseits gesagt, wir prüfen, andererseits wird gesagt, dass man gesetzliche Grundlagen brauche. Das schafft einfach kein Vertrauen. Ich habe mir überlegt, wann wir in den letzten zwei, drei Jahren überhaupt eine Asylgesetzrevision auf dem Tisch gehabt haben. Wir haben sie im Zusammenhang mit der Umsetzung des EU-Migrationspaktes auf dem Tisch gehabt. Da hätte man eine konkrete Umsetzung machen können. Wenn die Kommissionssprecherin sagt, wir seien in der Umsetzung: Wieso hat man dort nicht konkrete Vorlagen gebracht, die die Vorstösse des Parlamentes umgesetzt hätten? Oder wir haben das EP 27 auf dem Tisch gehabt. Dort hat sogar das Parlament selbst, Kollege Zopfi hat es erwähnt, aus der Finanzkommission heraus das Asylgesetz angepasst, hat für Mehrfachgesuche und Wiedererwägungsgesuche eine Karenzfrist eingebaut. Das können wir als Parlament schon machen, aber ich hätte eigentlich erwartet, dass das der Bundesrat macht, wenn er schon einen konkret überwiesenen Vorstoss hat, der in Richtung Beschleunigung geht, und wenn er schon den Befund sieht, dass wir komplett aus dem Ruder laufen, was die Verfahrensdauern anbelangt.
+Ich meine, so kann man natürlich kein Vertrauen aufbauen, und so muss man sich auch nicht wundern, dass laufend Vorstösse überwiesen werden. Kollegin Z'graggen, die Berichterstatterin, sagte, dass es sein könnte, dass diese Motion die Asylstrategie übersteuere. Ich bin institutionell an einem völlig anderen Ort: Ich muss sagen, die Asylstrategie kann nicht das Parlament übersteuern, denn das Parlament erteilt die Aufträge. Man kann doch nicht sagen, okay, wir machen einen dreijährigen Prozess, die Asylstrategie 2027, und das, was im Parlament läuft, das nehmen wir einfach laufend entgegen und schauen dann, wie und in welchem Rahmen auch immer wir es abarbeiten. So geht das doch nicht. Eine Legislatur kann man natürlich auch so absolvieren. So geht es aber eigentlich nicht, das ist nicht mein Verständnis vom Zusammenspiel zwischen Parlament und Regierung.
+Und dann lese ich in diesem Papier zur Asylstrategie 2027 - hören Sie gut zu -, dass tatsächlich darüber nachgedacht wird, einen neuen Zielwert im Bereich der erweiterten Verfahren festzulegen. Wir haben also den Befund, dass wir die Zielsetzung aus der Asylstrategie 2016 überschiessen, und wir überlegen, wie wir die Verfahren beschleunigen können, aber wir überlegen auch noch, wie wir einen neuen Zielwert setzen können. Das ist falsch angedacht. So kann es meines Erachtens nicht gehen.
+Es wird offensichtlich, wenn man diese Papiere liest - und das bestreite ich ja gar nicht -, dass es Konzepte für ausreichende und rasch aktivierbare Unterbringungsstrukturen, für ein abgestimmtes Krisenmanagement sowie für ein schwankungstaugliches Asylsystem braucht; so weit, so gut. Woran erinnern wir uns? Natürlich an die seinerzeitige Diskussion um die Asylcontainer. Ich kann auch zwischen den Zeilen lesen. Wieso sind die Kantone hier so motiviert? Wahrscheinlich, weil sie nochmals eine Erwartung in diese Richtung haben. Aber der Ständerat hat hier viermal Nein gesagt. Wir müssen beschleunigen und nicht Strukturen und Prozesse und Ressourcen aufbauen. Da liegt die Hauptpriorität, und darum ist diese Motion eben nach wie vor wichtig; nicht als Zeichen, das möchte ich betonen, es ist nicht eine Zeichensetzung, die wir hier machen, sondern die Motion ist materiell richtig und wichtig, damit uns der Bundesrat nun konkret die Vorlagen bringt, die er eigentlich auch im Zuge der Umsetzung bereits überwiesener Vorstösse unterbreiten müsste.
 Das sind meine Überlegungen, wieso diese Motion nach wie vor richtig und wichtig ist, wieso sie nach wie vor aktuell ist und wieso ich mit dieser Motion auch klar die Erwartung verbinde, Herr Bundesrat, dass man zur Umsetzung der überwiesenen Vorstösse nun endlich eine grössere Teilrevision des Asylgesetzes bringt. Unser Parlament kann letztlich nur Recht setzen, wenn wir eine Vorlage auf dem Tisch haben - mit Motionen erteilen wir nur Aufträge, aber Rechtsetzung passiert dann, wenn wir eine Vorlage haben. Und hier haben wir keine Vorlage, das ist doch das Problem, ausser eben im Zusammenhang mit dem EP 27 und dem EU-Migrations- und Asylpakt.
-In diesem Sinne bin ich dezidiert der Auffassung, dass die Motion nach wie vor richtig und wichtig ist. Die Kantone, Gemeinden und der Bund können weiterhin gut zusammenarbeiten. Aber einfach eine Strategie vorzuschieben und gleichzeitig die Bearbeitung und Umsetzung von Vorstössen auf die lange Bank zu schieben, das möchte ich persönlich, das muss ich klar sagen, nicht mehr akzeptieren.
+In diesem Sinne bin ich dezidiert der Auffassung, dass die Motion nach wie vor richtig und wichtig ist. Die Kantone, die Gemeinden und der Bund können weiterhin gut zusammenarbeiten. Aber einfach eine Strategie vorzuschieben und gleichzeitig die Bearbeitung und Umsetzung von Vorstössen auf die lange Bank zu schieben, das möchte ich persönlich, das muss ich klar sagen, nicht mehr akzeptieren.
 </t>
   </si>
   <si>
     <t xml:space="preserve">377598</t>
   </si>
   <si>
-    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen haben Sie im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Was Sie aber nicht können, ist in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Von dem her finde ich die Frage, die aufgew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen haben Sie im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Was Sie aber nicht können, ist in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Von dem her finde ich die Frage, die aufgeworfen wird, im Sinne der Zuständigkeit, der Rechtssicherheit und der Weiterentwicklung in diesem Gebiet durchaus interessant. 
-Ich sehe aber auch Punkte, die sehr genau geprüft werden müssen. Einerseits, was würde das für die Verfahrensbelastung oder für die Belastung, die Pendenzen am Bundesverwaltungsgericht bedeuten? Wir haben uns schon bei zwei Traktanden darüber unterhalten. Was würde das staatsorganisatorisch bedeuten? Hätten die Kantone plötzlich eine Aufsicht über eine Bundesbehörde - dieses Problem spricht der Bundesrat an - und letztlich, welcher Qualitätsgewinn oder Erkenntnisgewinn wäre daraus zu erwarten? In diesem Sinn scheint es mir angezeigt, dass sich die Kommission damit befasst, auch prüft, ob es allenfalls Alternativen gäbe, um das, was der Motionär will, zu gewährleisten. Ich bin deshalb der Ansicht, dass die Kommission sich hier vertiefen soll, habe dies auch mit dem Motionär abgesprochen und gehe davon aus, dass er sich damit einverstanden erklären kann.
+    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen gibt es im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Es ist aber nicht möglich, in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Insofern finde ich die aufgeworfene Frage zur Zus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Motionär wirft ein Thema auf, das durchaus interessant ist. Im Gegensatz zu anderen Fällen gibt es im Asylbeschwerdeverfahren tatsächlich nur die Möglichkeit, negative Entscheide des SEM zu überprüfen, weil die betroffenen Personen Beschwerde führen. Wir haben uns vorher eingehend darüber unterhalten. Es ist aber nicht möglich, in positiven Fällen, die von den Kantonen vielleicht hinterfragt werden, eine gerichtliche Überprüfung zu erreichen. Insofern finde ich die aufgeworfene Frage zur Zuständigkeit, zur Rechtssicherheit und zur Weiterentwicklung in diesem Gebiet durchaus interessant. 
+Ich sehe aber auch Punkte, die sehr genau geprüft werden müssen. Einerseits, was würde das für die Belastung und die Pendenzen am Bundesverwaltungsgericht bedeuten? Wir haben uns schon bei zwei Traktanden darüber unterhalten. Was würde das staatsorganisatorisch bedeuten? Hätten die Kantone plötzlich eine Aufsicht über eine Bundesbehörde? Der Bundesrat spricht ja dieses Problem an. Und letztlich: Welcher Qualitäts- oder Erkenntnisgewinn wäre daraus zu erwarten? In diesem Sinn scheint es mir angezeigt, dass sich die Kommission damit befasst, auch prüft, ob es allenfalls Alternativen gäbe, um das, was der Motionär will, zu gewährleisten. Ich bin deshalb der Ansicht, dass die Kommission sich hier vertiefen soll, habe dies auch mit dem Motionär abgesprochen und gehe davon aus, dass er sich damit einverstanden erklären kann.
 </t>
   </si>
   <si>
@@ -1477,11 +1483,11 @@
   <si>
     <t xml:space="preserve">Ich danke dem Bundesrat für seine Antwort, auch wenn ich feststelle, dass er sich - wie allzu oft, wenn es um Rückführungen geht - auf das absolute Minimum beschränkt. Die Suche nach funktionierenden Lösungen scheint vom EJPD mittlerweile als unverhältnismässiger Aufwand angesehen zu werden. Der einfachste Weg besteht offenbar darin, die bisherige Praxis fortzusetzen und Asylsuchende in der Schweiz zu behalten, die eigentlich nicht in die Zuständigkeit unseres Landes fallen. Von innovativen Ideen habe ich keine Spur gefunden.
 Herr Bundesrat, Sie liessen sich zum Amtsantritt prominent mit der Aussage zitieren, wer denke, linke Politik heisse Wegschauen von Problemen, irre sich. Ich muss Ihnen ganz offen sagen, dass ich diese Aussage mit Ihrer Stellungnahme zu diesem Vorstoss nicht in Einklang bringen kann.
-Die Umsetzung der Punkte 1 und 2 fordert vor allem guten Willen und eine gewisse Aufgeschlossenheit. Diese beiden Punkte beinhalten keinerlei Ergebnisverpflichtung. Sie zielen lediglich darauf ab, Verhandlungen mit Italien aufzunehmen. Ich bin nicht naiv und bin mir bewusst, dass diese Gespräche komplex werden und möglicherweise sogar scheitern können. Wenn wir es aber gar nicht erst versuchen, wird genau gar nichts passieren. Und das geht dann halt schon in Richtung Wegschauen von Problemen.
-Der Bundesrat erklärt lieber, warum Schritte scheitern könnten, anstatt sie zu unternehmen. Diese Haltung bedauere ich, zumal ich durchaus der Absicht bin, dass Italien ein Interesse an einer Zusammenarbeit mit der Schweiz hat, insbesondere, wenn diese eine finanzielle Unterstützung für seine Zentren in Albanien beinhaltet. Im Rahmen der Anwendung der Dublin-Verordnung kann Italien genau festlegen, wohin die Dublin-Fälle, für die es zuständig ist, zurückgeschickt werden sollen. Das kann Rom, Mailand oder ein anderer Ort sein. Grundsätzlich ist es also möglich, dass Italien die Schweiz bittet, bestimmte Fälle an Zentren in Albanien zurückzuschicken. Angesichts der engen Beziehung zwischen den Staaten könnte Italien sogar eine Anpassung des mit Albanien abgeschlossenen Abkommens in Betracht ziehen.
+Die Umsetzung der Punkte 1 und 2 fordert vor allem guten Willen und eine gewisse Aufgeschlossenheit. Diese beiden Punkte beinhalten keinerlei Ergebnisverpflichtung. Sie zielen lediglich darauf ab, Verhandlungen mit Italien aufzunehmen. Ich bin mir bewusst und nicht naiv, dass diese Gespräche komplex werden und möglicherweise sogar scheitern können. Wenn wir es aber gar nicht erst versuchen, wird genau gar nichts passieren. Und das geht dann halt schon in Richtung Wegschauen von Problemen.
+Der Bundesrat erklärt lieber, warum Schritte scheitern könnten, anstatt sie zu unternehmen. Diese Haltung bedauere ich, zumal ich durchaus der Ansicht bin, dass Italien ein Interesse an einer Zusammenarbeit mit der Schweiz hat, insbesondere, wenn diese eine finanzielle Unterstützung für seine Zentren in Albanien beinhaltet. Im Rahmen der Anwendung der Dublin-Verordnung kann Italien genau festlegen, wohin die Dublin-Fälle, für die es zuständig ist, zurückgeschickt werden sollen. Das kann Rom, Mailand oder ein anderer Ort sein. Grundsätzlich ist es also möglich, dass Italien die Schweiz bittet, bestimmte Fälle an Zentren in Albanien zurückzuschicken. Angesichts der engen Beziehung zwischen den Staaten könnte Italien sogar eine Anpassung des mit Albanien abgeschlossenen Abkommens in Betracht ziehen.
 Was Punkt 3 betrifft: Wenn ich die Antwort richtig interpretiere, schliesst der Bundesrat aufgrund einer Auslegeordnung im Rahmen des in der Antwort erwähnten Postulates Caroni aus, dass ein solches Modell mit einer Rückkehr das Schweizer System entlasten könnte.
 Jüngst wurde zwischen dem Rat der Europäischen Union und dem Europäischen Parlament eine Einigung über eine neue EU-Verordnung zur Weiterentwicklung der Rückführungsrichtlinie erzielt, die unter anderem die Schaffung von Rückführungszentren in Drittstaaten vorsieht. Herr Bundesrat, wie gedenken Sie, gestützt darauf die künftige Zusammenarbeit der Schweiz in diesem Bereich konkret auszugestalten? Und an welche Drittstaaten könnte sich die Schweiz bereits wenden?
-Es ist nun die Aufgabe des Parlaments, den Bundesrat dazu anzuhalten, Gespräche mit Italien aufzunehmen und die Möglichkeit einer Zusammenarbeit mit Rom konkret zu prüfen. Auch hier besteht keine Verpflichtung, ein bestimmtes Ergebnis zu erzielen, sondern lediglich die Verpflichtung, Gespräche mit Italien aufzunehmen, um dessen Interesse an einer Zusammenarbeit mit der Schweiz im Bereich der Rückführung auszuloten. Aus all diesen Gründen bitte ich Sie, diese Motion anzunehmen.
+Es ist nun die Aufgabe des Parlamentes, den Bundesrat dazu anzuhalten, Gespräche mit Italien aufzunehmen und die Möglichkeit einer Zusammenarbeit mit Rom konkret zu prüfen. Auch hier besteht keine Verpflichtung, ein bestimmtes Ergebnis zu erzielen, sondern lediglich die Verpflichtung, Gespräche mit Italien aufzunehmen, um dessen Interesse an einer Zusammenarbeit mit der Schweiz im Bereich der Rückführung auszuloten. Aus all diesen Gründen bitte ich Sie, diese Motion anzunehmen.
 Herr Bundesrat, ich gebe es offen zu, ich beneide Sie nicht. Die letzten Wochen und Monate haben deutlich gezeigt, welche Sorgen die Menschen in unserem Land haben. Die Bevölkerung spricht über Migration, über Asyl, über Sicherheit und über die Frage, ob unser Staat die Situation noch unter Kontrolle hat. Gerade deshalb erstaunt mich die Haltung Ihres Departements. Bei der Überarbeitung der Lex Koller geht alles sehr schnell. Dafür werden in kürzester Zeit Berichte erstellt, Varianten geprüft und Gesetzesänderungen vorbereitet. Wenn es aber um Rückführungen von Personen geht, die kein Bleiberecht in der Schweiz haben, höre ich immer wieder, weshalb etwas nicht möglich sein soll. Ich spreche hier nicht von Flüchtlingen.
 Was mich zunehmend stört: Wir sprechen ständig über Strategien, Konzepte und auch über Prüfaufträge. Die Bevölkerung erwartet etwas anderes. Sie erwartet Resultate, sie erwartet Taten, und sie erwartet Lösungen. Niemand verlangt Wunder, niemand verlangt, dass jede Verhandlung erfolgreich endet. Aber die Menschen dürfen erwarten, dass der Bundesrat aktiv Möglichkeiten auslotet, Partner sucht und neue Wege prüft, anstatt bereits zu Beginn zu erklären, weshalb etwas nicht funktionieren könnte. Genau das verlangt diese Motion, nicht mehr und nicht weniger. Sie verpflichtet den Bundesrat nicht zu einem bestimmten Ergebnis, sie verpflichtet ihn lediglich dazu, aktiv zu werden. Genau deshalb bitte ich Sie, die Motion zu unterstützen.
 </t>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1592,6 +1592,85 @@
 Verschiedene - Divers ... 3
 [VS]
 Le président (Page Pierre-André, président): J'adresse toutes mes félicitations à M. Attenhofer, Mme Hostettler et M. Theubet pour leur élection et leur souhaite plein succès dans l'exercice de leur nouvelle fonction. (Standing ovation)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badertscher Christine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ihre Aussenpolitische Kommission hat an ihrer Sitzung vom 23. März 2026 den Aussenpolitischen Bericht 2025 ausführlich beraten und anschliessend zur Kenntnis genommen. Die Kommission war sich in ihrer Beurteilung einig, dass der Bericht sehr interessant ist und einen umfassenden Überblick über das vielfältige, breit abgestützte und wichtige Engagement der Schweiz in der Welt vermittelt. Besonders positiv hob sie das gewählte Schwerpunktthema des Multilateralismus hervor. Die Kommissionsmitgliede</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ihre Aussenpolitische Kommission hat an ihrer Sitzung vom 23. März 2026 den Aussenpolitischen Bericht 2025 ausführlich beraten und anschliessend zur Kenntnis genommen. Die Kommission war sich in ihrer Beurteilung einig, dass der Bericht sehr interessant ist und einen umfassenden Überblick über das vielfältige, breit abgestützte und wichtige Engagement der Schweiz in der Welt vermittelt. Besonders positiv hob sie das gewählte Schwerpunktthema des Multilateralismus hervor. Die Kommissionsmitglieder beurteilten die historische Einordnung als aufschlussreich und spannend.
+Einigkeit bestand darin, dass der Multilateralismus heute vor grossen Herausforderungen steht, für die Schweiz jedoch von zentraler Bedeutung bleibt. Umso erstaunter zeigten sich einige Kommissionsmitglieder über gewisse Aussagen in diesem Kapitel. So spricht der Bericht von einer Erosion des innenpolitischen Rückhaltes für multilaterale Mitwirkung. Als Beispiele nennt er den UNO-Migrationspakt sowie das Urteil des Europäischen Gerichtshofes für Menschenrechte im Fall der Klimaseniorinnen. Zwar handelt es sich bei beiden Beispielen zweifellos um kontroverse und in der Schweiz intensiv diskutierte Themen. Aus Sicht einzelner Kommissionsmitglieder stellen sie jedoch Ausnahmen dar und sind deshalb nicht repräsentativ für die generelle Haltung der Schweizer Bevölkerung gegenüber multilateralen Institutionen und Entscheiden. Aus diesen beiden Fällen lässt sich ihrer Auffassung nach nicht der Schluss ziehen, dass die multilaterale Zusammenarbeit in der Schweiz grundsätzlich auf Ablehnung stösst. Zudem sollte die Diskussion nicht ausschliesslich auf die unmittelbare Nützlichkeit oder die Effizienz fokussieren.
+Multilateralismus ist seinem Wesen nach selten effizient. Sein Wert liegt vielmehr darin, Staaten und Akteure an einen Tisch zu bringen und den Dialog auch bei weit auseinanderliegenden Positionen aufrechtzuerhalten. Gerade die Friedensgespräche in Genf zeigen, dass nachhaltige Lösungen oft erst durch langwierige Verhandlungen und gegenseitiges Zuhören entstehen. Auch wenn der Multilateralismus derzeit unter Druck steht und machtpolitische Tendenzen vielerorts zunehmen, bietet er kleinen Staaten einen wichtigen Schutz gegenüber den Interessen der Stärkeren. Für ein Land wie die Schweiz mit begrenzter geopolitischer Macht kommt einer funktionierenden multilateralen Ordnung deshalb besondere Bedeutung zu, da sie Einflussnahme ermöglicht, verlässliche Rahmenbedingungen schafft und die internationale Zusammenarbeit stärkt.
+Dabei kommt auch dem internationalen Genf eine herausragende Rolle zu. Mit dem Sitz des Internationalen Komitees vom Roten Kreuz sowie zahlreicher internationaler Organisationen und Foren ist Genf ein zentraler Ort des multilateralen Dialoges. Diese Rolle ist nicht nur politisch und diplomatisch wichtig, sondern hat auch erhebliche volkswirtschaftliche Bedeutung für die Schweiz. Vor diesem Hintergrund erscheint es aus Sicht einzelner Kommissionsmitglieder bedauerlich, wenn nicht gar riskant, den Multilateralismus ohne zwingenden Grund infrage zu stellen oder seine Bedeutung zu relativieren. Gerade in einer Zeit zunehmender internationaler Spannungen ist es wichtig, dass die Schweiz am Multilateralismus festhält, sich aktiv für dessen Weiterentwicklung einsetzt und dessen Stärken klar hervorhebt. Allerdings wurden in der Kommission auch andere Stimmen laut, die die Auffassung vertraten, dass der Multilateralismus in seiner heutigen Form kein geeignetes Instrument mehr sei, um die drängenden globalen Herausforderungen wirksam zu lösen.
+Entsprechend wurden auch kritische Fragen zur zukünftigen Ausrichtung der Schweizer Aussenpolitik gestellt.
+Ebenfalls thematisiert wurde die Behandlung des afrikanischen Kontinentes im Bericht. Mehrere Kommissionsmitglieder vertraten die Ansicht, dass Afrika etwas zu kurz komme. Dabei handelt es sich um einen Kontinent, dessen Bedeutung für die Zukunft stetig zunimmt, sei es im Bereich der globalen Ernährungssicherheit, der wirtschaftlichen Entwicklung, des Bevölkerungswachstums oder der Migration. Aus Sicht der Kommission dürfte stärker sichtbar gemacht werden, dass sich die Schweiz weiterhin engagiert und die Zusammenarbeit mit den afrikanischen Ländern vertieft.
+Positiv hervorgehoben wurde hingegen, dass die Agenda 2030 in der Schweizer Aussenpolitik einen wichtigen Stellenwert einnimmt und dass sich die Schweiz bereits heute aktiv mit den Arbeiten an einer möglichen Folgeagenda post 2030 auseinandersetzt.
+Von grosser Bedeutung bleibt zudem das Engagement der Schweiz in den Bereichen Frieden und Sicherheit. Die entsprechenden Aktivitäten unseres Landes werden von der Kommission als wertvoll und wirkungsvoll beurteilt. Auch die nachhaltige Entwicklung im Rahmen der internationalen Zusammenarbeit wurde ausdrücklich gewürdigt. Das positive Zeugnis, das die OECD der Schweiz ausstellt, zeigt, dass unser Land auf diesem Gebiet einen wichtigen und anerkannten Beitrag leistet.
+Kritisch angemerkt wurde allerdings, dass das Thema Sicherheit im Bericht insgesamt etwas zu wenig Raum erhält. Sicherheit ist heute eng mit der Aussenpolitik verknüpft und sollte deshalb stärker als Querschnittthema verstanden und auch behandelt werden.
+Der Aussenpolitische Bericht macht zudem deutlich, dass gute und stabile Beziehungen zur Europäischen Union für die Schweiz von grosser Bedeutung bleiben. Die Kommission nimmt zur Kenntnis, dass das EDA bereit ist, sich weiterhin mit Nachdruck für diese Beziehungen einzusetzen.
+Zusammenfassend hat Ihre Aussenpolitische Kommission den Bericht als interessant und aufschlussreich beurteilt. Sie dankt den Mitarbeitenden des Eidgenössischen Departements für auswärtige Angelegenheiten für ihre engagierte und umfangreiche Arbeit. In einer Zeit zahlreicher internationaler Krisen, Unsicherheiten und geopolitischer Umbrüche leisten sie einen wichtigen und wertvollen Beitrag zur Wahrung der Interessen unseres Landes.
+Im Namen der Kommission bitte ich Sie deshalb, vom Aussenpolitischen Bericht 2025 Kenntnis zu nehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calame Didier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au nom de la Commission de politique extérieure du Conseil national, j'ai l'honneur de vous présenter le rapport de commission relatif à l'objet 26.009, le rapport sur la politique extérieure 2025. La commission a examiné ce rapport lors de sa séance consacrée à l'évaluation des activités de politique extérieure du Conseil fédéral durant l'année 2025. Elle a pris connaissance avec intérêt de l'analyse présentée ainsi que des principales orientations suivies par le Conseil fédéral dans un context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au nom de la Commission de politique extérieure du Conseil national, j'ai l'honneur de vous présenter le rapport de commission relatif à l'objet 26.009, le rapport sur la politique extérieure 2025. La commission a examiné ce rapport lors de sa séance consacrée à l'évaluation des activités de politique extérieure du Conseil fédéral durant l'année 2025. Elle a pris connaissance avec intérêt de l'analyse présentée ainsi que des principales orientations suivies par le Conseil fédéral dans un contexte international toujours marqué par de nombreuses incertitudes géopolitiques. Le rapport met en évidence les défis auxquels la Suisse est confrontée dans un environnement international en profonde mutation. Les conflits armés, les tensions entre grandes puissances, les questions liées à la sécurité européenne, aux migrations, au climat et aux transformations technologiques continuent d'influencer fortement l'action extérieure de notre pays.
+La commission a notamment examiné la mise en oeuvre de la stratégie de politique extérieure 2024-2027. Elle a relevé les efforts déployés par le Conseil fédéral pour défendre les intérêts de la Suisse tout en préservant les valeurs qui fondent traditionnellement son action extérieure, en particulier le respect du droit international, la promotion de la paix, le dialogue et la coopération internationale. La commission a également porté une attention particulière à l'engagement de la Suisse en faveur du multilatéralisme. Dans un contexte où les institutions internationales sont soumises à des pressions croissantes, la Suisse continue d'oeuvrer en faveur d'un ordre international fondé sur des règles et de promouvoir des solutions concertées aux défis mondiaux.
+Les activités de bons offices et de promotion de la paix ont également été abordées. La commission constate que la Suisse demeure un acteur reconnu dans ces domaines et qu'elle continue de mettre à disposition son expertise et sa crédibilité pour soutenir les processus de dialogue et de médiation.
+S'agissant des relations avec les principaux partenaires de la Suisse, la commission a pris note des développements intervenus au cours de l'année écoulée, notamment dans les relations avec l'Union européenne, les États partenaires et les organisations internationales. Elle souligne l'importance de maintenir des relations stables et prévisibles afin de préserver les intérêts politiques, économiques et sécuritaires de notre pays.
+Au cours de ces délibérations, la commission a eu l'occasion d'échanger avec les représentants du Département fédéral des affaires étrangères et d'approfondir plusieurs aspects du rapport. Ces discussions ont permis de clarifier les priorités retenues par le Conseil fédéral et les défis auxquels la politique extérieure suisse devra faire face dans les prochaines années.
+Au terme de son examen, la Commission de politique extérieure du Conseil national estime que le rapport présente de manière complète et transparente les activités de politique extérieure de la Confédération durant l'année 2025. La commission vous propose dès lors de prendre acte du rapport sur la politique extérieure 2025.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat unterbreitet Ihnen heute einen Verpflichtungskredit in der Höhe von 66,1 Millionen Franken für den Zeitraum 2026 bis 2032 zur Unterstützung der digitalen und organisatorischen Transformation der Zentralen Ausgleichsstelle (ZAS) in Genf. Diese Reform ist eine strategische Investition in die Zukunft der Schweizer Sozialversicherung. Sie ermöglicht der ZAS, ihre wesentlichen Aufgaben nachhaltig zu erfüllen, nämlich die Auszahlung von AHV- und IV-Renten ins Ausland, die Abwicklung des </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat unterbreitet Ihnen heute einen Verpflichtungskredit in der Höhe von 66,1 Millionen Franken für den Zeitraum 2026 bis 2032 zur Unterstützung der digitalen und organisatorischen Transformation der Zentralen Ausgleichsstelle (ZAS) in Genf. Diese Reform ist eine strategische Investition in die Zukunft der Schweizer Sozialversicherung. Sie ermöglicht der ZAS, ihre wesentlichen Aufgaben nachhaltig zu erfüllen, nämlich die Auszahlung von AHV- und IV-Renten ins Ausland, die Abwicklung des Zahlungsverkehrs mit den Ausgleichskassen, die Führung der Zentralregister sowie die Gewährleistung der Datenzuverlässigkeit für das gesamte Sozialversicherungssystem.
+Heute steht die ZAS vor mehreren Herausforderungen: veraltete IT-Systeme, zunehmende Komplexität infolge von Gesetzesreformen, ein kontinuierlicher Anstieg der Zahl der Leistungsempfänger sowie die Pensionierung eines hohen Anteiles des Personals. Das Programm zur digitalen Transformation zielt darauf ab, die Organisation und die Technologien der ZAS zu modernisieren. Es gliedert sich in vier Schwerpunkte:
+1. Neugestaltung der Geschäftsprozesse und der Organisation für einfache, kohärente und digitalisierte Dienstleistungen;
+2. Modernisierung der IT-Infrastruktur auf der Grundlage einer modularen Architektur, die den Standards der Bundesverwaltung entspricht;
+3. Automatisierung und integrierte Datenverwaltung, die Sicherheit und Effizienz gewährleisten;
+4. Begleitung des Wandels zur Sicherstellung der Beteiligung des Personals und des Kompetenztransfers.
+Dieses Programm ermöglicht es, das Wachstum des Leistungsvolumens ohne Personalaufstockung zu bewältigen und gleichzeitig Sicherheit, Zuverlässigkeit und Transparenz zu erhöhen. Es trägt zudem zur Strategie des Bundes zur Digitalisierung der Verwaltung und zur Nutzung einer souveränen IT-Infrastruktur des Bundes bei.
+Der Verpflichtungskredit deckt die Planung, Umsetzung und Konsolidierung des Programmes bis 2032 ab. Er stellt eine Zukunftsinvestition dar, die notwendig ist, um die Kontinuität und Leistungsfähigkeit der ersten Säule zu gewährleisten.
+Die ZAS ist das operative Rückgrat der ersten Säule. Sie betreibt zentrale Register, verwaltet die Finanzflüsse und zahlt weltweit über eine Million Renten aus. Ihre Systeme sind jedoch technisch veraltet und stark fragmentiert. Um die Leistungsfähigkeit und Datensicherheit langfristig zu gewährleisten, braucht es eben eine tiefgreifende Modernisierung.
+Das Transformationsprogramm PDIT besteht aus rund zwanzig Projekten und verläuft in drei Phasen von 2025 bis 2032. Es schafft die Grundlage für eine einheitliche, sichere und effiziente Daten- und Prozesslandschaft. Durch Automatisierung und Standardisierung kann die ZAS steigende Rentenvolumina ohne zusätzliches Personal bewältigen und gesetzliche Anpassungen künftig schneller umsetzen. Der beantragte Verpflichtungskredit deckt die Projektkosten für Entwicklung, Integration, Migration sowie das Change Management ab. Die Investition stärkt die digitale Handlungsfähigkeit der ZAS und trägt zur Modernisierung der Bundesverwaltung bei.
+Der Bundesrat bittet Sie, auf das Geschäft einzutreten und den Verpflichtungskredit zu bewilligen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich wäre froh, wenn die Finanzministerin bei diesem Geschäft Transparenz schaffen könnte, also aufzeigen könnte, was Subventionen sind. In der Studie des Luzerner Forschungsinstituts wird ein Subventionsvolumen von 48,6 Milliarden Franken genannt. Zuoberst auf der Liste steht die AHV. Hier wäre ich schon am Namen des Erstempfängers interessiert. Ich habe irgendwie das Gefühl, dass hier wie Kraut und Rüben alles durcheinander aufgelistet wird. 
+Wenn wir im Alltag von Subventionen reden, denken wi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich wäre froh, wenn die Finanzministerin bei diesem Geschäft Transparenz schaffen könnte, also aufzeigen könnte, was Subventionen sind. In der Studie des Luzerner Forschungsinstituts wird ein Subventionsvolumen von 48,6 Milliarden Franken genannt. Zuoberst auf der Liste steht die AHV. Hier wäre ich schon am Namen des Erstempfängers interessiert. Ich habe irgendwie das Gefühl, dass hier wie Kraut und Rüben alles durcheinander aufgelistet wird. 
+Wenn wir im Alltag von Subventionen reden, denken wir irgendwie an freiwillige Beiträge. Das ist es aber nicht, das sieht man schon, wenn man die Liste anschaut. Jetzt macht auch der Motionär eine Liste, und dabei ist mir etwas aufgefallen: Er listet zum Beispiel 18,9 Millionen Franken an Caritas für den Verfahrensaufwand für Asylsuchende auf. Das ist eine Abgeltung. Bei den Subventionen gibt es Abgeltungen und Finanzhilfen, die sich bezüglich rechtlicher Grundlage stark unterscheiden. Abgeltungen sind bundesrechtlich vorgeschriebene Aufgaben oder öffentlich-rechtliche Aufgaben mit einer Gesetzesgrundlage. Der Bund hat den Auftrag, diese Aufgaben zu erfüllen, und kann sie auch an private Organisationen delegieren.
+Worum geht es eigentlich überhaupt? Ist das ein sinnvolles Vorgehen, das der Motionär hier fordert? Ist es überhaupt umsetzbar? Welche Art von Transparenz ist hier notwendig? Ist die AHV wirklich eine Subvention?
+Ich wäre hier froh um Antworten. Sie merken es, ich stehe dem Anliegen kritisch gegenüber und kann mir nicht vorstellen, dass ich am Schluss aller Ausführungen der Motion zustimmen werde.
 </t>
   </si>
 </sst>
@@ -1640,8 +1719,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I75" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I79" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I79"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -4080,6 +4159,120 @@
         <v>313</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>314</v>
+      </c>
+      <c r="B76" t="s">
+        <v>315</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>316</v>
+      </c>
+      <c r="E76" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" t="s">
+        <v>39</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>317</v>
+      </c>
+      <c r="I76" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>319</v>
+      </c>
+      <c r="B77" t="s">
+        <v>315</v>
+      </c>
+      <c r="C77" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" t="s">
+        <v>320</v>
+      </c>
+      <c r="E77" t="s">
+        <v>38</v>
+      </c>
+      <c r="F77" t="s">
+        <v>156</v>
+      </c>
+      <c r="G77" t="s">
+        <v>27</v>
+      </c>
+      <c r="H77" t="s">
+        <v>321</v>
+      </c>
+      <c r="I77" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>323</v>
+      </c>
+      <c r="B78" t="s">
+        <v>315</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78"/>
+      <c r="F78" t="s">
+        <v>44</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>324</v>
+      </c>
+      <c r="I78" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>326</v>
+      </c>
+      <c r="B79" t="s">
+        <v>315</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>145</v>
+      </c>
+      <c r="E79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>327</v>
+      </c>
+      <c r="I79" t="s">
+        <v>328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -221,9 +221,9 @@
     <t xml:space="preserve">Die SVP-Fraktion tritt auf diese Revision ein, jedoch mit zahlreichen Vorbehalten und nicht ohne sehr kritische Anmerkungen. Mit dem Leistungskatalog des heutigen Opferhilfegesetzes sind wir grundsätzlich einverstanden. Die Schweiz hat ein gut organisiertes Netz aus Anlaufstellen, die dem Opfer und seinen Angehörigen umfassende Dienstleistungen bieten. Das darf an dieser Stelle gesagt werden. Wir müssen uns nichts vorwerfen lassen. Die SVP-Fraktion steht hinter den Leistungen der Opferhilfe und ortet keine grossen Lücken im Gesetz.
 Mit dieser Revision wird der Leistungskatalog um die rechtsmedizinische Hilfe ergänzt. Opfer sollen sich in der ganzen Schweiz an eine Stelle wenden können, die spezialisierte medizinische und rechtsmedizinische Leistungen erbringt und die entsprechenden Spuren sichert. Einige Kantone verfügen bereits über diese Angebote, neu soll der Zugang zu solchen Leistungen allen Opfern offenstehen. Jedes Verbrechen sollte möglichst auch der Justiz zugeführt werden. Dies gilt umso mehr, als es sich bei den hier behandelten Delikten um schwere Straftaten handelt und das Wiederholungsrisiko bei Sexualdelikten und Gewalt im häuslichen Bereich gross ist. Auch ist diesbezüglich zu hoffen, dass sich mehr Opfer für den Gang zu Polizei und Staatsanwaltschaft entscheiden.
 Wie sich diese Rechtsdokumentation in der Praxis bewährt, wird sich weisen. Zu hoffen ist einerseits auf offensichtlichere Beweislagen und vereinfachte Gerichtsverfahren, auf der anderen Seite aber auch auf schnellere Erledigungen bei ungerechtfertigten Beschuldigungen. Bei den meisten Vergewaltigungen handelt es sich um Vieraugendelikte, entsprechend schwierig ist leider die Beweisfindung. Es ist sehr zu wünschen, dass dieses kostenlose rechtsmedizinische Gutachten zu mehr Verurteilungen führt. Die SVP-Fraktion steht also hinter den rechtsmedizinischen Gutachten, wir versprechen uns einige Erleichterungen für die juristischen Verfahren.
-Den zweiten Teil der Revision, die zusätzlichen Unterkünfte, lehnen wir jedoch mehrheitlich ab. Es ist wichtig und richtig, dass in der Schweiz Frauenhäuser und andere niederschwellige Notunterkünfte zur Verfügung stehen. Nicht alle Kantone sollen eigene Frauenhäuser betreiben müssen, sondern die heutigen Standortkantone sollten flexibel genug sein, anderen diese Infrastruktur gegen ein entsprechendes Entgelt zur Verfügung zu stellen. Die Kantone können sich untereinander organisieren, so wie das heute auch getan wird. Wenn jeder Kanton nur für sich schauen müsste, würden sich zwei Probleme ergeben: Zum einen wären die Unterkünfte kaum ausgelastet und würden dann zu - provokativ gesagt - teuren Hotels, ohne Druck auf die Verantwortlichen, so schnell wie möglich eine Anschlusslösung für die Frauen zu suchen. Opfer sollen unseres Erachtens nicht verwaltet werden. Zum anderen würden die gewalttätigen Männer ihre Frauen sofort finden, weil sie im Haus des entsprechenden Kantons sein müssen. Das würde die Kosten für die Sicherheit nochmals in die Höhe treiben.
-Einer Studie der Konferenz der kantonalen Sozialdirektorinnen und Sozialdirektoren zufolge ist zwischen 2017 und 2024 die Zahl der Frauenhäuser von 18 auf 22 und jene der Betten von 292 auf 427 gestiegen. Das ist in bloss sieben Jahren geschehen. Auch in den anderen Schutzunterkünften hat sich die Bettenzahl von 150 auf 182 erhöht. Im Verhältnis zum Bevölkerungswachstum ist dieser Ausbau weit überproportional erfolgt. Im selben Zeitraum stieg auch die Belegung der Frauenhäuser von 72 auf 76 Prozent. In meiner eigenen Gemeinde mit mehr als 20 000 Einwohnern habe ich mir eine anonymisierte Liste der Aufenthaltsdauer in den Notunterkünften geben lassen. Danach gibt es sowohl Aufenthalte von 291 als auch von 120 Tagen, aber durchaus auch einen kürzeren Verbleib von rund 30 bis 60 Tagen.
-Schliesslich mangelt es - nicht in dieser Revision, hier liegt der Fokus auf den Opfern - völlig am politischen Willen der Ursachenbekämpfung, die angesichts der signifikant überproportional vertretenen ausländischen Täterschaft am effektivsten wäre. Wir wollen mehr Härte des Staates gegenüber den Tätern und damit den Verursachern des Leids. Entsprechend vermissen wir härtere Strafen, einen konsequenteren Entzug des Aufenthaltsrechts, forcierte Ausschaffungen und die Schadloshaltung des Staates gegenüber den Verursachern. Täter sollen wissen, dass ihnen eine Freiheitsstrafe und allenfalls die Ausweisung aus der Schweiz drohen, wenn sie jemandem Gewalt antun.
+Den zweiten Teil der Revision, die zusätzlichen Unterkünfte, lehnen wir jedoch mehrheitlich ab. Es ist wichtig und richtig, dass in der Schweiz Frauenhäuser und andere niederschwellige Notunterkünfte zur Verfügung stehen. Nicht alle Kantone sollen eigene Frauenhäuser betreiben müssen, sondern die heutigen Standortkantone sollten flexibel genug sein, anderen diese Infrastruktur gegen ein entsprechendes Entgelt zur Verfügung zu stellen. Die Kantone können sich untereinander organisieren, so wie das heute auch getan wird. Wenn jeder Kanton nur für sich schauen müsste, würden sich zwei Probleme ergeben: Zum einen wären die Unterkünfte kaum ausgelastet und würden dann zu - provokativ gesagt - teuren Hotels, ohne Druck auf die Verantwortlichen, so schnell wie möglich eine Anschlusslösung für die Frauen zu suchen. Opfer sollen unseres Erachtens nicht verwaltet werden. Zum andern würden die gewalttätigen Männer ihre Frauen sofort finden, weil sie im Haus des entsprechenden Kantons sein müssen. Das würde die Kosten für die Sicherheit nochmals in die Höhe treiben.
+Einer Studie der Konferenz der kantonalen Sozialdirektorinnen und Sozialdirektoren zufolge ist zwischen 2017 und 2024 die Zahl der Frauenhäuser von 18 auf 22 und jene der Betten von 292 auf 427 gestiegen. Das ist in bloss sieben Jahren geschehen. Auch in den anderen Schutzunterkünften hat sich die Bettenzahl von 150 auf 182 erhöht. Im Verhältnis zum Bevölkerungswachstum ist dieser Ausbau weit überproportional erfolgt. Im selben Zeitraum stieg auch die Belegung der Frauenhäuser von 72 auf 76 Prozent. In meiner eigenen Gemeinde mit mehr als 20[NB]000 Einwohnern habe ich mir eine anonymisierte Liste der Aufenthaltsdauer in den Notunterkünften geben lassen. Danach gibt es Aufenthalte von 291 und von 120 Tagen, aber durchaus auch einen kürzeren Verbleib von rund 30 bis 60 Tagen.
+Schliesslich mangelt es - nicht in dieser Revision, hier liegt der Fokus auf den Opfern - völlig am politischen Willen der Ursachenbekämpfung, die angesichts der signifikant überproportional vertretenen ausländischen Täterschaft am effektivsten wäre. Wir wollen mehr Härte des Staates gegenüber den Tätern und damit den Verursachern des Leids. Entsprechend vermissen wir härtere Strafen, einen konsequenteren Entzug des Aufenthaltsrechts, forcierte Ausschaffungen und die Schadloshaltung des Staates gegenüber den Verursachern. Täter sollen wissen, dass ihnen eine Freiheitsstrafe und allenfalls die Ausweisung aus der Schweiz drohen, wenn sie jemandem Gewalt antun. [GZ]
 Wir werden auf diese Vorlage eintreten.
 </t>
   </si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -421,7 +421,7 @@
   </si>
   <si>
     <t xml:space="preserve">L'iniziativa popolare "Stop al blackout" è un progetto del passato. Guarda indietro, mentre le sfide della politica energetica sono chiaramente davanti a noi. La Svizzera deve sviluppare energie rinnovabili, ridurre le proprie dipendenze e rafforzare la sicurezza dell'approvvigionamento. Per nessuno di questi obiettivi le nuove centrali nucleari rappresentano una risposta giusta. Non contribuiscono ad aumentare la produzione di elettricità invernale. Non creano capacità di accumulo supplementari. Non rafforzano né la sicurezza dell'approvvigionamento né la stabilità della rete.
-Wer heute neue AKW fordert, verspricht Lösungen für Probleme, die längst gelöst sein müssen, bevor ein neues Kraftwerk überhaupt Strom produzieren könnte. Die Energiewende findet eben nicht in dreissig, vierzig Jahren statt - sie findet jetzt statt, sie muss jetzt stattfinden. Die entscheidenden Investitionen betreffen erneuerbare Energien, Speicherlösungen, intelligente und energieeffiziente Netze. Dort entscheidet sich, ob die Schweiz in Zukunft sicher, umwelt- und klimafreundlich mit Strom versorgt wird. Deshalb ist nicht nur die Initiative abzulehnen, sondern auch der Gegenvorschlag, denn er öffnet dieselbe Tür, und diese Tür führt zurück ins letzte Jahrhundert. Neue Atomkraftwerke sind heute vor allem eins, ein sicherheits- und finanzpolitisches Risiko. Wer von Technologieoffenheit spricht, sollte auch offen sagen, wer die Milliardenrisiken tragen soll. Private Investoren sind es offensichtlich nicht, sonst würden sie längst Schlange stehen. Das tun sie nicht, und das sagt eigentlich schon alles.
+Wer heute neue AKW fordert, verspricht Lösungen für Probleme, die gelöst sein müssen, lange bevor ein neues Kraftwerk überhaupt Strom produzieren könnte. Die Energiewende findet eben nicht in dreissig, vierzig Jahren statt - sie findet jetzt statt, sie muss jetzt stattfinden. Die entscheidenden Investitionen betreffen erneuerbare Energien, Speicherlösungen, intelligente und energieeffiziente Netze. Dort entscheidet sich, ob die Schweiz in Zukunft sicher, umwelt- und klimafreundlich mit Strom versorgt wird. Deshalb ist nicht nur die Initiative abzulehnen, sondern auch der Gegenvorschlag, denn er öffnet dieselbe Tür, und diese Tür führt zurück ins letzte Jahrhundert. Neue Atomkraftwerke sind heute vor allem eins: ein sicherheits- und finanzpolitisches Risiko. Wer von Technologieoffenheit spricht, sollte auch offen sagen, wer die Milliardenrisiken tragen soll. Private Investoren sind es offensichtlich nicht, sonst würden sie längst Schlange stehen. Das tun sie nicht, und das sagt eigentlich schon alles.
 Ovunque siano stati avviati nuovi progetti, i costi e i tempi di realizzazione sono sfuggiti al controllo. Nessuna di queste centrali è stata costruita senza massicci aiuti pubblici, garanzie statali o l'assunzione dei rischi da parte dello Stato. Alla fine, il conto arriva sempre alle cittadine e ai cittadini.
 Particolarmente sorprendente oggi è la posizione del Centro. È stata una consigliera federale del Centro a decidere, difendere e spiegare con successo alla popolazione l'uscita dal nucleare dopo la catastrofe di Fukushima. Doris Leuthard aveva compreso che la sicurezza dell'approvvigionamento non dipende dall'attaccamento a vecchi modelli, ma dalla capacità di adattarsi a nuove realtà e a nuove conoscenze. Oggi una parte del suo stesso partito rimette in discussione proprio questo principio. Non è uno sguardo rivolto al futuro, è un tuffo nel passato. Mi chiedo sinceramente che cosa pensi Doris Leuthard nel vedere come una parte del suo stesso partito metta oggi in discussione quella politica energetica che lei ha contribuito a costruire e difendere con grande coraggio politico e con grande visione.
 Atomkraftwerke sind keine Investition, sie sind eine Hypothek, eine Hypothek auf Jahrzehnte und Jahrhunderte, eine Hypothek auf unsere Energiepolitik und auf die kommenden Generationen. Die Schweiz braucht keine energiepolitische Nostalgie. Sie braucht Planungssicherheit, sie braucht Investitionen in die Energien und Technologien der Zukunft. Deshalb sage ich klar Nein zur Blackout-Initiative, Nein zum Gegenvorschlag und Ja zu einer Energiepolitik, die unseren Kindern Lösungen hinterlässt und keine radioaktiven Altlasten. 
@@ -971,7 +971,7 @@
     <t xml:space="preserve">Diese Motion der FDP-Liberalen Fraktion beinhaltet im Wesentlichen drei Punkte. Es geht um die Verschärfung der Landesverweisung für straffällige Drittstaatenangehörige. Drittstaatenangehörige im Sinne des Schengen-Systems sind per Definition all jene Personen, die einem Staat ausserhalb von Europa, eben ausserhalb des Schengen-Raums angehören, also zum Beispiel aus Asien oder den USA stammen, oder südamerikanische Staatsangehörige sind. 
 Der Bundesrat wird beauftragt, die rechtlichen Grundlagen der Landesverweisung gemäss Artikel 66a und 66abis des Strafgesetzbuches zu überarbeiten und zu ergänzen, um sicherzustellen, dass die straffälligen Drittstaatenangehörigen, die eine schwere Straftat - und ich betone das bewusst: eine schwere Straftat - begangen haben, automatisch ausgeschafft werden können. Als Freisinnige sind wir der Überzeugung, dass dieser Automatismus notwendig ist, insbesondere, weil dadurch auch Asylverfahrenskosten gespart werden können. Für uns gilt auch bei diesem Automatismus das sogenannte Non-Refoulement-Prinzip, das heisst: Man darf eine Person nicht in einen Staat ausschaffen, wenn man riskiert, dass sie dort an Leib und Leben bedroht ist. Die Umsetzung der Ausschaffungs-Initiative ist in diesen Punkten immer noch offen.
 Wir wollen auch, dass darauf hingewirkt wird, dass die kantonalen Vollzugsbehörden endlich eine einheitliche Praxis in Bezug auf die Ausschaffungen einführen; es besteht ja oftmals das Problem, dass sie hier eine unterschiedliche Praxis anwenden. 
-Die Anwendung der Landesverweisung soll zudem stärker an das EU-Modell angelehnt werden, das unter bestimmten Voraussetzungen eine effizientere Rückführung ermöglicht. Es ist mir wichtig zu betonen, dass all diese Möglichkeiten nur darum bestehen, weil die Schweiz als assoziierter Staat bei Schengen-Dublin dabei ist. Die Rückführungsrichtlinie und die Schengen-Grenzsicherung sind enorm wichtige Voraussetzungen, damit wir überhaupt mit den EU-Staaten verhandeln und eine effizientere Rückführung veranlassen können. Es ist auch so, dass beispielsweise die Zusammenarbeit mit der Europäischen Agentur für die Grenz- und Küstenwache (Frontex), also der Grenzsicherungsbehörde der Europäischen Union für den Schengen-Raum, sehr vonnöten ist, denn ohne Frontex wären wir aufgeschmissen. Daher wählen wir auch hier das Verfahren so, dass die Rückführungen respektive die Ausschaffungen in Zusammenarbeit mit der EU-Agentur Frontex verbessert und vor allem beschleunigt werden können. 
+Die Anwendung der Landesverweisung soll zudem stärker an das EU-Modell angelehnt werden, das unter bestimmten Voraussetzungen eine effizientere Rückführung ermöglicht. Es ist mir wichtig zu betonen, dass all diese Möglichkeiten nur darum bestehen, weil die Schweiz als assoziierter Staat bei Schengen-Dublin dabei ist. Die EU-Richtlinie und die Schengen-Grenzsicherung sind enorm wichtige Voraussetzungen, damit wir überhaupt mit den EU-Staaten verhandeln und eine effizientere Rückführung veranlassen können. Es ist auch so, dass beispielsweise die Zusammenarbeit mit der Europäischen Agentur für die Grenz- und Küstenwache (Frontex), also der Grenzsicherungsbehörde der Europäischen Union für den Schengen-Raum, sehr vonnöten ist, denn ohne Frontex wären wir aufgeschmissen. Daher wählen wir auch hier das Verfahren so, dass die Rückführungen respektive die Ausschaffungen in Zusammenarbeit mit der EU-Agentur Frontex verbessert und vor allem beschleunigt werden können. 
 Wenn wir die Sicherheit ernst nehmen wollen, dann muss das Anliegen der Motion eigentlich eine Selbstverständlichkeit sein. Ich betone noch einmal: Diese drei Punkte, die ich Ihnen soeben erklärt habe, gilt es für straffällige Drittstaatenangehörige, die eine schwere Straftat begangen haben, konsequent umzusetzen. Es wird immer gesagt, das gehe nicht und man müsse diese Leute schützen, aber man darf nicht vergessen: Das sind alles Leute, die schwer straffällig geworden sind, hier in der Schweiz leben und zum Teil, wenn sie in Bezug auf den Asylstatus eine positive Verfügung erhalten haben, sogar noch Sozialhilfe beziehen. Das können sie der Bevölkerung einfach nicht mehr erklären, dass solche Leute dann nicht das Land verlassen müssen. 
 Aus dieser Optik bittet Sie die FDP-Fraktion, der Motion zuzustimmen.
 </t>
